--- a/web/RevOps_Platform_Demo_Sample.xlsx
+++ b/web/RevOps_Platform_Demo_Sample.xlsx
@@ -21,11 +21,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0 &quot;₽&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0 &quot;ср.&quot;"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -144,8 +145,43 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
       <color rgb="00DC2626"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="0016A34A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00334155"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -268,11 +304,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -379,26 +416,104 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -418,14 +533,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -436,7 +545,7 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -824,439 +933,447 @@
           <t>⚡ ЭКСПРЕСС-КАЛЬКУЛЯТОР УПУЩЕННОЙ ПРИБЫЛИ ОП (ДИАГНОСТИКА ЗА 30 СЕКУНД)</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>📄 1. One-Pager</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>⚡ 2. Пульс компании</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>📋 3. Пульт РОПа</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>💸 4. 7 Грехов ОП</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>🎯 5. Action Center</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>🎙️ 6. ИИ-Аудит</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>⚡ 7. Экспресс 3 цифры</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>🧪 8. QA Suite</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>⚙️ 9. Настройки</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>🎛️ ВВЕДИТЕ 3 ЦИФРЫ ВАШЕГО БИЗНЕСА:</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>📊 БАЗОВЫЕ ПОКАЗАТЕЛИ (AS-IS):</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Категория капитала</t>
         </is>
       </c>
-      <c r="H4" s="6" t="n"/>
+      <c r="H4" s="7" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>1. Входящий поток лидов в месяц (шт):</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="9" t="n">
         <v>150</v>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Емкость базы (при 100% конверсии):</t>
         </is>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="11">
         <f>B5*B6</f>
         <v/>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Факт выручки (As-Is)</t>
         </is>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="11" t="n">
         <v>1650000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>2. Средний чек закрытой сделки (₽):</t>
         </is>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="12" t="n">
         <v>400000</v>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Текущая конверсия в оплату (факт):</t>
         </is>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="13">
         <f>H5/D5</f>
         <v/>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>Упущенная прибыль ОП</t>
         </is>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="14" t="n">
         <v>1039500</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>3. Количество менеджеров в ОП (чел):</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Текущая выручка месяца (факт):</t>
         </is>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="11">
         <f>H5</f>
         <v/>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Потенциал кассы (To-Be)</t>
         </is>
       </c>
-      <c r="H7" s="15" t="n">
+      <c r="H7" s="16" t="n">
         <v>1961850</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Отраслевой сегмент компании:</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>B2B Услуги / Производство</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Нагрузка на одного менеджера (лидов):</t>
         </is>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <f>ROUND(B5/B7, 0) &amp; " лид/мес"</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>🔴 ВЫЯВЛЕННЫЙ РИСК ПОТЕРЬ</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>🟢 КОНСЕРВАТИВНЫЙ (+15%)</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>🚀 БАЗОВЫЙ ПЛАН (+30%)</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>⭐ ОПТИМИСТИЧНЫЙ (+50%)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="20">
+      <c r="A11" s="21">
         <f>H6</f>
         <v/>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="22">
         <f>H5*1.0945</f>
         <v/>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="23">
         <f>H5*1.189</f>
         <v/>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="24">
         <f>H5*1.315</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>📊 РАСШИФРОВКА ФИНАНСОВЫХ УТЕЧЕК ПО 4 УЗКИМ МЕСТАМ</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>Узкое место воронки продаж</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>Отраслевой бенчмарк потерь</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>Упущенная прибыль, ₽/мес</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>Причина утечки</t>
         </is>
       </c>
-      <c r="F14" s="24" t="inlineStr">
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>Как закрываем за 14 дней</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Слив лидов на звонках (нет Next Step)</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>30% выручки теряется из-за ошибок менеджеров</t>
         </is>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="11" t="n">
         <v>412500</v>
       </c>
-      <c r="E15" s="9" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>Менеджеры консультируют, но не закрывают на дату</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>ИИ-аудит 100% звонков + чек-лист Next Step</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="25" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Зависание сделок на этапе КП &gt; 48ч</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>18% выручки теряется из-за просрочки follow-up</t>
         </is>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="11" t="n">
         <v>297000</v>
       </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>Клиент остывает, пока менеджер ждет звонка</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>Авторадар SLA 48ч + эскалация РОПу на 3-й день</t>
         </is>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Брошенные отказники без дожима (L1-L4)</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>8% — потенциал реактивации списанных сделок</t>
         </is>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="11" t="n">
         <v>132000</v>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>Сделки списаны в архив без реактивации</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>AI Recovery Engine: автодожим в WhatsApp/TG</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="25" t="inlineStr">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Зависшая дебиторка и задержка оплат</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>12% выставленных счетов с просрочкой 20+ дней</t>
         </is>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="11" t="n">
         <v>198000</v>
       </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>Нет платежного календаря и контроля сроков</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>Платежный календарь DSO + автонапоминания</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="26" t="n"/>
-      <c r="B19" s="27" t="inlineStr">
+      <c r="A19" s="27" t="n"/>
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>ИТОГО УПУЩЕННОЙ ПРИБЫЛИ В МЕСЯЦ:</t>
         </is>
       </c>
-      <c r="C19" s="26" t="n"/>
-      <c r="D19" s="28">
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="29">
         <f>SUM(D15:D18)</f>
         <v/>
       </c>
-      <c r="E19" s="27" t="inlineStr">
+      <c r="E19" s="28" t="inlineStr">
         <is>
           <t>ПОТЕНЦИАЛ БЫСТРОГО ВОЗВРАТА:</t>
         </is>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <f>ROUND(D19*0.35, 0) &amp; " ₽ в первый месяц"</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="A21" s="31" t="inlineStr">
         <is>
           <t>🎁 СЛЕДУЮЩИЙ ШАГ: БЕСПЛАТНЫЙ ТЕСТ-ДРАЙВ НА 3 ВАШИХ ЗВОНКАХ</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="31" t="inlineStr">
+      <c r="A22" s="32" t="inlineStr">
         <is>
           <t>Хотите проверить эту математику на реальных данных вашей компании за 15 минут?</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="inlineStr">
+      <c r="A23" s="33" t="inlineStr">
         <is>
           <t>👉 Отправьте 3 аудиозаписи любых вчерашних звонков ваших менеджеров в Telegram бот.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="inlineStr">
+      <c r="A24" s="33" t="inlineStr">
         <is>
           <t>ИИ бесплатно разберет их по 13 критериям, покажет ошибки речи и рассчитает точную сумму под угрозой слива.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="33" t="inlineStr">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>🚀 ЗАПУСТИТЬ БЕСПЛАТНЫЙ ТЕСТ-ДРАЙВ: @RevOps_Super_Audit_Bot (https://t.me/RevOps_Super_Audit_Bot)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="A26" s="35" t="inlineStr">
         <is>
           <t>Нужен комплексный аудит отдела продаж? 👉 Экономика спринта оптимизации (450 000 ₽) на вкладке «4. 7 Грехов ОП»</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="35" t="inlineStr">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>🔒 Конфиденциально • Без передачи персональных данных • Экспресс-разбор за 15 минут (152-ФЗ РФ)</t>
         </is>
@@ -1314,445 +1431,452 @@
           <t>📋 СТРАТЕГИЧЕСКИЙ ПУЛЬТ СОБСТВЕННИКА: «5 РЕШЕНИЙ МЕСЯЦА»</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>📄 1. One-Pager</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>⚡ 2. Пульс компании</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>📋 3. Пульт РОПа</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>💸 4. 7 Грехов ОП</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>🎯 5. Action Center</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>🎙️ 6. ИИ-Аудит</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>⚡ 7. Экспресс 3 цифры</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>🧪 8. QA Suite</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>Звонков за вчера</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>Диалогов с браком (&lt;9)</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="38" t="inlineStr">
         <is>
           <t>Сделок с угрозой срыва</t>
         </is>
       </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="D4" s="38" t="inlineStr">
         <is>
           <t>Сумма в зоне риска прямо сейчас</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="E4" s="38" t="inlineStr">
         <is>
           <t>Статус дня для РОПа</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="38" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="39" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="21" t="n">
         <v>2730000</v>
       </c>
-      <c r="E5" s="40" t="inlineStr">
+      <c r="E5" s="41" t="inlineStr">
         <is>
           <t>🚨 ТРЕБУЕТСЯ 15 МИНУТ КОНТРОЛЯ РОПа</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>🎯 ТОП-5 СТРАТЕГИЧЕСКИХ РЕШЕНИЙ ДЛЯ ЗАЩИТЫ КАПИТАЛА БИЗНЕСА</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Сделка / Контрагент</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Суть проблемы и симптом</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>Сумма в риске</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>Срочное действие РОПа (Что сделать)</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>Чекбокс</t>
         </is>
       </c>
-      <c r="H8" s="24" t="inlineStr">
+      <c r="H8" s="25" t="inlineStr">
         <is>
           <t>🤖 Сгенерированный оффер ИИ-дожима (WhatsApp / Скрипт РОПа)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="A9" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Сделка D-104 (ООО «Вектор Плюс»)</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Зависание на этапе КП: 12 дней без ответа (норма 48ч)</t>
         </is>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="11" t="n">
         <v>850000</v>
       </c>
-      <c r="E9" s="41" t="inlineStr">
+      <c r="E9" s="42" t="inlineStr">
         <is>
           <t>🔴 КРИТИЧЕСКИЙ</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Запросить статус у КАМа Петрова, согласовать скидку/рассрочку</t>
         </is>
       </c>
-      <c r="G9" s="42" t="inlineStr">
+      <c r="G9" s="43" t="inlineStr">
         <is>
           <t>В РАБОТЕ</t>
         </is>
       </c>
-      <c r="H9" s="43" t="inlineStr">
+      <c r="H9" s="44" t="inlineStr">
         <is>
           <t>Добрый день, Алексей! Вижу, наш расчет по договору согласован. Чтобы зафиксировать спец-условия сентября со скидкой 7%, предлагаю сегодня подписать спецификацию. Слот для звонка: 14:30. Удобно?</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="41" t="n">
+      <c r="A10" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Звонок C-505 / Сделка D-109 (ООО «ПромКомплект»)</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Менеджер сорвал контакт (балл речи 2/13), клиент ушел в отказ</t>
         </is>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="11" t="n">
         <v>600000</v>
       </c>
-      <c r="E10" s="41" t="inlineStr">
+      <c r="E10" s="42" t="inlineStr">
         <is>
           <t>🔴 КРИТИЧЕСКИЙ</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>Личный звонок РОПа ЛПР до 12:00: перехват сделки от лица руководства</t>
         </is>
       </c>
-      <c r="G10" s="42" t="inlineStr">
+      <c r="G10" s="43" t="inlineStr">
         <is>
           <t>В РАБОТЕ</t>
         </is>
       </c>
-      <c r="H10" s="43" t="inlineStr">
+      <c r="H10" s="44" t="inlineStr">
         <is>
           <t>Михаил Сергеевич, добрый день! Это Дмитрий Иванов, коммерческий директор. Прослушал вчерашний диалог с нашим менеджером — приношу извинения за неполную консультацию. Лично подготовил для вас проект с расширенной гарантией 24 мес. Уделите 5 минут?</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="41" t="n">
+      <c r="A11" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Звонок C-503 / Сделка D-106 (ООО «СнабСервис»)</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>В диалоге не зафиксирована дата встречи (балл речи 6/13)</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="11" t="n">
         <v>280000</v>
       </c>
-      <c r="E11" s="41" t="inlineStr">
+      <c r="E11" s="42" t="inlineStr">
         <is>
           <t>🟡 СРЕДНИЙ</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>Поставить задачу менеджеру Петрову: перезвонить и назначить слот встречи</t>
         </is>
       </c>
-      <c r="G11" s="42" t="inlineStr">
+      <c r="G11" s="43" t="inlineStr">
         <is>
           <t>В РАБОТЕ</t>
         </is>
       </c>
-      <c r="H11" s="43" t="inlineStr">
+      <c r="H11" s="44" t="inlineStr">
         <is>
           <t>Игорь, приветствую! Направил вам 2 слота на онлайн-демо платформы: сегодня в 16:00 или завтра в 11:30. За 15 минут покажем связку с вашей CRM. Какой слот забронировать?</t>
         </is>
       </c>
     </row>
     <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="41" t="n">
+      <c r="A12" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Сделка D-107 (ООО «ТехноПром»)</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Счет просрочен на 9 дней (сумма 150 000 ₽)</t>
         </is>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="11" t="n">
         <v>150000</v>
       </c>
-      <c r="E12" s="41" t="inlineStr">
+      <c r="E12" s="42" t="inlineStr">
         <is>
           <t>🟡 СРЕДНИЙ</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>Отправить триггерное напоминание в WhatsApp бухгалтеру клиента</t>
         </is>
       </c>
-      <c r="G12" s="42" t="inlineStr">
+      <c r="G12" s="43" t="inlineStr">
         <is>
           <t>В РАБОТЕ</t>
         </is>
       </c>
-      <c r="H12" s="43" t="inlineStr">
+      <c r="H12" s="44" t="inlineStr">
         <is>
           <t>Ольга, здравствуйте! Бухгалтерия напоминает: по счету INV-203 сегодня крайний день резерва оборудования по льготному курсу. Выставить ссылку на моментальную оплату через СБП?</t>
         </is>
       </c>
     </row>
     <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="41" t="n">
+      <c r="A13" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Сделка D-103 (ООО «ИнвестХолдинг»)</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Нагрузка 80%, 4 ключевые сделки висят на РОПе</t>
         </is>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="11" t="n">
         <v>850000</v>
       </c>
-      <c r="E13" s="41" t="inlineStr">
+      <c r="E13" s="42" t="inlineStr">
         <is>
           <t>🟡 СРЕДНИЙ</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>Делегировать 2 входящие сделки на КАМа (у КАМа загрузка всего 4%)</t>
         </is>
       </c>
-      <c r="G13" s="42" t="inlineStr">
+      <c r="G13" s="43" t="inlineStr">
         <is>
           <t>В РАБОТЕ</t>
         </is>
       </c>
-      <c r="H13" s="43" t="inlineStr">
+      <c r="H13" s="44" t="inlineStr">
         <is>
           <t>Регламентное действие: передать права ответственного по сделке D-102 на КАМа Петрова (свободная емкость 75%). РОПу оставить контроль ключевых контрольных точек.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="26" t="n"/>
-      <c r="B14" s="27" t="inlineStr">
+      <c r="A14" s="27" t="n"/>
+      <c r="B14" s="28" t="inlineStr">
         <is>
           <t>ИТОГО ДЕНЕГ В ЗОНЕ РИСКА СЕГОДНЯ:</t>
         </is>
       </c>
-      <c r="C14" s="26" t="n"/>
-      <c r="D14" s="28">
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="29">
         <f>SUM(D9:D13)</f>
         <v/>
       </c>
-      <c r="E14" s="27" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>СПАСЕННАЯ ВЫРУЧКА:</t>
         </is>
       </c>
-      <c r="F14" s="44" t="inlineStr">
+      <c r="F14" s="45" t="inlineStr">
         <is>
           <t>При выполнении всех 5 действий</t>
         </is>
       </c>
-      <c r="G14" s="29" t="inlineStr">
+      <c r="G14" s="30" t="inlineStr">
         <is>
           <t>100% защита</t>
         </is>
       </c>
-      <c r="H14" s="26" t="n"/>
+      <c r="H14" s="27" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="E17" s="45" t="inlineStr">
+      <c r="E17" s="46" t="inlineStr">
         <is>
           <t>⏱️ ЭКСПРЕСС-РЕГЛАМЕНТ РОПа (15 МИНУТ/ДЕНЬ)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="E18" s="42" t="inlineStr">
+      <c r="E18" s="43" t="inlineStr">
         <is>
           <t>09:00 - 09:05</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>Проверка ночного ИИ-аудита: 2 звонка с браком (&lt;9 баллов)</t>
         </is>
       </c>
-      <c r="G18" s="46" t="n"/>
-      <c r="H18" s="46" t="n"/>
+      <c r="G18" s="47" t="n"/>
+      <c r="H18" s="47" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="E19" s="42" t="inlineStr">
+      <c r="E19" s="43" t="inlineStr">
         <is>
           <t>09:05 - 09:10</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>Перехват сделки D-109 (600 т.р.) и звонок ЛПР до 12:00</t>
         </is>
       </c>
-      <c r="G19" s="46" t="n"/>
-      <c r="H19" s="46" t="n"/>
+      <c r="G19" s="47" t="n"/>
+      <c r="H19" s="47" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="E20" s="42" t="inlineStr">
+      <c r="E20" s="43" t="inlineStr">
         <is>
           <t>09:10 - 09:13</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>Согласование спецусловий по D-104 (850 т.р.)</t>
         </is>
       </c>
-      <c r="G20" s="46" t="n"/>
-      <c r="H20" s="46" t="n"/>
+      <c r="G20" s="47" t="n"/>
+      <c r="H20" s="47" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="E21" s="42" t="inlineStr">
+      <c r="E21" s="43" t="inlineStr">
         <is>
           <t>09:13 - 09:15</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>Делегирование 2 сделок с РОПа на свободного КАМа</t>
         </is>
       </c>
-      <c r="G21" s="46" t="n"/>
-      <c r="H21" s="46" t="n"/>
+      <c r="G21" s="47" t="n"/>
+      <c r="H21" s="47" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="E22" s="17" t="inlineStr">
+      <c r="E22" s="18" t="inlineStr">
         <is>
           <t>Результат:</t>
         </is>
       </c>
-      <c r="F22" s="47" t="inlineStr">
+      <c r="F22" s="48" t="inlineStr">
         <is>
           <t>2 730 000 ₽ защищено от слива за 15 минут</t>
         </is>
       </c>
-      <c r="G22" s="46" t="n"/>
-      <c r="H22" s="46" t="n"/>
+      <c r="G22" s="47" t="n"/>
+      <c r="H22" s="47" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -1777,1087 +1901,3058 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:V60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🎙️ РЕЧЕВАЯ ИИ-АНАЛИТИКА: 13 ПАРАМЕТРОВ WHISPER + LLM</t>
-        </is>
-      </c>
+          <t>🎙️ ИИ-СУПЕРВАЙЗЕР ЗВОНКОВ: РЕЧЕВАЯ АНАЛИТИКА 100% ДИАЛОГОВ (WHISPER LARGE V3 + LLM)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
+      <c r="U1" s="2" t="n"/>
+      <c r="V1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>📄 1. One-Pager</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>⚡ 2. Пульс компании</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>📋 3. Пульт РОПа</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>💸 4. 7 Грехов ОП</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>🎯 5. Action Center</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>🎙️ 6. ИИ-Аудит</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>⚡ 7. Экспресс 3 цифры</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>🧪 8. QA Suite</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>⚙️ 9. Настройки</t>
         </is>
       </c>
+      <c r="J2" s="49" t="n"/>
+      <c r="K2" s="49" t="n"/>
+      <c r="L2" s="49" t="n"/>
+      <c r="M2" s="49" t="n"/>
+      <c r="N2" s="49" t="n"/>
+      <c r="O2" s="49" t="n"/>
+      <c r="P2" s="49" t="n"/>
+      <c r="Q2" s="49" t="n"/>
+      <c r="R2" s="49" t="n"/>
+      <c r="S2" s="49" t="n"/>
+      <c r="T2" s="49" t="n"/>
+      <c r="U2" s="49" t="n"/>
+      <c r="V2" s="49" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="36" t="inlineStr">
-        <is>
-          <t>Звонков проанализировано</t>
-        </is>
-      </c>
-      <c r="B3" s="48" t="inlineStr">
+      <c r="A3" s="37" t="inlineStr">
+        <is>
+          <t>Проанализировано звонков</t>
+        </is>
+      </c>
+      <c r="B3" s="50" t="inlineStr">
         <is>
           <t>Средний балл качества</t>
         </is>
       </c>
-      <c r="D3" s="36" t="inlineStr">
-        <is>
-          <t>Доля фиксации Next Step</t>
-        </is>
-      </c>
-      <c r="E3" s="37" t="inlineStr">
-        <is>
-          <t>Диалогов с браком (&lt;9)</t>
-        </is>
-      </c>
-      <c r="F3" s="37" t="inlineStr">
-        <is>
-          <t>Сумма пайплайна под угрозой</t>
-        </is>
-      </c>
-      <c r="H3" s="37" t="inlineStr">
-        <is>
-          <t>Финансовый вердикт ИИ</t>
-        </is>
-      </c>
+      <c r="C3" s="50" t="n"/>
+      <c r="D3" s="37" t="inlineStr">
+        <is>
+          <t>Фиксация жесткого Next Step</t>
+        </is>
+      </c>
+      <c r="E3" s="38" t="inlineStr">
+        <is>
+          <t>Критический брак речи (&lt;9)</t>
+        </is>
+      </c>
+      <c r="F3" s="38" t="inlineStr">
+        <is>
+          <t>Выручка под угрозой слива</t>
+        </is>
+      </c>
+      <c r="G3" s="38" t="n"/>
+      <c r="H3" s="38" t="inlineStr">
+        <is>
+          <t>Вердикт ИИ-супервайзера</t>
+        </is>
+      </c>
+      <c r="I3" s="38" t="n"/>
+      <c r="J3" s="38" t="n"/>
+      <c r="K3" s="38" t="n"/>
+      <c r="L3" s="38" t="n"/>
+      <c r="M3" s="38" t="n"/>
+      <c r="N3" s="38" t="n"/>
+      <c r="O3" s="38" t="n"/>
+      <c r="P3" s="38" t="n"/>
+      <c r="Q3" s="38" t="n"/>
+      <c r="R3" s="38" t="n"/>
+      <c r="S3" s="38" t="n"/>
+      <c r="T3" s="38" t="n"/>
+      <c r="U3" s="38" t="n"/>
+      <c r="V3" s="38" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="38" t="n">
+      <c r="A4" s="39" t="inlineStr">
+        <is>
+          <t>25 звонков / сут</t>
+        </is>
+      </c>
+      <c r="B4" s="51" t="inlineStr">
+        <is>
+          <t>8.9 из 13</t>
+        </is>
+      </c>
+      <c r="C4" s="51" t="n"/>
+      <c r="D4" s="52" t="inlineStr">
+        <is>
+          <t>60.0% (норма ≥85%)</t>
+        </is>
+      </c>
+      <c r="E4" s="40" t="inlineStr">
+        <is>
+          <t>6 диалогов</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="n">
+        <v>2840000</v>
+      </c>
+      <c r="G4" s="21" t="n"/>
+      <c r="H4" s="53" t="inlineStr">
+        <is>
+          <t>🚨 ВЫСОКИЙ РИСК СЛИВА VIP-КЛИЕНТОВ (ТРЕБУЕТСЯ ВМЕШАТЕЛЬСТВО РОПа)</t>
+        </is>
+      </c>
+      <c r="I4" s="53" t="n"/>
+      <c r="J4" s="53" t="n"/>
+      <c r="K4" s="53" t="n"/>
+      <c r="L4" s="53" t="n"/>
+      <c r="M4" s="53" t="n"/>
+      <c r="N4" s="53" t="n"/>
+      <c r="O4" s="53" t="n"/>
+      <c r="P4" s="53" t="n"/>
+      <c r="Q4" s="53" t="n"/>
+      <c r="R4" s="53" t="n"/>
+      <c r="S4" s="53" t="n"/>
+      <c r="T4" s="53" t="n"/>
+      <c r="U4" s="53" t="n"/>
+      <c r="V4" s="53" t="n"/>
+    </row>
+    <row r="5" ht="12" customHeight="1"/>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="54" t="inlineStr">
+        <is>
+          <t>👥 РЕЙТИНГ МЕНЕДЖЕРОВ ОП ПО КАЧЕСТВУ РЕЧИ (ЛИДЕРБОРД РОПа)</t>
+        </is>
+      </c>
+      <c r="B6" s="54" t="n"/>
+      <c r="C6" s="54" t="n"/>
+      <c r="D6" s="54" t="n"/>
+      <c r="E6" s="54" t="n"/>
+      <c r="F6" s="54" t="n"/>
+      <c r="G6" s="54" t="n"/>
+      <c r="H6" s="54" t="n"/>
+      <c r="I6" s="54" t="n"/>
+      <c r="J6" s="54" t="n"/>
+      <c r="K6" s="54" t="n"/>
+      <c r="L6" s="54" t="n"/>
+      <c r="M6" s="54" t="n"/>
+      <c r="N6" s="54" t="n"/>
+      <c r="O6" s="54" t="n"/>
+      <c r="P6" s="54" t="n"/>
+      <c r="Q6" s="54" t="n"/>
+      <c r="R6" s="54" t="n"/>
+      <c r="S6" s="54" t="n"/>
+      <c r="T6" s="54" t="n"/>
+      <c r="U6" s="54" t="n"/>
+      <c r="V6" s="54" t="n"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>Менеджер ОП</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>Звонков</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>Ср. балл /13</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>Next Step %</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>Talk/Listen (норма ≥45%)</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t>Зависших сделок</t>
+        </is>
+      </c>
+      <c r="H7" s="25" t="inlineStr">
+        <is>
+          <t>Сумма риска (₽)</t>
+        </is>
+      </c>
+      <c r="I7" s="25" t="inlineStr">
+        <is>
+          <t>Грейд ИИ</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="inlineStr">
+        <is>
+          <t>Статус и рекомендация РОПу</t>
+        </is>
+      </c>
+      <c r="K7" s="25" t="n"/>
+      <c r="L7" s="25" t="n"/>
+      <c r="M7" s="25" t="n"/>
+      <c r="N7" s="25" t="n"/>
+      <c r="O7" s="25" t="n"/>
+      <c r="P7" s="25" t="n"/>
+      <c r="Q7" s="25" t="n"/>
+      <c r="R7" s="25" t="n"/>
+      <c r="S7" s="25" t="n"/>
+      <c r="T7" s="25" t="n"/>
+      <c r="U7" s="25" t="n"/>
+      <c r="V7" s="25" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Алексей Мельников</t>
+        </is>
+      </c>
+      <c r="C8" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="B4" s="49" t="inlineStr">
-        <is>
-          <t>9.5 из 13</t>
-        </is>
-      </c>
-      <c r="D4" s="38" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="E4" s="39" t="n">
+      <c r="D8" s="55" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" s="42" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F8" s="42" t="inlineStr">
+        <is>
+          <t>48% / 52%</t>
+        </is>
+      </c>
+      <c r="G8" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="18" t="inlineStr">
+        <is>
+          <t>⭐ А (Эталон)</t>
+        </is>
+      </c>
+      <c r="J8" s="57" t="inlineStr">
+        <is>
+          <t>Эталонный скрипт, рекомендован в базу знаний компании</t>
+        </is>
+      </c>
+      <c r="K8" s="57" t="n"/>
+      <c r="L8" s="57" t="n"/>
+      <c r="M8" s="57" t="n"/>
+      <c r="N8" s="57" t="n"/>
+      <c r="O8" s="57" t="n"/>
+      <c r="P8" s="57" t="n"/>
+      <c r="Q8" s="57" t="n"/>
+      <c r="R8" s="57" t="n"/>
+      <c r="S8" s="57" t="n"/>
+      <c r="T8" s="57" t="n"/>
+      <c r="U8" s="57" t="n"/>
+      <c r="V8" s="57" t="n"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="F4" s="20" t="n">
-        <v>880000</v>
-      </c>
-      <c r="H4" s="50" t="inlineStr">
-        <is>
-          <t>🚨 ВЫСОКИЙ РИСК СЛИВА VIP-КЛИЕНТА</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>📋 РЕЕСТР ПРОБЛЕМНЫХ ЗВОНКОВ И РЕКОМЕНДАЦИИ ИИ (СИНХРОНИЗАЦИЯ С CRM)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
-        <is>
-          <t>ID звонка</t>
-        </is>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>ID сделки</t>
-        </is>
-      </c>
-      <c r="C7" s="24" t="inlineStr">
-        <is>
-          <t>Менеджер ID</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t>Длительность</t>
-        </is>
-      </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Елена Васильева</t>
+        </is>
+      </c>
+      <c r="C9" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="55" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="E9" s="42" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="F9" s="42" t="inlineStr">
+        <is>
+          <t>51% / 49%</t>
+        </is>
+      </c>
+      <c r="G9" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="58" t="n">
+        <v>160000</v>
+      </c>
+      <c r="I9" s="18" t="inlineStr">
+        <is>
+          <t>🟢 B (Норма)</t>
+        </is>
+      </c>
+      <c r="J9" s="57" t="inlineStr">
+        <is>
+          <t>Высокая конверсия, мелкие замечания по регламенту встречи</t>
+        </is>
+      </c>
+      <c r="K9" s="57" t="n"/>
+      <c r="L9" s="57" t="n"/>
+      <c r="M9" s="57" t="n"/>
+      <c r="N9" s="57" t="n"/>
+      <c r="O9" s="57" t="n"/>
+      <c r="P9" s="57" t="n"/>
+      <c r="Q9" s="57" t="n"/>
+      <c r="R9" s="57" t="n"/>
+      <c r="S9" s="57" t="n"/>
+      <c r="T9" s="57" t="n"/>
+      <c r="U9" s="57" t="n"/>
+      <c r="V9" s="57" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Анна Соколова</t>
+        </is>
+      </c>
+      <c r="C10" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="59" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="E10" s="42" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F10" s="42" t="inlineStr">
+        <is>
+          <t>58% / 42%</t>
+        </is>
+      </c>
+      <c r="G10" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="58" t="n">
+        <v>480000</v>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>🟡 C (Зона риска)</t>
+        </is>
+      </c>
+      <c r="J10" s="57" t="inlineStr">
+        <is>
+          <t>Забывает фиксировать дату звонка, требуется тренинг</t>
+        </is>
+      </c>
+      <c r="K10" s="57" t="n"/>
+      <c r="L10" s="57" t="n"/>
+      <c r="M10" s="57" t="n"/>
+      <c r="N10" s="57" t="n"/>
+      <c r="O10" s="57" t="n"/>
+      <c r="P10" s="57" t="n"/>
+      <c r="Q10" s="57" t="n"/>
+      <c r="R10" s="57" t="n"/>
+      <c r="S10" s="57" t="n"/>
+      <c r="T10" s="57" t="n"/>
+      <c r="U10" s="57" t="n"/>
+      <c r="V10" s="57" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Дмитрий Ковалев</t>
+        </is>
+      </c>
+      <c r="C11" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="60" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="E11" s="42" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F11" s="42" t="inlineStr">
+        <is>
+          <t>72% / 28%</t>
+        </is>
+      </c>
+      <c r="G11" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="58" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>🔴 D (Брак речи)</t>
+        </is>
+      </c>
+      <c r="J11" s="57" t="inlineStr">
+        <is>
+          <t>Срыв контакта, перебивание клиента, демпинг скидок</t>
+        </is>
+      </c>
+      <c r="K11" s="57" t="n"/>
+      <c r="L11" s="57" t="n"/>
+      <c r="M11" s="57" t="n"/>
+      <c r="N11" s="57" t="n"/>
+      <c r="O11" s="57" t="n"/>
+      <c r="P11" s="57" t="n"/>
+      <c r="Q11" s="57" t="n"/>
+      <c r="R11" s="57" t="n"/>
+      <c r="S11" s="57" t="n"/>
+      <c r="T11" s="57" t="n"/>
+      <c r="U11" s="57" t="n"/>
+      <c r="V11" s="57" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Иван Попов</t>
+        </is>
+      </c>
+      <c r="C12" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="60" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E12" s="42" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F12" s="42" t="inlineStr">
+        <is>
+          <t>79% / 21%</t>
+        </is>
+      </c>
+      <c r="G12" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="H12" s="58" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>🔴 D (Брак речи)</t>
+        </is>
+      </c>
+      <c r="J12" s="57" t="inlineStr">
+        <is>
+          <t>Режим 'автоответчика', нет попыток закрытия на встречу</t>
+        </is>
+      </c>
+      <c r="K12" s="57" t="n"/>
+      <c r="L12" s="57" t="n"/>
+      <c r="M12" s="57" t="n"/>
+      <c r="N12" s="57" t="n"/>
+      <c r="O12" s="57" t="n"/>
+      <c r="P12" s="57" t="n"/>
+      <c r="Q12" s="57" t="n"/>
+      <c r="R12" s="57" t="n"/>
+      <c r="S12" s="57" t="n"/>
+      <c r="T12" s="57" t="n"/>
+      <c r="U12" s="57" t="n"/>
+      <c r="V12" s="57" t="n"/>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="27" t="inlineStr"/>
+      <c r="B13" s="61" t="inlineStr">
+        <is>
+          <t>ИТОГО ПО ОТДЕЛУ ПРОДАЖ:</t>
+        </is>
+      </c>
+      <c r="C13" s="62">
+        <f>SUM(C8:C12)</f>
+        <v/>
+      </c>
+      <c r="D13" s="62" t="inlineStr">
+        <is>
+          <t>8.9 / 13</t>
+        </is>
+      </c>
+      <c r="E13" s="62" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F13" s="62" t="inlineStr">
+        <is>
+          <t>61% / 39%</t>
+        </is>
+      </c>
+      <c r="G13" s="62">
+        <f>SUM(G8:G12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="63">
+        <f>SUM(H8:H12)</f>
+        <v/>
+      </c>
+      <c r="I13" s="64" t="inlineStr">
+        <is>
+          <t>⚠️ РИСК</t>
+        </is>
+      </c>
+      <c r="J13" s="65" t="inlineStr">
+        <is>
+          <t>Требуется экспресс-коучинг по отработке возражений</t>
+        </is>
+      </c>
+      <c r="K13" s="65" t="n"/>
+      <c r="L13" s="65" t="n"/>
+      <c r="M13" s="65" t="n"/>
+      <c r="N13" s="65" t="n"/>
+      <c r="O13" s="65" t="n"/>
+      <c r="P13" s="65" t="n"/>
+      <c r="Q13" s="65" t="n"/>
+      <c r="R13" s="65" t="n"/>
+      <c r="S13" s="65" t="n"/>
+      <c r="T13" s="65" t="n"/>
+      <c r="U13" s="65" t="n"/>
+      <c r="V13" s="65" t="n"/>
+    </row>
+    <row r="14" ht="12" customHeight="1"/>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="54" t="inlineStr">
+        <is>
+          <t>🔍 ДЕТАЛИЗИРОВАННАЯ МАТРИЦА ОЦЕНКИ ЗВОНКОВ ПО ВСЕМ 13 КРИТЕРИЯМ (0 / 1)</t>
+        </is>
+      </c>
+      <c r="B15" s="54" t="n"/>
+      <c r="C15" s="54" t="n"/>
+      <c r="D15" s="54" t="n"/>
+      <c r="E15" s="54" t="n"/>
+      <c r="F15" s="54" t="n"/>
+      <c r="G15" s="54" t="n"/>
+      <c r="H15" s="54" t="n"/>
+      <c r="I15" s="54" t="n"/>
+      <c r="J15" s="54" t="n"/>
+      <c r="K15" s="54" t="n"/>
+      <c r="L15" s="54" t="n"/>
+      <c r="M15" s="54" t="n"/>
+      <c r="N15" s="54" t="n"/>
+      <c r="O15" s="54" t="n"/>
+      <c r="P15" s="54" t="n"/>
+      <c r="Q15" s="54" t="n"/>
+      <c r="R15" s="54" t="n"/>
+      <c r="S15" s="54" t="n"/>
+      <c r="T15" s="54" t="n"/>
+      <c r="U15" s="54" t="n"/>
+      <c r="V15" s="54" t="n"/>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>Call ID</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>Сделка / Клиент</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>Менеджер</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>Сумма (₽)</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
+        <is>
+          <t>Длит.</t>
+        </is>
+      </c>
+      <c r="F16" s="25" t="inlineStr">
+        <is>
+          <t>Этап CRM</t>
+        </is>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
+        <is>
+          <t>К1 NextStep</t>
+        </is>
+      </c>
+      <c r="H16" s="25" t="inlineStr">
+        <is>
+          <t>К2 Иниц.</t>
+        </is>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
+        <is>
+          <t>К3 ЛПР</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="inlineStr">
+        <is>
+          <t>К4 Боли</t>
+        </is>
+      </c>
+      <c r="K16" s="25" t="inlineStr">
+        <is>
+          <t>К5 Дорого</t>
+        </is>
+      </c>
+      <c r="L16" s="25" t="inlineStr">
+        <is>
+          <t>К6 Подумаю</t>
+        </is>
+      </c>
+      <c r="M16" s="25" t="inlineStr">
+        <is>
+          <t>К7 Кейсы</t>
+        </is>
+      </c>
+      <c r="N16" s="25" t="inlineStr">
+        <is>
+          <t>К8 Закрытие</t>
+        </is>
+      </c>
+      <c r="O16" s="25" t="inlineStr">
+        <is>
+          <t>К9 Привет.</t>
+        </is>
+      </c>
+      <c r="P16" s="25" t="inlineStr">
+        <is>
+          <t>К10 Речь</t>
+        </is>
+      </c>
+      <c r="Q16" s="25" t="inlineStr">
+        <is>
+          <t>К11 Слушан.</t>
+        </is>
+      </c>
+      <c r="R16" s="25" t="inlineStr">
+        <is>
+          <t>К12 Итог</t>
+        </is>
+      </c>
+      <c r="S16" s="25" t="inlineStr">
+        <is>
+          <t>К13 Маржа</t>
+        </is>
+      </c>
+      <c r="T16" s="25" t="inlineStr">
         <is>
           <t>Балл /13</t>
         </is>
       </c>
-      <c r="F7" s="24" t="inlineStr">
-        <is>
-          <t>Ошибка диалога</t>
-        </is>
-      </c>
-      <c r="G7" s="24" t="inlineStr">
-        <is>
-          <t>ИИ-рекомендация</t>
-        </is>
-      </c>
-      <c r="H7" s="24" t="inlineStr">
-        <is>
-          <t>Сумма сделки под угрозой, ₽</t>
-        </is>
-      </c>
-      <c r="I7" s="24" t="inlineStr">
-        <is>
-          <t>Уровень фин. риска</t>
-        </is>
-      </c>
-      <c r="J7" s="24" t="inlineStr">
-        <is>
-          <t>Срочное действие РОПа</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="U16" s="25" t="inlineStr">
+        <is>
+          <t>Статус ИИ</t>
+        </is>
+      </c>
+      <c r="V16" s="25" t="inlineStr">
+        <is>
+          <t>Сумма в риске, ₽</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="43" t="inlineStr">
+        <is>
+          <t>C-501</t>
+        </is>
+      </c>
+      <c r="B17" s="57" t="inlineStr">
+        <is>
+          <t>D-101 (ООО Вектор Плюс)</t>
+        </is>
+      </c>
+      <c r="C17" s="42" t="inlineStr">
+        <is>
+          <t>Мельников</t>
+        </is>
+      </c>
+      <c r="D17" s="66" t="n">
+        <v>850000</v>
+      </c>
+      <c r="E17" s="42" t="inlineStr">
+        <is>
+          <t>05:40</t>
+        </is>
+      </c>
+      <c r="F17" s="42" t="inlineStr">
+        <is>
+          <t>КП отправлено</t>
+        </is>
+      </c>
+      <c r="G17" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" s="55">
+        <f>SUM(G17:S17)</f>
+        <v/>
+      </c>
+      <c r="U17" s="18" t="inlineStr">
+        <is>
+          <t>⭐ ЭТАЛОН</t>
+        </is>
+      </c>
+      <c r="V17" s="56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>C-502</t>
+        </is>
+      </c>
+      <c r="B18" s="57" t="inlineStr">
+        <is>
+          <t>D-104 (ООО Вектор Плюс)</t>
+        </is>
+      </c>
+      <c r="C18" s="42" t="inlineStr">
+        <is>
+          <t>Васильева</t>
+        </is>
+      </c>
+      <c r="D18" s="66" t="n">
+        <v>850000</v>
+      </c>
+      <c r="E18" s="42" t="inlineStr">
+        <is>
+          <t>04:20</t>
+        </is>
+      </c>
+      <c r="F18" s="42" t="inlineStr">
+        <is>
+          <t>Переговоры</t>
+        </is>
+      </c>
+      <c r="G18" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="55">
+        <f>SUM(G18:S18)</f>
+        <v/>
+      </c>
+      <c r="U18" s="18" t="inlineStr">
+        <is>
+          <t>🟢 В НОРМЕ</t>
+        </is>
+      </c>
+      <c r="V18" s="56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="43" t="inlineStr">
+        <is>
+          <t>C-503</t>
+        </is>
+      </c>
+      <c r="B19" s="57" t="inlineStr">
+        <is>
+          <t>D-106 (ООО СнабСервис)</t>
+        </is>
+      </c>
+      <c r="C19" s="42" t="inlineStr">
+        <is>
+          <t>Соколова</t>
+        </is>
+      </c>
+      <c r="D19" s="66" t="n">
+        <v>280000</v>
+      </c>
+      <c r="E19" s="42" t="inlineStr">
+        <is>
+          <t>03:10</t>
+        </is>
+      </c>
+      <c r="F19" s="42" t="inlineStr">
+        <is>
+          <t>Встреча/Демо</t>
+        </is>
+      </c>
+      <c r="G19" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" s="60">
+        <f>SUM(G19:S19)</f>
+        <v/>
+      </c>
+      <c r="U19" s="20" t="inlineStr">
+        <is>
+          <t>⚠️ РИСК</t>
+        </is>
+      </c>
+      <c r="V19" s="58" t="n">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>C-504</t>
+        </is>
+      </c>
+      <c r="B20" s="57" t="inlineStr">
+        <is>
+          <t>D-107 (ООО ТехноПром)</t>
+        </is>
+      </c>
+      <c r="C20" s="42" t="inlineStr">
+        <is>
+          <t>Соколова</t>
+        </is>
+      </c>
+      <c r="D20" s="66" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E20" s="42" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="F20" s="42" t="inlineStr">
+        <is>
+          <t>Квалификация</t>
+        </is>
+      </c>
+      <c r="G20" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="59">
+        <f>SUM(G20:S20)</f>
+        <v/>
+      </c>
+      <c r="U20" s="20" t="inlineStr">
+        <is>
+          <t>⚠️ РИСК</t>
+        </is>
+      </c>
+      <c r="V20" s="58" t="n">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="43" t="inlineStr">
         <is>
           <t>C-505</t>
         </is>
       </c>
-      <c r="B8" s="25" t="inlineStr">
-        <is>
-          <t>D-109</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>102 (Петров)</t>
-        </is>
-      </c>
-      <c r="D8" s="25" t="inlineStr">
-        <is>
-          <t>210 сек</t>
-        </is>
-      </c>
-      <c r="E8" s="51" t="n">
+      <c r="B21" s="57" t="inlineStr">
+        <is>
+          <t>D-109 (ООО ПромКомплект)</t>
+        </is>
+      </c>
+      <c r="C21" s="42" t="inlineStr">
+        <is>
+          <t>Ковалев</t>
+        </is>
+      </c>
+      <c r="D21" s="66" t="n">
+        <v>600000</v>
+      </c>
+      <c r="E21" s="42" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="F21" s="42" t="inlineStr">
+        <is>
+          <t>КП отправлено</t>
+        </is>
+      </c>
+      <c r="G21" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" s="60">
+        <f>SUM(G21:S21)</f>
+        <v/>
+      </c>
+      <c r="U21" s="17" t="inlineStr">
+        <is>
+          <t>❌ СЛИВ</t>
+        </is>
+      </c>
+      <c r="V21" s="58" t="n">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>C-506</t>
+        </is>
+      </c>
+      <c r="B22" s="57" t="inlineStr">
+        <is>
+          <t>D-111 (ООО Глобал Инвест)</t>
+        </is>
+      </c>
+      <c r="C22" s="42" t="inlineStr">
+        <is>
+          <t>Мельников</t>
+        </is>
+      </c>
+      <c r="D22" s="66" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E22" s="42" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F22" s="42" t="inlineStr">
+        <is>
+          <t>Финальные условия</t>
+        </is>
+      </c>
+      <c r="G22" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="55">
+        <f>SUM(G22:S22)</f>
+        <v/>
+      </c>
+      <c r="U22" s="18" t="inlineStr">
+        <is>
+          <t>⭐ ЭТАЛОН</t>
+        </is>
+      </c>
+      <c r="V22" s="56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t>C-507</t>
+        </is>
+      </c>
+      <c r="B23" s="57" t="inlineStr">
+        <is>
+          <t>D-114 (ООО АльфаТрейд)</t>
+        </is>
+      </c>
+      <c r="C23" s="42" t="inlineStr">
+        <is>
+          <t>Ковалев</t>
+        </is>
+      </c>
+      <c r="D23" s="66" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E23" s="42" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="F23" s="42" t="inlineStr">
+        <is>
+          <t>Дожим договора</t>
+        </is>
+      </c>
+      <c r="G23" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="60">
+        <f>SUM(G23:S23)</f>
+        <v/>
+      </c>
+      <c r="U23" s="17" t="inlineStr">
+        <is>
+          <t>❌ СЛИВ</t>
+        </is>
+      </c>
+      <c r="V23" s="58" t="n">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t>C-508</t>
+        </is>
+      </c>
+      <c r="B24" s="57" t="inlineStr">
+        <is>
+          <t>D-118 (ООО СтройХолдинг)</t>
+        </is>
+      </c>
+      <c r="C24" s="42" t="inlineStr">
+        <is>
+          <t>Попов</t>
+        </is>
+      </c>
+      <c r="D24" s="66" t="n">
+        <v>650000</v>
+      </c>
+      <c r="E24" s="42" t="inlineStr">
+        <is>
+          <t>02:50</t>
+        </is>
+      </c>
+      <c r="F24" s="42" t="inlineStr">
+        <is>
+          <t>Входящий лид</t>
+        </is>
+      </c>
+      <c r="G24" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="60">
+        <f>SUM(G24:S24)</f>
+        <v/>
+      </c>
+      <c r="U24" s="17" t="inlineStr">
+        <is>
+          <t>❌ СЛИВ</t>
+        </is>
+      </c>
+      <c r="V24" s="58" t="n">
+        <v>650000</v>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="43" t="inlineStr">
+        <is>
+          <t>C-509</t>
+        </is>
+      </c>
+      <c r="B25" s="57" t="inlineStr">
+        <is>
+          <t>D-121 (ООО СпецМаш)</t>
+        </is>
+      </c>
+      <c r="C25" s="42" t="inlineStr">
+        <is>
+          <t>Васильева</t>
+        </is>
+      </c>
+      <c r="D25" s="66" t="n">
+        <v>420000</v>
+      </c>
+      <c r="E25" s="42" t="inlineStr">
+        <is>
+          <t>05:10</t>
+        </is>
+      </c>
+      <c r="F25" s="42" t="inlineStr">
+        <is>
+          <t>Презентация КП</t>
+        </is>
+      </c>
+      <c r="G25" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" s="55">
+        <f>SUM(G25:S25)</f>
+        <v/>
+      </c>
+      <c r="U25" s="18" t="inlineStr">
+        <is>
+          <t>🟢 В НОРМЕ</t>
+        </is>
+      </c>
+      <c r="V25" s="56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="43" t="inlineStr">
+        <is>
+          <t>C-510</t>
+        </is>
+      </c>
+      <c r="B26" s="57" t="inlineStr">
+        <is>
+          <t>D-125 (ООО МегаТранс)</t>
+        </is>
+      </c>
+      <c r="C26" s="42" t="inlineStr">
+        <is>
+          <t>Попов</t>
+        </is>
+      </c>
+      <c r="D26" s="66" t="n">
+        <v>450000</v>
+      </c>
+      <c r="E26" s="42" t="inlineStr">
+        <is>
+          <t>03:40</t>
+        </is>
+      </c>
+      <c r="F26" s="42" t="inlineStr">
+        <is>
+          <t>Квалификация</t>
+        </is>
+      </c>
+      <c r="G26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" s="68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="60">
+        <f>SUM(G26:S26)</f>
+        <v/>
+      </c>
+      <c r="U26" s="20" t="inlineStr">
+        <is>
+          <t>⚠️ РИСК</t>
+        </is>
+      </c>
+      <c r="V26" s="58" t="n">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="27" t="inlineStr"/>
+      <c r="B27" s="61" t="inlineStr">
+        <is>
+          <t>ИТОГО ПОТЕРЬ И РИСКОВ ПО ЗВОНКАМ:</t>
+        </is>
+      </c>
+      <c r="C27" s="27" t="inlineStr"/>
+      <c r="D27" s="69">
+        <f>SUM(D17:D26)</f>
+        <v/>
+      </c>
+      <c r="E27" s="27" t="inlineStr"/>
+      <c r="F27" s="27" t="inlineStr"/>
+      <c r="G27" s="27" t="inlineStr"/>
+      <c r="H27" s="27" t="inlineStr"/>
+      <c r="I27" s="27" t="inlineStr"/>
+      <c r="J27" s="27" t="inlineStr"/>
+      <c r="K27" s="27" t="inlineStr"/>
+      <c r="L27" s="27" t="inlineStr"/>
+      <c r="M27" s="27" t="inlineStr"/>
+      <c r="N27" s="27" t="inlineStr"/>
+      <c r="O27" s="27" t="inlineStr"/>
+      <c r="P27" s="27" t="inlineStr"/>
+      <c r="Q27" s="27" t="inlineStr"/>
+      <c r="R27" s="27" t="inlineStr"/>
+      <c r="S27" s="27" t="inlineStr"/>
+      <c r="T27" s="70">
+        <f>AVERAGE(T17:T26)</f>
+        <v/>
+      </c>
+      <c r="U27" s="71" t="inlineStr">
+        <is>
+          <t>6 сливов</t>
+        </is>
+      </c>
+      <c r="V27" s="63">
+        <f>SUM(V17:V26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="12" customHeight="1"/>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="54" t="inlineStr">
+        <is>
+          <t>🚨 РЕЕСТР ДЕФЕКТОВ РЕЧИ: РАСШИФРОВАННЫЕ ЦИТАТЫ ИЗ РАЗГОВОРОВ И РЕШЕНИЯ РОПа</t>
+        </is>
+      </c>
+      <c r="B29" s="54" t="n"/>
+      <c r="C29" s="54" t="n"/>
+      <c r="D29" s="54" t="n"/>
+      <c r="E29" s="54" t="n"/>
+      <c r="F29" s="54" t="n"/>
+      <c r="G29" s="54" t="n"/>
+      <c r="H29" s="54" t="n"/>
+      <c r="I29" s="54" t="n"/>
+      <c r="J29" s="54" t="n"/>
+      <c r="K29" s="54" t="n"/>
+      <c r="L29" s="54" t="n"/>
+      <c r="M29" s="54" t="n"/>
+      <c r="N29" s="54" t="n"/>
+      <c r="O29" s="54" t="n"/>
+      <c r="P29" s="54" t="n"/>
+      <c r="Q29" s="54" t="n"/>
+      <c r="R29" s="54" t="n"/>
+      <c r="S29" s="54" t="n"/>
+      <c r="T29" s="54" t="n"/>
+      <c r="U29" s="54" t="n"/>
+      <c r="V29" s="54" t="n"/>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Call ID</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>Сделка / Контрагент</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="inlineStr">
+        <is>
+          <t>Менеджер</t>
+        </is>
+      </c>
+      <c r="D30" s="25" t="inlineStr">
+        <is>
+          <t>Сумма в риске</t>
+        </is>
+      </c>
+      <c r="E30" s="25" t="inlineStr">
+        <is>
+          <t>Критический дефект речи</t>
+        </is>
+      </c>
+      <c r="F30" s="25" t="inlineStr">
+        <is>
+          <t>💬 Цитата из диалога (Расшифровка Whisper Large V3)</t>
+        </is>
+      </c>
+      <c r="G30" s="25" t="n"/>
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="25" t="n"/>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="25" t="n"/>
+      <c r="L30" s="25" t="n"/>
+      <c r="M30" s="25" t="inlineStr">
+        <is>
+          <t>🤖 Решение ИИ и Срочное действие РОПа</t>
+        </is>
+      </c>
+      <c r="N30" s="25" t="n"/>
+      <c r="O30" s="25" t="n"/>
+      <c r="P30" s="25" t="n"/>
+      <c r="Q30" s="25" t="n"/>
+      <c r="R30" s="25" t="n"/>
+      <c r="S30" s="25" t="n"/>
+      <c r="T30" s="25" t="n"/>
+      <c r="U30" s="25" t="n"/>
+      <c r="V30" s="25" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="43" t="inlineStr">
+        <is>
+          <t>C-505</t>
+        </is>
+      </c>
+      <c r="B31" s="72" t="inlineStr">
+        <is>
+          <t>D-109 (ООО «ПромКомплект»)</t>
+        </is>
+      </c>
+      <c r="C31" s="42" t="inlineStr">
+        <is>
+          <t>Дмитрий Ковалев</t>
+        </is>
+      </c>
+      <c r="D31" s="58" t="n">
+        <v>600000</v>
+      </c>
+      <c r="E31" s="73" t="inlineStr">
+        <is>
+          <t>Срыв контакта / грубость при цене</t>
+        </is>
+      </c>
+      <c r="F31" s="74" t="inlineStr">
+        <is>
+          <t>Клиент: «Почему у вас смета на 15% выше рынка?» → Менеджер: «Не знаю, везде всё дорожает. Не устраивает — берите у конкурентов без гарантии»</t>
+        </is>
+      </c>
+      <c r="G31" s="74" t="n"/>
+      <c r="H31" s="74" t="n"/>
+      <c r="I31" s="74" t="n"/>
+      <c r="J31" s="74" t="n"/>
+      <c r="K31" s="74" t="n"/>
+      <c r="L31" s="74" t="n"/>
+      <c r="M31" s="75" t="inlineStr">
+        <is>
+          <t>🚨 Экстренный звонок РОПа ЛПР до 12:00: принести извинения за консультацию, перехватить сделку, дать проект со спец-гарантией 24 мес.</t>
+        </is>
+      </c>
+      <c r="N31" s="75" t="n"/>
+      <c r="O31" s="75" t="n"/>
+      <c r="P31" s="75" t="n"/>
+      <c r="Q31" s="75" t="n"/>
+      <c r="R31" s="75" t="n"/>
+      <c r="S31" s="75" t="n"/>
+      <c r="T31" s="75" t="n"/>
+      <c r="U31" s="75" t="n"/>
+      <c r="V31" s="75" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>C-503</t>
+        </is>
+      </c>
+      <c r="B32" s="72" t="inlineStr">
+        <is>
+          <t>D-106 (ООО «СнабСервис»)</t>
+        </is>
+      </c>
+      <c r="C32" s="42" t="inlineStr">
+        <is>
+          <t>Анна Соколова</t>
+        </is>
+      </c>
+      <c r="D32" s="58" t="n">
+        <v>280000</v>
+      </c>
+      <c r="E32" s="73" t="inlineStr">
+        <is>
+          <t>Слив жесткого Next Step (в никуда)</t>
+        </is>
+      </c>
+      <c r="F32" s="74" t="inlineStr">
+        <is>
+          <t>Менеджер: «Я вам КП на почту сбросила, посмотрите когда время будет». Клиент: «Хорошо, если что наберу»</t>
+        </is>
+      </c>
+      <c r="G32" s="74" t="n"/>
+      <c r="H32" s="74" t="n"/>
+      <c r="I32" s="74" t="n"/>
+      <c r="J32" s="74" t="n"/>
+      <c r="K32" s="74" t="n"/>
+      <c r="L32" s="74" t="n"/>
+      <c r="M32" s="75" t="inlineStr">
+        <is>
+          <t>Направить клиенту в WhatsApp 2 конкретных слота встречи (сегодня 16:00 / завтра 11:30) с демонстрацией интеграции с CRM.</t>
+        </is>
+      </c>
+      <c r="N32" s="75" t="n"/>
+      <c r="O32" s="75" t="n"/>
+      <c r="P32" s="75" t="n"/>
+      <c r="Q32" s="75" t="n"/>
+      <c r="R32" s="75" t="n"/>
+      <c r="S32" s="75" t="n"/>
+      <c r="T32" s="75" t="n"/>
+      <c r="U32" s="75" t="n"/>
+      <c r="V32" s="75" t="n"/>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>C-507</t>
+        </is>
+      </c>
+      <c r="B33" s="72" t="inlineStr">
+        <is>
+          <t>D-114 (ООО «АльфаТрейд»)</t>
+        </is>
+      </c>
+      <c r="C33" s="42" t="inlineStr">
+        <is>
+          <t>Дмитрий Ковалев</t>
+        </is>
+      </c>
+      <c r="D33" s="58" t="n">
+        <v>500000</v>
+      </c>
+      <c r="E33" s="73" t="inlineStr">
+        <is>
+          <t>Необоснованная скидка вместо ценности</t>
+        </is>
+      </c>
+      <c r="F33" s="74" t="inlineStr">
+        <is>
+          <t>Клиент: «У нас бюджет строго ограничен». Менеджер: «Ну ладно, согласую вам скидку 10% прямо сейчас»</t>
+        </is>
+      </c>
+      <c r="G33" s="74" t="n"/>
+      <c r="H33" s="74" t="n"/>
+      <c r="I33" s="74" t="n"/>
+      <c r="J33" s="74" t="n"/>
+      <c r="K33" s="74" t="n"/>
+      <c r="L33" s="74" t="n"/>
+      <c r="M33" s="75" t="inlineStr">
+        <is>
+          <t>Заблокировать выставление счета со скидкой в CRM. РОПу пересогласовать условия: скидка 5% только в обмен на 100% предоплату за 24ч.</t>
+        </is>
+      </c>
+      <c r="N33" s="75" t="n"/>
+      <c r="O33" s="75" t="n"/>
+      <c r="P33" s="75" t="n"/>
+      <c r="Q33" s="75" t="n"/>
+      <c r="R33" s="75" t="n"/>
+      <c r="S33" s="75" t="n"/>
+      <c r="T33" s="75" t="n"/>
+      <c r="U33" s="75" t="n"/>
+      <c r="V33" s="75" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="43" t="inlineStr">
+        <is>
+          <t>C-508</t>
+        </is>
+      </c>
+      <c r="B34" s="72" t="inlineStr">
+        <is>
+          <t>D-118 (ООО «СтройХолдинг»)</t>
+        </is>
+      </c>
+      <c r="C34" s="42" t="inlineStr">
+        <is>
+          <t>Иван Попов</t>
+        </is>
+      </c>
+      <c r="D34" s="58" t="n">
+        <v>650000</v>
+      </c>
+      <c r="E34" s="73" t="inlineStr">
+        <is>
+          <t>Слив возражения «Я подумаю»</t>
+        </is>
+      </c>
+      <c r="F34" s="74" t="inlineStr">
+        <is>
+          <t>Клиент: «Нам нужно всё обдумать и посоветоваться с руководством». Менеджер: «Да, конечно, думайте» (повесил трубку)</t>
+        </is>
+      </c>
+      <c r="G34" s="74" t="n"/>
+      <c r="H34" s="74" t="n"/>
+      <c r="I34" s="74" t="n"/>
+      <c r="J34" s="74" t="n"/>
+      <c r="K34" s="74" t="n"/>
+      <c r="L34" s="74" t="n"/>
+      <c r="M34" s="75" t="inlineStr">
+        <is>
+          <t>Передать лида старшему КАМу. Отправить в WhatsApp отраслевой кейс с аналогичным объектом и окупаемостью за 21 день.</t>
+        </is>
+      </c>
+      <c r="N34" s="75" t="n"/>
+      <c r="O34" s="75" t="n"/>
+      <c r="P34" s="75" t="n"/>
+      <c r="Q34" s="75" t="n"/>
+      <c r="R34" s="75" t="n"/>
+      <c r="S34" s="75" t="n"/>
+      <c r="T34" s="75" t="n"/>
+      <c r="U34" s="75" t="n"/>
+      <c r="V34" s="75" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="43" t="inlineStr">
+        <is>
+          <t>C-510</t>
+        </is>
+      </c>
+      <c r="B35" s="72" t="inlineStr">
+        <is>
+          <t>D-125 (ООО «МегаТранс»)</t>
+        </is>
+      </c>
+      <c r="C35" s="42" t="inlineStr">
+        <is>
+          <t>Иван Попов</t>
+        </is>
+      </c>
+      <c r="D35" s="58" t="n">
+        <v>450000</v>
+      </c>
+      <c r="E35" s="73" t="inlineStr">
+        <is>
+          <t>Режим автоответчика, не выявлен ЛПР</t>
+        </is>
+      </c>
+      <c r="F35" s="74" t="inlineStr">
+        <is>
+          <t>Менеджер 5 минут зачитывал прайс-лист секретарю, не спросив, кто принимает решение по закупкам</t>
+        </is>
+      </c>
+      <c r="G35" s="74" t="n"/>
+      <c r="H35" s="74" t="n"/>
+      <c r="I35" s="74" t="n"/>
+      <c r="J35" s="74" t="n"/>
+      <c r="K35" s="74" t="n"/>
+      <c r="L35" s="74" t="n"/>
+      <c r="M35" s="75" t="inlineStr">
+        <is>
+          <t>Разбор на летучке: регламент квалификации BANT. Назначить повторный звонок с прямым выходом на генерального директора.</t>
+        </is>
+      </c>
+      <c r="N35" s="75" t="n"/>
+      <c r="O35" s="75" t="n"/>
+      <c r="P35" s="75" t="n"/>
+      <c r="Q35" s="75" t="n"/>
+      <c r="R35" s="75" t="n"/>
+      <c r="S35" s="75" t="n"/>
+      <c r="T35" s="75" t="n"/>
+      <c r="U35" s="75" t="n"/>
+      <c r="V35" s="75" t="n"/>
+    </row>
+    <row r="36" ht="12" customHeight="1"/>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="54" t="inlineStr">
+        <is>
+          <t>📋 ЭТАЛОННЫЙ СТАНДАРТ 13 КРИТЕРИЕВ ОЦЕНКИ B2B-ДИАЛОГОВ (WHISPER LARGE V3 + LLM SUPERVISOR)</t>
+        </is>
+      </c>
+      <c r="B37" s="54" t="n"/>
+      <c r="C37" s="54" t="n"/>
+      <c r="D37" s="54" t="n"/>
+      <c r="E37" s="54" t="n"/>
+      <c r="F37" s="54" t="n"/>
+      <c r="G37" s="54" t="n"/>
+      <c r="H37" s="54" t="n"/>
+      <c r="I37" s="54" t="n"/>
+      <c r="J37" s="54" t="n"/>
+      <c r="K37" s="54" t="n"/>
+      <c r="L37" s="54" t="n"/>
+      <c r="M37" s="54" t="n"/>
+      <c r="N37" s="54" t="n"/>
+      <c r="O37" s="54" t="n"/>
+      <c r="P37" s="54" t="n"/>
+      <c r="Q37" s="54" t="n"/>
+      <c r="R37" s="54" t="n"/>
+      <c r="S37" s="54" t="n"/>
+      <c r="T37" s="54" t="n"/>
+      <c r="U37" s="54" t="n"/>
+      <c r="V37" s="54" t="n"/>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B38" s="25" t="inlineStr">
+        <is>
+          <t>Параметр оценки диалога</t>
+        </is>
+      </c>
+      <c r="C38" s="25" t="inlineStr">
+        <is>
+          <t>Вес</t>
+        </is>
+      </c>
+      <c r="D38" s="25" t="inlineStr">
+        <is>
+          <t>Приоритет</t>
+        </is>
+      </c>
+      <c r="E38" s="25" t="inlineStr">
+        <is>
+          <t>Что проверяет алгоритм ИИ (Суть критерия)</t>
+        </is>
+      </c>
+      <c r="F38" s="25" t="n"/>
+      <c r="G38" s="25" t="n"/>
+      <c r="H38" s="25" t="inlineStr">
+        <is>
+          <t>Маркеры дефекта в речи (Почему сделка срывается)</t>
+        </is>
+      </c>
+      <c r="I38" s="25" t="n"/>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="25" t="n"/>
+      <c r="L38" s="25" t="n"/>
+      <c r="M38" s="25" t="inlineStr">
+        <is>
+          <t>Coaching Tip: как обучить менеджера и защитить выручку</t>
+        </is>
+      </c>
+      <c r="N38" s="25" t="n"/>
+      <c r="O38" s="25" t="n"/>
+      <c r="P38" s="25" t="n"/>
+      <c r="Q38" s="25" t="n"/>
+      <c r="R38" s="25" t="n"/>
+      <c r="S38" s="25" t="n"/>
+      <c r="T38" s="25" t="n"/>
+      <c r="U38" s="25" t="n"/>
+      <c r="V38" s="25" t="n"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Жёсткий Next Step</t>
+        </is>
+      </c>
+      <c r="C39" s="42" t="inlineStr">
+        <is>
+          <t>2.0x</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>🔴 P0 (Критический)</t>
+        </is>
+      </c>
+      <c r="E39" s="76" t="inlineStr">
+        <is>
+          <t>Зафиксирована точная дата и время следующего контакта (календарный слот)</t>
+        </is>
+      </c>
+      <c r="F39" s="76" t="n"/>
+      <c r="G39" s="76" t="n"/>
+      <c r="H39" s="77" t="inlineStr">
+        <is>
+          <t>«Я вам перезвоню на днях», «Подумайте, наберите», отпускание без времени</t>
+        </is>
+      </c>
+      <c r="I39" s="77" t="n"/>
+      <c r="J39" s="77" t="n"/>
+      <c r="K39" s="77" t="n"/>
+      <c r="L39" s="77" t="n"/>
+      <c r="M39" s="78" t="inlineStr">
+        <is>
+          <t>Внедрить обязательный вопрос в конце диалога: «Во вторник в 14:30 или в среду в 11:00 удобно?»</t>
+        </is>
+      </c>
+      <c r="N39" s="78" t="n"/>
+      <c r="O39" s="78" t="n"/>
+      <c r="P39" s="78" t="n"/>
+      <c r="Q39" s="78" t="n"/>
+      <c r="R39" s="78" t="n"/>
+      <c r="S39" s="78" t="n"/>
+      <c r="T39" s="78" t="n"/>
+      <c r="U39" s="78" t="n"/>
+      <c r="V39" s="78" t="n"/>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>Срыв контакта / грубость</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>Личный звонок РОПа с извинениями</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>600000</v>
-      </c>
-      <c r="I8" s="25" t="inlineStr">
-        <is>
-          <t>🔴 ВЫСОКИЙ (VIP-чек)</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>🚨 Личный перезвон РОПа ЛПР</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>C-503</t>
-        </is>
-      </c>
-      <c r="B9" s="25" t="inlineStr">
-        <is>
-          <t>D-106</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>102 (Петров)</t>
-        </is>
-      </c>
-      <c r="D9" s="25" t="inlineStr">
-        <is>
-          <t>180 сек</t>
-        </is>
-      </c>
-      <c r="E9" s="51" t="n">
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Инициатива диалога</t>
+        </is>
+      </c>
+      <c r="C40" s="42" t="inlineStr">
+        <is>
+          <t>1.0x</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>🟡 P1 (Высокий)</t>
+        </is>
+      </c>
+      <c r="E40" s="76" t="inlineStr">
+        <is>
+          <t>Менеджер ведёт диалог вопросами, держит сценарий, а не работает автоответчиком</t>
+        </is>
+      </c>
+      <c r="F40" s="76" t="n"/>
+      <c r="G40" s="76" t="n"/>
+      <c r="H40" s="77" t="inlineStr">
+        <is>
+          <t>Клиент задает все вопросы сам, менеджер только отвечает короткими репликами</t>
+        </is>
+      </c>
+      <c r="I40" s="77" t="n"/>
+      <c r="J40" s="77" t="n"/>
+      <c r="K40" s="77" t="n"/>
+      <c r="L40" s="77" t="n"/>
+      <c r="M40" s="78" t="inlineStr">
+        <is>
+          <t>Правило «Ответ + Встречный вопрос». Завершать каждую реплику квалифицирующим вопросом.</t>
+        </is>
+      </c>
+      <c r="N40" s="78" t="n"/>
+      <c r="O40" s="78" t="n"/>
+      <c r="P40" s="78" t="n"/>
+      <c r="Q40" s="78" t="n"/>
+      <c r="R40" s="78" t="n"/>
+      <c r="S40" s="78" t="n"/>
+      <c r="T40" s="78" t="n"/>
+      <c r="U40" s="78" t="n"/>
+      <c r="V40" s="78" t="n"/>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Квалификация ЛПР / ЛВПР</t>
+        </is>
+      </c>
+      <c r="C41" s="42" t="inlineStr">
+        <is>
+          <t>1.5x</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>🔴 P0 (Критический)</t>
+        </is>
+      </c>
+      <c r="E41" s="76" t="inlineStr">
+        <is>
+          <t>Установлен статус собеседника: принимает ли решения по бюджету и согласованию</t>
+        </is>
+      </c>
+      <c r="F41" s="76" t="n"/>
+      <c r="G41" s="76" t="n"/>
+      <c r="H41" s="77" t="inlineStr">
+        <is>
+          <t>Трата 40 минут на презентацию инженеру или секретарю без полномочий подписания</t>
+        </is>
+      </c>
+      <c r="I41" s="77" t="n"/>
+      <c r="J41" s="77" t="n"/>
+      <c r="K41" s="77" t="n"/>
+      <c r="L41" s="77" t="n"/>
+      <c r="M41" s="78" t="inlineStr">
+        <is>
+          <t>«Кто кроме вас участвует в согласовании проекта и утверждении финансового бюджета?»</t>
+        </is>
+      </c>
+      <c r="N41" s="78" t="n"/>
+      <c r="O41" s="78" t="n"/>
+      <c r="P41" s="78" t="n"/>
+      <c r="Q41" s="78" t="n"/>
+      <c r="R41" s="78" t="n"/>
+      <c r="S41" s="78" t="n"/>
+      <c r="T41" s="78" t="n"/>
+      <c r="U41" s="78" t="n"/>
+      <c r="V41" s="78" t="n"/>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Выявление болей и срочности</t>
+        </is>
+      </c>
+      <c r="C42" s="42" t="inlineStr">
+        <is>
+          <t>1.2x</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>🟡 P1 (Высокий)</t>
+        </is>
+      </c>
+      <c r="E42" s="76" t="inlineStr">
+        <is>
+          <t>Понятна ли бизнес-задача клиента, текущие потери и дедлайн решения проблемы</t>
+        </is>
+      </c>
+      <c r="F42" s="76" t="n"/>
+      <c r="G42" s="76" t="n"/>
+      <c r="H42" s="77" t="inlineStr">
+        <is>
+          <t>Менеджер сразу начинает презентовать продукт, не узнав текущую ситуацию клиента</t>
+        </is>
+      </c>
+      <c r="I42" s="77" t="n"/>
+      <c r="J42" s="77" t="n"/>
+      <c r="K42" s="77" t="n"/>
+      <c r="L42" s="77" t="n"/>
+      <c r="M42" s="78" t="inlineStr">
+        <is>
+          <t>Сначала диагностика по методологии SPIN/BANT, затем презентация под конкретную боль.</t>
+        </is>
+      </c>
+      <c r="N42" s="78" t="n"/>
+      <c r="O42" s="78" t="n"/>
+      <c r="P42" s="78" t="n"/>
+      <c r="Q42" s="78" t="n"/>
+      <c r="R42" s="78" t="n"/>
+      <c r="S42" s="78" t="n"/>
+      <c r="T42" s="78" t="n"/>
+      <c r="U42" s="78" t="n"/>
+      <c r="V42" s="78" t="n"/>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Отработка возражения «Дорого»</t>
+        </is>
+      </c>
+      <c r="C43" s="42" t="inlineStr">
+        <is>
+          <t>1.5x</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>🔴 P0 (Критический)</t>
+        </is>
+      </c>
+      <c r="E43" s="76" t="inlineStr">
+        <is>
+          <t>Обоснование ценности, расчет ROI/окупаемости, рассрочка (без моментальной скидки)</t>
+        </is>
+      </c>
+      <c r="F43" s="76" t="n"/>
+      <c r="G43" s="76" t="n"/>
+      <c r="H43" s="77" t="inlineStr">
+        <is>
+          <t>Моментальная скидка при первом сомнении клиента или согласие («Да, у нас недешево»)</t>
+        </is>
+      </c>
+      <c r="I43" s="77" t="n"/>
+      <c r="J43" s="77" t="n"/>
+      <c r="K43" s="77" t="n"/>
+      <c r="L43" s="77" t="n"/>
+      <c r="M43" s="78" t="inlineStr">
+        <is>
+          <t>Обосновать окупаемость: показать, сколько клиент теряет каждый день без внедрения решения.</t>
+        </is>
+      </c>
+      <c r="N43" s="78" t="n"/>
+      <c r="O43" s="78" t="n"/>
+      <c r="P43" s="78" t="n"/>
+      <c r="Q43" s="78" t="n"/>
+      <c r="R43" s="78" t="n"/>
+      <c r="S43" s="78" t="n"/>
+      <c r="T43" s="78" t="n"/>
+      <c r="U43" s="78" t="n"/>
+      <c r="V43" s="78" t="n"/>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>Нет фиксации даты встречи</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>Направить 2 слота в мессенджер</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>280000</v>
-      </c>
-      <c r="I9" s="25" t="inlineStr">
-        <is>
-          <t>🟡 СРЕДНИЙ</t>
-        </is>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>Тренинг менеджера по скрипту</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
-        <is>
-          <t>C-502</t>
-        </is>
-      </c>
-      <c r="B10" s="25" t="inlineStr">
-        <is>
-          <t>D-104</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>101 (Сидоров)</t>
-        </is>
-      </c>
-      <c r="D10" s="25" t="inlineStr">
-        <is>
-          <t>310 сек</t>
-        </is>
-      </c>
-      <c r="E10" s="52" t="n">
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Отработка «Я подумаю»</t>
+        </is>
+      </c>
+      <c r="C44" s="42" t="inlineStr">
+        <is>
+          <t>1.0x</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>🟡 P1 (Высокий)</t>
+        </is>
+      </c>
+      <c r="E44" s="76" t="inlineStr">
+        <is>
+          <t>Вскрытие истинного сомнения клиента, а не молчаливое отпускание в архив</t>
+        </is>
+      </c>
+      <c r="F44" s="76" t="n"/>
+      <c r="G44" s="76" t="n"/>
+      <c r="H44" s="77" t="inlineStr">
+        <is>
+          <t>«Хорошо, думайте, ждем вашего звонка», завершение диалога на неопределенности</t>
+        </is>
+      </c>
+      <c r="I44" s="77" t="n"/>
+      <c r="J44" s="77" t="n"/>
+      <c r="K44" s="77" t="n"/>
+      <c r="L44" s="77" t="n"/>
+      <c r="M44" s="78" t="inlineStr">
+        <is>
+          <t>«Алексей, обычно говорят 'подумаю', когда смущает цена или функционал. Что именно из этого?»</t>
+        </is>
+      </c>
+      <c r="N44" s="78" t="n"/>
+      <c r="O44" s="78" t="n"/>
+      <c r="P44" s="78" t="n"/>
+      <c r="Q44" s="78" t="n"/>
+      <c r="R44" s="78" t="n"/>
+      <c r="S44" s="78" t="n"/>
+      <c r="T44" s="78" t="n"/>
+      <c r="U44" s="78" t="n"/>
+      <c r="V44" s="78" t="n"/>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Презентация через кейсы и цифры</t>
+        </is>
+      </c>
+      <c r="C45" s="42" t="inlineStr">
+        <is>
+          <t>1.0x</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>🟡 P1 (Высокий)</t>
+        </is>
+      </c>
+      <c r="E45" s="76" t="inlineStr">
+        <is>
+          <t>Приведение аналогичных проектов, оцифрованных результатов и сроков возврата</t>
+        </is>
+      </c>
+      <c r="F45" s="76" t="n"/>
+      <c r="G45" s="76" t="n"/>
+      <c r="H45" s="77" t="inlineStr">
+        <is>
+          <t>Абстрактные слова «мы надежные», «у нас высокое качество» без конкретных фактов</t>
+        </is>
+      </c>
+      <c r="I45" s="77" t="n"/>
+      <c r="J45" s="77" t="n"/>
+      <c r="K45" s="77" t="n"/>
+      <c r="L45" s="77" t="n"/>
+      <c r="M45" s="78" t="inlineStr">
+        <is>
+          <t>Показать схожий кейс из отрасли клиента: «Для завода X мы сократили потери на 1.4 млн ₽ за 21 день».</t>
+        </is>
+      </c>
+      <c r="N45" s="78" t="n"/>
+      <c r="O45" s="78" t="n"/>
+      <c r="P45" s="78" t="n"/>
+      <c r="Q45" s="78" t="n"/>
+      <c r="R45" s="78" t="n"/>
+      <c r="S45" s="78" t="n"/>
+      <c r="T45" s="78" t="n"/>
+      <c r="U45" s="78" t="n"/>
+      <c r="V45" s="78" t="n"/>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Попытка закрытия сделки</t>
+        </is>
+      </c>
+      <c r="C46" s="42" t="inlineStr">
+        <is>
+          <t>1.5x</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
+        <is>
+          <t>🔴 P0 (Критический)</t>
+        </is>
+      </c>
+      <c r="E46" s="76" t="inlineStr">
+        <is>
+          <t>Прямое предложение заключить договор, забронировать слот аудита или выставить счет</t>
+        </is>
+      </c>
+      <c r="F46" s="76" t="n"/>
+      <c r="G46" s="76" t="n"/>
+      <c r="H46" s="77" t="inlineStr">
+        <is>
+          <t>Разговор закончился тепло, но менеджер не предложил сделать следующий шаг к оплате</t>
+        </is>
+      </c>
+      <c r="I46" s="77" t="n"/>
+      <c r="J46" s="77" t="n"/>
+      <c r="K46" s="77" t="n"/>
+      <c r="L46" s="77" t="n"/>
+      <c r="M46" s="78" t="inlineStr">
+        <is>
+          <t>«Если все параметры подходят, предлагаю сегодня запустить пилот. Куда отправить договор?»</t>
+        </is>
+      </c>
+      <c r="N46" s="78" t="n"/>
+      <c r="O46" s="78" t="n"/>
+      <c r="P46" s="78" t="n"/>
+      <c r="Q46" s="78" t="n"/>
+      <c r="R46" s="78" t="n"/>
+      <c r="S46" s="78" t="n"/>
+      <c r="T46" s="78" t="n"/>
+      <c r="U46" s="78" t="n"/>
+      <c r="V46" s="78" t="n"/>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Регламент приветствия и повестка</t>
+        </is>
+      </c>
+      <c r="C47" s="42" t="inlineStr">
+        <is>
+          <t>0.8x</t>
+        </is>
+      </c>
+      <c r="D47" s="79" t="inlineStr">
+        <is>
+          <t>🟢 P2 (Стандарт)</t>
+        </is>
+      </c>
+      <c r="E47" s="76" t="inlineStr">
+        <is>
+          <t>Представление имени, компании, уточнение времени и согласование цели разговора</t>
+        </is>
+      </c>
+      <c r="F47" s="76" t="n"/>
+      <c r="G47" s="76" t="n"/>
+      <c r="H47" s="77" t="inlineStr">
+        <is>
+          <t>Невнятное приветствие, вопрос «Вам удобно говорить?» без обозначения повестки</t>
+        </is>
+      </c>
+      <c r="I47" s="77" t="n"/>
+      <c r="J47" s="77" t="n"/>
+      <c r="K47" s="77" t="n"/>
+      <c r="L47" s="77" t="n"/>
+      <c r="M47" s="78" t="inlineStr">
+        <is>
+          <t>«Добрый день! Дмитрий, компания RevOps. Звоню по вашей заявке на аудит воронки. Уделите 5 минут?»</t>
+        </is>
+      </c>
+      <c r="N47" s="78" t="n"/>
+      <c r="O47" s="78" t="n"/>
+      <c r="P47" s="78" t="n"/>
+      <c r="Q47" s="78" t="n"/>
+      <c r="R47" s="78" t="n"/>
+      <c r="S47" s="78" t="n"/>
+      <c r="T47" s="78" t="n"/>
+      <c r="U47" s="78" t="n"/>
+      <c r="V47" s="78" t="n"/>
+    </row>
+    <row r="48" ht="34" customHeight="1">
+      <c r="A48" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Чистота речи и уверенность</t>
+        </is>
+      </c>
+      <c r="C48" s="42" t="inlineStr">
+        <is>
+          <t>0.8x</t>
+        </is>
+      </c>
+      <c r="D48" s="79" t="inlineStr">
+        <is>
+          <t>🟢 P2 (Стандарт)</t>
+        </is>
+      </c>
+      <c r="E48" s="76" t="inlineStr">
+        <is>
+          <t>Отсутствие слов-паразитов («как бы», «э-э-э»), пауз и извиняющихся интонаций при цене</t>
+        </is>
+      </c>
+      <c r="F48" s="76" t="n"/>
+      <c r="G48" s="76" t="n"/>
+      <c r="H48" s="77" t="inlineStr">
+        <is>
+          <t>Дрожащий голос при озвучивании чека, слова сомнения («может быть», «наверное»)</t>
+        </is>
+      </c>
+      <c r="I48" s="77" t="n"/>
+      <c r="J48" s="77" t="n"/>
+      <c r="K48" s="77" t="n"/>
+      <c r="L48" s="77" t="n"/>
+      <c r="M48" s="78" t="inlineStr">
+        <is>
+          <t>Отработать блок цены на тренажере: уверенная пауза после озвучивания стоимости.</t>
+        </is>
+      </c>
+      <c r="N48" s="78" t="n"/>
+      <c r="O48" s="78" t="n"/>
+      <c r="P48" s="78" t="n"/>
+      <c r="Q48" s="78" t="n"/>
+      <c r="R48" s="78" t="n"/>
+      <c r="S48" s="78" t="n"/>
+      <c r="T48" s="78" t="n"/>
+      <c r="U48" s="78" t="n"/>
+      <c r="V48" s="78" t="n"/>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="42" t="n">
         <v>11</v>
       </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>Слабая отработка возражения цены</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>Предложить расчет окупаемости и рассрочку</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="n">
-        <v>850000</v>
-      </c>
-      <c r="I10" s="25" t="inlineStr">
-        <is>
-          <t>🟢 КОНТРОЛЬ</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>Перепроверить отправку КП</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>C-504</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="inlineStr">
-        <is>
-          <t>D-107</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>103 (Иванова)</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="inlineStr">
-        <is>
-          <t>540 сек</t>
-        </is>
-      </c>
-      <c r="E11" s="52" t="n">
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Слушание клиента (Talk/Listen)</t>
+        </is>
+      </c>
+      <c r="C49" s="42" t="inlineStr">
+        <is>
+          <t>1.2x</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>🟡 P1 (Высокий)</t>
+        </is>
+      </c>
+      <c r="E49" s="76" t="inlineStr">
+        <is>
+          <t>Менеджер слушает клиента не менее 45–50% общего времени разговора</t>
+        </is>
+      </c>
+      <c r="F49" s="76" t="n"/>
+      <c r="G49" s="76" t="n"/>
+      <c r="H49" s="77" t="inlineStr">
+        <is>
+          <t>Монолог менеджера &gt; 70% времени: клиент молчит и теряет фокус внимания</t>
+        </is>
+      </c>
+      <c r="I49" s="77" t="n"/>
+      <c r="J49" s="77" t="n"/>
+      <c r="K49" s="77" t="n"/>
+      <c r="L49" s="77" t="n"/>
+      <c r="M49" s="78" t="inlineStr">
+        <is>
+          <t>Держать баланс 50/50. Задавать открытые вопросы и давать клиенту выговориться о проблеме.</t>
+        </is>
+      </c>
+      <c r="N49" s="78" t="n"/>
+      <c r="O49" s="78" t="n"/>
+      <c r="P49" s="78" t="n"/>
+      <c r="Q49" s="78" t="n"/>
+      <c r="R49" s="78" t="n"/>
+      <c r="S49" s="78" t="n"/>
+      <c r="T49" s="78" t="n"/>
+      <c r="U49" s="78" t="n"/>
+      <c r="V49" s="78" t="n"/>
+    </row>
+    <row r="50" ht="34" customHeight="1">
+      <c r="A50" s="42" t="n">
         <v>12</v>
       </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>Не выявлен дедлайн бюджета</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>Задать прямой вопрос о сроках согласования</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="n">
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Фиксация договорённостей</t>
+        </is>
+      </c>
+      <c r="C50" s="42" t="inlineStr">
+        <is>
+          <t>1.0x</t>
+        </is>
+      </c>
+      <c r="D50" s="79" t="inlineStr">
+        <is>
+          <t>🟢 P2 (Стандарт)</t>
+        </is>
+      </c>
+      <c r="E50" s="76" t="inlineStr">
+        <is>
+          <t>Резюмирование договоренностей перед окончанием звонка: кто, что и когда делает</t>
+        </is>
+      </c>
+      <c r="F50" s="76" t="n"/>
+      <c r="G50" s="76" t="n"/>
+      <c r="H50" s="77" t="inlineStr">
+        <is>
+          <t>Диалог оборвался, у клиента и менеджера разное понимание следующих действий</t>
+        </is>
+      </c>
+      <c r="I50" s="77" t="n"/>
+      <c r="J50" s="77" t="n"/>
+      <c r="K50" s="77" t="n"/>
+      <c r="L50" s="77" t="n"/>
+      <c r="M50" s="78" t="inlineStr">
+        <is>
+          <t>«Итак, резюмирую: я отправляю КП в WhatsApp до 15:00, а завтра в 11:00 мы созваниваемся по условиям».</t>
+        </is>
+      </c>
+      <c r="N50" s="78" t="n"/>
+      <c r="O50" s="78" t="n"/>
+      <c r="P50" s="78" t="n"/>
+      <c r="Q50" s="78" t="n"/>
+      <c r="R50" s="78" t="n"/>
+      <c r="S50" s="78" t="n"/>
+      <c r="T50" s="78" t="n"/>
+      <c r="U50" s="78" t="n"/>
+      <c r="V50" s="78" t="n"/>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="42" t="n">
+        <v>13</v>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Защита маржинальности</t>
+        </is>
+      </c>
+      <c r="C51" s="42" t="inlineStr">
+        <is>
+          <t>1.5x</t>
+        </is>
+      </c>
+      <c r="D51" s="17" t="inlineStr">
+        <is>
+          <t>🔴 P0 (Критический)</t>
+        </is>
+      </c>
+      <c r="E51" s="76" t="inlineStr">
+        <is>
+          <t>Отсутствие необоснованных скидок без встречных уступок по объему или предоплате</t>
+        </is>
+      </c>
+      <c r="F51" s="76" t="n"/>
+      <c r="G51" s="76" t="n"/>
+      <c r="H51" s="77" t="inlineStr">
+        <is>
+          <t>Раздача скидок из маржи компании без требования 100% предоплаты или большего объема</t>
+        </is>
+      </c>
+      <c r="I51" s="77" t="n"/>
+      <c r="J51" s="77" t="n"/>
+      <c r="K51" s="77" t="n"/>
+      <c r="L51" s="77" t="n"/>
+      <c r="M51" s="78" t="inlineStr">
+        <is>
+          <t>Скидка возможна только в обмен на ценность: «Готовы дать 5% при оплате счета в течение 24 часов».</t>
+        </is>
+      </c>
+      <c r="N51" s="78" t="n"/>
+      <c r="O51" s="78" t="n"/>
+      <c r="P51" s="78" t="n"/>
+      <c r="Q51" s="78" t="n"/>
+      <c r="R51" s="78" t="n"/>
+      <c r="S51" s="78" t="n"/>
+      <c r="T51" s="78" t="n"/>
+      <c r="U51" s="78" t="n"/>
+      <c r="V51" s="78" t="n"/>
+    </row>
+    <row r="52" ht="12" customHeight="1"/>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="54" t="inlineStr">
+        <is>
+          <t>💰 ЭКОНОМИЧЕСКИЙ ЭФФЕКТ РЕЧЕВОЙ АНАЛИТИКИ (ROI ВНЕДРЕНИЯ И ОКУПАЕМОСТЬ)</t>
+        </is>
+      </c>
+      <c r="B53" s="54" t="n"/>
+      <c r="C53" s="54" t="n"/>
+      <c r="D53" s="54" t="n"/>
+      <c r="E53" s="54" t="n"/>
+      <c r="F53" s="54" t="n"/>
+      <c r="G53" s="54" t="n"/>
+      <c r="H53" s="54" t="n"/>
+      <c r="I53" s="54" t="n"/>
+      <c r="J53" s="54" t="n"/>
+      <c r="K53" s="54" t="n"/>
+      <c r="L53" s="54" t="n"/>
+      <c r="M53" s="54" t="n"/>
+      <c r="N53" s="54" t="n"/>
+      <c r="O53" s="54" t="n"/>
+      <c r="P53" s="54" t="n"/>
+      <c r="Q53" s="54" t="n"/>
+      <c r="R53" s="54" t="n"/>
+      <c r="S53" s="54" t="n"/>
+      <c r="T53" s="54" t="n"/>
+      <c r="U53" s="54" t="n"/>
+      <c r="V53" s="54" t="n"/>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="25" t="inlineStr">
+        <is>
+          <t>Параметр эффекта речевой аналитики</t>
+        </is>
+      </c>
+      <c r="B54" s="25" t="n"/>
+      <c r="C54" s="25" t="n"/>
+      <c r="D54" s="25" t="inlineStr">
+        <is>
+          <t>Значение</t>
+        </is>
+      </c>
+      <c r="E54" s="25" t="n"/>
+      <c r="F54" s="25" t="inlineStr">
+        <is>
+          <t>Комментарий и логика окупаемости</t>
+        </is>
+      </c>
+      <c r="G54" s="25" t="n"/>
+      <c r="H54" s="25" t="n"/>
+      <c r="I54" s="25" t="n"/>
+      <c r="J54" s="25" t="n"/>
+      <c r="K54" s="25" t="n"/>
+      <c r="L54" s="25" t="n"/>
+      <c r="M54" s="25" t="n"/>
+      <c r="N54" s="25" t="n"/>
+      <c r="O54" s="25" t="n"/>
+      <c r="P54" s="25" t="n"/>
+      <c r="Q54" s="25" t="n"/>
+      <c r="R54" s="25" t="n"/>
+      <c r="S54" s="25" t="n"/>
+      <c r="T54" s="25" t="n"/>
+      <c r="U54" s="25" t="n"/>
+      <c r="V54" s="25" t="n"/>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="A55" s="72" t="inlineStr">
+        <is>
+          <t>Текущие потери от брака звонков в месяц (As-Is)</t>
+        </is>
+      </c>
+      <c r="B55" s="72" t="n"/>
+      <c r="C55" s="72" t="n"/>
+      <c r="D55" s="80" t="n">
+        <v>1382500</v>
+      </c>
+      <c r="E55" s="80" t="n"/>
+      <c r="F55" s="57" t="inlineStr">
+        <is>
+          <t>Сливы на этапе первичного звонка из-за отсутствия Next Step и слабой отработки возражений</t>
+        </is>
+      </c>
+      <c r="G55" s="57" t="n"/>
+      <c r="H55" s="57" t="n"/>
+      <c r="I55" s="57" t="n"/>
+      <c r="J55" s="57" t="n"/>
+      <c r="K55" s="57" t="n"/>
+      <c r="L55" s="57" t="n"/>
+      <c r="M55" s="57" t="n"/>
+      <c r="N55" s="57" t="n"/>
+      <c r="O55" s="57" t="n"/>
+      <c r="P55" s="57" t="n"/>
+      <c r="Q55" s="57" t="n"/>
+      <c r="R55" s="57" t="n"/>
+      <c r="S55" s="57" t="n"/>
+      <c r="T55" s="57" t="n"/>
+      <c r="U55" s="57" t="n"/>
+      <c r="V55" s="57" t="n"/>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="72" t="inlineStr">
+        <is>
+          <t>Ожидаемый возврат выручки в кассу (M1 To-Be)</t>
+        </is>
+      </c>
+      <c r="B56" s="72" t="n"/>
+      <c r="C56" s="72" t="n"/>
+      <c r="D56" s="81" t="n">
+        <v>414750</v>
+      </c>
+      <c r="E56" s="81" t="n"/>
+      <c r="F56" s="57" t="inlineStr">
+        <is>
+          <t>Консервативный сценарий: устранение всего 30% выявленных дефектов речи</t>
+        </is>
+      </c>
+      <c r="G56" s="57" t="n"/>
+      <c r="H56" s="57" t="n"/>
+      <c r="I56" s="57" t="n"/>
+      <c r="J56" s="57" t="n"/>
+      <c r="K56" s="57" t="n"/>
+      <c r="L56" s="57" t="n"/>
+      <c r="M56" s="57" t="n"/>
+      <c r="N56" s="57" t="n"/>
+      <c r="O56" s="57" t="n"/>
+      <c r="P56" s="57" t="n"/>
+      <c r="Q56" s="57" t="n"/>
+      <c r="R56" s="57" t="n"/>
+      <c r="S56" s="57" t="n"/>
+      <c r="T56" s="57" t="n"/>
+      <c r="U56" s="57" t="n"/>
+      <c r="V56" s="57" t="n"/>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="72" t="inlineStr">
+        <is>
+          <t>Стоимость модуля речевого ИИ-супервайзера</t>
+        </is>
+      </c>
+      <c r="B57" s="72" t="n"/>
+      <c r="C57" s="72" t="n"/>
+      <c r="D57" s="82" t="n">
         <v>150000</v>
       </c>
-      <c r="I11" s="25" t="inlineStr">
-        <is>
-          <t>🟢 КОНТРОЛЬ</t>
-        </is>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>Контроль выставления счета</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
-        <is>
-          <t>C-501</t>
-        </is>
-      </c>
-      <c r="B12" s="25" t="inlineStr">
-        <is>
-          <t>D-101</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>102 (Петров)</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="inlineStr">
-        <is>
-          <t>420 сек</t>
-        </is>
-      </c>
-      <c r="E12" s="52" t="n">
-        <v>13</v>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>Без дефектов (Эталонный диалог)</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Использовать в базе знаний компании</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="n">
-        <v>700000</v>
-      </c>
-      <c r="I12" s="25" t="inlineStr">
-        <is>
-          <t>⭐ ЭТАЛОН</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t>Похвала сотрудника на летучке</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
-        <is>
-          <t>C-506</t>
-        </is>
-      </c>
-      <c r="B13" s="25" t="inlineStr">
-        <is>
-          <t>D-108</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>103 (Иванова)</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="inlineStr">
-        <is>
-          <t>290 сек</t>
-        </is>
-      </c>
-      <c r="E13" s="52" t="n">
-        <v>13</v>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>Без дефектов (Эталонный диалог)</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>Быстрый квалификационный переход</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="n">
-        <v>320000</v>
-      </c>
-      <c r="I13" s="25" t="inlineStr">
-        <is>
-          <t>⭐ ЭТАЛОН</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="inlineStr">
-        <is>
-          <t>Перевод сделки на этап демо</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="26" t="n"/>
-      <c r="B14" s="27" t="inlineStr">
-        <is>
-          <t>ИТОГО ПОТЕРЬ ИЗ-ЗА БРАКА ЗВОНКОВ:</t>
-        </is>
-      </c>
-      <c r="C14" s="26" t="n"/>
-      <c r="D14" s="26" t="n"/>
-      <c r="E14" s="26" t="n"/>
-      <c r="F14" s="26" t="n"/>
-      <c r="G14" s="26" t="n"/>
-      <c r="H14" s="28">
-        <f>SUM(H8:H9)</f>
-        <v/>
-      </c>
-      <c r="I14" s="53" t="inlineStr">
-        <is>
-          <t>ИТОГО В РИСКЕ</t>
-        </is>
-      </c>
-      <c r="J14" s="44" t="inlineStr">
-        <is>
-          <t>Срочный разбор с менеджерами</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="45" t="inlineStr">
-        <is>
-          <t>🎙️ ЭТАЛОННАЯ СИСТЕМА 13 КРИТЕРИЕВ ОЦЕНКИ ЗВОНКОВ (WHISPER LARGE V3 + LLM SUPERVISOR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>Параметр оценки диалога</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>Вес</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>Приоритет</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="inlineStr">
-        <is>
-          <t>Что проверяет алгоритм ИИ (Суть критерия)</t>
-        </is>
-      </c>
-      <c r="F17" s="24" t="inlineStr">
-        <is>
-          <t>Маркеры брака и речевые дефекты</t>
-        </is>
-      </c>
-      <c r="G17" s="54" t="n"/>
-      <c r="H17" s="24" t="inlineStr">
-        <is>
-          <t>Coaching Tip: как обучить менеджера и предотвратить слив</t>
-        </is>
-      </c>
-      <c r="I17" s="54" t="n"/>
-      <c r="J17" s="54" t="n"/>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Жёсткий Next Step</t>
-        </is>
-      </c>
-      <c r="C18" s="41" t="inlineStr">
-        <is>
-          <t>2.0x</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>🔴 P0 (Критический)</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>Зафиксирована точная дата и время следующего контакта (календарный слот)</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>«Я вам перезвоню на днях», «Подумайте, наберите», отпускание без времени</t>
-        </is>
-      </c>
-      <c r="G18" s="9" t="n"/>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>Внедрить обязательный вопрос в конце диалога: «Во вторник в 14:30 или в среду в 11:00 удобно?»</t>
-        </is>
-      </c>
-      <c r="I18" s="9" t="n"/>
-      <c r="J18" s="9" t="n"/>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Инициатива диалога</t>
-        </is>
-      </c>
-      <c r="C19" s="41" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>🟡 P1 (Высокий)</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>Менеджер ведёт диалог вопросами, держит сценарий, а не работает автоответчиком</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
-        <is>
-          <t>Клиент задает все вопросы сам, менеджер только отвечает короткими репликами</t>
-        </is>
-      </c>
-      <c r="G19" s="9" t="n"/>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>Правило «Ответ + Встречный вопрос». Завершать каждую реплику квалифицирующим вопросом.</t>
-        </is>
-      </c>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="41" t="n">
-        <v>3</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Квалификация ЛПР / ЛВПР</t>
-        </is>
-      </c>
-      <c r="C20" s="41" t="inlineStr">
-        <is>
-          <t>1.5x</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>🔴 P0 (Критический)</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>Установлен статус собеседника: принимает ли решения по бюджету и согласованию</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>Трата 40 минут на презентацию инженеру или секретарю без полномочий подписания</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>«Кто кроме вас участвует в согласовании проекта и утверждении финансового бюджета?»</t>
-        </is>
-      </c>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="9" t="n"/>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="41" t="n">
-        <v>4</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Выявление болей и срочности</t>
-        </is>
-      </c>
-      <c r="C21" s="41" t="inlineStr">
-        <is>
-          <t>1.2x</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>🟡 P1 (Высокий)</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>Понятна ли бизнес-задача клиента, текущие потери и дедлайн решения проблемы</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>Менеджер сразу начинает презентовать продукт, не узнав текущую ситуацию клиента</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="inlineStr">
-        <is>
-          <t>Сначала диагностика по методологии SPIN/BANT, затем презентация под конкретную боль.</t>
-        </is>
-      </c>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="41" t="n">
-        <v>5</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Отработка возражения «Дорого»</t>
-        </is>
-      </c>
-      <c r="C22" s="41" t="inlineStr">
-        <is>
-          <t>1.5x</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>🔴 P0 (Критический)</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>Обоснование ценности, расчет ROI/окупаемости, рассрочка (без моментальной скидки)</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>Моментальная скидка при первом сомнении клиента или согласие («Да, у нас недешево»)</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="inlineStr">
-        <is>
-          <t>Обосновать окупаемость: показать, сколько клиент теряет каждый день без внедрения решения.</t>
-        </is>
-      </c>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="41" t="n">
-        <v>6</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Отработка «Я подумаю»</t>
-        </is>
-      </c>
-      <c r="C23" s="41" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>🟡 P1 (Высокий)</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>Вскрытие истинного сомнения клиента, а не молчаливое отпускание в архив</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>«Хорошо, думайте, ждем вашего звонка», завершение диалога на неопределенности</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>«Алексей, обычно говорят 'подумаю', когда смущает цена или функционал. Что именно из этого?»</t>
-        </is>
-      </c>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="41" t="n">
-        <v>7</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Презентация через кейсы и цифры</t>
-        </is>
-      </c>
-      <c r="C24" s="41" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>🟡 P1 (Высокий)</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>Приведение аналогичных проектов, оцифрованных результатов и сроков возврата</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>Абстрактные слова «мы надежные», «у нас высокое качество» без конкретных фактов</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="inlineStr">
-        <is>
-          <t>Показать схожий кейс из отрасли клиента: «Для завода X мы сократили потери на 1.4 млн ₽ за 21 день».</t>
-        </is>
-      </c>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="41" t="n">
-        <v>8</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Попытка закрытия сделки</t>
-        </is>
-      </c>
-      <c r="C25" s="41" t="inlineStr">
-        <is>
-          <t>1.5x</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>🔴 P0 (Критический)</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>Прямое предложение заключить договор, забронировать слот аудита или выставить счет</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>Разговор закончился тепло, но менеджер не предложил сделать следующий шаг к оплате</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="inlineStr">
-        <is>
-          <t>«Если все параметры подходят, предлагаю сегодня запустить пилот. Куда отправить договор?»</t>
-        </is>
-      </c>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="41" t="n">
-        <v>9</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Регламент приветствия и повестка</t>
-        </is>
-      </c>
-      <c r="C26" s="41" t="inlineStr">
-        <is>
-          <t>0.8x</t>
-        </is>
-      </c>
-      <c r="D26" s="55" t="inlineStr">
-        <is>
-          <t>🟢 P2 (Стандарт)</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>Представление имени, компании, уточнение времени и согласование цели разговора</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>Невнятное приветствие, вопрос «Вам удобно говорить?» без обозначения повестки</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t>«Добрый день! Дмитрий, компания RevOps. Звоню по вашей заявке на аудит воронки. Уделите 5 минут?»</t>
-        </is>
-      </c>
-      <c r="I26" s="9" t="n"/>
-      <c r="J26" s="9" t="n"/>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="41" t="n">
-        <v>10</v>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Чистота речи и уверенность</t>
-        </is>
-      </c>
-      <c r="C27" s="41" t="inlineStr">
-        <is>
-          <t>0.8x</t>
-        </is>
-      </c>
-      <c r="D27" s="55" t="inlineStr">
-        <is>
-          <t>🟢 P2 (Стандарт)</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>Отсутствие слов-паразитов («как бы», «э-э-э»), пауз и извиняющихся интонаций при цене</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>Дрожащий голос при озвучивании чека, слова сомнения («может быть», «наверное»)</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="inlineStr">
-        <is>
-          <t>Отработать блок цены на тренажере: уверенная пауза после озвучивания стоимости.</t>
-        </is>
-      </c>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="41" t="n">
-        <v>11</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Слушание клиента (Talk/Listen)</t>
-        </is>
-      </c>
-      <c r="C28" s="41" t="inlineStr">
-        <is>
-          <t>1.2x</t>
-        </is>
-      </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>🟡 P1 (Высокий)</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>Менеджер слушает клиента не менее 45–50% общего времени разговора</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>Монолог менеджера &gt; 70% времени: клиент молчит и теряет фокус внимания</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="n"/>
-      <c r="H28" s="9" t="inlineStr">
-        <is>
-          <t>Держать баланс 50/50. Задавать открытые вопросы и давать клиенту выговориться о проблеме.</t>
-        </is>
-      </c>
-      <c r="I28" s="9" t="n"/>
-      <c r="J28" s="9" t="n"/>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="41" t="n">
-        <v>12</v>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Фиксация договорённостей</t>
-        </is>
-      </c>
-      <c r="C29" s="41" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="D29" s="55" t="inlineStr">
-        <is>
-          <t>🟢 P2 (Стандарт)</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>Резюмирование договоренностей перед окончанием звонка: кто, что и когда делает</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Диалог оборвался, у клиента и менеджера разное понимание следующих действий</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="n"/>
-      <c r="H29" s="9" t="inlineStr">
-        <is>
-          <t>«Итак, резюмирую: я отправляю КП в WhatsApp до 15:00, а завтра в 11:00 мы созваниваемся по условиям».</t>
-        </is>
-      </c>
-      <c r="I29" s="9" t="n"/>
-      <c r="J29" s="9" t="n"/>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="41" t="n">
-        <v>13</v>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Защита маржинальности</t>
-        </is>
-      </c>
-      <c r="C30" s="41" t="inlineStr">
-        <is>
-          <t>1.5x</t>
-        </is>
-      </c>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>🔴 P0 (Критический)</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>Отсутствие необоснованных скидок без встречных уступок по объему или предоплате</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>Раздача скидок из маржи компании без требования 100% предоплаты или большего объема</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>Скидка возможна только в обмен на ценность: «Готовы дать 5% при оплате счета в течение 24 часов».</t>
-        </is>
-      </c>
-      <c r="I30" s="9" t="n"/>
-      <c r="J30" s="9" t="n"/>
+      <c r="E57" s="82" t="n"/>
+      <c r="F57" s="57" t="inlineStr">
+        <is>
+          <t>В составе комплексного 4-недельного спринта оптимизации отдела продаж</t>
+        </is>
+      </c>
+      <c r="G57" s="57" t="n"/>
+      <c r="H57" s="57" t="n"/>
+      <c r="I57" s="57" t="n"/>
+      <c r="J57" s="57" t="n"/>
+      <c r="K57" s="57" t="n"/>
+      <c r="L57" s="57" t="n"/>
+      <c r="M57" s="57" t="n"/>
+      <c r="N57" s="57" t="n"/>
+      <c r="O57" s="57" t="n"/>
+      <c r="P57" s="57" t="n"/>
+      <c r="Q57" s="57" t="n"/>
+      <c r="R57" s="57" t="n"/>
+      <c r="S57" s="57" t="n"/>
+      <c r="T57" s="57" t="n"/>
+      <c r="U57" s="57" t="n"/>
+      <c r="V57" s="57" t="n"/>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="72" t="inlineStr">
+        <is>
+          <t>Чистая прибыль компании от внедрения в первый месяц</t>
+        </is>
+      </c>
+      <c r="B58" s="72" t="n"/>
+      <c r="C58" s="72" t="n"/>
+      <c r="D58" s="81" t="n">
+        <v>264750</v>
+      </c>
+      <c r="E58" s="81" t="n"/>
+      <c r="F58" s="57" t="inlineStr">
+        <is>
+          <t>Чистый денежный плюс в кассе компании уже в первый месяц работы</t>
+        </is>
+      </c>
+      <c r="G58" s="57" t="n"/>
+      <c r="H58" s="57" t="n"/>
+      <c r="I58" s="57" t="n"/>
+      <c r="J58" s="57" t="n"/>
+      <c r="K58" s="57" t="n"/>
+      <c r="L58" s="57" t="n"/>
+      <c r="M58" s="57" t="n"/>
+      <c r="N58" s="57" t="n"/>
+      <c r="O58" s="57" t="n"/>
+      <c r="P58" s="57" t="n"/>
+      <c r="Q58" s="57" t="n"/>
+      <c r="R58" s="57" t="n"/>
+      <c r="S58" s="57" t="n"/>
+      <c r="T58" s="57" t="n"/>
+      <c r="U58" s="57" t="n"/>
+      <c r="V58" s="57" t="n"/>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="72" t="inlineStr">
+        <is>
+          <t>Чистый ROI речевой аналитики</t>
+        </is>
+      </c>
+      <c r="B59" s="72" t="n"/>
+      <c r="C59" s="72" t="n"/>
+      <c r="D59" s="55" t="inlineStr">
+        <is>
+          <t>276%</t>
+        </is>
+      </c>
+      <c r="E59" s="55" t="n"/>
+      <c r="F59" s="57" t="inlineStr">
+        <is>
+          <t>Отдача на каждый вложенный рубль в первый месяц</t>
+        </is>
+      </c>
+      <c r="G59" s="57" t="n"/>
+      <c r="H59" s="57" t="n"/>
+      <c r="I59" s="57" t="n"/>
+      <c r="J59" s="57" t="n"/>
+      <c r="K59" s="57" t="n"/>
+      <c r="L59" s="57" t="n"/>
+      <c r="M59" s="57" t="n"/>
+      <c r="N59" s="57" t="n"/>
+      <c r="O59" s="57" t="n"/>
+      <c r="P59" s="57" t="n"/>
+      <c r="Q59" s="57" t="n"/>
+      <c r="R59" s="57" t="n"/>
+      <c r="S59" s="57" t="n"/>
+      <c r="T59" s="57" t="n"/>
+      <c r="U59" s="57" t="n"/>
+      <c r="V59" s="57" t="n"/>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" s="72" t="inlineStr">
+        <is>
+          <t>Срок полной окупаемости модуля</t>
+        </is>
+      </c>
+      <c r="B60" s="72" t="n"/>
+      <c r="C60" s="72" t="n"/>
+      <c r="D60" s="55" t="inlineStr">
+        <is>
+          <t>11 дней</t>
+        </is>
+      </c>
+      <c r="E60" s="55" t="n"/>
+      <c r="F60" s="57" t="inlineStr">
+        <is>
+          <t>Количество рабочих дней до полной окупаемости внедрения речевого ИИ</t>
+        </is>
+      </c>
+      <c r="G60" s="57" t="n"/>
+      <c r="H60" s="57" t="n"/>
+      <c r="I60" s="57" t="n"/>
+      <c r="J60" s="57" t="n"/>
+      <c r="K60" s="57" t="n"/>
+      <c r="L60" s="57" t="n"/>
+      <c r="M60" s="57" t="n"/>
+      <c r="N60" s="57" t="n"/>
+      <c r="O60" s="57" t="n"/>
+      <c r="P60" s="57" t="n"/>
+      <c r="Q60" s="57" t="n"/>
+      <c r="R60" s="57" t="n"/>
+      <c r="S60" s="57" t="n"/>
+      <c r="T60" s="57" t="n"/>
+      <c r="U60" s="57" t="n"/>
+      <c r="V60" s="57" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="94">
+    <mergeCell ref="D60:E60"/>
+    <mergeCell ref="M41:V41"/>
+    <mergeCell ref="H43:L43"/>
+    <mergeCell ref="E40:G40"/>
+    <mergeCell ref="H41:L41"/>
+    <mergeCell ref="A29:V29"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="H49:L49"/>
+    <mergeCell ref="A15:V15"/>
+    <mergeCell ref="M39:V39"/>
+    <mergeCell ref="J9:V9"/>
+    <mergeCell ref="M48:V48"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F33:L33"/>
+    <mergeCell ref="E42:G42"/>
+    <mergeCell ref="M31:V31"/>
+    <mergeCell ref="H48:L48"/>
+    <mergeCell ref="E44:G44"/>
+    <mergeCell ref="H4:V4"/>
+    <mergeCell ref="F31:L31"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="H38:L38"/>
+    <mergeCell ref="H44:L44"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="M38:V38"/>
+    <mergeCell ref="H40:L40"/>
+    <mergeCell ref="E46:G46"/>
+    <mergeCell ref="H51:L51"/>
+    <mergeCell ref="F59:V59"/>
+    <mergeCell ref="M43:V43"/>
+    <mergeCell ref="J8:V8"/>
+    <mergeCell ref="F55:V55"/>
+    <mergeCell ref="J10:V10"/>
+    <mergeCell ref="E41:G41"/>
+    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="E47:G47"/>
+    <mergeCell ref="M35:V35"/>
+    <mergeCell ref="E43:G43"/>
+    <mergeCell ref="A60:C60"/>
+    <mergeCell ref="F58:V58"/>
+    <mergeCell ref="H42:L42"/>
+    <mergeCell ref="M30:V30"/>
+    <mergeCell ref="F60:V60"/>
+    <mergeCell ref="M46:V46"/>
+    <mergeCell ref="M33:V33"/>
     <mergeCell ref="F4:G4"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="F57:V57"/>
+    <mergeCell ref="M42:V42"/>
+    <mergeCell ref="J12:V12"/>
+    <mergeCell ref="A53:V53"/>
+    <mergeCell ref="M32:V32"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="H46:L46"/>
+    <mergeCell ref="M44:V44"/>
+    <mergeCell ref="H45:L45"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="M51:V51"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="H47:L47"/>
+    <mergeCell ref="F32:L32"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="F56:V56"/>
+    <mergeCell ref="F35:L35"/>
+    <mergeCell ref="A37:V37"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="J11:V11"/>
+    <mergeCell ref="A54:C54"/>
+    <mergeCell ref="M45:V45"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="H50:L50"/>
+    <mergeCell ref="F54:V54"/>
+    <mergeCell ref="M47:V47"/>
     <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H28:J28"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="H27:J27"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H39:L39"/>
+    <mergeCell ref="E49:G49"/>
+    <mergeCell ref="M50:V50"/>
+    <mergeCell ref="D57:E57"/>
+    <mergeCell ref="M34:V34"/>
+    <mergeCell ref="F34:L34"/>
+    <mergeCell ref="J7:V7"/>
+    <mergeCell ref="H3:V3"/>
+    <mergeCell ref="M49:V49"/>
+    <mergeCell ref="J13:V13"/>
+    <mergeCell ref="F30:L30"/>
+    <mergeCell ref="A6:V6"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="D58:E58"/>
+    <mergeCell ref="M40:V40"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="D59:E59"/>
+    <mergeCell ref="E38:G38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2888,595 +4983,602 @@
           <t>💸 ДИАГНОСТИЧЕСКИЙ АУДИТ УПУЩЕННОЙ ПРИБЫЛИ И УЗКИХ МЕСТ ОТДЕЛА ПРОДАЖ</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>📄 1. One-Pager</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>⚡ 2. Пульс компании</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>📋 3. Пульт РОПа</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>💸 4. 7 Грехов ОП</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>🎯 5. Action Center</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>🎙️ 6. ИИ-Аудит</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>⚡ 7. Экспресс 3 цифры</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>🧪 8. QA Suite</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>Фактическая выручка месяца</t>
         </is>
       </c>
-      <c r="B4" s="48" t="inlineStr">
+      <c r="B4" s="50" t="inlineStr">
         <is>
           <t>Взвешенный пайплайн в работе</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
+      <c r="C4" s="38" t="inlineStr">
         <is>
           <t>Выявленная упущенная прибыль</t>
         </is>
       </c>
-      <c r="D4" s="56" t="inlineStr">
+      <c r="D4" s="83" t="inlineStr">
         <is>
           <t>Потенциал выручки (To-Be)</t>
         </is>
       </c>
-      <c r="E4" s="56" t="inlineStr">
+      <c r="E4" s="83" t="inlineStr">
         <is>
           <t>Ожидаемый чистый ROI</t>
         </is>
       </c>
-      <c r="G4" s="56" t="inlineStr">
+      <c r="G4" s="83" t="inlineStr">
         <is>
           <t>Срок окупаемости проекта</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="57" t="n">
+      <c r="A5" s="84" t="n">
         <v>1650000</v>
       </c>
-      <c r="B5" s="22" t="n">
+      <c r="B5" s="23" t="n">
         <v>2754000</v>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="21" t="n">
         <v>7001000</v>
       </c>
-      <c r="D5" s="21" t="n">
+      <c r="D5" s="22" t="n">
         <v>8651000</v>
       </c>
-      <c r="E5" s="58" t="inlineStr">
+      <c r="E5" s="85" t="inlineStr">
         <is>
           <t>367%</t>
         </is>
       </c>
-      <c r="G5" s="58" t="inlineStr">
+      <c r="G5" s="85" t="inlineStr">
         <is>
           <t>6 дн.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>🔴 7 СМЕРТНЫХ ГРЕХОВ ОТДЕЛА ПРОДАЖ (АНАТОМИЯ СБОЕВ И ИХ УСТРАНЕНИЕ)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Смертный грех ОП (Системный сбой)</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Симптом и диагностика в компании</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>Объем базы в риске</t>
         </is>
       </c>
-      <c r="E8" s="24" t="inlineStr">
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>Упущенная выгода / Риск, ₽</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>Как закрывает наша платформа</t>
         </is>
       </c>
-      <c r="H8" s="24" t="inlineStr">
+      <c r="H8" s="25" t="inlineStr">
         <is>
           <t>Ожидаемый эффект</t>
         </is>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="41" t="inlineStr">
+      <c r="A9" s="42" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>«Черный ящик» CRM: иллюзорный пайплайн</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>В CRM висит 5.3 млн ₽, но реальный взвешенный объем всего 2.6 млн ₽. Фаундер живет в иллюзии плана</t>
         </is>
       </c>
-      <c r="D9" s="59" t="n">
+      <c r="D9" s="86" t="n">
         <v>5530000</v>
       </c>
-      <c r="E9" s="10" t="n">
+      <c r="E9" s="11" t="n">
         <v>2776000</v>
       </c>
-      <c r="F9" s="60" t="inlineStr">
+      <c r="F9" s="87" t="inlineStr">
         <is>
           <t>🔴 P0 (Критический)</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Взвешенный прогноз воронки (SSOT) + исключение зомби-сделок</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>100% точность прогноза Run-Rate без иллюзий</t>
         </is>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="41" t="inlineStr">
+      <c r="A10" s="42" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>«Кладбище сделок»: срыв регламентов SLA</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Сделки маринуются на этапе КП по 12–14 дней (норма 48ч). Вероятность закрытия падает на 45%</t>
         </is>
       </c>
-      <c r="D10" s="59" t="n">
+      <c r="D10" s="86" t="n">
         <v>3850000</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="11" t="n">
         <v>1732500</v>
       </c>
-      <c r="F10" s="60" t="inlineStr">
+      <c r="F10" s="87" t="inlineStr">
         <is>
           <t>🔴 P0 (Критический)</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Авторадар зависания сделок + эскалация РОПу на 3-й день</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>+45% к конверсии этапа КП в оплату</t>
         </is>
       </c>
     </row>
     <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="41" t="inlineStr">
+      <c r="A11" s="42" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>РОП — «играющий тренер» и узкое горлышко</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>РОП ведет 80% сделок и перегружен (нагрузка 80%), а КАМы простаивают с 4% загрузки. Сделки тухнут без внимания</t>
         </is>
       </c>
-      <c r="D11" s="59" t="n">
+      <c r="D11" s="86" t="n">
         <v>850000</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="11" t="n">
         <v>255000</v>
       </c>
-      <c r="F11" s="60" t="inlineStr">
+      <c r="F11" s="87" t="inlineStr">
         <is>
           <t>🔴 P0 (Критический)</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Матрица емкости (Capacity Planning) + автоперелив сделок на КАМов</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Разгрузка РОПа на 60% для управления и коучинга</t>
         </is>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="41" t="inlineStr">
+      <c r="A12" s="42" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Менеджеры-автоответчики и слив звонков</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>В 33% звонков не зафиксирован Next Step. Средний балл речи &lt; 9/13. Лиды уходят в «подумаю»</t>
         </is>
       </c>
-      <c r="D12" s="59" t="n">
+      <c r="D12" s="86" t="n">
         <v>5530000</v>
       </c>
-      <c r="E12" s="10" t="n">
+      <c r="E12" s="11" t="n">
         <v>1382500</v>
       </c>
-      <c r="F12" s="60" t="inlineStr">
+      <c r="F12" s="87" t="inlineStr">
         <is>
           <t>🔴 P0 (Критический)</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>13-факторная речевая аналитика + чек-листы BANT + мотивация от речи</t>
         </is>
       </c>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>+30% к конверсии из первого звонка во встречу</t>
         </is>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="41" t="inlineStr">
+      <c r="A13" s="42" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>«Кладбище отказников» без реактивации</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>1 млн ₽ списан в отказ (L1 «дорого», L2 «подумаю»). База брошена в архиве без повторного прогрева</t>
         </is>
       </c>
-      <c r="D13" s="59" t="n">
+      <c r="D13" s="86" t="n">
         <v>1000000</v>
       </c>
-      <c r="E13" s="10" t="n">
+      <c r="E13" s="11" t="n">
         <v>440000</v>
       </c>
-      <c r="F13" s="61" t="inlineStr">
+      <c r="F13" s="88" t="inlineStr">
         <is>
           <t>🟡 P1 (Высокий)</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Agentic AI Recovery Engine: сегментация отказников + офферы даунсейла</t>
         </is>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>Возврат до 20–30% списанной выручки из архива</t>
         </is>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="41" t="inlineStr">
+      <c r="A14" s="42" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Зависшая дебиторка и кассовые разрывы</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Счета выставлены, но не оплачены (DSO &gt; 25 дней). 330к просрочки грозит кассовым разрывом</t>
         </is>
       </c>
-      <c r="D14" s="59" t="n">
+      <c r="D14" s="86" t="n">
         <v>330000</v>
       </c>
-      <c r="E14" s="10" t="n">
+      <c r="E14" s="11" t="n">
         <v>330000</v>
       </c>
-      <c r="F14" s="61" t="inlineStr">
+      <c r="F14" s="88" t="inlineStr">
         <is>
           <t>🟡 P1 (Высокий)</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>Платежный календарь DSO + триггерные AI-уведомления бухгалтерии клиента</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>Сокращение срока дебиторки DSO с 27 до 7 дней</t>
         </is>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="41" t="inlineStr">
+      <c r="A15" s="42" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Слив маркетинга и война с отделом продаж</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Google Ads слил 85 000 ₽ с ROMI -100% (0 оплат). Деньги сожжены без сквозного контроля окупаемости</t>
         </is>
       </c>
-      <c r="D15" s="59" t="n">
+      <c r="D15" s="86" t="n">
         <v>850000</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E15" s="11" t="n">
         <v>85000</v>
       </c>
-      <c r="F15" s="61" t="inlineStr">
+      <c r="F15" s="88" t="inlineStr">
         <is>
           <t>🟡 P1 (Высокий)</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Сквозная RevOps-атрибуция W-Shaped: автоотключение убыточных связок</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>Экономия рекламного бюджета + перелив в прибыльный Контур/Директ</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="26" t="n"/>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="A16" s="27" t="n"/>
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>ИТОГО ВЫЯВЛЕННЫХ ПОТЕРЬ И РИСКОВ В МЕСЯЦ:</t>
         </is>
       </c>
-      <c r="C16" s="26" t="n"/>
-      <c r="D16" s="62">
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="89">
         <f>SUM(D9:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <f>SUM(E9:E15)</f>
         <v/>
       </c>
-      <c r="F16" s="53" t="inlineStr">
+      <c r="F16" s="90" t="inlineStr">
         <is>
           <t>ИТОГО ПОТЕРЬ</t>
         </is>
       </c>
-      <c r="G16" s="44" t="inlineStr">
+      <c r="G16" s="45" t="inlineStr">
         <is>
           <t>Потенциал возврата в кассу</t>
         </is>
       </c>
-      <c r="H16" s="29" t="inlineStr">
+      <c r="H16" s="30" t="inlineStr">
         <is>
           <t>Окупаемость за счет устранения узких мест</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="45" t="inlineStr">
+      <c r="A18" s="46" t="inlineStr">
         <is>
           <t>🚀 ЭКОНОМИКА ПРОЕКТА ОПТИМИЗАЦИИ И СРОК ОКУПАЕМОСТИ ДЛЯ КЛИЕНТА</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Параметр экономики проекта</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>Комментарий и логика расчета</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Стоимость проекта оптимизации ОП</t>
         </is>
       </c>
-      <c r="B20" s="46" t="n"/>
-      <c r="C20" s="46" t="n"/>
-      <c r="D20" s="63" t="n">
+      <c r="B20" s="47" t="n"/>
+      <c r="C20" s="47" t="n"/>
+      <c r="D20" s="82" t="n">
         <v>450000</v>
       </c>
-      <c r="E20" s="9" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>Фиксированная стоимость внедрения (4 недели спринтов)</t>
         </is>
       </c>
-      <c r="F20" s="46" t="n"/>
-      <c r="G20" s="46" t="n"/>
-      <c r="H20" s="46" t="n"/>
+      <c r="F20" s="47" t="n"/>
+      <c r="G20" s="47" t="n"/>
+      <c r="H20" s="47" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Ожидаемый возврат выручки (M1 факт)</t>
         </is>
       </c>
-      <c r="B21" s="46" t="n"/>
-      <c r="C21" s="46" t="n"/>
-      <c r="D21" s="64" t="n">
+      <c r="B21" s="47" t="n"/>
+      <c r="C21" s="47" t="n"/>
+      <c r="D21" s="81" t="n">
         <v>2100300</v>
       </c>
-      <c r="E21" s="9" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>Консервативный ориентир: устранение всего 30% найденных узких мест</t>
         </is>
       </c>
-      <c r="F21" s="46" t="n"/>
-      <c r="G21" s="46" t="n"/>
-      <c r="H21" s="46" t="n"/>
+      <c r="F21" s="47" t="n"/>
+      <c r="G21" s="47" t="n"/>
+      <c r="H21" s="47" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Чистая прибыль собственника за вычетом услуг</t>
         </is>
       </c>
-      <c r="B22" s="46" t="n"/>
-      <c r="C22" s="46" t="n"/>
-      <c r="D22" s="64">
+      <c r="B22" s="47" t="n"/>
+      <c r="C22" s="47" t="n"/>
+      <c r="D22" s="81">
         <f>D21-D20</f>
         <v/>
       </c>
-      <c r="E22" s="9" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>Чистый денежный плюс в кассе компании в первый же месяц</t>
         </is>
       </c>
-      <c r="F22" s="46" t="n"/>
-      <c r="G22" s="46" t="n"/>
-      <c r="H22" s="46" t="n"/>
+      <c r="F22" s="47" t="n"/>
+      <c r="G22" s="47" t="n"/>
+      <c r="H22" s="47" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>Чистый ROI инвестиций в проект</t>
         </is>
       </c>
-      <c r="B23" s="46" t="n"/>
-      <c r="C23" s="46" t="n"/>
-      <c r="D23" s="65">
+      <c r="B23" s="47" t="n"/>
+      <c r="C23" s="47" t="n"/>
+      <c r="D23" s="55">
         <f>(D22/D20)*100 &amp; "%"</f>
         <v/>
       </c>
-      <c r="E23" s="9" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>Процент отдачи на каждый вложенный рубль</t>
         </is>
       </c>
-      <c r="F23" s="46" t="n"/>
-      <c r="G23" s="46" t="n"/>
-      <c r="H23" s="46" t="n"/>
+      <c r="F23" s="47" t="n"/>
+      <c r="G23" s="47" t="n"/>
+      <c r="H23" s="47" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Срок полной окупаемости проекта</t>
         </is>
       </c>
-      <c r="B24" s="46" t="n"/>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="65">
+      <c r="B24" s="47" t="n"/>
+      <c r="C24" s="47" t="n"/>
+      <c r="D24" s="55">
         <f>ROUND(D20/(D21/30), 0) &amp; " дн."</f>
         <v/>
       </c>
-      <c r="E24" s="9" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>Количество дней работы ОП до полной окупаемости чека внедрения</t>
         </is>
       </c>
-      <c r="F24" s="46" t="n"/>
-      <c r="G24" s="46" t="n"/>
-      <c r="H24" s="46" t="n"/>
+      <c r="F24" s="47" t="n"/>
+      <c r="G24" s="47" t="n"/>
+      <c r="H24" s="47" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="66" t="inlineStr">
+      <c r="A26" s="91" t="inlineStr">
         <is>
           <t>👉 УТВЕРДИТЬ ПРОЕКТ ОПТИМИЗАЦИИ И СФОРМИРОВАТЬ ИНВОЙС (450 000 ₽)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="34" t="inlineStr">
+      <c r="A27" s="35" t="inlineStr">
         <is>
           <t>Не готовы к спринту? 👉 Бесплатный тест-драйв на 3 звонках на вкладке «⚡ Экспресс_Калькулятор_3_Цифры»</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="35" t="inlineStr">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>🔒 Безопасный B2B-расчет: безналичный платеж по счету (УПД / Диадок) • 152-ФЗ РФ • Старт спринта за 24 часа</t>
         </is>
@@ -3538,372 +5640,380 @@
           <t>📄 REVOPS ENTERPRISE EXECUTIVE ONE-PAGER (УПРАВЛЕНЧЕСКИЙ ДАЙДЖЕСТ)</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>📄 1. One-Pager</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>⚡ 2. Пульс компании</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>📋 3. Пульт РОПа</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>💸 4. 7 Грехов ОП</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>🎯 5. Action Center</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>🎙️ 6. ИИ-Аудит</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>⚡ 7. Экспресс 3 цифры</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>🧪 8. QA Suite</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>⚙️ 9. Настройки</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="37" t="inlineStr">
         <is>
           <t>Выручка (Факт Closed-Won)</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>% Выполнения плана</t>
         </is>
       </c>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="C4" s="37" t="inlineStr">
         <is>
           <t>Взвешенный прогноз (SSOT)</t>
         </is>
       </c>
-      <c r="D4" s="36" t="inlineStr">
+      <c r="D4" s="37" t="inlineStr">
         <is>
           <t>Run-Rate касса (Прогноз)</t>
         </is>
       </c>
-      <c r="E4" s="36" t="inlineStr">
+      <c r="E4" s="37" t="inlineStr">
         <is>
           <t>Активный пайплайн в работе</t>
         </is>
       </c>
-      <c r="F4" s="36" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Сделок под угрозой SLA</t>
         </is>
       </c>
-      <c r="G4" s="36" t="inlineStr">
+      <c r="G4" s="37" t="inlineStr">
         <is>
           <t>Качество речи ОП (ИИ)</t>
         </is>
       </c>
-      <c r="H4" s="56" t="inlineStr">
+      <c r="H4" s="83" t="inlineStr">
         <is>
           <t>Data Quality Index</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="57" t="n">
+      <c r="A5" s="84" t="n">
         <v>1650000</v>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>33.0%</t>
         </is>
       </c>
-      <c r="C5" s="67" t="n">
+      <c r="C5" s="92" t="n">
         <v>2754000</v>
       </c>
-      <c r="D5" s="57" t="n">
+      <c r="D5" s="84" t="n">
         <v>1706897</v>
       </c>
-      <c r="E5" s="57" t="n">
+      <c r="E5" s="84" t="n">
         <v>5530000</v>
       </c>
-      <c r="F5" s="68" t="inlineStr">
+      <c r="F5" s="93" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G5" s="38" t="inlineStr">
+      <c r="G5" s="39" t="inlineStr">
         <is>
           <t>73.1%</t>
         </is>
       </c>
-      <c r="H5" s="58" t="inlineStr">
+      <c r="H5" s="85" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>📊 ВОРОНКА ПРОДАЖ &amp; УЗКИЕ ГОРЛЫШКИ (AS-IS)</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>🚨 ТОП-5 КРИТИЧЕСКИХ РИСКОВ ВЫРУЧКИ (ACTION CENTER)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Этап сделки</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Сделок</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Объем, ₽</t>
         </is>
       </c>
-      <c r="D8" s="24" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>SLA норматив (ч)</t>
         </is>
       </c>
-      <c r="F8" s="24" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>Сделка / Клиент</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>Проблема &amp; Симптом</t>
         </is>
       </c>
-      <c r="H8" s="24" t="inlineStr">
+      <c r="H8" s="25" t="inlineStr">
         <is>
           <t>Сумма в риске, ₽</t>
         </is>
       </c>
-      <c r="I8" s="24" t="inlineStr">
+      <c r="I8" s="25" t="inlineStr">
         <is>
           <t>Срочное действие РОПа</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>1. Новый лид</t>
         </is>
       </c>
-      <c r="B9" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="10" t="n">
+      <c r="B9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="11" t="n">
         <v>950000</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="26" t="n">
         <v>24</v>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>D-104 (ООО Вектор)</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>КП без ответа &gt; 48ч</t>
         </is>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="14" t="n">
         <v>850000</v>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>Повторный контакт с ЛПР + звонок РОПа</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>2. Квалификация / ЛПР</t>
         </is>
       </c>
-      <c r="B10" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="10" t="n">
+      <c r="B10" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="11" t="n">
         <v>120000</v>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="26" t="n">
         <v>48</v>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>D-103 (ИнвестХолдинг)</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Просрочен счёт на оплату</t>
         </is>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="H10" s="14" t="n">
         <v>150000</v>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>Дожим счета через AI-бота + автозвонок</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>3. Встреча / Демо</t>
         </is>
       </c>
-      <c r="B11" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="10" t="n">
+      <c r="B11" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="11" t="n">
         <v>280000</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>D-109 (ПромКомплект)</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Критический брак речи (&lt;9)</t>
         </is>
       </c>
-      <c r="H11" s="13" t="n">
+      <c r="H11" s="14" t="n">
         <v>600000</v>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>Личный перезвон РОПа ЛПР до 12:00</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>4. КП и согласование</t>
         </is>
       </c>
-      <c r="B12" s="25" t="n">
+      <c r="B12" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="10" t="n">
+      <c r="C12" s="11" t="n">
         <v>3850000</v>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="26" t="n">
         <v>48</v>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>D-106 (СнабСервис)</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Зависание на этапе КП</t>
         </is>
       </c>
-      <c r="H12" s="13" t="n">
+      <c r="H12" s="14" t="n">
         <v>280000</v>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>Эскалация РОПу, согласование слота</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>5. Счет выставлен</t>
         </is>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="11" t="n">
         <v>330000</v>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="26" t="n">
         <v>72</v>
       </c>
-      <c r="F13" s="7" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>D-107 (ТехноПром)</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Крупная сделка без движения</t>
         </is>
       </c>
-      <c r="H13" s="13" t="n">
+      <c r="H13" s="14" t="n">
         <v>3000000</v>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>Подключение генерального директора</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>6. Успешно реализовано</t>
         </is>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="10" t="n">
+      <c r="C14" s="11" t="n">
         <v>1650000</v>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="69" t="inlineStr">
+      <c r="A16" s="94" t="inlineStr">
         <is>
           <t>🎯 ГЛАВНЫЙ ФОКУС РУКОВОДСТВА ДО КОНЦА МЕСЯЦА: Перехват сделки D-104 (850 000 ₽) и перераспределение 3 лидов с перегруженного РОПа на КАМов.</t>
         </is>
@@ -3945,253 +6055,258 @@
           <t>🔐 ЮРИДИЧЕСКИЙ КОНТУР БЕЗОПАСНОСТИ И ОБЕЗЛИЧИВАНИЯ ПДН (152-ФЗ РФ)</t>
         </is>
       </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>📄 1. One-Pager</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>⚡ 2. Пульс компании</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>📋 3. Пульт РОПа</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>💸 4. 7 Грехов ОП</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>🎯 5. Action Center</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>🎙️ 6. ИИ-Аудит</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>🛡️ ГАРАНТИЯ СООТВЕТСТВИЯ ЗАКОНОДАТЕЛЬСТВУ И РЕГЛАМЕНТАМ БЕЗОПАСНОСТИ РФ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Параметр безопасности</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Требование законодательства РФ</t>
         </is>
       </c>
-      <c r="D5" s="24" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Архитектурная реализация платформы RevOps</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Статус проверки</t>
         </is>
       </c>
-      <c r="F5" s="24" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Юридическое обоснование</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="A6" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Локализация баз данных</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Хранение ПДн граждан РФ строго на серверах в РФ</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Дата-центры в Москве (Yandex Cloud / Selectel), аттестация ФСТЭК УЗ 1-2</t>
         </is>
       </c>
-      <c r="E6" s="58" t="inlineStr">
+      <c r="E6" s="85" t="inlineStr">
         <is>
           <t>✅ 100% Соответствие</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>ст. 18.1 Федерального закона № 152-ФЗ</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="41" t="n">
+      <c r="A7" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Криптографическая токенизация</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Запрет передачи персональных данных во внешние контуры</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Модуль PIISanitizer: замена телефонов, ФИО и карт на токены [PHONE_TOKEN_X]</t>
         </is>
       </c>
-      <c r="E7" s="58" t="inlineStr">
+      <c r="E7" s="85" t="inlineStr">
         <is>
           <t>✅ Автоматически</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>ст. 6 Федерального закона № 152-ФЗ</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="41" t="n">
+      <c r="A8" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>Срок хранения аудиозаписей</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Удаление данных после достижения цели обработки</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Автоматическое безвозвратное удаление исходных аудио через 30 дней</t>
         </is>
       </c>
-      <c r="E8" s="58" t="inlineStr">
+      <c r="E8" s="85" t="inlineStr">
         <is>
           <t>✅ Настроено в cron</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>ст. 5 Федерального закона № 152-ФЗ</t>
         </is>
       </c>
     </row>
     <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="41" t="n">
+      <c r="A9" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>Согласие сотрудников ОП</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Уведомление персонала о контроле качества переговоров</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Готовый пакет документов: Приказ, Положение о контроле, Согласие</t>
         </is>
       </c>
-      <c r="E9" s="58" t="inlineStr">
+      <c r="E9" s="85" t="inlineStr">
         <is>
           <t>✅ Комплект включен</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>ст. 86 Трудового Кодекса РФ</t>
         </is>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="41" t="n">
+      <c r="A10" s="42" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Юридический статус исполнителя</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Прозрачность расчетов с юридическими лицами</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Плательщик НПД (Самозанятый), чек приложения «Мой Налог», договор, акт</t>
         </is>
       </c>
-      <c r="E10" s="58" t="inlineStr">
+      <c r="E10" s="85" t="inlineStr">
         <is>
           <t>✅ Безопасно для бухгалтерии</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>ст. 15 Федерального закона № 422-ФЗ</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="41" t="n">
+      <c r="A11" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>Гарантия конфиденциальности NDA</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Защита коммерческой тайны и клиентской базы компании</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Подписание двустороннего соглашения о неразглашении конфиденциальных данных</t>
         </is>
       </c>
-      <c r="E11" s="58" t="inlineStr">
+      <c r="E11" s="85" t="inlineStr">
         <is>
           <t>✅ Подписание в ЭДО</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>Федеральный закон № 98-ФЗ «О коммерческой тайне»</t>
         </is>

--- a/web/RevOps_Platform_Demo_Sample.xlsx
+++ b/web/RevOps_Platform_Demo_Sample.xlsx
@@ -43,13 +43,13 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="0094A3B8"/>
+      <color rgb="0060A5FA"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="0060A5FA"/>
+      <color rgb="0094A3B8"/>
       <sz val="9"/>
     </font>
     <font>
@@ -134,7 +134,7 @@
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00DC2626"/>
-      <sz val="13"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -205,6 +205,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="002563EB"/>
+        <bgColor rgb="002563EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001E293B"/>
         <bgColor rgb="001E293B"/>
       </patternFill>
@@ -243,12 +249,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFBEB"/>
         <bgColor rgb="00FFFBEB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002563EB"/>
-        <bgColor rgb="002563EB"/>
       </patternFill>
     </fill>
     <fill>
@@ -304,41 +304,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -348,188 +345,194 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -539,14 +542,14 @@
     <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -917,11 +920,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
@@ -942,50 +945,38 @@
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>📄 1. One-Pager</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>⚡ 2. Пульс компании</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>📋 3. Пульт РОПа</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>💸 4. 7 Грехов ОП</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>🎯 5. Action Center</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>🎙️ 6. ИИ-Аудит</t>
+          <t>⚡ Экспресс-Калькулятор</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>📋 Пульт РОПа (15 мин)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>🎙️ ИИ-Аудит звонков</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>💸 7 Грехов (Диагностика)</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>⚡ 7. Экспресс 3 цифры</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>🧪 8. QA Suite</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>⚙️ 9. Настройки</t>
+          <t>📄 Executive One-Pager</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>🔐 152-ФЗ Безопасность</t>
         </is>
       </c>
     </row>
@@ -1188,220 +1179,287 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
+    <row r="15" ht="28" customHeight="1">
       <c r="A15" s="26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>Слив лидов на звонках (нет Next Step)</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>30% выручки теряется из-за ошибок менеджеров</t>
         </is>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="28" t="n">
         <v>412500</v>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>Менеджеры консультируют, но не закрывают на дату</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="F15" s="27" t="inlineStr">
         <is>
           <t>ИИ-аудит 100% звонков + чек-лист Next Step</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
+    <row r="16" ht="28" customHeight="1">
       <c r="A16" s="26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>Зависание сделок на этапе КП &gt; 48ч</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>18% выручки теряется из-за просрочки follow-up</t>
         </is>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="28" t="n">
         <v>297000</v>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>Клиент остывает, пока менеджер ждет звонка</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F16" s="27" t="inlineStr">
         <is>
           <t>Авторадар SLA 48ч + эскалация РОПу на 3-й день</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
+    <row r="17" ht="28" customHeight="1">
       <c r="A17" s="26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>Брошенные отказники без дожима (L1-L4)</t>
         </is>
       </c>
-      <c r="C17" s="10" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>8% — потенциал реактивации списанных сделок</t>
         </is>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="28" t="n">
         <v>132000</v>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>Сделки списаны в архив без реактивации</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="F17" s="27" t="inlineStr">
         <is>
           <t>AI Recovery Engine: автодожим в WhatsApp/TG</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
+    <row r="18" ht="28" customHeight="1">
       <c r="A18" s="26" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>Зависшая дебиторка и задержка оплат</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>12% выставленных счетов с просрочкой 20+ дней</t>
         </is>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="28" t="n">
         <v>198000</v>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>Нет платежного календаря и контроля сроков</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F18" s="27" t="inlineStr">
         <is>
           <t>Платежный календарь DSO + автонапоминания</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="27" t="n"/>
-      <c r="B19" s="28" t="inlineStr">
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="29" t="n"/>
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>ИТОГО УПУЩЕННОЙ ПРИБЫЛИ В МЕСЯЦ:</t>
         </is>
       </c>
-      <c r="C19" s="27" t="n"/>
-      <c r="D19" s="29">
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="31">
         <f>SUM(D15:D18)</f>
         <v/>
       </c>
-      <c r="E19" s="28" t="inlineStr">
+      <c r="E19" s="30" t="inlineStr">
         <is>
           <t>ПОТЕНЦИАЛ БЫСТРОГО ВОЗВРАТА:</t>
         </is>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="32">
         <f>ROUND(D19*0.35, 0) &amp; " ₽ в первый месяц"</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="31" t="inlineStr">
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="33" t="inlineStr">
         <is>
           <t>🎁 СЛЕДУЮЩИЙ ШАГ: БЕСПЛАТНЫЙ ТЕСТ-ДРАЙВ НА 3 ВАШИХ ЗВОНКАХ</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="32" t="inlineStr">
+      <c r="B21" s="33" t="n"/>
+      <c r="C21" s="33" t="n"/>
+      <c r="D21" s="33" t="n"/>
+      <c r="E21" s="33" t="n"/>
+      <c r="F21" s="33" t="n"/>
+      <c r="G21" s="33" t="n"/>
+      <c r="H21" s="33" t="n"/>
+      <c r="I21" s="33" t="n"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>Хотите проверить эту математику на реальных данных вашей компании за 15 минут?</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="33" t="inlineStr">
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="34" t="n"/>
+      <c r="D22" s="34" t="n"/>
+      <c r="E22" s="34" t="n"/>
+      <c r="F22" s="34" t="n"/>
+      <c r="G22" s="34" t="n"/>
+      <c r="H22" s="34" t="n"/>
+      <c r="I22" s="34" t="n"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>👉 Отправьте 3 аудиозаписи любых вчерашних звонков ваших менеджеров в Telegram бот.</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="33" t="inlineStr">
+      <c r="B23" s="35" t="n"/>
+      <c r="C23" s="35" t="n"/>
+      <c r="D23" s="35" t="n"/>
+      <c r="E23" s="35" t="n"/>
+      <c r="F23" s="35" t="n"/>
+      <c r="G23" s="35" t="n"/>
+      <c r="H23" s="35" t="n"/>
+      <c r="I23" s="35" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="35" t="inlineStr">
         <is>
           <t>ИИ бесплатно разберет их по 13 критериям, покажет ошибки речи и рассчитает точную сумму под угрозой слива.</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="34" t="inlineStr">
+      <c r="B24" s="35" t="n"/>
+      <c r="C24" s="35" t="n"/>
+      <c r="D24" s="35" t="n"/>
+      <c r="E24" s="35" t="n"/>
+      <c r="F24" s="35" t="n"/>
+      <c r="G24" s="35" t="n"/>
+      <c r="H24" s="35" t="n"/>
+      <c r="I24" s="35" t="n"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>🚀 ЗАПУСТИТЬ БЕСПЛАТНЫЙ ТЕСТ-ДРАЙВ: @RevOps_Super_Audit_Bot (https://t.me/RevOps_Super_Audit_Bot)</t>
         </is>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="35" t="inlineStr">
+      <c r="B25" s="36" t="n"/>
+      <c r="C25" s="36" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="36" t="n"/>
+      <c r="F25" s="36" t="n"/>
+      <c r="G25" s="36" t="n"/>
+      <c r="H25" s="36" t="n"/>
+      <c r="I25" s="36" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="37" t="inlineStr">
         <is>
           <t>Нужен комплексный аудит отдела продаж? 👉 Экономика спринта оптимизации (450 000 ₽) на вкладке «4. 7 Грехов ОП»</t>
         </is>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="36" t="inlineStr">
+      <c r="B26" s="37" t="n"/>
+      <c r="C26" s="37" t="n"/>
+      <c r="D26" s="37" t="n"/>
+      <c r="E26" s="37" t="n"/>
+      <c r="F26" s="37" t="n"/>
+      <c r="G26" s="37" t="n"/>
+      <c r="H26" s="37" t="n"/>
+      <c r="I26" s="37" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="38" t="inlineStr">
         <is>
           <t>🔒 Конфиденциально • Без передачи персональных данных • Экспресс-разбор за 15 минут (152-ФЗ РФ)</t>
         </is>
       </c>
+      <c r="B27" s="38" t="n"/>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="38" t="n"/>
+      <c r="E27" s="38" t="n"/>
+      <c r="F27" s="38" t="n"/>
+      <c r="G27" s="38" t="n"/>
+      <c r="H27" s="38" t="n"/>
+      <c r="I27" s="38" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="23">
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="G2:H2"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="G11:H11"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A21:I21"/>
     <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B2:C2"/>
     <mergeCell ref="C10:D10"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A22:I22"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="E11:F11"/>
+    <mergeCell ref="A24:I24"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1415,10 +1473,10 @@
   <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="42" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -1439,99 +1497,91 @@
       <c r="G1" s="2" t="n"/>
       <c r="H1" s="2" t="n"/>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>📄 1. One-Pager</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>⚡ 2. Пульс компании</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>📋 3. Пульт РОПа</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>💸 4. 7 Грехов ОП</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>🎯 5. Action Center</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>🎙️ 6. ИИ-Аудит</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>⚡ 7. Экспресс 3 цифры</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>🧪 8. QA Suite</t>
-        </is>
-      </c>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>⚡ Экспресс-Калькулятор</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>📋 Пульт РОПа</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>🎙️ ИИ-Аудит</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>💸 7 Грехов ОП</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>📄 One-Pager</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>🔐 152-ФЗ Безопасность</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Звонков за вчера</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="39" t="n"/>
+      <c r="C4" s="40" t="inlineStr">
         <is>
           <t>Диалогов с браком (&lt;9)</t>
         </is>
       </c>
-      <c r="C4" s="38" t="inlineStr">
+      <c r="D4" s="40" t="inlineStr">
         <is>
           <t>Сделок с угрозой срыва</t>
         </is>
       </c>
-      <c r="D4" s="38" t="inlineStr">
-        <is>
-          <t>Сумма в зоне риска прямо сейчас</t>
-        </is>
-      </c>
-      <c r="E4" s="38" t="inlineStr">
+      <c r="E4" s="40" t="inlineStr">
+        <is>
+          <t>Сумма в зоне риска</t>
+        </is>
+      </c>
+      <c r="F4" s="40" t="inlineStr">
         <is>
           <t>Статус дня для РОПа</t>
         </is>
       </c>
+      <c r="G4" s="40" t="n"/>
+      <c r="H4" s="40" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B5" s="40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C5" s="40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D5" s="21" t="n">
+      <c r="A5" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" s="41" t="n"/>
+      <c r="C5" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="21" t="n">
         <v>2730000</v>
       </c>
-      <c r="E5" s="41" t="inlineStr">
+      <c r="F5" s="43" t="inlineStr">
         <is>
           <t>🚨 ТРЕБУЕТСЯ 15 МИНУТ КОНТРОЛЯ РОПа</t>
         </is>
       </c>
+      <c r="G5" s="43" t="n"/>
+      <c r="H5" s="43" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -1582,234 +1632,234 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>Сделка D-104 (ООО «Вектор Плюс»)</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Зависание на этапе КП: 12 дней без ответа (норма 48ч)</t>
         </is>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="28" t="n">
         <v>850000</v>
       </c>
-      <c r="E9" s="42" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>🔴 КРИТИЧЕСКИЙ</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="27" t="inlineStr">
         <is>
           <t>Запросить статус у КАМа Петрова, согласовать скидку/рассрочку</t>
         </is>
       </c>
-      <c r="G9" s="43" t="inlineStr">
+      <c r="G9" s="44" t="inlineStr">
         <is>
           <t>В РАБОТЕ</t>
         </is>
       </c>
-      <c r="H9" s="44" t="inlineStr">
+      <c r="H9" s="45" t="inlineStr">
         <is>
           <t>Добрый день, Алексей! Вижу, наш расчет по договору согласован. Чтобы зафиксировать спец-условия сентября со скидкой 7%, предлагаю сегодня подписать спецификацию. Слот для звонка: 14:30. Удобно?</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="42" t="n">
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>Звонок C-505 / Сделка D-109 (ООО «ПромКомплект»)</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>Менеджер сорвал контакт (балл речи 2/13), клиент ушел в отказ</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="28" t="n">
         <v>600000</v>
       </c>
-      <c r="E10" s="42" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>🔴 КРИТИЧЕСКИЙ</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="27" t="inlineStr">
         <is>
           <t>Личный звонок РОПа ЛПР до 12:00: перехват сделки от лица руководства</t>
         </is>
       </c>
-      <c r="G10" s="43" t="inlineStr">
+      <c r="G10" s="44" t="inlineStr">
         <is>
           <t>В РАБОТЕ</t>
         </is>
       </c>
-      <c r="H10" s="44" t="inlineStr">
+      <c r="H10" s="45" t="inlineStr">
         <is>
           <t>Михаил Сергеевич, добрый день! Это Дмитрий Иванов, коммерческий директор. Прослушал вчерашний диалог с нашим менеджером — приношу извинения за неполную консультацию. Лично подготовил для вас проект с расширенной гарантией 24 мес. Уделите 5 минут?</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="42" t="n">
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>Звонок C-503 / Сделка D-106 (ООО «СнабСервис»)</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>В диалоге не зафиксирована дата встречи (балл речи 6/13)</t>
         </is>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="28" t="n">
         <v>280000</v>
       </c>
-      <c r="E11" s="42" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>🟡 СРЕДНИЙ</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="27" t="inlineStr">
         <is>
           <t>Поставить задачу менеджеру Петрову: перезвонить и назначить слот встречи</t>
         </is>
       </c>
-      <c r="G11" s="43" t="inlineStr">
+      <c r="G11" s="44" t="inlineStr">
         <is>
           <t>В РАБОТЕ</t>
         </is>
       </c>
-      <c r="H11" s="44" t="inlineStr">
+      <c r="H11" s="45" t="inlineStr">
         <is>
           <t>Игорь, приветствую! Направил вам 2 слота на онлайн-демо платформы: сегодня в 16:00 или завтра в 11:30. За 15 минут покажем связку с вашей CRM. Какой слот забронировать?</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1">
-      <c r="A12" s="42" t="n">
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>Сделка D-107 (ООО «ТехноПром»)</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>Счет просрочен на 9 дней (сумма 150 000 ₽)</t>
         </is>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="28" t="n">
         <v>150000</v>
       </c>
-      <c r="E12" s="42" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t>🟡 СРЕДНИЙ</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="F12" s="27" t="inlineStr">
         <is>
           <t>Отправить триггерное напоминание в WhatsApp бухгалтеру клиента</t>
         </is>
       </c>
-      <c r="G12" s="43" t="inlineStr">
+      <c r="G12" s="44" t="inlineStr">
         <is>
           <t>В РАБОТЕ</t>
         </is>
       </c>
-      <c r="H12" s="44" t="inlineStr">
+      <c r="H12" s="45" t="inlineStr">
         <is>
           <t>Ольга, здравствуйте! Бухгалтерия напоминает: по счету INV-203 сегодня крайний день резерва оборудования по льготному курсу. Выставить ссылку на моментальную оплату через СБП?</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="42" t="n">
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>Сделка D-103 (ООО «ИнвестХолдинг»)</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>Нагрузка 80%, 4 ключевые сделки висят на РОПе</t>
         </is>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="28" t="n">
         <v>850000</v>
       </c>
-      <c r="E13" s="42" t="inlineStr">
+      <c r="E13" s="26" t="inlineStr">
         <is>
           <t>🟡 СРЕДНИЙ</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="F13" s="27" t="inlineStr">
         <is>
           <t>Делегировать 2 входящие сделки на КАМа (у КАМа загрузка всего 4%)</t>
         </is>
       </c>
-      <c r="G13" s="43" t="inlineStr">
+      <c r="G13" s="44" t="inlineStr">
         <is>
           <t>В РАБОТЕ</t>
         </is>
       </c>
-      <c r="H13" s="44" t="inlineStr">
+      <c r="H13" s="45" t="inlineStr">
         <is>
           <t>Регламентное действие: передать права ответственного по сделке D-102 на КАМа Петрова (свободная емкость 75%). РОПу оставить контроль ключевых контрольных точек.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="27" t="n"/>
-      <c r="B14" s="28" t="inlineStr">
+      <c r="A14" s="29" t="n"/>
+      <c r="B14" s="46" t="inlineStr">
         <is>
           <t>ИТОГО ДЕНЕГ В ЗОНЕ РИСКА СЕГОДНЯ:</t>
         </is>
       </c>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="29">
+      <c r="C14" s="29" t="n"/>
+      <c r="D14" s="47">
         <f>SUM(D9:D13)</f>
         <v/>
       </c>
-      <c r="E14" s="28" t="inlineStr">
+      <c r="E14" s="46" t="inlineStr">
         <is>
           <t>СПАСЕННАЯ ВЫРУЧКА:</t>
         </is>
       </c>
-      <c r="F14" s="45" t="inlineStr">
+      <c r="F14" s="48" t="inlineStr">
         <is>
           <t>При выполнении всех 5 действий</t>
         </is>
       </c>
-      <c r="G14" s="30" t="inlineStr">
+      <c r="G14" s="49" t="inlineStr">
         <is>
           <t>100% защита</t>
         </is>
       </c>
-      <c r="H14" s="27" t="n"/>
+      <c r="H14" s="29" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="E17" s="46" t="inlineStr">
+      <c r="E17" s="50" t="inlineStr">
         <is>
           <t>⏱️ ЭКСПРЕСС-РЕГЛАМЕНТ РОПа (15 МИНУТ/ДЕНЬ)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="E18" s="43" t="inlineStr">
+    <row r="18" ht="22" customHeight="1">
+      <c r="E18" s="44" t="inlineStr">
         <is>
           <t>09:00 - 09:05</t>
         </is>
@@ -1819,11 +1869,11 @@
           <t>Проверка ночного ИИ-аудита: 2 звонка с браком (&lt;9 баллов)</t>
         </is>
       </c>
-      <c r="G18" s="47" t="n"/>
-      <c r="H18" s="47" t="n"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="E19" s="43" t="inlineStr">
+      <c r="G18" s="51" t="n"/>
+      <c r="H18" s="51" t="n"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="E19" s="44" t="inlineStr">
         <is>
           <t>09:05 - 09:10</t>
         </is>
@@ -1833,11 +1883,11 @@
           <t>Перехват сделки D-109 (600 т.р.) и звонок ЛПР до 12:00</t>
         </is>
       </c>
-      <c r="G19" s="47" t="n"/>
-      <c r="H19" s="47" t="n"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="E20" s="43" t="inlineStr">
+      <c r="G19" s="51" t="n"/>
+      <c r="H19" s="51" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="E20" s="44" t="inlineStr">
         <is>
           <t>09:10 - 09:13</t>
         </is>
@@ -1847,11 +1897,11 @@
           <t>Согласование спецусловий по D-104 (850 т.р.)</t>
         </is>
       </c>
-      <c r="G20" s="47" t="n"/>
-      <c r="H20" s="47" t="n"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="E21" s="43" t="inlineStr">
+      <c r="G20" s="51" t="n"/>
+      <c r="H20" s="51" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="E21" s="44" t="inlineStr">
         <is>
           <t>09:13 - 09:15</t>
         </is>
@@ -1861,36 +1911,48 @@
           <t>Делегирование 2 сделок с РОПа на свободного КАМа</t>
         </is>
       </c>
-      <c r="G21" s="47" t="n"/>
-      <c r="H21" s="47" t="n"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
+      <c r="G21" s="51" t="n"/>
+      <c r="H21" s="51" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
       <c r="E22" s="18" t="inlineStr">
         <is>
           <t>Результат:</t>
         </is>
       </c>
-      <c r="F22" s="48" t="inlineStr">
+      <c r="F22" s="52" t="inlineStr">
         <is>
           <t>2 730 000 ₽ защищено от слива за 15 минут</t>
         </is>
       </c>
-      <c r="G22" s="47" t="n"/>
-      <c r="H22" s="47" t="n"/>
+      <c r="G22" s="51" t="n"/>
+      <c r="H22" s="51" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="14">
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="F20:H20"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="E17:H17"/>
+    <mergeCell ref="F5:H5"/>
     <mergeCell ref="F19:H19"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="F18:H18"/>
     <mergeCell ref="F22:H22"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="F4:H4"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="F21:H21"/>
-    <mergeCell ref="E5:H5"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1904,11 +1966,11 @@
   <dimension ref="A1:V60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
@@ -1923,9 +1985,9 @@
     <col width="11" customWidth="1" min="17" max="17"/>
     <col width="11" customWidth="1" min="18" max="18"/>
     <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
     <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -1956,188 +2018,176 @@
       <c r="U1" s="2" t="n"/>
       <c r="V1" s="2" t="n"/>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>📄 1. One-Pager</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>⚡ 2. Пульс компании</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>📋 3. Пульт РОПа</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>💸 4. 7 Грехов ОП</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>🎯 5. Action Center</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>🎙️ 6. ИИ-Аудит</t>
-        </is>
-      </c>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>⚡ Экспресс-Калькулятор</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>📋 Пульт РОПа (15 мин)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>⚡ 7. Экспресс 3 цифры</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>🧪 8. QA Suite</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>⚙️ 9. Настройки</t>
-        </is>
-      </c>
-      <c r="J2" s="49" t="n"/>
-      <c r="K2" s="49" t="n"/>
-      <c r="L2" s="49" t="n"/>
-      <c r="M2" s="49" t="n"/>
-      <c r="N2" s="49" t="n"/>
-      <c r="O2" s="49" t="n"/>
-      <c r="P2" s="49" t="n"/>
-      <c r="Q2" s="49" t="n"/>
-      <c r="R2" s="49" t="n"/>
-      <c r="S2" s="49" t="n"/>
-      <c r="T2" s="49" t="n"/>
-      <c r="U2" s="49" t="n"/>
-      <c r="V2" s="49" t="n"/>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+          <t>🎙️ ИИ-Аудит звонков</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="3" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>💸 7 Грехов (Диагностика)</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>📄 Executive One-Pager</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="n"/>
+      <c r="P2" s="4" t="n"/>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
+          <t>🔐 152-ФЗ Безопасность</t>
+        </is>
+      </c>
+      <c r="R2" s="4" t="n"/>
+      <c r="S2" s="4" t="n"/>
+      <c r="T2" s="4" t="n"/>
+      <c r="U2" s="4" t="n"/>
+      <c r="V2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>Проанализировано звонков</t>
         </is>
       </c>
-      <c r="B3" s="50" t="inlineStr">
+      <c r="B3" s="39" t="n"/>
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>Средний балл качества</t>
         </is>
       </c>
-      <c r="C3" s="50" t="n"/>
-      <c r="D3" s="37" t="inlineStr">
+      <c r="D3" s="53" t="n"/>
+      <c r="E3" s="54" t="inlineStr">
         <is>
           <t>Фиксация жесткого Next Step</t>
         </is>
       </c>
-      <c r="E3" s="38" t="inlineStr">
+      <c r="F3" s="54" t="n"/>
+      <c r="G3" s="40" t="inlineStr">
         <is>
           <t>Критический брак речи (&lt;9)</t>
         </is>
       </c>
-      <c r="F3" s="38" t="inlineStr">
+      <c r="H3" s="40" t="n"/>
+      <c r="I3" s="40" t="n"/>
+      <c r="J3" s="40" t="inlineStr">
         <is>
           <t>Выручка под угрозой слива</t>
         </is>
       </c>
-      <c r="G3" s="38" t="n"/>
-      <c r="H3" s="38" t="inlineStr">
+      <c r="K3" s="40" t="n"/>
+      <c r="L3" s="40" t="n"/>
+      <c r="M3" s="40" t="inlineStr">
         <is>
           <t>Вердикт ИИ-супервайзера</t>
         </is>
       </c>
-      <c r="I3" s="38" t="n"/>
-      <c r="J3" s="38" t="n"/>
-      <c r="K3" s="38" t="n"/>
-      <c r="L3" s="38" t="n"/>
-      <c r="M3" s="38" t="n"/>
-      <c r="N3" s="38" t="n"/>
-      <c r="O3" s="38" t="n"/>
-      <c r="P3" s="38" t="n"/>
-      <c r="Q3" s="38" t="n"/>
-      <c r="R3" s="38" t="n"/>
-      <c r="S3" s="38" t="n"/>
-      <c r="T3" s="38" t="n"/>
-      <c r="U3" s="38" t="n"/>
-      <c r="V3" s="38" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="N3" s="40" t="n"/>
+      <c r="O3" s="40" t="n"/>
+      <c r="P3" s="40" t="n"/>
+      <c r="Q3" s="40" t="n"/>
+      <c r="R3" s="40" t="n"/>
+      <c r="S3" s="40" t="n"/>
+      <c r="T3" s="40" t="n"/>
+      <c r="U3" s="40" t="n"/>
+      <c r="V3" s="40" t="n"/>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>25 звонков / сут</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr">
+      <c r="B4" s="41" t="n"/>
+      <c r="C4" s="55" t="inlineStr">
         <is>
           <t>8.9 из 13</t>
         </is>
       </c>
-      <c r="C4" s="51" t="n"/>
-      <c r="D4" s="52" t="inlineStr">
+      <c r="D4" s="55" t="n"/>
+      <c r="E4" s="56" t="inlineStr">
         <is>
           <t>60.0% (норма ≥85%)</t>
         </is>
       </c>
-      <c r="E4" s="40" t="inlineStr">
+      <c r="F4" s="56" t="n"/>
+      <c r="G4" s="42" t="inlineStr">
         <is>
           <t>6 диалогов</t>
         </is>
       </c>
-      <c r="F4" s="21" t="n">
+      <c r="H4" s="42" t="n"/>
+      <c r="I4" s="42" t="n"/>
+      <c r="J4" s="21" t="n">
         <v>2840000</v>
       </c>
-      <c r="G4" s="21" t="n"/>
-      <c r="H4" s="53" t="inlineStr">
+      <c r="K4" s="21" t="n"/>
+      <c r="L4" s="21" t="n"/>
+      <c r="M4" s="57" t="inlineStr">
         <is>
           <t>🚨 ВЫСОКИЙ РИСК СЛИВА VIP-КЛИЕНТОВ (ТРЕБУЕТСЯ ВМЕШАТЕЛЬСТВО РОПа)</t>
         </is>
       </c>
-      <c r="I4" s="53" t="n"/>
-      <c r="J4" s="53" t="n"/>
-      <c r="K4" s="53" t="n"/>
-      <c r="L4" s="53" t="n"/>
-      <c r="M4" s="53" t="n"/>
-      <c r="N4" s="53" t="n"/>
-      <c r="O4" s="53" t="n"/>
-      <c r="P4" s="53" t="n"/>
-      <c r="Q4" s="53" t="n"/>
-      <c r="R4" s="53" t="n"/>
-      <c r="S4" s="53" t="n"/>
-      <c r="T4" s="53" t="n"/>
-      <c r="U4" s="53" t="n"/>
-      <c r="V4" s="53" t="n"/>
+      <c r="N4" s="57" t="n"/>
+      <c r="O4" s="57" t="n"/>
+      <c r="P4" s="57" t="n"/>
+      <c r="Q4" s="57" t="n"/>
+      <c r="R4" s="57" t="n"/>
+      <c r="S4" s="57" t="n"/>
+      <c r="T4" s="57" t="n"/>
+      <c r="U4" s="57" t="n"/>
+      <c r="V4" s="57" t="n"/>
     </row>
     <row r="5" ht="12" customHeight="1"/>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="54" t="inlineStr">
+      <c r="A6" s="58" t="inlineStr">
         <is>
           <t>👥 РЕЙТИНГ МЕНЕДЖЕРОВ ОП ПО КАЧЕСТВУ РЕЧИ (ЛИДЕРБОРД РОПа)</t>
         </is>
       </c>
-      <c r="B6" s="54" t="n"/>
-      <c r="C6" s="54" t="n"/>
-      <c r="D6" s="54" t="n"/>
-      <c r="E6" s="54" t="n"/>
-      <c r="F6" s="54" t="n"/>
-      <c r="G6" s="54" t="n"/>
-      <c r="H6" s="54" t="n"/>
-      <c r="I6" s="54" t="n"/>
-      <c r="J6" s="54" t="n"/>
-      <c r="K6" s="54" t="n"/>
-      <c r="L6" s="54" t="n"/>
-      <c r="M6" s="54" t="n"/>
-      <c r="N6" s="54" t="n"/>
-      <c r="O6" s="54" t="n"/>
-      <c r="P6" s="54" t="n"/>
-      <c r="Q6" s="54" t="n"/>
-      <c r="R6" s="54" t="n"/>
-      <c r="S6" s="54" t="n"/>
-      <c r="T6" s="54" t="n"/>
-      <c r="U6" s="54" t="n"/>
-      <c r="V6" s="54" t="n"/>
+      <c r="B6" s="58" t="n"/>
+      <c r="C6" s="58" t="n"/>
+      <c r="D6" s="58" t="n"/>
+      <c r="E6" s="58" t="n"/>
+      <c r="F6" s="58" t="n"/>
+      <c r="G6" s="58" t="n"/>
+      <c r="H6" s="58" t="n"/>
+      <c r="I6" s="58" t="n"/>
+      <c r="J6" s="58" t="n"/>
+      <c r="K6" s="58" t="n"/>
+      <c r="L6" s="58" t="n"/>
+      <c r="M6" s="58" t="n"/>
+      <c r="N6" s="58" t="n"/>
+      <c r="O6" s="58" t="n"/>
+      <c r="P6" s="58" t="n"/>
+      <c r="Q6" s="58" t="n"/>
+      <c r="R6" s="58" t="n"/>
+      <c r="S6" s="58" t="n"/>
+      <c r="T6" s="58" t="n"/>
+      <c r="U6" s="58" t="n"/>
+      <c r="V6" s="58" t="n"/>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="25" t="inlineStr">
@@ -2204,7 +2254,7 @@
       <c r="V7" s="25" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="42" t="n">
+      <c r="A8" s="26" t="n">
         <v>1</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -2212,26 +2262,26 @@
           <t>Алексей Мельников</t>
         </is>
       </c>
-      <c r="C8" s="42" t="n">
+      <c r="C8" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="D8" s="55" t="n">
+      <c r="D8" s="59" t="n">
         <v>12.2</v>
       </c>
-      <c r="E8" s="42" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F8" s="42" t="inlineStr">
+      <c r="F8" s="26" t="inlineStr">
         <is>
           <t>48% / 52%</t>
         </is>
       </c>
-      <c r="G8" s="42" t="n">
+      <c r="G8" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="56" t="n">
+      <c r="H8" s="28" t="n">
         <v>0</v>
       </c>
       <c r="I8" s="18" t="inlineStr">
@@ -2239,26 +2289,26 @@
           <t>⭐ А (Эталон)</t>
         </is>
       </c>
-      <c r="J8" s="57" t="inlineStr">
+      <c r="J8" s="60" t="inlineStr">
         <is>
           <t>Эталонный скрипт, рекомендован в базу знаний компании</t>
         </is>
       </c>
-      <c r="K8" s="57" t="n"/>
-      <c r="L8" s="57" t="n"/>
-      <c r="M8" s="57" t="n"/>
-      <c r="N8" s="57" t="n"/>
-      <c r="O8" s="57" t="n"/>
-      <c r="P8" s="57" t="n"/>
-      <c r="Q8" s="57" t="n"/>
-      <c r="R8" s="57" t="n"/>
-      <c r="S8" s="57" t="n"/>
-      <c r="T8" s="57" t="n"/>
-      <c r="U8" s="57" t="n"/>
-      <c r="V8" s="57" t="n"/>
+      <c r="K8" s="60" t="n"/>
+      <c r="L8" s="60" t="n"/>
+      <c r="M8" s="60" t="n"/>
+      <c r="N8" s="60" t="n"/>
+      <c r="O8" s="60" t="n"/>
+      <c r="P8" s="60" t="n"/>
+      <c r="Q8" s="60" t="n"/>
+      <c r="R8" s="60" t="n"/>
+      <c r="S8" s="60" t="n"/>
+      <c r="T8" s="60" t="n"/>
+      <c r="U8" s="60" t="n"/>
+      <c r="V8" s="60" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="42" t="n">
+      <c r="A9" s="26" t="n">
         <v>2</v>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -2266,26 +2316,26 @@
           <t>Елена Васильева</t>
         </is>
       </c>
-      <c r="C9" s="42" t="n">
+      <c r="C9" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="55" t="n">
+      <c r="D9" s="59" t="n">
         <v>10.8</v>
       </c>
-      <c r="E9" s="42" t="inlineStr">
+      <c r="E9" s="26" t="inlineStr">
         <is>
           <t>80.0%</t>
         </is>
       </c>
-      <c r="F9" s="42" t="inlineStr">
+      <c r="F9" s="26" t="inlineStr">
         <is>
           <t>51% / 49%</t>
         </is>
       </c>
-      <c r="G9" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="58" t="n">
+      <c r="G9" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="61" t="n">
         <v>160000</v>
       </c>
       <c r="I9" s="18" t="inlineStr">
@@ -2293,26 +2343,26 @@
           <t>🟢 B (Норма)</t>
         </is>
       </c>
-      <c r="J9" s="57" t="inlineStr">
+      <c r="J9" s="60" t="inlineStr">
         <is>
           <t>Высокая конверсия, мелкие замечания по регламенту встречи</t>
         </is>
       </c>
-      <c r="K9" s="57" t="n"/>
-      <c r="L9" s="57" t="n"/>
-      <c r="M9" s="57" t="n"/>
-      <c r="N9" s="57" t="n"/>
-      <c r="O9" s="57" t="n"/>
-      <c r="P9" s="57" t="n"/>
-      <c r="Q9" s="57" t="n"/>
-      <c r="R9" s="57" t="n"/>
-      <c r="S9" s="57" t="n"/>
-      <c r="T9" s="57" t="n"/>
-      <c r="U9" s="57" t="n"/>
-      <c r="V9" s="57" t="n"/>
+      <c r="K9" s="60" t="n"/>
+      <c r="L9" s="60" t="n"/>
+      <c r="M9" s="60" t="n"/>
+      <c r="N9" s="60" t="n"/>
+      <c r="O9" s="60" t="n"/>
+      <c r="P9" s="60" t="n"/>
+      <c r="Q9" s="60" t="n"/>
+      <c r="R9" s="60" t="n"/>
+      <c r="S9" s="60" t="n"/>
+      <c r="T9" s="60" t="n"/>
+      <c r="U9" s="60" t="n"/>
+      <c r="V9" s="60" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="42" t="n">
+      <c r="A10" s="26" t="n">
         <v>3</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -2320,26 +2370,26 @@
           <t>Анна Соколова</t>
         </is>
       </c>
-      <c r="C10" s="42" t="n">
+      <c r="C10" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="59" t="n">
+      <c r="D10" s="62" t="n">
         <v>8.4</v>
       </c>
-      <c r="E10" s="42" t="inlineStr">
+      <c r="E10" s="26" t="inlineStr">
         <is>
           <t>60.0%</t>
         </is>
       </c>
-      <c r="F10" s="42" t="inlineStr">
+      <c r="F10" s="26" t="inlineStr">
         <is>
           <t>58% / 42%</t>
         </is>
       </c>
-      <c r="G10" s="42" t="n">
+      <c r="G10" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="58" t="n">
+      <c r="H10" s="61" t="n">
         <v>480000</v>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -2347,26 +2397,26 @@
           <t>🟡 C (Зона риска)</t>
         </is>
       </c>
-      <c r="J10" s="57" t="inlineStr">
+      <c r="J10" s="60" t="inlineStr">
         <is>
           <t>Забывает фиксировать дату звонка, требуется тренинг</t>
         </is>
       </c>
-      <c r="K10" s="57" t="n"/>
-      <c r="L10" s="57" t="n"/>
-      <c r="M10" s="57" t="n"/>
-      <c r="N10" s="57" t="n"/>
-      <c r="O10" s="57" t="n"/>
-      <c r="P10" s="57" t="n"/>
-      <c r="Q10" s="57" t="n"/>
-      <c r="R10" s="57" t="n"/>
-      <c r="S10" s="57" t="n"/>
-      <c r="T10" s="57" t="n"/>
-      <c r="U10" s="57" t="n"/>
-      <c r="V10" s="57" t="n"/>
+      <c r="K10" s="60" t="n"/>
+      <c r="L10" s="60" t="n"/>
+      <c r="M10" s="60" t="n"/>
+      <c r="N10" s="60" t="n"/>
+      <c r="O10" s="60" t="n"/>
+      <c r="P10" s="60" t="n"/>
+      <c r="Q10" s="60" t="n"/>
+      <c r="R10" s="60" t="n"/>
+      <c r="S10" s="60" t="n"/>
+      <c r="T10" s="60" t="n"/>
+      <c r="U10" s="60" t="n"/>
+      <c r="V10" s="60" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="42" t="n">
+      <c r="A11" s="26" t="n">
         <v>4</v>
       </c>
       <c r="B11" s="8" t="inlineStr">
@@ -2374,26 +2424,26 @@
           <t>Дмитрий Ковалев</t>
         </is>
       </c>
-      <c r="C11" s="42" t="n">
+      <c r="C11" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="60" t="n">
+      <c r="D11" s="63" t="n">
         <v>6.2</v>
       </c>
-      <c r="E11" s="42" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>40.0%</t>
         </is>
       </c>
-      <c r="F11" s="42" t="inlineStr">
+      <c r="F11" s="26" t="inlineStr">
         <is>
           <t>72% / 28%</t>
         </is>
       </c>
-      <c r="G11" s="42" t="n">
+      <c r="G11" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="58" t="n">
+      <c r="H11" s="61" t="n">
         <v>1100000</v>
       </c>
       <c r="I11" s="17" t="inlineStr">
@@ -2401,26 +2451,26 @@
           <t>🔴 D (Брак речи)</t>
         </is>
       </c>
-      <c r="J11" s="57" t="inlineStr">
+      <c r="J11" s="60" t="inlineStr">
         <is>
           <t>Срыв контакта, перебивание клиента, демпинг скидок</t>
         </is>
       </c>
-      <c r="K11" s="57" t="n"/>
-      <c r="L11" s="57" t="n"/>
-      <c r="M11" s="57" t="n"/>
-      <c r="N11" s="57" t="n"/>
-      <c r="O11" s="57" t="n"/>
-      <c r="P11" s="57" t="n"/>
-      <c r="Q11" s="57" t="n"/>
-      <c r="R11" s="57" t="n"/>
-      <c r="S11" s="57" t="n"/>
-      <c r="T11" s="57" t="n"/>
-      <c r="U11" s="57" t="n"/>
-      <c r="V11" s="57" t="n"/>
+      <c r="K11" s="60" t="n"/>
+      <c r="L11" s="60" t="n"/>
+      <c r="M11" s="60" t="n"/>
+      <c r="N11" s="60" t="n"/>
+      <c r="O11" s="60" t="n"/>
+      <c r="P11" s="60" t="n"/>
+      <c r="Q11" s="60" t="n"/>
+      <c r="R11" s="60" t="n"/>
+      <c r="S11" s="60" t="n"/>
+      <c r="T11" s="60" t="n"/>
+      <c r="U11" s="60" t="n"/>
+      <c r="V11" s="60" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="42" t="n">
+      <c r="A12" s="26" t="n">
         <v>5</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
@@ -2428,26 +2478,26 @@
           <t>Иван Попов</t>
         </is>
       </c>
-      <c r="C12" s="42" t="n">
+      <c r="C12" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="60" t="n">
+      <c r="D12" s="63" t="n">
         <v>5.5</v>
       </c>
-      <c r="E12" s="42" t="inlineStr">
+      <c r="E12" s="26" t="inlineStr">
         <is>
           <t>25.0%</t>
         </is>
       </c>
-      <c r="F12" s="42" t="inlineStr">
+      <c r="F12" s="26" t="inlineStr">
         <is>
           <t>79% / 21%</t>
         </is>
       </c>
-      <c r="G12" s="42" t="n">
+      <c r="G12" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="58" t="n">
+      <c r="H12" s="61" t="n">
         <v>1100000</v>
       </c>
       <c r="I12" s="17" t="inlineStr">
@@ -2455,109 +2505,109 @@
           <t>🔴 D (Брак речи)</t>
         </is>
       </c>
-      <c r="J12" s="57" t="inlineStr">
+      <c r="J12" s="60" t="inlineStr">
         <is>
           <t>Режим 'автоответчика', нет попыток закрытия на встречу</t>
         </is>
       </c>
-      <c r="K12" s="57" t="n"/>
-      <c r="L12" s="57" t="n"/>
-      <c r="M12" s="57" t="n"/>
-      <c r="N12" s="57" t="n"/>
-      <c r="O12" s="57" t="n"/>
-      <c r="P12" s="57" t="n"/>
-      <c r="Q12" s="57" t="n"/>
-      <c r="R12" s="57" t="n"/>
-      <c r="S12" s="57" t="n"/>
-      <c r="T12" s="57" t="n"/>
-      <c r="U12" s="57" t="n"/>
-      <c r="V12" s="57" t="n"/>
+      <c r="K12" s="60" t="n"/>
+      <c r="L12" s="60" t="n"/>
+      <c r="M12" s="60" t="n"/>
+      <c r="N12" s="60" t="n"/>
+      <c r="O12" s="60" t="n"/>
+      <c r="P12" s="60" t="n"/>
+      <c r="Q12" s="60" t="n"/>
+      <c r="R12" s="60" t="n"/>
+      <c r="S12" s="60" t="n"/>
+      <c r="T12" s="60" t="n"/>
+      <c r="U12" s="60" t="n"/>
+      <c r="V12" s="60" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="27" t="inlineStr"/>
-      <c r="B13" s="61" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr"/>
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>ИТОГО ПО ОТДЕЛУ ПРОДАЖ:</t>
         </is>
       </c>
-      <c r="C13" s="62">
+      <c r="C13" s="64">
         <f>SUM(C8:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="62" t="inlineStr">
+      <c r="D13" s="64" t="inlineStr">
         <is>
           <t>8.9 / 13</t>
         </is>
       </c>
-      <c r="E13" s="62" t="inlineStr">
+      <c r="E13" s="64" t="inlineStr">
         <is>
           <t>60.0%</t>
         </is>
       </c>
-      <c r="F13" s="62" t="inlineStr">
+      <c r="F13" s="64" t="inlineStr">
         <is>
           <t>61% / 39%</t>
         </is>
       </c>
-      <c r="G13" s="62">
+      <c r="G13" s="64">
         <f>SUM(G8:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="63">
+      <c r="H13" s="31">
         <f>SUM(H8:H12)</f>
         <v/>
       </c>
-      <c r="I13" s="64" t="inlineStr">
+      <c r="I13" s="65" t="inlineStr">
         <is>
           <t>⚠️ РИСК</t>
         </is>
       </c>
-      <c r="J13" s="65" t="inlineStr">
+      <c r="J13" s="66" t="inlineStr">
         <is>
           <t>Требуется экспресс-коучинг по отработке возражений</t>
         </is>
       </c>
-      <c r="K13" s="65" t="n"/>
-      <c r="L13" s="65" t="n"/>
-      <c r="M13" s="65" t="n"/>
-      <c r="N13" s="65" t="n"/>
-      <c r="O13" s="65" t="n"/>
-      <c r="P13" s="65" t="n"/>
-      <c r="Q13" s="65" t="n"/>
-      <c r="R13" s="65" t="n"/>
-      <c r="S13" s="65" t="n"/>
-      <c r="T13" s="65" t="n"/>
-      <c r="U13" s="65" t="n"/>
-      <c r="V13" s="65" t="n"/>
+      <c r="K13" s="66" t="n"/>
+      <c r="L13" s="66" t="n"/>
+      <c r="M13" s="66" t="n"/>
+      <c r="N13" s="66" t="n"/>
+      <c r="O13" s="66" t="n"/>
+      <c r="P13" s="66" t="n"/>
+      <c r="Q13" s="66" t="n"/>
+      <c r="R13" s="66" t="n"/>
+      <c r="S13" s="66" t="n"/>
+      <c r="T13" s="66" t="n"/>
+      <c r="U13" s="66" t="n"/>
+      <c r="V13" s="66" t="n"/>
     </row>
     <row r="14" ht="12" customHeight="1"/>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="54" t="inlineStr">
+      <c r="A15" s="58" t="inlineStr">
         <is>
           <t>🔍 ДЕТАЛИЗИРОВАННАЯ МАТРИЦА ОЦЕНКИ ЗВОНКОВ ПО ВСЕМ 13 КРИТЕРИЯМ (0 / 1)</t>
         </is>
       </c>
-      <c r="B15" s="54" t="n"/>
-      <c r="C15" s="54" t="n"/>
-      <c r="D15" s="54" t="n"/>
-      <c r="E15" s="54" t="n"/>
-      <c r="F15" s="54" t="n"/>
-      <c r="G15" s="54" t="n"/>
-      <c r="H15" s="54" t="n"/>
-      <c r="I15" s="54" t="n"/>
-      <c r="J15" s="54" t="n"/>
-      <c r="K15" s="54" t="n"/>
-      <c r="L15" s="54" t="n"/>
-      <c r="M15" s="54" t="n"/>
-      <c r="N15" s="54" t="n"/>
-      <c r="O15" s="54" t="n"/>
-      <c r="P15" s="54" t="n"/>
-      <c r="Q15" s="54" t="n"/>
-      <c r="R15" s="54" t="n"/>
-      <c r="S15" s="54" t="n"/>
-      <c r="T15" s="54" t="n"/>
-      <c r="U15" s="54" t="n"/>
-      <c r="V15" s="54" t="n"/>
+      <c r="B15" s="58" t="n"/>
+      <c r="C15" s="58" t="n"/>
+      <c r="D15" s="58" t="n"/>
+      <c r="E15" s="58" t="n"/>
+      <c r="F15" s="58" t="n"/>
+      <c r="G15" s="58" t="n"/>
+      <c r="H15" s="58" t="n"/>
+      <c r="I15" s="58" t="n"/>
+      <c r="J15" s="58" t="n"/>
+      <c r="K15" s="58" t="n"/>
+      <c r="L15" s="58" t="n"/>
+      <c r="M15" s="58" t="n"/>
+      <c r="N15" s="58" t="n"/>
+      <c r="O15" s="58" t="n"/>
+      <c r="P15" s="58" t="n"/>
+      <c r="Q15" s="58" t="n"/>
+      <c r="R15" s="58" t="n"/>
+      <c r="S15" s="58" t="n"/>
+      <c r="T15" s="58" t="n"/>
+      <c r="U15" s="58" t="n"/>
+      <c r="V15" s="58" t="n"/>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="25" t="inlineStr">
@@ -2672,74 +2722,74 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="43" t="inlineStr">
+      <c r="A17" s="44" t="inlineStr">
         <is>
           <t>C-501</t>
         </is>
       </c>
-      <c r="B17" s="57" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>D-101 (ООО Вектор Плюс)</t>
         </is>
       </c>
-      <c r="C17" s="42" t="inlineStr">
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>Мельников</t>
         </is>
       </c>
-      <c r="D17" s="66" t="n">
+      <c r="D17" s="67" t="n">
         <v>850000</v>
       </c>
-      <c r="E17" s="42" t="inlineStr">
+      <c r="E17" s="26" t="inlineStr">
         <is>
           <t>05:40</t>
         </is>
       </c>
-      <c r="F17" s="42" t="inlineStr">
+      <c r="F17" s="26" t="inlineStr">
         <is>
           <t>КП отправлено</t>
         </is>
       </c>
-      <c r="G17" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" s="55">
+      <c r="G17" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" s="59">
         <f>SUM(G17:S17)</f>
         <v/>
       </c>
@@ -2748,79 +2798,79 @@
           <t>⭐ ЭТАЛОН</t>
         </is>
       </c>
-      <c r="V17" s="56" t="n">
+      <c r="V17" s="28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="44" t="inlineStr">
         <is>
           <t>C-502</t>
         </is>
       </c>
-      <c r="B18" s="57" t="inlineStr">
+      <c r="B18" s="60" t="inlineStr">
         <is>
           <t>D-104 (ООО Вектор Плюс)</t>
         </is>
       </c>
-      <c r="C18" s="42" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>Васильева</t>
         </is>
       </c>
-      <c r="D18" s="66" t="n">
+      <c r="D18" s="67" t="n">
         <v>850000</v>
       </c>
-      <c r="E18" s="42" t="inlineStr">
+      <c r="E18" s="26" t="inlineStr">
         <is>
           <t>04:20</t>
         </is>
       </c>
-      <c r="F18" s="42" t="inlineStr">
+      <c r="F18" s="26" t="inlineStr">
         <is>
           <t>Переговоры</t>
         </is>
       </c>
-      <c r="G18" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="68" t="n">
+      <c r="G18" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" s="55">
+      <c r="M18" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="59">
         <f>SUM(G18:S18)</f>
         <v/>
       </c>
@@ -2829,79 +2879,79 @@
           <t>🟢 В НОРМЕ</t>
         </is>
       </c>
-      <c r="V18" s="56" t="n">
+      <c r="V18" s="28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="43" t="inlineStr">
+      <c r="A19" s="44" t="inlineStr">
         <is>
           <t>C-503</t>
         </is>
       </c>
-      <c r="B19" s="57" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
         <is>
           <t>D-106 (ООО СнабСервис)</t>
         </is>
       </c>
-      <c r="C19" s="42" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>Соколова</t>
         </is>
       </c>
-      <c r="D19" s="66" t="n">
+      <c r="D19" s="67" t="n">
         <v>280000</v>
       </c>
-      <c r="E19" s="42" t="inlineStr">
+      <c r="E19" s="26" t="inlineStr">
         <is>
           <t>03:10</t>
         </is>
       </c>
-      <c r="F19" s="42" t="inlineStr">
+      <c r="F19" s="26" t="inlineStr">
         <is>
           <t>Встреча/Демо</t>
         </is>
       </c>
-      <c r="G19" s="68" t="n">
+      <c r="G19" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="68" t="n">
+      <c r="H19" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" s="68" t="n">
+      <c r="K19" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" s="68" t="n">
+      <c r="M19" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="O19" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" s="68" t="n">
+      <c r="O19" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" s="68" t="n">
+      <c r="Q19" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="S19" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" s="60">
+      <c r="S19" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" s="63">
         <f>SUM(G19:S19)</f>
         <v/>
       </c>
@@ -2910,79 +2960,79 @@
           <t>⚠️ РИСК</t>
         </is>
       </c>
-      <c r="V19" s="58" t="n">
+      <c r="V19" s="61" t="n">
         <v>280000</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="43" t="inlineStr">
+      <c r="A20" s="44" t="inlineStr">
         <is>
           <t>C-504</t>
         </is>
       </c>
-      <c r="B20" s="57" t="inlineStr">
+      <c r="B20" s="60" t="inlineStr">
         <is>
           <t>D-107 (ООО ТехноПром)</t>
         </is>
       </c>
-      <c r="C20" s="42" t="inlineStr">
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>Соколова</t>
         </is>
       </c>
-      <c r="D20" s="66" t="n">
+      <c r="D20" s="67" t="n">
         <v>150000</v>
       </c>
-      <c r="E20" s="42" t="inlineStr">
+      <c r="E20" s="26" t="inlineStr">
         <is>
           <t>06:15</t>
         </is>
       </c>
-      <c r="F20" s="42" t="inlineStr">
+      <c r="F20" s="26" t="inlineStr">
         <is>
           <t>Квалификация</t>
         </is>
       </c>
-      <c r="G20" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="68" t="n">
+      <c r="G20" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" s="68" t="n">
+      <c r="K20" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="68" t="n">
+      <c r="N20" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="O20" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="68" t="n">
+      <c r="O20" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="R20" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" s="59">
+      <c r="R20" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="62">
         <f>SUM(G20:S20)</f>
         <v/>
       </c>
@@ -2991,79 +3041,79 @@
           <t>⚠️ РИСК</t>
         </is>
       </c>
-      <c r="V20" s="58" t="n">
+      <c r="V20" s="61" t="n">
         <v>150000</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="43" t="inlineStr">
+      <c r="A21" s="44" t="inlineStr">
         <is>
           <t>C-505</t>
         </is>
       </c>
-      <c r="B21" s="57" t="inlineStr">
+      <c r="B21" s="60" t="inlineStr">
         <is>
           <t>D-109 (ООО ПромКомплект)</t>
         </is>
       </c>
-      <c r="C21" s="42" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
         <is>
           <t>Ковалев</t>
         </is>
       </c>
-      <c r="D21" s="66" t="n">
+      <c r="D21" s="67" t="n">
         <v>600000</v>
       </c>
-      <c r="E21" s="42" t="inlineStr">
+      <c r="E21" s="26" t="inlineStr">
         <is>
           <t>03:30</t>
         </is>
       </c>
-      <c r="F21" s="42" t="inlineStr">
+      <c r="F21" s="26" t="inlineStr">
         <is>
           <t>КП отправлено</t>
         </is>
       </c>
-      <c r="G21" s="68" t="n">
+      <c r="G21" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="68" t="n">
+      <c r="H21" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="68" t="n">
+      <c r="I21" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="68" t="n">
+      <c r="J21" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="68" t="n">
+      <c r="K21" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="68" t="n">
+      <c r="L21" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="M21" s="68" t="n">
+      <c r="M21" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="68" t="n">
+      <c r="N21" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" s="68" t="n">
+      <c r="O21" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" s="68" t="n">
+      <c r="Q21" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="R21" s="68" t="n">
+      <c r="R21" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="S21" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" s="60">
+      <c r="S21" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" s="63">
         <f>SUM(G21:S21)</f>
         <v/>
       </c>
@@ -3072,79 +3122,79 @@
           <t>❌ СЛИВ</t>
         </is>
       </c>
-      <c r="V21" s="58" t="n">
+      <c r="V21" s="61" t="n">
         <v>600000</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="43" t="inlineStr">
+      <c r="A22" s="44" t="inlineStr">
         <is>
           <t>C-506</t>
         </is>
       </c>
-      <c r="B22" s="57" t="inlineStr">
+      <c r="B22" s="60" t="inlineStr">
         <is>
           <t>D-111 (ООО Глобал Инвест)</t>
         </is>
       </c>
-      <c r="C22" s="42" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
         <is>
           <t>Мельников</t>
         </is>
       </c>
-      <c r="D22" s="66" t="n">
+      <c r="D22" s="67" t="n">
         <v>3000000</v>
       </c>
-      <c r="E22" s="42" t="inlineStr">
+      <c r="E22" s="26" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F22" s="42" t="inlineStr">
+      <c r="F22" s="26" t="inlineStr">
         <is>
           <t>Финальные условия</t>
         </is>
       </c>
-      <c r="G22" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" s="55">
+      <c r="G22" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="59">
         <f>SUM(G22:S22)</f>
         <v/>
       </c>
@@ -3153,79 +3203,79 @@
           <t>⭐ ЭТАЛОН</t>
         </is>
       </c>
-      <c r="V22" s="56" t="n">
+      <c r="V22" s="28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="43" t="inlineStr">
+      <c r="A23" s="44" t="inlineStr">
         <is>
           <t>C-507</t>
         </is>
       </c>
-      <c r="B23" s="57" t="inlineStr">
+      <c r="B23" s="60" t="inlineStr">
         <is>
           <t>D-114 (ООО АльфаТрейд)</t>
         </is>
       </c>
-      <c r="C23" s="42" t="inlineStr">
+      <c r="C23" s="26" t="inlineStr">
         <is>
           <t>Ковалев</t>
         </is>
       </c>
-      <c r="D23" s="66" t="n">
+      <c r="D23" s="67" t="n">
         <v>500000</v>
       </c>
-      <c r="E23" s="42" t="inlineStr">
+      <c r="E23" s="26" t="inlineStr">
         <is>
           <t>04:45</t>
         </is>
       </c>
-      <c r="F23" s="42" t="inlineStr">
+      <c r="F23" s="26" t="inlineStr">
         <is>
           <t>Дожим договора</t>
         </is>
       </c>
-      <c r="G23" s="68" t="n">
+      <c r="G23" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="68" t="n">
+      <c r="H23" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="K23" s="68" t="n">
+      <c r="K23" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L23" s="68" t="n">
+      <c r="L23" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" s="68" t="n">
+      <c r="M23" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="O23" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="P23" s="68" t="n">
+      <c r="O23" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" s="68" t="n">
+      <c r="Q23" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="R23" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" s="68" t="n">
+      <c r="R23" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="T23" s="60">
+      <c r="T23" s="63">
         <f>SUM(G23:S23)</f>
         <v/>
       </c>
@@ -3234,79 +3284,79 @@
           <t>❌ СЛИВ</t>
         </is>
       </c>
-      <c r="V23" s="58" t="n">
+      <c r="V23" s="61" t="n">
         <v>500000</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="43" t="inlineStr">
+      <c r="A24" s="44" t="inlineStr">
         <is>
           <t>C-508</t>
         </is>
       </c>
-      <c r="B24" s="57" t="inlineStr">
+      <c r="B24" s="60" t="inlineStr">
         <is>
           <t>D-118 (ООО СтройХолдинг)</t>
         </is>
       </c>
-      <c r="C24" s="42" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>Попов</t>
         </is>
       </c>
-      <c r="D24" s="66" t="n">
+      <c r="D24" s="67" t="n">
         <v>650000</v>
       </c>
-      <c r="E24" s="42" t="inlineStr">
+      <c r="E24" s="26" t="inlineStr">
         <is>
           <t>02:50</t>
         </is>
       </c>
-      <c r="F24" s="42" t="inlineStr">
+      <c r="F24" s="26" t="inlineStr">
         <is>
           <t>Входящий лид</t>
         </is>
       </c>
-      <c r="G24" s="68" t="n">
+      <c r="G24" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="68" t="n">
+      <c r="H24" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="68" t="n">
+      <c r="I24" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="68" t="n">
+      <c r="K24" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="68" t="n">
+      <c r="L24" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="68" t="n">
+      <c r="M24" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="68" t="n">
+      <c r="N24" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="68" t="n">
+      <c r="O24" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="R24" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" s="68" t="n">
+      <c r="R24" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="T24" s="60">
+      <c r="T24" s="63">
         <f>SUM(G24:S24)</f>
         <v/>
       </c>
@@ -3315,79 +3365,79 @@
           <t>❌ СЛИВ</t>
         </is>
       </c>
-      <c r="V24" s="58" t="n">
+      <c r="V24" s="61" t="n">
         <v>650000</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="43" t="inlineStr">
+      <c r="A25" s="44" t="inlineStr">
         <is>
           <t>C-509</t>
         </is>
       </c>
-      <c r="B25" s="57" t="inlineStr">
+      <c r="B25" s="60" t="inlineStr">
         <is>
           <t>D-121 (ООО СпецМаш)</t>
         </is>
       </c>
-      <c r="C25" s="42" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
         <is>
           <t>Васильева</t>
         </is>
       </c>
-      <c r="D25" s="66" t="n">
+      <c r="D25" s="67" t="n">
         <v>420000</v>
       </c>
-      <c r="E25" s="42" t="inlineStr">
+      <c r="E25" s="26" t="inlineStr">
         <is>
           <t>05:10</t>
         </is>
       </c>
-      <c r="F25" s="42" t="inlineStr">
+      <c r="F25" s="26" t="inlineStr">
         <is>
           <t>Презентация КП</t>
         </is>
       </c>
-      <c r="G25" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" s="68" t="n">
+      <c r="G25" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" s="55">
+      <c r="O25" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" s="59">
         <f>SUM(G25:S25)</f>
         <v/>
       </c>
@@ -3396,79 +3446,79 @@
           <t>🟢 В НОРМЕ</t>
         </is>
       </c>
-      <c r="V25" s="56" t="n">
+      <c r="V25" s="28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="43" t="inlineStr">
+      <c r="A26" s="44" t="inlineStr">
         <is>
           <t>C-510</t>
         </is>
       </c>
-      <c r="B26" s="57" t="inlineStr">
+      <c r="B26" s="60" t="inlineStr">
         <is>
           <t>D-125 (ООО МегаТранс)</t>
         </is>
       </c>
-      <c r="C26" s="42" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>Попов</t>
         </is>
       </c>
-      <c r="D26" s="66" t="n">
+      <c r="D26" s="67" t="n">
         <v>450000</v>
       </c>
-      <c r="E26" s="42" t="inlineStr">
+      <c r="E26" s="26" t="inlineStr">
         <is>
           <t>03:40</t>
         </is>
       </c>
-      <c r="F26" s="42" t="inlineStr">
+      <c r="F26" s="26" t="inlineStr">
         <is>
           <t>Квалификация</t>
         </is>
       </c>
-      <c r="G26" s="68" t="n">
+      <c r="G26" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="68" t="n">
+      <c r="H26" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="68" t="n">
+      <c r="I26" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" s="68" t="n">
+      <c r="J26" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" s="68" t="n">
+      <c r="M26" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="68" t="n">
+      <c r="O26" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="R26" s="67" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" s="68" t="n">
+      <c r="R26" s="68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" s="69" t="n">
         <v>0</v>
       </c>
-      <c r="T26" s="60">
+      <c r="T26" s="63">
         <f>SUM(G26:S26)</f>
         <v/>
       </c>
@@ -3477,79 +3527,79 @@
           <t>⚠️ РИСК</t>
         </is>
       </c>
-      <c r="V26" s="58" t="n">
+      <c r="V26" s="61" t="n">
         <v>450000</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="27" t="inlineStr"/>
-      <c r="B27" s="61" t="inlineStr">
+      <c r="A27" s="29" t="inlineStr"/>
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <t>ИТОГО ПОТЕРЬ И РИСКОВ ПО ЗВОНКАМ:</t>
         </is>
       </c>
-      <c r="C27" s="27" t="inlineStr"/>
-      <c r="D27" s="69">
+      <c r="C27" s="29" t="inlineStr"/>
+      <c r="D27" s="70">
         <f>SUM(D17:D26)</f>
         <v/>
       </c>
-      <c r="E27" s="27" t="inlineStr"/>
-      <c r="F27" s="27" t="inlineStr"/>
-      <c r="G27" s="27" t="inlineStr"/>
-      <c r="H27" s="27" t="inlineStr"/>
-      <c r="I27" s="27" t="inlineStr"/>
-      <c r="J27" s="27" t="inlineStr"/>
-      <c r="K27" s="27" t="inlineStr"/>
-      <c r="L27" s="27" t="inlineStr"/>
-      <c r="M27" s="27" t="inlineStr"/>
-      <c r="N27" s="27" t="inlineStr"/>
-      <c r="O27" s="27" t="inlineStr"/>
-      <c r="P27" s="27" t="inlineStr"/>
-      <c r="Q27" s="27" t="inlineStr"/>
-      <c r="R27" s="27" t="inlineStr"/>
-      <c r="S27" s="27" t="inlineStr"/>
-      <c r="T27" s="70">
+      <c r="E27" s="29" t="inlineStr"/>
+      <c r="F27" s="29" t="inlineStr"/>
+      <c r="G27" s="29" t="inlineStr"/>
+      <c r="H27" s="29" t="inlineStr"/>
+      <c r="I27" s="29" t="inlineStr"/>
+      <c r="J27" s="29" t="inlineStr"/>
+      <c r="K27" s="29" t="inlineStr"/>
+      <c r="L27" s="29" t="inlineStr"/>
+      <c r="M27" s="29" t="inlineStr"/>
+      <c r="N27" s="29" t="inlineStr"/>
+      <c r="O27" s="29" t="inlineStr"/>
+      <c r="P27" s="29" t="inlineStr"/>
+      <c r="Q27" s="29" t="inlineStr"/>
+      <c r="R27" s="29" t="inlineStr"/>
+      <c r="S27" s="29" t="inlineStr"/>
+      <c r="T27" s="71">
         <f>AVERAGE(T17:T26)</f>
         <v/>
       </c>
-      <c r="U27" s="71" t="inlineStr">
+      <c r="U27" s="72" t="inlineStr">
         <is>
           <t>6 сливов</t>
         </is>
       </c>
-      <c r="V27" s="63">
+      <c r="V27" s="31">
         <f>SUM(V17:V26)</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="12" customHeight="1"/>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="54" t="inlineStr">
+      <c r="A29" s="58" t="inlineStr">
         <is>
           <t>🚨 РЕЕСТР ДЕФЕКТОВ РЕЧИ: РАСШИФРОВАННЫЕ ЦИТАТЫ ИЗ РАЗГОВОРОВ И РЕШЕНИЯ РОПа</t>
         </is>
       </c>
-      <c r="B29" s="54" t="n"/>
-      <c r="C29" s="54" t="n"/>
-      <c r="D29" s="54" t="n"/>
-      <c r="E29" s="54" t="n"/>
-      <c r="F29" s="54" t="n"/>
-      <c r="G29" s="54" t="n"/>
-      <c r="H29" s="54" t="n"/>
-      <c r="I29" s="54" t="n"/>
-      <c r="J29" s="54" t="n"/>
-      <c r="K29" s="54" t="n"/>
-      <c r="L29" s="54" t="n"/>
-      <c r="M29" s="54" t="n"/>
-      <c r="N29" s="54" t="n"/>
-      <c r="O29" s="54" t="n"/>
-      <c r="P29" s="54" t="n"/>
-      <c r="Q29" s="54" t="n"/>
-      <c r="R29" s="54" t="n"/>
-      <c r="S29" s="54" t="n"/>
-      <c r="T29" s="54" t="n"/>
-      <c r="U29" s="54" t="n"/>
-      <c r="V29" s="54" t="n"/>
+      <c r="B29" s="58" t="n"/>
+      <c r="C29" s="58" t="n"/>
+      <c r="D29" s="58" t="n"/>
+      <c r="E29" s="58" t="n"/>
+      <c r="F29" s="58" t="n"/>
+      <c r="G29" s="58" t="n"/>
+      <c r="H29" s="58" t="n"/>
+      <c r="I29" s="58" t="n"/>
+      <c r="J29" s="58" t="n"/>
+      <c r="K29" s="58" t="n"/>
+      <c r="L29" s="58" t="n"/>
+      <c r="M29" s="58" t="n"/>
+      <c r="N29" s="58" t="n"/>
+      <c r="O29" s="58" t="n"/>
+      <c r="P29" s="58" t="n"/>
+      <c r="Q29" s="58" t="n"/>
+      <c r="R29" s="58" t="n"/>
+      <c r="S29" s="58" t="n"/>
+      <c r="T29" s="58" t="n"/>
+      <c r="U29" s="58" t="n"/>
+      <c r="V29" s="58" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="25" t="inlineStr">
@@ -3577,23 +3627,23 @@
           <t>Критический дефект речи</t>
         </is>
       </c>
-      <c r="F30" s="25" t="inlineStr">
+      <c r="F30" s="25" t="n"/>
+      <c r="G30" s="25" t="inlineStr">
         <is>
           <t>💬 Цитата из диалога (Расшифровка Whisper Large V3)</t>
         </is>
       </c>
-      <c r="G30" s="25" t="n"/>
       <c r="H30" s="25" t="n"/>
       <c r="I30" s="25" t="n"/>
       <c r="J30" s="25" t="n"/>
       <c r="K30" s="25" t="n"/>
       <c r="L30" s="25" t="n"/>
-      <c r="M30" s="25" t="inlineStr">
+      <c r="M30" s="25" t="n"/>
+      <c r="N30" s="25" t="inlineStr">
         <is>
           <t>🤖 Решение ИИ и Срочное действие РОПа</t>
         </is>
       </c>
-      <c r="N30" s="25" t="n"/>
       <c r="O30" s="25" t="n"/>
       <c r="P30" s="25" t="n"/>
       <c r="Q30" s="25" t="n"/>
@@ -3603,284 +3653,284 @@
       <c r="U30" s="25" t="n"/>
       <c r="V30" s="25" t="n"/>
     </row>
-    <row r="31" ht="48" customHeight="1">
-      <c r="A31" s="43" t="inlineStr">
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="44" t="inlineStr">
         <is>
           <t>C-505</t>
         </is>
       </c>
-      <c r="B31" s="72" t="inlineStr">
+      <c r="B31" s="73" t="inlineStr">
         <is>
           <t>D-109 (ООО «ПромКомплект»)</t>
         </is>
       </c>
-      <c r="C31" s="42" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>Дмитрий Ковалев</t>
         </is>
       </c>
-      <c r="D31" s="58" t="n">
+      <c r="D31" s="61" t="n">
         <v>600000</v>
       </c>
-      <c r="E31" s="73" t="inlineStr">
+      <c r="E31" s="74" t="inlineStr">
         <is>
           <t>Срыв контакта / грубость при цене</t>
         </is>
       </c>
-      <c r="F31" s="74" t="inlineStr">
+      <c r="F31" s="74" t="n"/>
+      <c r="G31" s="75" t="inlineStr">
         <is>
           <t>Клиент: «Почему у вас смета на 15% выше рынка?» → Менеджер: «Не знаю, везде всё дорожает. Не устраивает — берите у конкурентов без гарантии»</t>
         </is>
       </c>
-      <c r="G31" s="74" t="n"/>
-      <c r="H31" s="74" t="n"/>
-      <c r="I31" s="74" t="n"/>
-      <c r="J31" s="74" t="n"/>
-      <c r="K31" s="74" t="n"/>
-      <c r="L31" s="74" t="n"/>
-      <c r="M31" s="75" t="inlineStr">
+      <c r="H31" s="75" t="n"/>
+      <c r="I31" s="75" t="n"/>
+      <c r="J31" s="75" t="n"/>
+      <c r="K31" s="75" t="n"/>
+      <c r="L31" s="75" t="n"/>
+      <c r="M31" s="75" t="n"/>
+      <c r="N31" s="76" t="inlineStr">
         <is>
           <t>🚨 Экстренный звонок РОПа ЛПР до 12:00: принести извинения за консультацию, перехватить сделку, дать проект со спец-гарантией 24 мес.</t>
         </is>
       </c>
-      <c r="N31" s="75" t="n"/>
-      <c r="O31" s="75" t="n"/>
-      <c r="P31" s="75" t="n"/>
-      <c r="Q31" s="75" t="n"/>
-      <c r="R31" s="75" t="n"/>
-      <c r="S31" s="75" t="n"/>
-      <c r="T31" s="75" t="n"/>
-      <c r="U31" s="75" t="n"/>
-      <c r="V31" s="75" t="n"/>
-    </row>
-    <row r="32" ht="48" customHeight="1">
-      <c r="A32" s="43" t="inlineStr">
+      <c r="O31" s="76" t="n"/>
+      <c r="P31" s="76" t="n"/>
+      <c r="Q31" s="76" t="n"/>
+      <c r="R31" s="76" t="n"/>
+      <c r="S31" s="76" t="n"/>
+      <c r="T31" s="76" t="n"/>
+      <c r="U31" s="76" t="n"/>
+      <c r="V31" s="76" t="n"/>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="44" t="inlineStr">
         <is>
           <t>C-503</t>
         </is>
       </c>
-      <c r="B32" s="72" t="inlineStr">
+      <c r="B32" s="73" t="inlineStr">
         <is>
           <t>D-106 (ООО «СнабСервис»)</t>
         </is>
       </c>
-      <c r="C32" s="42" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
         <is>
           <t>Анна Соколова</t>
         </is>
       </c>
-      <c r="D32" s="58" t="n">
+      <c r="D32" s="61" t="n">
         <v>280000</v>
       </c>
-      <c r="E32" s="73" t="inlineStr">
+      <c r="E32" s="74" t="inlineStr">
         <is>
           <t>Слив жесткого Next Step (в никуда)</t>
         </is>
       </c>
-      <c r="F32" s="74" t="inlineStr">
+      <c r="F32" s="74" t="n"/>
+      <c r="G32" s="75" t="inlineStr">
         <is>
           <t>Менеджер: «Я вам КП на почту сбросила, посмотрите когда время будет». Клиент: «Хорошо, если что наберу»</t>
         </is>
       </c>
-      <c r="G32" s="74" t="n"/>
-      <c r="H32" s="74" t="n"/>
-      <c r="I32" s="74" t="n"/>
-      <c r="J32" s="74" t="n"/>
-      <c r="K32" s="74" t="n"/>
-      <c r="L32" s="74" t="n"/>
-      <c r="M32" s="75" t="inlineStr">
+      <c r="H32" s="75" t="n"/>
+      <c r="I32" s="75" t="n"/>
+      <c r="J32" s="75" t="n"/>
+      <c r="K32" s="75" t="n"/>
+      <c r="L32" s="75" t="n"/>
+      <c r="M32" s="75" t="n"/>
+      <c r="N32" s="76" t="inlineStr">
         <is>
           <t>Направить клиенту в WhatsApp 2 конкретных слота встречи (сегодня 16:00 / завтра 11:30) с демонстрацией интеграции с CRM.</t>
         </is>
       </c>
-      <c r="N32" s="75" t="n"/>
-      <c r="O32" s="75" t="n"/>
-      <c r="P32" s="75" t="n"/>
-      <c r="Q32" s="75" t="n"/>
-      <c r="R32" s="75" t="n"/>
-      <c r="S32" s="75" t="n"/>
-      <c r="T32" s="75" t="n"/>
-      <c r="U32" s="75" t="n"/>
-      <c r="V32" s="75" t="n"/>
-    </row>
-    <row r="33" ht="48" customHeight="1">
-      <c r="A33" s="43" t="inlineStr">
+      <c r="O32" s="76" t="n"/>
+      <c r="P32" s="76" t="n"/>
+      <c r="Q32" s="76" t="n"/>
+      <c r="R32" s="76" t="n"/>
+      <c r="S32" s="76" t="n"/>
+      <c r="T32" s="76" t="n"/>
+      <c r="U32" s="76" t="n"/>
+      <c r="V32" s="76" t="n"/>
+    </row>
+    <row r="33" ht="54" customHeight="1">
+      <c r="A33" s="44" t="inlineStr">
         <is>
           <t>C-507</t>
         </is>
       </c>
-      <c r="B33" s="72" t="inlineStr">
+      <c r="B33" s="73" t="inlineStr">
         <is>
           <t>D-114 (ООО «АльфаТрейд»)</t>
         </is>
       </c>
-      <c r="C33" s="42" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>Дмитрий Ковалев</t>
         </is>
       </c>
-      <c r="D33" s="58" t="n">
+      <c r="D33" s="61" t="n">
         <v>500000</v>
       </c>
-      <c r="E33" s="73" t="inlineStr">
+      <c r="E33" s="74" t="inlineStr">
         <is>
           <t>Необоснованная скидка вместо ценности</t>
         </is>
       </c>
-      <c r="F33" s="74" t="inlineStr">
+      <c r="F33" s="74" t="n"/>
+      <c r="G33" s="75" t="inlineStr">
         <is>
           <t>Клиент: «У нас бюджет строго ограничен». Менеджер: «Ну ладно, согласую вам скидку 10% прямо сейчас»</t>
         </is>
       </c>
-      <c r="G33" s="74" t="n"/>
-      <c r="H33" s="74" t="n"/>
-      <c r="I33" s="74" t="n"/>
-      <c r="J33" s="74" t="n"/>
-      <c r="K33" s="74" t="n"/>
-      <c r="L33" s="74" t="n"/>
-      <c r="M33" s="75" t="inlineStr">
+      <c r="H33" s="75" t="n"/>
+      <c r="I33" s="75" t="n"/>
+      <c r="J33" s="75" t="n"/>
+      <c r="K33" s="75" t="n"/>
+      <c r="L33" s="75" t="n"/>
+      <c r="M33" s="75" t="n"/>
+      <c r="N33" s="76" t="inlineStr">
         <is>
           <t>Заблокировать выставление счета со скидкой в CRM. РОПу пересогласовать условия: скидка 5% только в обмен на 100% предоплату за 24ч.</t>
         </is>
       </c>
-      <c r="N33" s="75" t="n"/>
-      <c r="O33" s="75" t="n"/>
-      <c r="P33" s="75" t="n"/>
-      <c r="Q33" s="75" t="n"/>
-      <c r="R33" s="75" t="n"/>
-      <c r="S33" s="75" t="n"/>
-      <c r="T33" s="75" t="n"/>
-      <c r="U33" s="75" t="n"/>
-      <c r="V33" s="75" t="n"/>
-    </row>
-    <row r="34" ht="48" customHeight="1">
-      <c r="A34" s="43" t="inlineStr">
+      <c r="O33" s="76" t="n"/>
+      <c r="P33" s="76" t="n"/>
+      <c r="Q33" s="76" t="n"/>
+      <c r="R33" s="76" t="n"/>
+      <c r="S33" s="76" t="n"/>
+      <c r="T33" s="76" t="n"/>
+      <c r="U33" s="76" t="n"/>
+      <c r="V33" s="76" t="n"/>
+    </row>
+    <row r="34" ht="54" customHeight="1">
+      <c r="A34" s="44" t="inlineStr">
         <is>
           <t>C-508</t>
         </is>
       </c>
-      <c r="B34" s="72" t="inlineStr">
+      <c r="B34" s="73" t="inlineStr">
         <is>
           <t>D-118 (ООО «СтройХолдинг»)</t>
         </is>
       </c>
-      <c r="C34" s="42" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
         <is>
           <t>Иван Попов</t>
         </is>
       </c>
-      <c r="D34" s="58" t="n">
+      <c r="D34" s="61" t="n">
         <v>650000</v>
       </c>
-      <c r="E34" s="73" t="inlineStr">
+      <c r="E34" s="74" t="inlineStr">
         <is>
           <t>Слив возражения «Я подумаю»</t>
         </is>
       </c>
-      <c r="F34" s="74" t="inlineStr">
+      <c r="F34" s="74" t="n"/>
+      <c r="G34" s="75" t="inlineStr">
         <is>
           <t>Клиент: «Нам нужно всё обдумать и посоветоваться с руководством». Менеджер: «Да, конечно, думайте» (повесил трубку)</t>
         </is>
       </c>
-      <c r="G34" s="74" t="n"/>
-      <c r="H34" s="74" t="n"/>
-      <c r="I34" s="74" t="n"/>
-      <c r="J34" s="74" t="n"/>
-      <c r="K34" s="74" t="n"/>
-      <c r="L34" s="74" t="n"/>
-      <c r="M34" s="75" t="inlineStr">
+      <c r="H34" s="75" t="n"/>
+      <c r="I34" s="75" t="n"/>
+      <c r="J34" s="75" t="n"/>
+      <c r="K34" s="75" t="n"/>
+      <c r="L34" s="75" t="n"/>
+      <c r="M34" s="75" t="n"/>
+      <c r="N34" s="76" t="inlineStr">
         <is>
           <t>Передать лида старшему КАМу. Отправить в WhatsApp отраслевой кейс с аналогичным объектом и окупаемостью за 21 день.</t>
         </is>
       </c>
-      <c r="N34" s="75" t="n"/>
-      <c r="O34" s="75" t="n"/>
-      <c r="P34" s="75" t="n"/>
-      <c r="Q34" s="75" t="n"/>
-      <c r="R34" s="75" t="n"/>
-      <c r="S34" s="75" t="n"/>
-      <c r="T34" s="75" t="n"/>
-      <c r="U34" s="75" t="n"/>
-      <c r="V34" s="75" t="n"/>
-    </row>
-    <row r="35" ht="48" customHeight="1">
-      <c r="A35" s="43" t="inlineStr">
+      <c r="O34" s="76" t="n"/>
+      <c r="P34" s="76" t="n"/>
+      <c r="Q34" s="76" t="n"/>
+      <c r="R34" s="76" t="n"/>
+      <c r="S34" s="76" t="n"/>
+      <c r="T34" s="76" t="n"/>
+      <c r="U34" s="76" t="n"/>
+      <c r="V34" s="76" t="n"/>
+    </row>
+    <row r="35" ht="54" customHeight="1">
+      <c r="A35" s="44" t="inlineStr">
         <is>
           <t>C-510</t>
         </is>
       </c>
-      <c r="B35" s="72" t="inlineStr">
+      <c r="B35" s="73" t="inlineStr">
         <is>
           <t>D-125 (ООО «МегаТранс»)</t>
         </is>
       </c>
-      <c r="C35" s="42" t="inlineStr">
+      <c r="C35" s="26" t="inlineStr">
         <is>
           <t>Иван Попов</t>
         </is>
       </c>
-      <c r="D35" s="58" t="n">
+      <c r="D35" s="61" t="n">
         <v>450000</v>
       </c>
-      <c r="E35" s="73" t="inlineStr">
+      <c r="E35" s="74" t="inlineStr">
         <is>
           <t>Режим автоответчика, не выявлен ЛПР</t>
         </is>
       </c>
-      <c r="F35" s="74" t="inlineStr">
+      <c r="F35" s="74" t="n"/>
+      <c r="G35" s="75" t="inlineStr">
         <is>
           <t>Менеджер 5 минут зачитывал прайс-лист секретарю, не спросив, кто принимает решение по закупкам</t>
         </is>
       </c>
-      <c r="G35" s="74" t="n"/>
-      <c r="H35" s="74" t="n"/>
-      <c r="I35" s="74" t="n"/>
-      <c r="J35" s="74" t="n"/>
-      <c r="K35" s="74" t="n"/>
-      <c r="L35" s="74" t="n"/>
-      <c r="M35" s="75" t="inlineStr">
+      <c r="H35" s="75" t="n"/>
+      <c r="I35" s="75" t="n"/>
+      <c r="J35" s="75" t="n"/>
+      <c r="K35" s="75" t="n"/>
+      <c r="L35" s="75" t="n"/>
+      <c r="M35" s="75" t="n"/>
+      <c r="N35" s="76" t="inlineStr">
         <is>
           <t>Разбор на летучке: регламент квалификации BANT. Назначить повторный звонок с прямым выходом на генерального директора.</t>
         </is>
       </c>
-      <c r="N35" s="75" t="n"/>
-      <c r="O35" s="75" t="n"/>
-      <c r="P35" s="75" t="n"/>
-      <c r="Q35" s="75" t="n"/>
-      <c r="R35" s="75" t="n"/>
-      <c r="S35" s="75" t="n"/>
-      <c r="T35" s="75" t="n"/>
-      <c r="U35" s="75" t="n"/>
-      <c r="V35" s="75" t="n"/>
+      <c r="O35" s="76" t="n"/>
+      <c r="P35" s="76" t="n"/>
+      <c r="Q35" s="76" t="n"/>
+      <c r="R35" s="76" t="n"/>
+      <c r="S35" s="76" t="n"/>
+      <c r="T35" s="76" t="n"/>
+      <c r="U35" s="76" t="n"/>
+      <c r="V35" s="76" t="n"/>
     </row>
     <row r="36" ht="12" customHeight="1"/>
     <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="54" t="inlineStr">
+      <c r="A37" s="58" t="inlineStr">
         <is>
           <t>📋 ЭТАЛОННЫЙ СТАНДАРТ 13 КРИТЕРИЕВ ОЦЕНКИ B2B-ДИАЛОГОВ (WHISPER LARGE V3 + LLM SUPERVISOR)</t>
         </is>
       </c>
-      <c r="B37" s="54" t="n"/>
-      <c r="C37" s="54" t="n"/>
-      <c r="D37" s="54" t="n"/>
-      <c r="E37" s="54" t="n"/>
-      <c r="F37" s="54" t="n"/>
-      <c r="G37" s="54" t="n"/>
-      <c r="H37" s="54" t="n"/>
-      <c r="I37" s="54" t="n"/>
-      <c r="J37" s="54" t="n"/>
-      <c r="K37" s="54" t="n"/>
-      <c r="L37" s="54" t="n"/>
-      <c r="M37" s="54" t="n"/>
-      <c r="N37" s="54" t="n"/>
-      <c r="O37" s="54" t="n"/>
-      <c r="P37" s="54" t="n"/>
-      <c r="Q37" s="54" t="n"/>
-      <c r="R37" s="54" t="n"/>
-      <c r="S37" s="54" t="n"/>
-      <c r="T37" s="54" t="n"/>
-      <c r="U37" s="54" t="n"/>
-      <c r="V37" s="54" t="n"/>
+      <c r="B37" s="58" t="n"/>
+      <c r="C37" s="58" t="n"/>
+      <c r="D37" s="58" t="n"/>
+      <c r="E37" s="58" t="n"/>
+      <c r="F37" s="58" t="n"/>
+      <c r="G37" s="58" t="n"/>
+      <c r="H37" s="58" t="n"/>
+      <c r="I37" s="58" t="n"/>
+      <c r="J37" s="58" t="n"/>
+      <c r="K37" s="58" t="n"/>
+      <c r="L37" s="58" t="n"/>
+      <c r="M37" s="58" t="n"/>
+      <c r="N37" s="58" t="n"/>
+      <c r="O37" s="58" t="n"/>
+      <c r="P37" s="58" t="n"/>
+      <c r="Q37" s="58" t="n"/>
+      <c r="R37" s="58" t="n"/>
+      <c r="S37" s="58" t="n"/>
+      <c r="T37" s="58" t="n"/>
+      <c r="U37" s="58" t="n"/>
+      <c r="V37" s="58" t="n"/>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="25" t="inlineStr">
@@ -3935,7 +3985,7 @@
       <c r="V38" s="25" t="n"/>
     </row>
     <row r="39" ht="34" customHeight="1">
-      <c r="A39" s="42" t="n">
+      <c r="A39" s="26" t="n">
         <v>1</v>
       </c>
       <c r="B39" s="8" t="inlineStr">
@@ -3943,7 +3993,7 @@
           <t>Жёсткий Next Step</t>
         </is>
       </c>
-      <c r="C39" s="42" t="inlineStr">
+      <c r="C39" s="26" t="inlineStr">
         <is>
           <t>2.0x</t>
         </is>
@@ -3953,13 +4003,13 @@
           <t>🔴 P0 (Критический)</t>
         </is>
       </c>
-      <c r="E39" s="76" t="inlineStr">
+      <c r="E39" s="27" t="inlineStr">
         <is>
           <t>Зафиксирована точная дата и время следующего контакта (календарный слот)</t>
         </is>
       </c>
-      <c r="F39" s="76" t="n"/>
-      <c r="G39" s="76" t="n"/>
+      <c r="F39" s="27" t="n"/>
+      <c r="G39" s="27" t="n"/>
       <c r="H39" s="77" t="inlineStr">
         <is>
           <t>«Я вам перезвоню на днях», «Подумайте, наберите», отпускание без времени</t>
@@ -3969,23 +4019,23 @@
       <c r="J39" s="77" t="n"/>
       <c r="K39" s="77" t="n"/>
       <c r="L39" s="77" t="n"/>
-      <c r="M39" s="78" t="inlineStr">
+      <c r="M39" s="73" t="inlineStr">
         <is>
           <t>Внедрить обязательный вопрос в конце диалога: «Во вторник в 14:30 или в среду в 11:00 удобно?»</t>
         </is>
       </c>
-      <c r="N39" s="78" t="n"/>
-      <c r="O39" s="78" t="n"/>
-      <c r="P39" s="78" t="n"/>
-      <c r="Q39" s="78" t="n"/>
-      <c r="R39" s="78" t="n"/>
-      <c r="S39" s="78" t="n"/>
-      <c r="T39" s="78" t="n"/>
-      <c r="U39" s="78" t="n"/>
-      <c r="V39" s="78" t="n"/>
+      <c r="N39" s="73" t="n"/>
+      <c r="O39" s="73" t="n"/>
+      <c r="P39" s="73" t="n"/>
+      <c r="Q39" s="73" t="n"/>
+      <c r="R39" s="73" t="n"/>
+      <c r="S39" s="73" t="n"/>
+      <c r="T39" s="73" t="n"/>
+      <c r="U39" s="73" t="n"/>
+      <c r="V39" s="73" t="n"/>
     </row>
     <row r="40" ht="34" customHeight="1">
-      <c r="A40" s="42" t="n">
+      <c r="A40" s="26" t="n">
         <v>2</v>
       </c>
       <c r="B40" s="8" t="inlineStr">
@@ -3993,7 +4043,7 @@
           <t>Инициатива диалога</t>
         </is>
       </c>
-      <c r="C40" s="42" t="inlineStr">
+      <c r="C40" s="26" t="inlineStr">
         <is>
           <t>1.0x</t>
         </is>
@@ -4003,13 +4053,13 @@
           <t>🟡 P1 (Высокий)</t>
         </is>
       </c>
-      <c r="E40" s="76" t="inlineStr">
+      <c r="E40" s="27" t="inlineStr">
         <is>
           <t>Менеджер ведёт диалог вопросами, держит сценарий, а не работает автоответчиком</t>
         </is>
       </c>
-      <c r="F40" s="76" t="n"/>
-      <c r="G40" s="76" t="n"/>
+      <c r="F40" s="27" t="n"/>
+      <c r="G40" s="27" t="n"/>
       <c r="H40" s="77" t="inlineStr">
         <is>
           <t>Клиент задает все вопросы сам, менеджер только отвечает короткими репликами</t>
@@ -4019,23 +4069,23 @@
       <c r="J40" s="77" t="n"/>
       <c r="K40" s="77" t="n"/>
       <c r="L40" s="77" t="n"/>
-      <c r="M40" s="78" t="inlineStr">
+      <c r="M40" s="73" t="inlineStr">
         <is>
           <t>Правило «Ответ + Встречный вопрос». Завершать каждую реплику квалифицирующим вопросом.</t>
         </is>
       </c>
-      <c r="N40" s="78" t="n"/>
-      <c r="O40" s="78" t="n"/>
-      <c r="P40" s="78" t="n"/>
-      <c r="Q40" s="78" t="n"/>
-      <c r="R40" s="78" t="n"/>
-      <c r="S40" s="78" t="n"/>
-      <c r="T40" s="78" t="n"/>
-      <c r="U40" s="78" t="n"/>
-      <c r="V40" s="78" t="n"/>
+      <c r="N40" s="73" t="n"/>
+      <c r="O40" s="73" t="n"/>
+      <c r="P40" s="73" t="n"/>
+      <c r="Q40" s="73" t="n"/>
+      <c r="R40" s="73" t="n"/>
+      <c r="S40" s="73" t="n"/>
+      <c r="T40" s="73" t="n"/>
+      <c r="U40" s="73" t="n"/>
+      <c r="V40" s="73" t="n"/>
     </row>
     <row r="41" ht="34" customHeight="1">
-      <c r="A41" s="42" t="n">
+      <c r="A41" s="26" t="n">
         <v>3</v>
       </c>
       <c r="B41" s="8" t="inlineStr">
@@ -4043,7 +4093,7 @@
           <t>Квалификация ЛПР / ЛВПР</t>
         </is>
       </c>
-      <c r="C41" s="42" t="inlineStr">
+      <c r="C41" s="26" t="inlineStr">
         <is>
           <t>1.5x</t>
         </is>
@@ -4053,13 +4103,13 @@
           <t>🔴 P0 (Критический)</t>
         </is>
       </c>
-      <c r="E41" s="76" t="inlineStr">
+      <c r="E41" s="27" t="inlineStr">
         <is>
           <t>Установлен статус собеседника: принимает ли решения по бюджету и согласованию</t>
         </is>
       </c>
-      <c r="F41" s="76" t="n"/>
-      <c r="G41" s="76" t="n"/>
+      <c r="F41" s="27" t="n"/>
+      <c r="G41" s="27" t="n"/>
       <c r="H41" s="77" t="inlineStr">
         <is>
           <t>Трата 40 минут на презентацию инженеру или секретарю без полномочий подписания</t>
@@ -4069,23 +4119,23 @@
       <c r="J41" s="77" t="n"/>
       <c r="K41" s="77" t="n"/>
       <c r="L41" s="77" t="n"/>
-      <c r="M41" s="78" t="inlineStr">
+      <c r="M41" s="73" t="inlineStr">
         <is>
           <t>«Кто кроме вас участвует в согласовании проекта и утверждении финансового бюджета?»</t>
         </is>
       </c>
-      <c r="N41" s="78" t="n"/>
-      <c r="O41" s="78" t="n"/>
-      <c r="P41" s="78" t="n"/>
-      <c r="Q41" s="78" t="n"/>
-      <c r="R41" s="78" t="n"/>
-      <c r="S41" s="78" t="n"/>
-      <c r="T41" s="78" t="n"/>
-      <c r="U41" s="78" t="n"/>
-      <c r="V41" s="78" t="n"/>
+      <c r="N41" s="73" t="n"/>
+      <c r="O41" s="73" t="n"/>
+      <c r="P41" s="73" t="n"/>
+      <c r="Q41" s="73" t="n"/>
+      <c r="R41" s="73" t="n"/>
+      <c r="S41" s="73" t="n"/>
+      <c r="T41" s="73" t="n"/>
+      <c r="U41" s="73" t="n"/>
+      <c r="V41" s="73" t="n"/>
     </row>
     <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="42" t="n">
+      <c r="A42" s="26" t="n">
         <v>4</v>
       </c>
       <c r="B42" s="8" t="inlineStr">
@@ -4093,7 +4143,7 @@
           <t>Выявление болей и срочности</t>
         </is>
       </c>
-      <c r="C42" s="42" t="inlineStr">
+      <c r="C42" s="26" t="inlineStr">
         <is>
           <t>1.2x</t>
         </is>
@@ -4103,13 +4153,13 @@
           <t>🟡 P1 (Высокий)</t>
         </is>
       </c>
-      <c r="E42" s="76" t="inlineStr">
+      <c r="E42" s="27" t="inlineStr">
         <is>
           <t>Понятна ли бизнес-задача клиента, текущие потери и дедлайн решения проблемы</t>
         </is>
       </c>
-      <c r="F42" s="76" t="n"/>
-      <c r="G42" s="76" t="n"/>
+      <c r="F42" s="27" t="n"/>
+      <c r="G42" s="27" t="n"/>
       <c r="H42" s="77" t="inlineStr">
         <is>
           <t>Менеджер сразу начинает презентовать продукт, не узнав текущую ситуацию клиента</t>
@@ -4119,23 +4169,23 @@
       <c r="J42" s="77" t="n"/>
       <c r="K42" s="77" t="n"/>
       <c r="L42" s="77" t="n"/>
-      <c r="M42" s="78" t="inlineStr">
+      <c r="M42" s="73" t="inlineStr">
         <is>
           <t>Сначала диагностика по методологии SPIN/BANT, затем презентация под конкретную боль.</t>
         </is>
       </c>
-      <c r="N42" s="78" t="n"/>
-      <c r="O42" s="78" t="n"/>
-      <c r="P42" s="78" t="n"/>
-      <c r="Q42" s="78" t="n"/>
-      <c r="R42" s="78" t="n"/>
-      <c r="S42" s="78" t="n"/>
-      <c r="T42" s="78" t="n"/>
-      <c r="U42" s="78" t="n"/>
-      <c r="V42" s="78" t="n"/>
+      <c r="N42" s="73" t="n"/>
+      <c r="O42" s="73" t="n"/>
+      <c r="P42" s="73" t="n"/>
+      <c r="Q42" s="73" t="n"/>
+      <c r="R42" s="73" t="n"/>
+      <c r="S42" s="73" t="n"/>
+      <c r="T42" s="73" t="n"/>
+      <c r="U42" s="73" t="n"/>
+      <c r="V42" s="73" t="n"/>
     </row>
     <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="42" t="n">
+      <c r="A43" s="26" t="n">
         <v>5</v>
       </c>
       <c r="B43" s="8" t="inlineStr">
@@ -4143,7 +4193,7 @@
           <t>Отработка возражения «Дорого»</t>
         </is>
       </c>
-      <c r="C43" s="42" t="inlineStr">
+      <c r="C43" s="26" t="inlineStr">
         <is>
           <t>1.5x</t>
         </is>
@@ -4153,13 +4203,13 @@
           <t>🔴 P0 (Критический)</t>
         </is>
       </c>
-      <c r="E43" s="76" t="inlineStr">
+      <c r="E43" s="27" t="inlineStr">
         <is>
           <t>Обоснование ценности, расчет ROI/окупаемости, рассрочка (без моментальной скидки)</t>
         </is>
       </c>
-      <c r="F43" s="76" t="n"/>
-      <c r="G43" s="76" t="n"/>
+      <c r="F43" s="27" t="n"/>
+      <c r="G43" s="27" t="n"/>
       <c r="H43" s="77" t="inlineStr">
         <is>
           <t>Моментальная скидка при первом сомнении клиента или согласие («Да, у нас недешево»)</t>
@@ -4169,23 +4219,23 @@
       <c r="J43" s="77" t="n"/>
       <c r="K43" s="77" t="n"/>
       <c r="L43" s="77" t="n"/>
-      <c r="M43" s="78" t="inlineStr">
+      <c r="M43" s="73" t="inlineStr">
         <is>
           <t>Обосновать окупаемость: показать, сколько клиент теряет каждый день без внедрения решения.</t>
         </is>
       </c>
-      <c r="N43" s="78" t="n"/>
-      <c r="O43" s="78" t="n"/>
-      <c r="P43" s="78" t="n"/>
-      <c r="Q43" s="78" t="n"/>
-      <c r="R43" s="78" t="n"/>
-      <c r="S43" s="78" t="n"/>
-      <c r="T43" s="78" t="n"/>
-      <c r="U43" s="78" t="n"/>
-      <c r="V43" s="78" t="n"/>
+      <c r="N43" s="73" t="n"/>
+      <c r="O43" s="73" t="n"/>
+      <c r="P43" s="73" t="n"/>
+      <c r="Q43" s="73" t="n"/>
+      <c r="R43" s="73" t="n"/>
+      <c r="S43" s="73" t="n"/>
+      <c r="T43" s="73" t="n"/>
+      <c r="U43" s="73" t="n"/>
+      <c r="V43" s="73" t="n"/>
     </row>
     <row r="44" ht="34" customHeight="1">
-      <c r="A44" s="42" t="n">
+      <c r="A44" s="26" t="n">
         <v>6</v>
       </c>
       <c r="B44" s="8" t="inlineStr">
@@ -4193,7 +4243,7 @@
           <t>Отработка «Я подумаю»</t>
         </is>
       </c>
-      <c r="C44" s="42" t="inlineStr">
+      <c r="C44" s="26" t="inlineStr">
         <is>
           <t>1.0x</t>
         </is>
@@ -4203,13 +4253,13 @@
           <t>🟡 P1 (Высокий)</t>
         </is>
       </c>
-      <c r="E44" s="76" t="inlineStr">
+      <c r="E44" s="27" t="inlineStr">
         <is>
           <t>Вскрытие истинного сомнения клиента, а не молчаливое отпускание в архив</t>
         </is>
       </c>
-      <c r="F44" s="76" t="n"/>
-      <c r="G44" s="76" t="n"/>
+      <c r="F44" s="27" t="n"/>
+      <c r="G44" s="27" t="n"/>
       <c r="H44" s="77" t="inlineStr">
         <is>
           <t>«Хорошо, думайте, ждем вашего звонка», завершение диалога на неопределенности</t>
@@ -4219,23 +4269,23 @@
       <c r="J44" s="77" t="n"/>
       <c r="K44" s="77" t="n"/>
       <c r="L44" s="77" t="n"/>
-      <c r="M44" s="78" t="inlineStr">
+      <c r="M44" s="73" t="inlineStr">
         <is>
           <t>«Алексей, обычно говорят 'подумаю', когда смущает цена или функционал. Что именно из этого?»</t>
         </is>
       </c>
-      <c r="N44" s="78" t="n"/>
-      <c r="O44" s="78" t="n"/>
-      <c r="P44" s="78" t="n"/>
-      <c r="Q44" s="78" t="n"/>
-      <c r="R44" s="78" t="n"/>
-      <c r="S44" s="78" t="n"/>
-      <c r="T44" s="78" t="n"/>
-      <c r="U44" s="78" t="n"/>
-      <c r="V44" s="78" t="n"/>
+      <c r="N44" s="73" t="n"/>
+      <c r="O44" s="73" t="n"/>
+      <c r="P44" s="73" t="n"/>
+      <c r="Q44" s="73" t="n"/>
+      <c r="R44" s="73" t="n"/>
+      <c r="S44" s="73" t="n"/>
+      <c r="T44" s="73" t="n"/>
+      <c r="U44" s="73" t="n"/>
+      <c r="V44" s="73" t="n"/>
     </row>
     <row r="45" ht="34" customHeight="1">
-      <c r="A45" s="42" t="n">
+      <c r="A45" s="26" t="n">
         <v>7</v>
       </c>
       <c r="B45" s="8" t="inlineStr">
@@ -4243,7 +4293,7 @@
           <t>Презентация через кейсы и цифры</t>
         </is>
       </c>
-      <c r="C45" s="42" t="inlineStr">
+      <c r="C45" s="26" t="inlineStr">
         <is>
           <t>1.0x</t>
         </is>
@@ -4253,13 +4303,13 @@
           <t>🟡 P1 (Высокий)</t>
         </is>
       </c>
-      <c r="E45" s="76" t="inlineStr">
+      <c r="E45" s="27" t="inlineStr">
         <is>
           <t>Приведение аналогичных проектов, оцифрованных результатов и сроков возврата</t>
         </is>
       </c>
-      <c r="F45" s="76" t="n"/>
-      <c r="G45" s="76" t="n"/>
+      <c r="F45" s="27" t="n"/>
+      <c r="G45" s="27" t="n"/>
       <c r="H45" s="77" t="inlineStr">
         <is>
           <t>Абстрактные слова «мы надежные», «у нас высокое качество» без конкретных фактов</t>
@@ -4269,23 +4319,23 @@
       <c r="J45" s="77" t="n"/>
       <c r="K45" s="77" t="n"/>
       <c r="L45" s="77" t="n"/>
-      <c r="M45" s="78" t="inlineStr">
+      <c r="M45" s="73" t="inlineStr">
         <is>
           <t>Показать схожий кейс из отрасли клиента: «Для завода X мы сократили потери на 1.4 млн ₽ за 21 день».</t>
         </is>
       </c>
-      <c r="N45" s="78" t="n"/>
-      <c r="O45" s="78" t="n"/>
-      <c r="P45" s="78" t="n"/>
-      <c r="Q45" s="78" t="n"/>
-      <c r="R45" s="78" t="n"/>
-      <c r="S45" s="78" t="n"/>
-      <c r="T45" s="78" t="n"/>
-      <c r="U45" s="78" t="n"/>
-      <c r="V45" s="78" t="n"/>
+      <c r="N45" s="73" t="n"/>
+      <c r="O45" s="73" t="n"/>
+      <c r="P45" s="73" t="n"/>
+      <c r="Q45" s="73" t="n"/>
+      <c r="R45" s="73" t="n"/>
+      <c r="S45" s="73" t="n"/>
+      <c r="T45" s="73" t="n"/>
+      <c r="U45" s="73" t="n"/>
+      <c r="V45" s="73" t="n"/>
     </row>
     <row r="46" ht="34" customHeight="1">
-      <c r="A46" s="42" t="n">
+      <c r="A46" s="26" t="n">
         <v>8</v>
       </c>
       <c r="B46" s="8" t="inlineStr">
@@ -4293,7 +4343,7 @@
           <t>Попытка закрытия сделки</t>
         </is>
       </c>
-      <c r="C46" s="42" t="inlineStr">
+      <c r="C46" s="26" t="inlineStr">
         <is>
           <t>1.5x</t>
         </is>
@@ -4303,13 +4353,13 @@
           <t>🔴 P0 (Критический)</t>
         </is>
       </c>
-      <c r="E46" s="76" t="inlineStr">
+      <c r="E46" s="27" t="inlineStr">
         <is>
           <t>Прямое предложение заключить договор, забронировать слот аудита или выставить счет</t>
         </is>
       </c>
-      <c r="F46" s="76" t="n"/>
-      <c r="G46" s="76" t="n"/>
+      <c r="F46" s="27" t="n"/>
+      <c r="G46" s="27" t="n"/>
       <c r="H46" s="77" t="inlineStr">
         <is>
           <t>Разговор закончился тепло, но менеджер не предложил сделать следующий шаг к оплате</t>
@@ -4319,23 +4369,23 @@
       <c r="J46" s="77" t="n"/>
       <c r="K46" s="77" t="n"/>
       <c r="L46" s="77" t="n"/>
-      <c r="M46" s="78" t="inlineStr">
+      <c r="M46" s="73" t="inlineStr">
         <is>
           <t>«Если все параметры подходят, предлагаю сегодня запустить пилот. Куда отправить договор?»</t>
         </is>
       </c>
-      <c r="N46" s="78" t="n"/>
-      <c r="O46" s="78" t="n"/>
-      <c r="P46" s="78" t="n"/>
-      <c r="Q46" s="78" t="n"/>
-      <c r="R46" s="78" t="n"/>
-      <c r="S46" s="78" t="n"/>
-      <c r="T46" s="78" t="n"/>
-      <c r="U46" s="78" t="n"/>
-      <c r="V46" s="78" t="n"/>
+      <c r="N46" s="73" t="n"/>
+      <c r="O46" s="73" t="n"/>
+      <c r="P46" s="73" t="n"/>
+      <c r="Q46" s="73" t="n"/>
+      <c r="R46" s="73" t="n"/>
+      <c r="S46" s="73" t="n"/>
+      <c r="T46" s="73" t="n"/>
+      <c r="U46" s="73" t="n"/>
+      <c r="V46" s="73" t="n"/>
     </row>
     <row r="47" ht="34" customHeight="1">
-      <c r="A47" s="42" t="n">
+      <c r="A47" s="26" t="n">
         <v>9</v>
       </c>
       <c r="B47" s="8" t="inlineStr">
@@ -4343,23 +4393,23 @@
           <t>Регламент приветствия и повестка</t>
         </is>
       </c>
-      <c r="C47" s="42" t="inlineStr">
+      <c r="C47" s="26" t="inlineStr">
         <is>
           <t>0.8x</t>
         </is>
       </c>
-      <c r="D47" s="79" t="inlineStr">
+      <c r="D47" s="78" t="inlineStr">
         <is>
           <t>🟢 P2 (Стандарт)</t>
         </is>
       </c>
-      <c r="E47" s="76" t="inlineStr">
+      <c r="E47" s="27" t="inlineStr">
         <is>
           <t>Представление имени, компании, уточнение времени и согласование цели разговора</t>
         </is>
       </c>
-      <c r="F47" s="76" t="n"/>
-      <c r="G47" s="76" t="n"/>
+      <c r="F47" s="27" t="n"/>
+      <c r="G47" s="27" t="n"/>
       <c r="H47" s="77" t="inlineStr">
         <is>
           <t>Невнятное приветствие, вопрос «Вам удобно говорить?» без обозначения повестки</t>
@@ -4369,23 +4419,23 @@
       <c r="J47" s="77" t="n"/>
       <c r="K47" s="77" t="n"/>
       <c r="L47" s="77" t="n"/>
-      <c r="M47" s="78" t="inlineStr">
+      <c r="M47" s="73" t="inlineStr">
         <is>
           <t>«Добрый день! Дмитрий, компания RevOps. Звоню по вашей заявке на аудит воронки. Уделите 5 минут?»</t>
         </is>
       </c>
-      <c r="N47" s="78" t="n"/>
-      <c r="O47" s="78" t="n"/>
-      <c r="P47" s="78" t="n"/>
-      <c r="Q47" s="78" t="n"/>
-      <c r="R47" s="78" t="n"/>
-      <c r="S47" s="78" t="n"/>
-      <c r="T47" s="78" t="n"/>
-      <c r="U47" s="78" t="n"/>
-      <c r="V47" s="78" t="n"/>
+      <c r="N47" s="73" t="n"/>
+      <c r="O47" s="73" t="n"/>
+      <c r="P47" s="73" t="n"/>
+      <c r="Q47" s="73" t="n"/>
+      <c r="R47" s="73" t="n"/>
+      <c r="S47" s="73" t="n"/>
+      <c r="T47" s="73" t="n"/>
+      <c r="U47" s="73" t="n"/>
+      <c r="V47" s="73" t="n"/>
     </row>
     <row r="48" ht="34" customHeight="1">
-      <c r="A48" s="42" t="n">
+      <c r="A48" s="26" t="n">
         <v>10</v>
       </c>
       <c r="B48" s="8" t="inlineStr">
@@ -4393,23 +4443,23 @@
           <t>Чистота речи и уверенность</t>
         </is>
       </c>
-      <c r="C48" s="42" t="inlineStr">
+      <c r="C48" s="26" t="inlineStr">
         <is>
           <t>0.8x</t>
         </is>
       </c>
-      <c r="D48" s="79" t="inlineStr">
+      <c r="D48" s="78" t="inlineStr">
         <is>
           <t>🟢 P2 (Стандарт)</t>
         </is>
       </c>
-      <c r="E48" s="76" t="inlineStr">
+      <c r="E48" s="27" t="inlineStr">
         <is>
           <t>Отсутствие слов-паразитов («как бы», «э-э-э»), пауз и извиняющихся интонаций при цене</t>
         </is>
       </c>
-      <c r="F48" s="76" t="n"/>
-      <c r="G48" s="76" t="n"/>
+      <c r="F48" s="27" t="n"/>
+      <c r="G48" s="27" t="n"/>
       <c r="H48" s="77" t="inlineStr">
         <is>
           <t>Дрожащий голос при озвучивании чека, слова сомнения («может быть», «наверное»)</t>
@@ -4419,23 +4469,23 @@
       <c r="J48" s="77" t="n"/>
       <c r="K48" s="77" t="n"/>
       <c r="L48" s="77" t="n"/>
-      <c r="M48" s="78" t="inlineStr">
+      <c r="M48" s="73" t="inlineStr">
         <is>
           <t>Отработать блок цены на тренажере: уверенная пауза после озвучивания стоимости.</t>
         </is>
       </c>
-      <c r="N48" s="78" t="n"/>
-      <c r="O48" s="78" t="n"/>
-      <c r="P48" s="78" t="n"/>
-      <c r="Q48" s="78" t="n"/>
-      <c r="R48" s="78" t="n"/>
-      <c r="S48" s="78" t="n"/>
-      <c r="T48" s="78" t="n"/>
-      <c r="U48" s="78" t="n"/>
-      <c r="V48" s="78" t="n"/>
+      <c r="N48" s="73" t="n"/>
+      <c r="O48" s="73" t="n"/>
+      <c r="P48" s="73" t="n"/>
+      <c r="Q48" s="73" t="n"/>
+      <c r="R48" s="73" t="n"/>
+      <c r="S48" s="73" t="n"/>
+      <c r="T48" s="73" t="n"/>
+      <c r="U48" s="73" t="n"/>
+      <c r="V48" s="73" t="n"/>
     </row>
     <row r="49" ht="34" customHeight="1">
-      <c r="A49" s="42" t="n">
+      <c r="A49" s="26" t="n">
         <v>11</v>
       </c>
       <c r="B49" s="8" t="inlineStr">
@@ -4443,7 +4493,7 @@
           <t>Слушание клиента (Talk/Listen)</t>
         </is>
       </c>
-      <c r="C49" s="42" t="inlineStr">
+      <c r="C49" s="26" t="inlineStr">
         <is>
           <t>1.2x</t>
         </is>
@@ -4453,13 +4503,13 @@
           <t>🟡 P1 (Высокий)</t>
         </is>
       </c>
-      <c r="E49" s="76" t="inlineStr">
+      <c r="E49" s="27" t="inlineStr">
         <is>
           <t>Менеджер слушает клиента не менее 45–50% общего времени разговора</t>
         </is>
       </c>
-      <c r="F49" s="76" t="n"/>
-      <c r="G49" s="76" t="n"/>
+      <c r="F49" s="27" t="n"/>
+      <c r="G49" s="27" t="n"/>
       <c r="H49" s="77" t="inlineStr">
         <is>
           <t>Монолог менеджера &gt; 70% времени: клиент молчит и теряет фокус внимания</t>
@@ -4469,23 +4519,23 @@
       <c r="J49" s="77" t="n"/>
       <c r="K49" s="77" t="n"/>
       <c r="L49" s="77" t="n"/>
-      <c r="M49" s="78" t="inlineStr">
+      <c r="M49" s="73" t="inlineStr">
         <is>
           <t>Держать баланс 50/50. Задавать открытые вопросы и давать клиенту выговориться о проблеме.</t>
         </is>
       </c>
-      <c r="N49" s="78" t="n"/>
-      <c r="O49" s="78" t="n"/>
-      <c r="P49" s="78" t="n"/>
-      <c r="Q49" s="78" t="n"/>
-      <c r="R49" s="78" t="n"/>
-      <c r="S49" s="78" t="n"/>
-      <c r="T49" s="78" t="n"/>
-      <c r="U49" s="78" t="n"/>
-      <c r="V49" s="78" t="n"/>
+      <c r="N49" s="73" t="n"/>
+      <c r="O49" s="73" t="n"/>
+      <c r="P49" s="73" t="n"/>
+      <c r="Q49" s="73" t="n"/>
+      <c r="R49" s="73" t="n"/>
+      <c r="S49" s="73" t="n"/>
+      <c r="T49" s="73" t="n"/>
+      <c r="U49" s="73" t="n"/>
+      <c r="V49" s="73" t="n"/>
     </row>
     <row r="50" ht="34" customHeight="1">
-      <c r="A50" s="42" t="n">
+      <c r="A50" s="26" t="n">
         <v>12</v>
       </c>
       <c r="B50" s="8" t="inlineStr">
@@ -4493,23 +4543,23 @@
           <t>Фиксация договорённостей</t>
         </is>
       </c>
-      <c r="C50" s="42" t="inlineStr">
+      <c r="C50" s="26" t="inlineStr">
         <is>
           <t>1.0x</t>
         </is>
       </c>
-      <c r="D50" s="79" t="inlineStr">
+      <c r="D50" s="78" t="inlineStr">
         <is>
           <t>🟢 P2 (Стандарт)</t>
         </is>
       </c>
-      <c r="E50" s="76" t="inlineStr">
+      <c r="E50" s="27" t="inlineStr">
         <is>
           <t>Резюмирование договоренностей перед окончанием звонка: кто, что и когда делает</t>
         </is>
       </c>
-      <c r="F50" s="76" t="n"/>
-      <c r="G50" s="76" t="n"/>
+      <c r="F50" s="27" t="n"/>
+      <c r="G50" s="27" t="n"/>
       <c r="H50" s="77" t="inlineStr">
         <is>
           <t>Диалог оборвался, у клиента и менеджера разное понимание следующих действий</t>
@@ -4519,23 +4569,23 @@
       <c r="J50" s="77" t="n"/>
       <c r="K50" s="77" t="n"/>
       <c r="L50" s="77" t="n"/>
-      <c r="M50" s="78" t="inlineStr">
+      <c r="M50" s="73" t="inlineStr">
         <is>
           <t>«Итак, резюмирую: я отправляю КП в WhatsApp до 15:00, а завтра в 11:00 мы созваниваемся по условиям».</t>
         </is>
       </c>
-      <c r="N50" s="78" t="n"/>
-      <c r="O50" s="78" t="n"/>
-      <c r="P50" s="78" t="n"/>
-      <c r="Q50" s="78" t="n"/>
-      <c r="R50" s="78" t="n"/>
-      <c r="S50" s="78" t="n"/>
-      <c r="T50" s="78" t="n"/>
-      <c r="U50" s="78" t="n"/>
-      <c r="V50" s="78" t="n"/>
+      <c r="N50" s="73" t="n"/>
+      <c r="O50" s="73" t="n"/>
+      <c r="P50" s="73" t="n"/>
+      <c r="Q50" s="73" t="n"/>
+      <c r="R50" s="73" t="n"/>
+      <c r="S50" s="73" t="n"/>
+      <c r="T50" s="73" t="n"/>
+      <c r="U50" s="73" t="n"/>
+      <c r="V50" s="73" t="n"/>
     </row>
     <row r="51" ht="34" customHeight="1">
-      <c r="A51" s="42" t="n">
+      <c r="A51" s="26" t="n">
         <v>13</v>
       </c>
       <c r="B51" s="8" t="inlineStr">
@@ -4543,7 +4593,7 @@
           <t>Защита маржинальности</t>
         </is>
       </c>
-      <c r="C51" s="42" t="inlineStr">
+      <c r="C51" s="26" t="inlineStr">
         <is>
           <t>1.5x</t>
         </is>
@@ -4553,13 +4603,13 @@
           <t>🔴 P0 (Критический)</t>
         </is>
       </c>
-      <c r="E51" s="76" t="inlineStr">
+      <c r="E51" s="27" t="inlineStr">
         <is>
           <t>Отсутствие необоснованных скидок без встречных уступок по объему или предоплате</t>
         </is>
       </c>
-      <c r="F51" s="76" t="n"/>
-      <c r="G51" s="76" t="n"/>
+      <c r="F51" s="27" t="n"/>
+      <c r="G51" s="27" t="n"/>
       <c r="H51" s="77" t="inlineStr">
         <is>
           <t>Раздача скидок из маржи компании без требования 100% предоплаты или большего объема</t>
@@ -4569,49 +4619,49 @@
       <c r="J51" s="77" t="n"/>
       <c r="K51" s="77" t="n"/>
       <c r="L51" s="77" t="n"/>
-      <c r="M51" s="78" t="inlineStr">
+      <c r="M51" s="73" t="inlineStr">
         <is>
           <t>Скидка возможна только в обмен на ценность: «Готовы дать 5% при оплате счета в течение 24 часов».</t>
         </is>
       </c>
-      <c r="N51" s="78" t="n"/>
-      <c r="O51" s="78" t="n"/>
-      <c r="P51" s="78" t="n"/>
-      <c r="Q51" s="78" t="n"/>
-      <c r="R51" s="78" t="n"/>
-      <c r="S51" s="78" t="n"/>
-      <c r="T51" s="78" t="n"/>
-      <c r="U51" s="78" t="n"/>
-      <c r="V51" s="78" t="n"/>
+      <c r="N51" s="73" t="n"/>
+      <c r="O51" s="73" t="n"/>
+      <c r="P51" s="73" t="n"/>
+      <c r="Q51" s="73" t="n"/>
+      <c r="R51" s="73" t="n"/>
+      <c r="S51" s="73" t="n"/>
+      <c r="T51" s="73" t="n"/>
+      <c r="U51" s="73" t="n"/>
+      <c r="V51" s="73" t="n"/>
     </row>
     <row r="52" ht="12" customHeight="1"/>
     <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="54" t="inlineStr">
+      <c r="A53" s="58" t="inlineStr">
         <is>
           <t>💰 ЭКОНОМИЧЕСКИЙ ЭФФЕКТ РЕЧЕВОЙ АНАЛИТИКИ (ROI ВНЕДРЕНИЯ И ОКУПАЕМОСТЬ)</t>
         </is>
       </c>
-      <c r="B53" s="54" t="n"/>
-      <c r="C53" s="54" t="n"/>
-      <c r="D53" s="54" t="n"/>
-      <c r="E53" s="54" t="n"/>
-      <c r="F53" s="54" t="n"/>
-      <c r="G53" s="54" t="n"/>
-      <c r="H53" s="54" t="n"/>
-      <c r="I53" s="54" t="n"/>
-      <c r="J53" s="54" t="n"/>
-      <c r="K53" s="54" t="n"/>
-      <c r="L53" s="54" t="n"/>
-      <c r="M53" s="54" t="n"/>
-      <c r="N53" s="54" t="n"/>
-      <c r="O53" s="54" t="n"/>
-      <c r="P53" s="54" t="n"/>
-      <c r="Q53" s="54" t="n"/>
-      <c r="R53" s="54" t="n"/>
-      <c r="S53" s="54" t="n"/>
-      <c r="T53" s="54" t="n"/>
-      <c r="U53" s="54" t="n"/>
-      <c r="V53" s="54" t="n"/>
+      <c r="B53" s="58" t="n"/>
+      <c r="C53" s="58" t="n"/>
+      <c r="D53" s="58" t="n"/>
+      <c r="E53" s="58" t="n"/>
+      <c r="F53" s="58" t="n"/>
+      <c r="G53" s="58" t="n"/>
+      <c r="H53" s="58" t="n"/>
+      <c r="I53" s="58" t="n"/>
+      <c r="J53" s="58" t="n"/>
+      <c r="K53" s="58" t="n"/>
+      <c r="L53" s="58" t="n"/>
+      <c r="M53" s="58" t="n"/>
+      <c r="N53" s="58" t="n"/>
+      <c r="O53" s="58" t="n"/>
+      <c r="P53" s="58" t="n"/>
+      <c r="Q53" s="58" t="n"/>
+      <c r="R53" s="58" t="n"/>
+      <c r="S53" s="58" t="n"/>
+      <c r="T53" s="58" t="n"/>
+      <c r="U53" s="58" t="n"/>
+      <c r="V53" s="58" t="n"/>
     </row>
     <row r="54" ht="26" customHeight="1">
       <c r="A54" s="25" t="inlineStr">
@@ -4650,216 +4700,218 @@
       <c r="V54" s="25" t="n"/>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="72" t="inlineStr">
+      <c r="A55" s="79" t="inlineStr">
         <is>
           <t>Текущие потери от брака звонков в месяц (As-Is)</t>
         </is>
       </c>
-      <c r="B55" s="72" t="n"/>
-      <c r="C55" s="72" t="n"/>
+      <c r="B55" s="79" t="n"/>
+      <c r="C55" s="79" t="n"/>
       <c r="D55" s="80" t="n">
         <v>1382500</v>
       </c>
       <c r="E55" s="80" t="n"/>
-      <c r="F55" s="57" t="inlineStr">
+      <c r="F55" s="60" t="inlineStr">
         <is>
           <t>Сливы на этапе первичного звонка из-за отсутствия Next Step и слабой отработки возражений</t>
         </is>
       </c>
-      <c r="G55" s="57" t="n"/>
-      <c r="H55" s="57" t="n"/>
-      <c r="I55" s="57" t="n"/>
-      <c r="J55" s="57" t="n"/>
-      <c r="K55" s="57" t="n"/>
-      <c r="L55" s="57" t="n"/>
-      <c r="M55" s="57" t="n"/>
-      <c r="N55" s="57" t="n"/>
-      <c r="O55" s="57" t="n"/>
-      <c r="P55" s="57" t="n"/>
-      <c r="Q55" s="57" t="n"/>
-      <c r="R55" s="57" t="n"/>
-      <c r="S55" s="57" t="n"/>
-      <c r="T55" s="57" t="n"/>
-      <c r="U55" s="57" t="n"/>
-      <c r="V55" s="57" t="n"/>
+      <c r="G55" s="60" t="n"/>
+      <c r="H55" s="60" t="n"/>
+      <c r="I55" s="60" t="n"/>
+      <c r="J55" s="60" t="n"/>
+      <c r="K55" s="60" t="n"/>
+      <c r="L55" s="60" t="n"/>
+      <c r="M55" s="60" t="n"/>
+      <c r="N55" s="60" t="n"/>
+      <c r="O55" s="60" t="n"/>
+      <c r="P55" s="60" t="n"/>
+      <c r="Q55" s="60" t="n"/>
+      <c r="R55" s="60" t="n"/>
+      <c r="S55" s="60" t="n"/>
+      <c r="T55" s="60" t="n"/>
+      <c r="U55" s="60" t="n"/>
+      <c r="V55" s="60" t="n"/>
     </row>
     <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="72" t="inlineStr">
+      <c r="A56" s="79" t="inlineStr">
         <is>
           <t>Ожидаемый возврат выручки в кассу (M1 To-Be)</t>
         </is>
       </c>
-      <c r="B56" s="72" t="n"/>
-      <c r="C56" s="72" t="n"/>
+      <c r="B56" s="79" t="n"/>
+      <c r="C56" s="79" t="n"/>
       <c r="D56" s="81" t="n">
         <v>414750</v>
       </c>
       <c r="E56" s="81" t="n"/>
-      <c r="F56" s="57" t="inlineStr">
+      <c r="F56" s="60" t="inlineStr">
         <is>
           <t>Консервативный сценарий: устранение всего 30% выявленных дефектов речи</t>
         </is>
       </c>
-      <c r="G56" s="57" t="n"/>
-      <c r="H56" s="57" t="n"/>
-      <c r="I56" s="57" t="n"/>
-      <c r="J56" s="57" t="n"/>
-      <c r="K56" s="57" t="n"/>
-      <c r="L56" s="57" t="n"/>
-      <c r="M56" s="57" t="n"/>
-      <c r="N56" s="57" t="n"/>
-      <c r="O56" s="57" t="n"/>
-      <c r="P56" s="57" t="n"/>
-      <c r="Q56" s="57" t="n"/>
-      <c r="R56" s="57" t="n"/>
-      <c r="S56" s="57" t="n"/>
-      <c r="T56" s="57" t="n"/>
-      <c r="U56" s="57" t="n"/>
-      <c r="V56" s="57" t="n"/>
+      <c r="G56" s="60" t="n"/>
+      <c r="H56" s="60" t="n"/>
+      <c r="I56" s="60" t="n"/>
+      <c r="J56" s="60" t="n"/>
+      <c r="K56" s="60" t="n"/>
+      <c r="L56" s="60" t="n"/>
+      <c r="M56" s="60" t="n"/>
+      <c r="N56" s="60" t="n"/>
+      <c r="O56" s="60" t="n"/>
+      <c r="P56" s="60" t="n"/>
+      <c r="Q56" s="60" t="n"/>
+      <c r="R56" s="60" t="n"/>
+      <c r="S56" s="60" t="n"/>
+      <c r="T56" s="60" t="n"/>
+      <c r="U56" s="60" t="n"/>
+      <c r="V56" s="60" t="n"/>
     </row>
     <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="72" t="inlineStr">
+      <c r="A57" s="79" t="inlineStr">
         <is>
           <t>Стоимость модуля речевого ИИ-супервайзера</t>
         </is>
       </c>
-      <c r="B57" s="72" t="n"/>
-      <c r="C57" s="72" t="n"/>
+      <c r="B57" s="79" t="n"/>
+      <c r="C57" s="79" t="n"/>
       <c r="D57" s="82" t="n">
         <v>150000</v>
       </c>
       <c r="E57" s="82" t="n"/>
-      <c r="F57" s="57" t="inlineStr">
+      <c r="F57" s="60" t="inlineStr">
         <is>
           <t>В составе комплексного 4-недельного спринта оптимизации отдела продаж</t>
         </is>
       </c>
-      <c r="G57" s="57" t="n"/>
-      <c r="H57" s="57" t="n"/>
-      <c r="I57" s="57" t="n"/>
-      <c r="J57" s="57" t="n"/>
-      <c r="K57" s="57" t="n"/>
-      <c r="L57" s="57" t="n"/>
-      <c r="M57" s="57" t="n"/>
-      <c r="N57" s="57" t="n"/>
-      <c r="O57" s="57" t="n"/>
-      <c r="P57" s="57" t="n"/>
-      <c r="Q57" s="57" t="n"/>
-      <c r="R57" s="57" t="n"/>
-      <c r="S57" s="57" t="n"/>
-      <c r="T57" s="57" t="n"/>
-      <c r="U57" s="57" t="n"/>
-      <c r="V57" s="57" t="n"/>
+      <c r="G57" s="60" t="n"/>
+      <c r="H57" s="60" t="n"/>
+      <c r="I57" s="60" t="n"/>
+      <c r="J57" s="60" t="n"/>
+      <c r="K57" s="60" t="n"/>
+      <c r="L57" s="60" t="n"/>
+      <c r="M57" s="60" t="n"/>
+      <c r="N57" s="60" t="n"/>
+      <c r="O57" s="60" t="n"/>
+      <c r="P57" s="60" t="n"/>
+      <c r="Q57" s="60" t="n"/>
+      <c r="R57" s="60" t="n"/>
+      <c r="S57" s="60" t="n"/>
+      <c r="T57" s="60" t="n"/>
+      <c r="U57" s="60" t="n"/>
+      <c r="V57" s="60" t="n"/>
     </row>
     <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="72" t="inlineStr">
+      <c r="A58" s="79" t="inlineStr">
         <is>
           <t>Чистая прибыль компании от внедрения в первый месяц</t>
         </is>
       </c>
-      <c r="B58" s="72" t="n"/>
-      <c r="C58" s="72" t="n"/>
+      <c r="B58" s="79" t="n"/>
+      <c r="C58" s="79" t="n"/>
       <c r="D58" s="81" t="n">
         <v>264750</v>
       </c>
       <c r="E58" s="81" t="n"/>
-      <c r="F58" s="57" t="inlineStr">
+      <c r="F58" s="60" t="inlineStr">
         <is>
           <t>Чистый денежный плюс в кассе компании уже в первый месяц работы</t>
         </is>
       </c>
-      <c r="G58" s="57" t="n"/>
-      <c r="H58" s="57" t="n"/>
-      <c r="I58" s="57" t="n"/>
-      <c r="J58" s="57" t="n"/>
-      <c r="K58" s="57" t="n"/>
-      <c r="L58" s="57" t="n"/>
-      <c r="M58" s="57" t="n"/>
-      <c r="N58" s="57" t="n"/>
-      <c r="O58" s="57" t="n"/>
-      <c r="P58" s="57" t="n"/>
-      <c r="Q58" s="57" t="n"/>
-      <c r="R58" s="57" t="n"/>
-      <c r="S58" s="57" t="n"/>
-      <c r="T58" s="57" t="n"/>
-      <c r="U58" s="57" t="n"/>
-      <c r="V58" s="57" t="n"/>
+      <c r="G58" s="60" t="n"/>
+      <c r="H58" s="60" t="n"/>
+      <c r="I58" s="60" t="n"/>
+      <c r="J58" s="60" t="n"/>
+      <c r="K58" s="60" t="n"/>
+      <c r="L58" s="60" t="n"/>
+      <c r="M58" s="60" t="n"/>
+      <c r="N58" s="60" t="n"/>
+      <c r="O58" s="60" t="n"/>
+      <c r="P58" s="60" t="n"/>
+      <c r="Q58" s="60" t="n"/>
+      <c r="R58" s="60" t="n"/>
+      <c r="S58" s="60" t="n"/>
+      <c r="T58" s="60" t="n"/>
+      <c r="U58" s="60" t="n"/>
+      <c r="V58" s="60" t="n"/>
     </row>
     <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="72" t="inlineStr">
+      <c r="A59" s="79" t="inlineStr">
         <is>
           <t>Чистый ROI речевой аналитики</t>
         </is>
       </c>
-      <c r="B59" s="72" t="n"/>
-      <c r="C59" s="72" t="n"/>
-      <c r="D59" s="55" t="inlineStr">
+      <c r="B59" s="79" t="n"/>
+      <c r="C59" s="79" t="n"/>
+      <c r="D59" s="59" t="inlineStr">
         <is>
           <t>276%</t>
         </is>
       </c>
-      <c r="E59" s="55" t="n"/>
-      <c r="F59" s="57" t="inlineStr">
+      <c r="E59" s="59" t="n"/>
+      <c r="F59" s="60" t="inlineStr">
         <is>
           <t>Отдача на каждый вложенный рубль в первый месяц</t>
         </is>
       </c>
-      <c r="G59" s="57" t="n"/>
-      <c r="H59" s="57" t="n"/>
-      <c r="I59" s="57" t="n"/>
-      <c r="J59" s="57" t="n"/>
-      <c r="K59" s="57" t="n"/>
-      <c r="L59" s="57" t="n"/>
-      <c r="M59" s="57" t="n"/>
-      <c r="N59" s="57" t="n"/>
-      <c r="O59" s="57" t="n"/>
-      <c r="P59" s="57" t="n"/>
-      <c r="Q59" s="57" t="n"/>
-      <c r="R59" s="57" t="n"/>
-      <c r="S59" s="57" t="n"/>
-      <c r="T59" s="57" t="n"/>
-      <c r="U59" s="57" t="n"/>
-      <c r="V59" s="57" t="n"/>
+      <c r="G59" s="60" t="n"/>
+      <c r="H59" s="60" t="n"/>
+      <c r="I59" s="60" t="n"/>
+      <c r="J59" s="60" t="n"/>
+      <c r="K59" s="60" t="n"/>
+      <c r="L59" s="60" t="n"/>
+      <c r="M59" s="60" t="n"/>
+      <c r="N59" s="60" t="n"/>
+      <c r="O59" s="60" t="n"/>
+      <c r="P59" s="60" t="n"/>
+      <c r="Q59" s="60" t="n"/>
+      <c r="R59" s="60" t="n"/>
+      <c r="S59" s="60" t="n"/>
+      <c r="T59" s="60" t="n"/>
+      <c r="U59" s="60" t="n"/>
+      <c r="V59" s="60" t="n"/>
     </row>
     <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="72" t="inlineStr">
+      <c r="A60" s="79" t="inlineStr">
         <is>
           <t>Срок полной окупаемости модуля</t>
         </is>
       </c>
-      <c r="B60" s="72" t="n"/>
-      <c r="C60" s="72" t="n"/>
-      <c r="D60" s="55" t="inlineStr">
+      <c r="B60" s="79" t="n"/>
+      <c r="C60" s="79" t="n"/>
+      <c r="D60" s="59" t="inlineStr">
         <is>
           <t>11 дней</t>
         </is>
       </c>
-      <c r="E60" s="55" t="n"/>
-      <c r="F60" s="57" t="inlineStr">
+      <c r="E60" s="59" t="n"/>
+      <c r="F60" s="60" t="inlineStr">
         <is>
           <t>Количество рабочих дней до полной окупаемости внедрения речевого ИИ</t>
         </is>
       </c>
-      <c r="G60" s="57" t="n"/>
-      <c r="H60" s="57" t="n"/>
-      <c r="I60" s="57" t="n"/>
-      <c r="J60" s="57" t="n"/>
-      <c r="K60" s="57" t="n"/>
-      <c r="L60" s="57" t="n"/>
-      <c r="M60" s="57" t="n"/>
-      <c r="N60" s="57" t="n"/>
-      <c r="O60" s="57" t="n"/>
-      <c r="P60" s="57" t="n"/>
-      <c r="Q60" s="57" t="n"/>
-      <c r="R60" s="57" t="n"/>
-      <c r="S60" s="57" t="n"/>
-      <c r="T60" s="57" t="n"/>
-      <c r="U60" s="57" t="n"/>
-      <c r="V60" s="57" t="n"/>
+      <c r="G60" s="60" t="n"/>
+      <c r="H60" s="60" t="n"/>
+      <c r="I60" s="60" t="n"/>
+      <c r="J60" s="60" t="n"/>
+      <c r="K60" s="60" t="n"/>
+      <c r="L60" s="60" t="n"/>
+      <c r="M60" s="60" t="n"/>
+      <c r="N60" s="60" t="n"/>
+      <c r="O60" s="60" t="n"/>
+      <c r="P60" s="60" t="n"/>
+      <c r="Q60" s="60" t="n"/>
+      <c r="R60" s="60" t="n"/>
+      <c r="S60" s="60" t="n"/>
+      <c r="T60" s="60" t="n"/>
+      <c r="U60" s="60" t="n"/>
+      <c r="V60" s="60" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="94">
+  <mergeCells count="112">
+    <mergeCell ref="D2:F2"/>
     <mergeCell ref="D60:E60"/>
+    <mergeCell ref="N2:P2"/>
     <mergeCell ref="M41:V41"/>
     <mergeCell ref="H43:L43"/>
     <mergeCell ref="E40:G40"/>
@@ -4867,93 +4919,117 @@
     <mergeCell ref="A29:V29"/>
     <mergeCell ref="A57:C57"/>
     <mergeCell ref="H49:L49"/>
+    <mergeCell ref="N31:V31"/>
+    <mergeCell ref="J3:L3"/>
     <mergeCell ref="A15:V15"/>
+    <mergeCell ref="E34:F34"/>
     <mergeCell ref="M39:V39"/>
     <mergeCell ref="J9:V9"/>
     <mergeCell ref="M48:V48"/>
     <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F33:L33"/>
+    <mergeCell ref="N35:V35"/>
     <mergeCell ref="E42:G42"/>
-    <mergeCell ref="M31:V31"/>
     <mergeCell ref="H48:L48"/>
     <mergeCell ref="E44:G44"/>
-    <mergeCell ref="H4:V4"/>
-    <mergeCell ref="F31:L31"/>
-    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="G33:M33"/>
+    <mergeCell ref="E3:F3"/>
     <mergeCell ref="H38:L38"/>
+    <mergeCell ref="G35:M35"/>
     <mergeCell ref="H44:L44"/>
     <mergeCell ref="A55:C55"/>
+    <mergeCell ref="C4:D4"/>
     <mergeCell ref="M38:V38"/>
     <mergeCell ref="H40:L40"/>
+    <mergeCell ref="E4:F4"/>
     <mergeCell ref="E46:G46"/>
     <mergeCell ref="H51:L51"/>
     <mergeCell ref="F59:V59"/>
     <mergeCell ref="M43:V43"/>
     <mergeCell ref="J8:V8"/>
     <mergeCell ref="F55:V55"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="N30:V30"/>
     <mergeCell ref="J10:V10"/>
     <mergeCell ref="E41:G41"/>
     <mergeCell ref="A58:C58"/>
     <mergeCell ref="E47:G47"/>
-    <mergeCell ref="M35:V35"/>
     <mergeCell ref="E43:G43"/>
     <mergeCell ref="A60:C60"/>
     <mergeCell ref="F58:V58"/>
+    <mergeCell ref="N32:V32"/>
+    <mergeCell ref="G30:M30"/>
     <mergeCell ref="H42:L42"/>
-    <mergeCell ref="M30:V30"/>
     <mergeCell ref="F60:V60"/>
     <mergeCell ref="M46:V46"/>
-    <mergeCell ref="M33:V33"/>
-    <mergeCell ref="F4:G4"/>
     <mergeCell ref="F57:V57"/>
     <mergeCell ref="M42:V42"/>
+    <mergeCell ref="M3:V3"/>
+    <mergeCell ref="N33:V33"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J4:L4"/>
     <mergeCell ref="J12:V12"/>
     <mergeCell ref="A53:V53"/>
-    <mergeCell ref="M32:V32"/>
+    <mergeCell ref="G32:M32"/>
+    <mergeCell ref="A2:C2"/>
     <mergeCell ref="E45:G45"/>
+    <mergeCell ref="M4:V4"/>
     <mergeCell ref="H46:L46"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="E31:F31"/>
     <mergeCell ref="M44:V44"/>
+    <mergeCell ref="Q2:V2"/>
     <mergeCell ref="H45:L45"/>
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="M51:V51"/>
     <mergeCell ref="A59:C59"/>
     <mergeCell ref="H47:L47"/>
-    <mergeCell ref="F32:L32"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="D55:E55"/>
     <mergeCell ref="F56:V56"/>
-    <mergeCell ref="F35:L35"/>
+    <mergeCell ref="E32:F32"/>
     <mergeCell ref="A37:V37"/>
     <mergeCell ref="D54:E54"/>
+    <mergeCell ref="J11:V11"/>
     <mergeCell ref="E51:G51"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="J11:V11"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="M45:V45"/>
+    <mergeCell ref="E33:F33"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="H50:L50"/>
     <mergeCell ref="F54:V54"/>
     <mergeCell ref="M47:V47"/>
-    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="G31:M31"/>
+    <mergeCell ref="K2:M2"/>
     <mergeCell ref="H39:L39"/>
     <mergeCell ref="E49:G49"/>
     <mergeCell ref="M50:V50"/>
     <mergeCell ref="D57:E57"/>
-    <mergeCell ref="M34:V34"/>
-    <mergeCell ref="F34:L34"/>
     <mergeCell ref="J7:V7"/>
-    <mergeCell ref="H3:V3"/>
+    <mergeCell ref="N34:V34"/>
     <mergeCell ref="M49:V49"/>
+    <mergeCell ref="E30:F30"/>
     <mergeCell ref="J13:V13"/>
-    <mergeCell ref="F30:L30"/>
     <mergeCell ref="A6:V6"/>
     <mergeCell ref="E50:G50"/>
     <mergeCell ref="D58:E58"/>
     <mergeCell ref="M40:V40"/>
     <mergeCell ref="E39:G39"/>
     <mergeCell ref="E48:G48"/>
+    <mergeCell ref="G34:M34"/>
     <mergeCell ref="D59:E59"/>
     <mergeCell ref="E38:G38"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4967,10 +5043,10 @@
   <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
@@ -4991,70 +5067,63 @@
       <c r="G1" s="2" t="n"/>
       <c r="H1" s="2" t="n"/>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>📄 1. One-Pager</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>⚡ 2. Пульс компании</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>📋 3. Пульт РОПа</t>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>⚡ Экспресс-Калькулятор</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>📋 Пульт РОПа</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>💸 4. 7 Грехов ОП</t>
+          <t>🎙️ ИИ-Аудит</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>🎯 5. Action Center</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>🎙️ 6. ИИ-Аудит</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>⚡ 7. Экспресс 3 цифры</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>🧪 8. QA Suite</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+          <t>💸 7 Грехов ОП</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>📄 One-Pager</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>🔐 152-ФЗ Безопасность</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n"/>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Фактическая выручка месяца</t>
         </is>
       </c>
-      <c r="B4" s="50" t="inlineStr">
+      <c r="B4" s="39" t="n"/>
+      <c r="C4" s="53" t="inlineStr">
         <is>
           <t>Взвешенный пайплайн в работе</t>
         </is>
       </c>
-      <c r="C4" s="38" t="inlineStr">
+      <c r="D4" s="40" t="inlineStr">
         <is>
           <t>Выявленная упущенная прибыль</t>
         </is>
       </c>
-      <c r="D4" s="83" t="inlineStr">
+      <c r="E4" s="83" t="inlineStr">
         <is>
           <t>Потенциал выручки (To-Be)</t>
         </is>
       </c>
-      <c r="E4" s="83" t="inlineStr">
+      <c r="F4" s="83" t="inlineStr">
         <is>
           <t>Ожидаемый чистый ROI</t>
         </is>
@@ -5064,21 +5133,23 @@
           <t>Срок окупаемости проекта</t>
         </is>
       </c>
+      <c r="H4" s="83" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="84" t="n">
         <v>1650000</v>
       </c>
-      <c r="B5" s="23" t="n">
+      <c r="B5" s="84" t="n"/>
+      <c r="C5" s="23" t="n">
         <v>2754000</v>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="D5" s="21" t="n">
         <v>7001000</v>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="E5" s="22" t="n">
         <v>8651000</v>
       </c>
-      <c r="E5" s="85" t="inlineStr">
+      <c r="F5" s="85" t="inlineStr">
         <is>
           <t>367%</t>
         </is>
@@ -5088,6 +5159,7 @@
           <t>6 дн.</t>
         </is>
       </c>
+      <c r="H5" s="85" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -5138,306 +5210,306 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="42" t="inlineStr">
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="73" t="inlineStr">
         <is>
           <t>«Черный ящик» CRM: иллюзорный пайплайн</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>В CRM висит 5.3 млн ₽, но реальный взвешенный объем всего 2.6 млн ₽. Фаундер живет в иллюзии плана</t>
         </is>
       </c>
-      <c r="D9" s="86" t="n">
+      <c r="D9" s="67" t="n">
         <v>5530000</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="28" t="n">
         <v>2776000</v>
       </c>
-      <c r="F9" s="87" t="inlineStr">
+      <c r="F9" s="86" t="inlineStr">
         <is>
           <t>🔴 P0 (Критический)</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>Взвешенный прогноз воронки (SSOT) + исключение зомби-сделок</t>
         </is>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="H9" s="27" t="inlineStr">
         <is>
           <t>100% точность прогноза Run-Rate без иллюзий</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="36" customHeight="1">
-      <c r="A10" s="42" t="inlineStr">
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="73" t="inlineStr">
         <is>
           <t>«Кладбище сделок»: срыв регламентов SLA</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>Сделки маринуются на этапе КП по 12–14 дней (норма 48ч). Вероятность закрытия падает на 45%</t>
         </is>
       </c>
-      <c r="D10" s="86" t="n">
+      <c r="D10" s="67" t="n">
         <v>3850000</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="28" t="n">
         <v>1732500</v>
       </c>
-      <c r="F10" s="87" t="inlineStr">
+      <c r="F10" s="86" t="inlineStr">
         <is>
           <t>🔴 P0 (Критический)</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t>Авторадар зависания сделок + эскалация РОПу на 3-й день</t>
         </is>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="H10" s="27" t="inlineStr">
         <is>
           <t>+45% к конверсии этапа КП в оплату</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="36" customHeight="1">
-      <c r="A11" s="42" t="inlineStr">
+    <row r="11" ht="48" customHeight="1">
+      <c r="A11" s="26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="73" t="inlineStr">
         <is>
           <t>РОП — «играющий тренер» и узкое горлышко</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>РОП ведет 80% сделок и перегружен (нагрузка 80%), а КАМы простаивают с 4% загрузки. Сделки тухнут без внимания</t>
         </is>
       </c>
-      <c r="D11" s="86" t="n">
+      <c r="D11" s="67" t="n">
         <v>850000</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="28" t="n">
         <v>255000</v>
       </c>
-      <c r="F11" s="87" t="inlineStr">
+      <c r="F11" s="86" t="inlineStr">
         <is>
           <t>🔴 P0 (Критический)</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t>Матрица емкости (Capacity Planning) + автоперелив сделок на КАМов</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="27" t="inlineStr">
         <is>
           <t>Разгрузка РОПа на 60% для управления и коучинга</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="42" t="inlineStr">
+    <row r="12" ht="48" customHeight="1">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="73" t="inlineStr">
         <is>
           <t>Менеджеры-автоответчики и слив звонков</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>В 33% звонков не зафиксирован Next Step. Средний балл речи &lt; 9/13. Лиды уходят в «подумаю»</t>
         </is>
       </c>
-      <c r="D12" s="86" t="n">
+      <c r="D12" s="67" t="n">
         <v>5530000</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="28" t="n">
         <v>1382500</v>
       </c>
-      <c r="F12" s="87" t="inlineStr">
+      <c r="F12" s="86" t="inlineStr">
         <is>
           <t>🔴 P0 (Критический)</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>13-факторная речевая аналитика + чек-листы BANT + мотивация от речи</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="27" t="inlineStr">
         <is>
           <t>+30% к конверсии из первого звонка во встречу</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="42" t="inlineStr">
+    <row r="13" ht="48" customHeight="1">
+      <c r="A13" s="26" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="73" t="inlineStr">
         <is>
           <t>«Кладбище отказников» без реактивации</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>1 млн ₽ списан в отказ (L1 «дорого», L2 «подумаю»). База брошена в архиве без повторного прогрева</t>
         </is>
       </c>
-      <c r="D13" s="86" t="n">
+      <c r="D13" s="67" t="n">
         <v>1000000</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="28" t="n">
         <v>440000</v>
       </c>
-      <c r="F13" s="88" t="inlineStr">
+      <c r="F13" s="87" t="inlineStr">
         <is>
           <t>🟡 P1 (Высокий)</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="27" t="inlineStr">
         <is>
           <t>Agentic AI Recovery Engine: сегментация отказников + офферы даунсейла</t>
         </is>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="H13" s="27" t="inlineStr">
         <is>
           <t>Возврат до 20–30% списанной выручки из архива</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="36" customHeight="1">
-      <c r="A14" s="42" t="inlineStr">
+    <row r="14" ht="48" customHeight="1">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="73" t="inlineStr">
         <is>
           <t>Зависшая дебиторка и кассовые разрывы</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>Счета выставлены, но не оплачены (DSO &gt; 25 дней). 330к просрочки грозит кассовым разрывом</t>
         </is>
       </c>
-      <c r="D14" s="86" t="n">
+      <c r="D14" s="67" t="n">
         <v>330000</v>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="28" t="n">
         <v>330000</v>
       </c>
-      <c r="F14" s="88" t="inlineStr">
+      <c r="F14" s="87" t="inlineStr">
         <is>
           <t>🟡 P1 (Высокий)</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="27" t="inlineStr">
         <is>
           <t>Платежный календарь DSO + триггерные AI-уведомления бухгалтерии клиента</t>
         </is>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="H14" s="27" t="inlineStr">
         <is>
           <t>Сокращение срока дебиторки DSO с 27 до 7 дней</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="42" t="inlineStr">
+    <row r="15" ht="48" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="73" t="inlineStr">
         <is>
           <t>Слив маркетинга и война с отделом продаж</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>Google Ads слил 85 000 ₽ с ROMI -100% (0 оплат). Деньги сожжены без сквозного контроля окупаемости</t>
         </is>
       </c>
-      <c r="D15" s="86" t="n">
+      <c r="D15" s="67" t="n">
         <v>850000</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="28" t="n">
         <v>85000</v>
       </c>
-      <c r="F15" s="88" t="inlineStr">
+      <c r="F15" s="87" t="inlineStr">
         <is>
           <t>🟡 P1 (Высокий)</t>
         </is>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="G15" s="27" t="inlineStr">
         <is>
           <t>Сквозная RevOps-атрибуция W-Shaped: автоотключение убыточных связок</t>
         </is>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="H15" s="27" t="inlineStr">
         <is>
           <t>Экономия рекламного бюджета + перелив в прибыльный Контур/Директ</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="27" t="n"/>
-      <c r="B16" s="28" t="inlineStr">
+      <c r="A16" s="29" t="n"/>
+      <c r="B16" s="46" t="inlineStr">
         <is>
           <t>ИТОГО ВЫЯВЛЕННЫХ ПОТЕРЬ И РИСКОВ В МЕСЯЦ:</t>
         </is>
       </c>
-      <c r="C16" s="27" t="n"/>
-      <c r="D16" s="89">
+      <c r="C16" s="29" t="n"/>
+      <c r="D16" s="88">
         <f>SUM(D9:D15)</f>
         <v/>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="47">
         <f>SUM(E9:E15)</f>
         <v/>
       </c>
-      <c r="F16" s="90" t="inlineStr">
+      <c r="F16" s="89" t="inlineStr">
         <is>
           <t>ИТОГО ПОТЕРЬ</t>
         </is>
       </c>
-      <c r="G16" s="45" t="inlineStr">
+      <c r="G16" s="48" t="inlineStr">
         <is>
           <t>Потенциал возврата в кассу</t>
         </is>
       </c>
-      <c r="H16" s="30" t="inlineStr">
+      <c r="H16" s="49" t="inlineStr">
         <is>
           <t>Окупаемость за счет устранения узких мест</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="46" t="inlineStr">
+      <c r="A18" s="50" t="inlineStr">
         <is>
           <t>🚀 ЭКОНОМИКА ПРОЕКТА ОПТИМИЗАЦИИ И СРОК ОКУПАЕМОСТИ ДЛЯ КЛИЕНТА</t>
         </is>
@@ -5466,8 +5538,8 @@
           <t>Стоимость проекта оптимизации ОП</t>
         </is>
       </c>
-      <c r="B20" s="47" t="n"/>
-      <c r="C20" s="47" t="n"/>
+      <c r="B20" s="51" t="n"/>
+      <c r="C20" s="51" t="n"/>
       <c r="D20" s="82" t="n">
         <v>450000</v>
       </c>
@@ -5476,9 +5548,9 @@
           <t>Фиксированная стоимость внедрения (4 недели спринтов)</t>
         </is>
       </c>
-      <c r="F20" s="47" t="n"/>
-      <c r="G20" s="47" t="n"/>
-      <c r="H20" s="47" t="n"/>
+      <c r="F20" s="51" t="n"/>
+      <c r="G20" s="51" t="n"/>
+      <c r="H20" s="51" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
@@ -5486,8 +5558,8 @@
           <t>Ожидаемый возврат выручки (M1 факт)</t>
         </is>
       </c>
-      <c r="B21" s="47" t="n"/>
-      <c r="C21" s="47" t="n"/>
+      <c r="B21" s="51" t="n"/>
+      <c r="C21" s="51" t="n"/>
       <c r="D21" s="81" t="n">
         <v>2100300</v>
       </c>
@@ -5496,9 +5568,9 @@
           <t>Консервативный ориентир: устранение всего 30% найденных узких мест</t>
         </is>
       </c>
-      <c r="F21" s="47" t="n"/>
-      <c r="G21" s="47" t="n"/>
-      <c r="H21" s="47" t="n"/>
+      <c r="F21" s="51" t="n"/>
+      <c r="G21" s="51" t="n"/>
+      <c r="H21" s="51" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -5506,8 +5578,8 @@
           <t>Чистая прибыль собственника за вычетом услуг</t>
         </is>
       </c>
-      <c r="B22" s="47" t="n"/>
-      <c r="C22" s="47" t="n"/>
+      <c r="B22" s="51" t="n"/>
+      <c r="C22" s="51" t="n"/>
       <c r="D22" s="81">
         <f>D21-D20</f>
         <v/>
@@ -5517,9 +5589,9 @@
           <t>Чистый денежный плюс в кассе компании в первый же месяц</t>
         </is>
       </c>
-      <c r="F22" s="47" t="n"/>
-      <c r="G22" s="47" t="n"/>
-      <c r="H22" s="47" t="n"/>
+      <c r="F22" s="51" t="n"/>
+      <c r="G22" s="51" t="n"/>
+      <c r="H22" s="51" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
@@ -5527,9 +5599,9 @@
           <t>Чистый ROI инвестиций в проект</t>
         </is>
       </c>
-      <c r="B23" s="47" t="n"/>
-      <c r="C23" s="47" t="n"/>
-      <c r="D23" s="55">
+      <c r="B23" s="51" t="n"/>
+      <c r="C23" s="51" t="n"/>
+      <c r="D23" s="59">
         <f>(D22/D20)*100 &amp; "%"</f>
         <v/>
       </c>
@@ -5538,9 +5610,9 @@
           <t>Процент отдачи на каждый вложенный рубль</t>
         </is>
       </c>
-      <c r="F23" s="47" t="n"/>
-      <c r="G23" s="47" t="n"/>
-      <c r="H23" s="47" t="n"/>
+      <c r="F23" s="51" t="n"/>
+      <c r="G23" s="51" t="n"/>
+      <c r="H23" s="51" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
@@ -5548,9 +5620,9 @@
           <t>Срок полной окупаемости проекта</t>
         </is>
       </c>
-      <c r="B24" s="47" t="n"/>
-      <c r="C24" s="47" t="n"/>
-      <c r="D24" s="55">
+      <c r="B24" s="51" t="n"/>
+      <c r="C24" s="51" t="n"/>
+      <c r="D24" s="59">
         <f>ROUND(D20/(D21/30), 0) &amp; " дн."</f>
         <v/>
       </c>
@@ -5559,38 +5631,37 @@
           <t>Количество дней работы ОП до полной окупаемости чека внедрения</t>
         </is>
       </c>
-      <c r="F24" s="47" t="n"/>
-      <c r="G24" s="47" t="n"/>
-      <c r="H24" s="47" t="n"/>
+      <c r="F24" s="51" t="n"/>
+      <c r="G24" s="51" t="n"/>
+      <c r="H24" s="51" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="91" t="inlineStr">
+      <c r="A26" s="90" t="inlineStr">
         <is>
           <t>👉 УТВЕРДИТЬ ПРОЕКТ ОПТИМИЗАЦИИ И СФОРМИРОВАТЬ ИНВОЙС (450 000 ₽)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="35" t="inlineStr">
+      <c r="A27" s="91" t="inlineStr">
         <is>
           <t>Не готовы к спринту? 👉 Бесплатный тест-драйв на 3 звонках на вкладке «⚡ Экспресс_Калькулятор_3_Цифры»</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="36" t="inlineStr">
+      <c r="A28" s="92" t="inlineStr">
         <is>
           <t>🔒 Безопасный B2B-расчет: безналичный платеж по счету (УПД / Диадок) • 152-ФЗ РФ • Старт спринта за 24 часа</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="E5:F5"/>
+  <mergeCells count="25">
+    <mergeCell ref="G2:H2"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="E22:H22"/>
-    <mergeCell ref="E4:F4"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A22:C22"/>
@@ -5601,15 +5672,26 @@
     <mergeCell ref="E24:H24"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="E23:H23"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
     <mergeCell ref="E20:H20"/>
-    <mergeCell ref="G5:H5"/>
     <mergeCell ref="E19:H19"/>
     <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A28:H28"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5624,13 +5706,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
     <col width="44" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -5649,126 +5731,114 @@
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>
     </row>
-    <row r="2" ht="22" customHeight="1">
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>📄 1. One-Pager</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>⚡ 2. Пульс компании</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>📋 3. Пульт РОПа</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>💸 4. 7 Грехов ОП</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>🎯 5. Action Center</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>🎙️ 6. ИИ-Аудит</t>
+          <t>⚡ Экспресс-Калькулятор</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>📋 Пульт РОПа (15 мин)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>🎙️ ИИ-Аудит звонков</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>💸 7 Грехов (Диагностика)</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>⚡ 7. Экспресс 3 цифры</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>🧪 8. QA Suite</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>⚙️ 9. Настройки</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
-        <is>
-          <t>Выручка (Факт Closed-Won)</t>
-        </is>
-      </c>
-      <c r="B4" s="37" t="inlineStr">
+          <t>📄 Executive One-Pager</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="n"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>🔐 152-ФЗ Безопасность</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="39" t="inlineStr">
+        <is>
+          <t>Выручка (Closed-Won)</t>
+        </is>
+      </c>
+      <c r="B4" s="39" t="inlineStr">
         <is>
           <t>% Выполнения плана</t>
         </is>
       </c>
-      <c r="C4" s="37" t="inlineStr">
-        <is>
-          <t>Взвешенный прогноз (SSOT)</t>
-        </is>
-      </c>
-      <c r="D4" s="37" t="inlineStr">
+      <c r="C4" s="53" t="inlineStr">
+        <is>
+          <t>Взвешенный прогноз</t>
+        </is>
+      </c>
+      <c r="D4" s="39" t="inlineStr">
         <is>
           <t>Run-Rate касса (Прогноз)</t>
         </is>
       </c>
-      <c r="E4" s="37" t="inlineStr">
+      <c r="F4" s="39" t="inlineStr">
         <is>
           <t>Активный пайплайн в работе</t>
         </is>
       </c>
-      <c r="F4" s="37" t="inlineStr">
+      <c r="G4" s="40" t="inlineStr">
         <is>
           <t>Сделок под угрозой SLA</t>
         </is>
       </c>
-      <c r="G4" s="37" t="inlineStr">
+      <c r="H4" s="39" t="inlineStr">
         <is>
           <t>Качество речи ОП (ИИ)</t>
         </is>
       </c>
-      <c r="H4" s="83" t="inlineStr">
+      <c r="I4" s="83" t="inlineStr">
         <is>
           <t>Data Quality Index</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="84" t="n">
         <v>1650000</v>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>33.0%</t>
         </is>
       </c>
-      <c r="C5" s="92" t="n">
+      <c r="C5" s="23" t="n">
         <v>2754000</v>
       </c>
       <c r="D5" s="84" t="n">
         <v>1706897</v>
       </c>
-      <c r="E5" s="84" t="n">
+      <c r="F5" s="84" t="n">
         <v>5530000</v>
       </c>
-      <c r="F5" s="93" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G5" s="39" t="inlineStr">
+      <c r="G5" s="42" t="inlineStr">
+        <is>
+          <t>4 сделки</t>
+        </is>
+      </c>
+      <c r="H5" s="41" t="inlineStr">
         <is>
           <t>73.1%</t>
         </is>
       </c>
-      <c r="H5" s="85" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="I5" s="85" t="inlineStr">
+        <is>
+          <t>100.0% (Эталон)</t>
         </is>
       </c>
     </row>
@@ -5826,8 +5896,8 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>1. Новый лид</t>
         </is>
@@ -5835,33 +5905,33 @@
       <c r="B9" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="28" t="n">
         <v>950000</v>
       </c>
       <c r="D9" s="26" t="n">
         <v>24</v>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="79" t="inlineStr">
         <is>
           <t>D-104 (ООО Вектор)</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>КП без ответа &gt; 48ч</t>
         </is>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="H9" s="61" t="n">
         <v>850000</v>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="I9" s="27" t="inlineStr">
         <is>
           <t>Повторный контакт с ЛПР + звонок РОПа</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>2. Квалификация / ЛПР</t>
         </is>
@@ -5869,33 +5939,33 @@
       <c r="B10" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="28" t="n">
         <v>120000</v>
       </c>
       <c r="D10" s="26" t="n">
         <v>48</v>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="79" t="inlineStr">
         <is>
           <t>D-103 (ИнвестХолдинг)</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="27" t="inlineStr">
         <is>
           <t>Просрочен счёт на оплату</t>
         </is>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="61" t="n">
         <v>150000</v>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="I10" s="27" t="inlineStr">
         <is>
           <t>Дожим счета через AI-бота + автозвонок</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>3. Встреча / Демо</t>
         </is>
@@ -5903,33 +5973,33 @@
       <c r="B11" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="28" t="n">
         <v>280000</v>
       </c>
       <c r="D11" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="79" t="inlineStr">
         <is>
           <t>D-109 (ПромКомплект)</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t>Критический брак речи (&lt;9)</t>
         </is>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="H11" s="61" t="n">
         <v>600000</v>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="27" t="inlineStr">
         <is>
           <t>Личный перезвон РОПа ЛПР до 12:00</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>4. КП и согласование</t>
         </is>
@@ -5937,33 +6007,33 @@
       <c r="B12" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="28" t="n">
         <v>3850000</v>
       </c>
       <c r="D12" s="26" t="n">
         <v>48</v>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="79" t="inlineStr">
         <is>
           <t>D-106 (СнабСервис)</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="27" t="inlineStr">
         <is>
           <t>Зависание на этапе КП</t>
         </is>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="61" t="n">
         <v>280000</v>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="I12" s="27" t="inlineStr">
         <is>
           <t>Эскалация РОПу, согласование слота</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>5. Счет выставлен</t>
         </is>
@@ -5971,33 +6041,33 @@
       <c r="B13" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="28" t="n">
         <v>330000</v>
       </c>
       <c r="D13" s="26" t="n">
         <v>72</v>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="79" t="inlineStr">
         <is>
           <t>D-107 (ТехноПром)</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="27" t="inlineStr">
         <is>
           <t>Крупная сделка без движения</t>
         </is>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="H13" s="61" t="n">
         <v>3000000</v>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="I13" s="27" t="inlineStr">
         <is>
           <t>Подключение генерального директора</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
+    <row r="14" ht="28" customHeight="1">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>6. Успешно реализовано</t>
         </is>
@@ -6005,29 +6075,46 @@
       <c r="B14" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="28" t="n">
         <v>1650000</v>
       </c>
       <c r="D14" s="26" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="94" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="93" t="inlineStr">
         <is>
           <t>🎯 ГЛАВНЫЙ ФОКУС РУКОВОДСТВА ДО КОНЦА МЕСЯЦА: Перехват сделки D-104 (850 000 ₽) и перераспределение 3 лидов с перегруженного РОПа на КАМов.</t>
         </is>
       </c>
+      <c r="B16" s="93" t="n"/>
+      <c r="C16" s="93" t="n"/>
+      <c r="D16" s="93" t="n"/>
+      <c r="E16" s="93" t="n"/>
+      <c r="F16" s="93" t="n"/>
+      <c r="G16" s="93" t="n"/>
+      <c r="H16" s="93" t="n"/>
+      <c r="I16" s="93" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="G2:H2"/>
     <mergeCell ref="F7:I7"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A7:D7"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H4:I4"/>
     <mergeCell ref="A16:I16"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6041,12 +6128,12 @@
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="54" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="56" customWidth="1" min="4" max="4"/>
     <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -6061,35 +6148,35 @@
       <c r="E1" s="2" t="n"/>
       <c r="F1" s="2" t="n"/>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>📄 1. One-Pager</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>⚡ 2. Пульс компании</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>📋 3. Пульт РОПа</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>💸 4. 7 Грехов ОП</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>🎯 5. Action Center</t>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>⚡ Экспресс-Калькулятор</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>📋 Пульт РОПа (15 мин)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>🎙️ ИИ-Аудит звонков</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>💸 7 Грехов (Диагностика)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>📄 Executive One-Pager</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>🎙️ 6. ИИ-Аудит</t>
+          <t>🔐 152-ФЗ Безопасность</t>
         </is>
       </c>
     </row>
@@ -6132,21 +6219,21 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="73" t="inlineStr">
         <is>
           <t>Локализация баз данных</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>Хранение ПДн граждан РФ строго на серверах в РФ</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>Дата-центры в Москве (Yandex Cloud / Selectel), аттестация ФСТЭК УЗ 1-2</t>
         </is>
@@ -6156,27 +6243,27 @@
           <t>✅ 100% Соответствие</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="F6" s="27" t="inlineStr">
         <is>
           <t>ст. 18.1 Федерального закона № 152-ФЗ</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="42" t="n">
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="73" t="inlineStr">
         <is>
           <t>Криптографическая токенизация</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>Запрет передачи персональных данных во внешние контуры</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>Модуль PIISanitizer: замена телефонов, ФИО и карт на токены [PHONE_TOKEN_X]</t>
         </is>
@@ -6186,27 +6273,27 @@
           <t>✅ Автоматически</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="F7" s="27" t="inlineStr">
         <is>
           <t>ст. 6 Федерального закона № 152-ФЗ</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="42" t="n">
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="73" t="inlineStr">
         <is>
           <t>Срок хранения аудиозаписей</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>Удаление данных после достижения цели обработки</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>Автоматическое безвозвратное удаление исходных аудио через 30 дней</t>
         </is>
@@ -6216,27 +6303,27 @@
           <t>✅ Настроено в cron</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F8" s="27" t="inlineStr">
         <is>
           <t>ст. 5 Федерального закона № 152-ФЗ</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="42" t="n">
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="73" t="inlineStr">
         <is>
           <t>Согласие сотрудников ОП</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Уведомление персонала о контроле качества переговоров</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D9" s="27" t="inlineStr">
         <is>
           <t>Готовый пакет документов: Приказ, Положение о контроле, Согласие</t>
         </is>
@@ -6246,27 +6333,27 @@
           <t>✅ Комплект включен</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
+      <c r="F9" s="27" t="inlineStr">
         <is>
           <t>ст. 86 Трудового Кодекса РФ</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="42" t="n">
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="73" t="inlineStr">
         <is>
           <t>Юридический статус исполнителя</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>Прозрачность расчетов с юридическими лицами</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>Плательщик НПД (Самозанятый), чек приложения «Мой Налог», договор, акт</t>
         </is>
@@ -6276,27 +6363,27 @@
           <t>✅ Безопасно для бухгалтерии</t>
         </is>
       </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="F10" s="27" t="inlineStr">
         <is>
           <t>ст. 15 Федерального закона № 422-ФЗ</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="42" t="n">
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="73" t="inlineStr">
         <is>
           <t>Гарантия конфиденциальности NDA</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t>Защита коммерческой тайны и клиентской базы компании</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>Подписание двустороннего соглашения о неразглашении конфиденциальных данных</t>
         </is>
@@ -6306,7 +6393,7 @@
           <t>✅ Подписание в ЭДО</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="F11" s="27" t="inlineStr">
         <is>
           <t>Федеральный закон № 98-ФЗ «О коммерческой тайне»</t>
         </is>
@@ -6317,6 +6404,14 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:F4"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/web/RevOps_Platform_Demo_Sample.xlsx
+++ b/web/RevOps_Platform_Demo_Sample.xlsx
@@ -304,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -448,6 +448,9 @@
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -519,6 +522,9 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -547,6 +553,12 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1632,7 +1644,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1">
+    <row r="9" ht="58" customHeight="1">
       <c r="A9" s="26" t="n">
         <v>1</v>
       </c>
@@ -1670,7 +1682,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1">
+    <row r="10" ht="58" customHeight="1">
       <c r="A10" s="26" t="n">
         <v>2</v>
       </c>
@@ -1708,7 +1720,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1">
+    <row r="11" ht="58" customHeight="1">
       <c r="A11" s="26" t="n">
         <v>3</v>
       </c>
@@ -1746,7 +1758,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1">
+    <row r="12" ht="58" customHeight="1">
       <c r="A12" s="26" t="n">
         <v>4</v>
       </c>
@@ -1784,7 +1796,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="48" customHeight="1">
+    <row r="13" ht="58" customHeight="1">
       <c r="A13" s="26" t="n">
         <v>5</v>
       </c>
@@ -1967,14 +1979,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
@@ -2189,48 +2201,48 @@
       <c r="U6" s="58" t="n"/>
       <c r="V6" s="58" t="n"/>
     </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="59" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
         <is>
           <t>Менеджер ОП</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="59" t="inlineStr">
         <is>
           <t>Звонков</t>
         </is>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="59" t="inlineStr">
         <is>
           <t>Ср. балл /13</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="59" t="inlineStr">
         <is>
           <t>Next Step %</t>
         </is>
       </c>
-      <c r="F7" s="25" t="inlineStr">
+      <c r="F7" s="59" t="inlineStr">
         <is>
           <t>Talk/Listen (норма ≥45%)</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="59" t="inlineStr">
         <is>
           <t>Зависших сделок</t>
         </is>
       </c>
-      <c r="H7" s="25" t="inlineStr">
+      <c r="H7" s="59" t="inlineStr">
         <is>
           <t>Сумма риска (₽)</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="59" t="inlineStr">
         <is>
           <t>Грейд ИИ</t>
         </is>
@@ -2265,7 +2277,7 @@
       <c r="C8" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="D8" s="59" t="n">
+      <c r="D8" s="60" t="n">
         <v>12.2</v>
       </c>
       <c r="E8" s="26" t="inlineStr">
@@ -2289,23 +2301,23 @@
           <t>⭐ А (Эталон)</t>
         </is>
       </c>
-      <c r="J8" s="60" t="inlineStr">
+      <c r="J8" s="61" t="inlineStr">
         <is>
           <t>Эталонный скрипт, рекомендован в базу знаний компании</t>
         </is>
       </c>
-      <c r="K8" s="60" t="n"/>
-      <c r="L8" s="60" t="n"/>
-      <c r="M8" s="60" t="n"/>
-      <c r="N8" s="60" t="n"/>
-      <c r="O8" s="60" t="n"/>
-      <c r="P8" s="60" t="n"/>
-      <c r="Q8" s="60" t="n"/>
-      <c r="R8" s="60" t="n"/>
-      <c r="S8" s="60" t="n"/>
-      <c r="T8" s="60" t="n"/>
-      <c r="U8" s="60" t="n"/>
-      <c r="V8" s="60" t="n"/>
+      <c r="K8" s="61" t="n"/>
+      <c r="L8" s="61" t="n"/>
+      <c r="M8" s="61" t="n"/>
+      <c r="N8" s="61" t="n"/>
+      <c r="O8" s="61" t="n"/>
+      <c r="P8" s="61" t="n"/>
+      <c r="Q8" s="61" t="n"/>
+      <c r="R8" s="61" t="n"/>
+      <c r="S8" s="61" t="n"/>
+      <c r="T8" s="61" t="n"/>
+      <c r="U8" s="61" t="n"/>
+      <c r="V8" s="61" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="26" t="n">
@@ -2319,7 +2331,7 @@
       <c r="C9" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="59" t="n">
+      <c r="D9" s="60" t="n">
         <v>10.8</v>
       </c>
       <c r="E9" s="26" t="inlineStr">
@@ -2335,7 +2347,7 @@
       <c r="G9" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="61" t="n">
+      <c r="H9" s="62" t="n">
         <v>160000</v>
       </c>
       <c r="I9" s="18" t="inlineStr">
@@ -2343,23 +2355,23 @@
           <t>🟢 B (Норма)</t>
         </is>
       </c>
-      <c r="J9" s="60" t="inlineStr">
+      <c r="J9" s="61" t="inlineStr">
         <is>
           <t>Высокая конверсия, мелкие замечания по регламенту встречи</t>
         </is>
       </c>
-      <c r="K9" s="60" t="n"/>
-      <c r="L9" s="60" t="n"/>
-      <c r="M9" s="60" t="n"/>
-      <c r="N9" s="60" t="n"/>
-      <c r="O9" s="60" t="n"/>
-      <c r="P9" s="60" t="n"/>
-      <c r="Q9" s="60" t="n"/>
-      <c r="R9" s="60" t="n"/>
-      <c r="S9" s="60" t="n"/>
-      <c r="T9" s="60" t="n"/>
-      <c r="U9" s="60" t="n"/>
-      <c r="V9" s="60" t="n"/>
+      <c r="K9" s="61" t="n"/>
+      <c r="L9" s="61" t="n"/>
+      <c r="M9" s="61" t="n"/>
+      <c r="N9" s="61" t="n"/>
+      <c r="O9" s="61" t="n"/>
+      <c r="P9" s="61" t="n"/>
+      <c r="Q9" s="61" t="n"/>
+      <c r="R9" s="61" t="n"/>
+      <c r="S9" s="61" t="n"/>
+      <c r="T9" s="61" t="n"/>
+      <c r="U9" s="61" t="n"/>
+      <c r="V9" s="61" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="26" t="n">
@@ -2373,7 +2385,7 @@
       <c r="C10" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="62" t="n">
+      <c r="D10" s="63" t="n">
         <v>8.4</v>
       </c>
       <c r="E10" s="26" t="inlineStr">
@@ -2389,7 +2401,7 @@
       <c r="G10" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="61" t="n">
+      <c r="H10" s="62" t="n">
         <v>480000</v>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -2397,23 +2409,23 @@
           <t>🟡 C (Зона риска)</t>
         </is>
       </c>
-      <c r="J10" s="60" t="inlineStr">
+      <c r="J10" s="61" t="inlineStr">
         <is>
           <t>Забывает фиксировать дату звонка, требуется тренинг</t>
         </is>
       </c>
-      <c r="K10" s="60" t="n"/>
-      <c r="L10" s="60" t="n"/>
-      <c r="M10" s="60" t="n"/>
-      <c r="N10" s="60" t="n"/>
-      <c r="O10" s="60" t="n"/>
-      <c r="P10" s="60" t="n"/>
-      <c r="Q10" s="60" t="n"/>
-      <c r="R10" s="60" t="n"/>
-      <c r="S10" s="60" t="n"/>
-      <c r="T10" s="60" t="n"/>
-      <c r="U10" s="60" t="n"/>
-      <c r="V10" s="60" t="n"/>
+      <c r="K10" s="61" t="n"/>
+      <c r="L10" s="61" t="n"/>
+      <c r="M10" s="61" t="n"/>
+      <c r="N10" s="61" t="n"/>
+      <c r="O10" s="61" t="n"/>
+      <c r="P10" s="61" t="n"/>
+      <c r="Q10" s="61" t="n"/>
+      <c r="R10" s="61" t="n"/>
+      <c r="S10" s="61" t="n"/>
+      <c r="T10" s="61" t="n"/>
+      <c r="U10" s="61" t="n"/>
+      <c r="V10" s="61" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="26" t="n">
@@ -2427,7 +2439,7 @@
       <c r="C11" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="63" t="n">
+      <c r="D11" s="64" t="n">
         <v>6.2</v>
       </c>
       <c r="E11" s="26" t="inlineStr">
@@ -2443,7 +2455,7 @@
       <c r="G11" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="61" t="n">
+      <c r="H11" s="62" t="n">
         <v>1100000</v>
       </c>
       <c r="I11" s="17" t="inlineStr">
@@ -2451,23 +2463,23 @@
           <t>🔴 D (Брак речи)</t>
         </is>
       </c>
-      <c r="J11" s="60" t="inlineStr">
+      <c r="J11" s="61" t="inlineStr">
         <is>
           <t>Срыв контакта, перебивание клиента, демпинг скидок</t>
         </is>
       </c>
-      <c r="K11" s="60" t="n"/>
-      <c r="L11" s="60" t="n"/>
-      <c r="M11" s="60" t="n"/>
-      <c r="N11" s="60" t="n"/>
-      <c r="O11" s="60" t="n"/>
-      <c r="P11" s="60" t="n"/>
-      <c r="Q11" s="60" t="n"/>
-      <c r="R11" s="60" t="n"/>
-      <c r="S11" s="60" t="n"/>
-      <c r="T11" s="60" t="n"/>
-      <c r="U11" s="60" t="n"/>
-      <c r="V11" s="60" t="n"/>
+      <c r="K11" s="61" t="n"/>
+      <c r="L11" s="61" t="n"/>
+      <c r="M11" s="61" t="n"/>
+      <c r="N11" s="61" t="n"/>
+      <c r="O11" s="61" t="n"/>
+      <c r="P11" s="61" t="n"/>
+      <c r="Q11" s="61" t="n"/>
+      <c r="R11" s="61" t="n"/>
+      <c r="S11" s="61" t="n"/>
+      <c r="T11" s="61" t="n"/>
+      <c r="U11" s="61" t="n"/>
+      <c r="V11" s="61" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="26" t="n">
@@ -2481,7 +2493,7 @@
       <c r="C12" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="63" t="n">
+      <c r="D12" s="64" t="n">
         <v>5.5</v>
       </c>
       <c r="E12" s="26" t="inlineStr">
@@ -2497,7 +2509,7 @@
       <c r="G12" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="61" t="n">
+      <c r="H12" s="62" t="n">
         <v>1100000</v>
       </c>
       <c r="I12" s="17" t="inlineStr">
@@ -2505,23 +2517,23 @@
           <t>🔴 D (Брак речи)</t>
         </is>
       </c>
-      <c r="J12" s="60" t="inlineStr">
+      <c r="J12" s="61" t="inlineStr">
         <is>
           <t>Режим 'автоответчика', нет попыток закрытия на встречу</t>
         </is>
       </c>
-      <c r="K12" s="60" t="n"/>
-      <c r="L12" s="60" t="n"/>
-      <c r="M12" s="60" t="n"/>
-      <c r="N12" s="60" t="n"/>
-      <c r="O12" s="60" t="n"/>
-      <c r="P12" s="60" t="n"/>
-      <c r="Q12" s="60" t="n"/>
-      <c r="R12" s="60" t="n"/>
-      <c r="S12" s="60" t="n"/>
-      <c r="T12" s="60" t="n"/>
-      <c r="U12" s="60" t="n"/>
-      <c r="V12" s="60" t="n"/>
+      <c r="K12" s="61" t="n"/>
+      <c r="L12" s="61" t="n"/>
+      <c r="M12" s="61" t="n"/>
+      <c r="N12" s="61" t="n"/>
+      <c r="O12" s="61" t="n"/>
+      <c r="P12" s="61" t="n"/>
+      <c r="Q12" s="61" t="n"/>
+      <c r="R12" s="61" t="n"/>
+      <c r="S12" s="61" t="n"/>
+      <c r="T12" s="61" t="n"/>
+      <c r="U12" s="61" t="n"/>
+      <c r="V12" s="61" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="29" t="inlineStr"/>
@@ -2530,26 +2542,26 @@
           <t>ИТОГО ПО ОТДЕЛУ ПРОДАЖ:</t>
         </is>
       </c>
-      <c r="C13" s="64">
+      <c r="C13" s="65">
         <f>SUM(C8:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="64" t="inlineStr">
+      <c r="D13" s="65" t="inlineStr">
         <is>
           <t>8.9 / 13</t>
         </is>
       </c>
-      <c r="E13" s="64" t="inlineStr">
+      <c r="E13" s="65" t="inlineStr">
         <is>
           <t>60.0%</t>
         </is>
       </c>
-      <c r="F13" s="64" t="inlineStr">
+      <c r="F13" s="65" t="inlineStr">
         <is>
           <t>61% / 39%</t>
         </is>
       </c>
-      <c r="G13" s="64">
+      <c r="G13" s="65">
         <f>SUM(G8:G12)</f>
         <v/>
       </c>
@@ -2557,28 +2569,28 @@
         <f>SUM(H8:H12)</f>
         <v/>
       </c>
-      <c r="I13" s="65" t="inlineStr">
+      <c r="I13" s="66" t="inlineStr">
         <is>
           <t>⚠️ РИСК</t>
         </is>
       </c>
-      <c r="J13" s="66" t="inlineStr">
+      <c r="J13" s="67" t="inlineStr">
         <is>
           <t>Требуется экспресс-коучинг по отработке возражений</t>
         </is>
       </c>
-      <c r="K13" s="66" t="n"/>
-      <c r="L13" s="66" t="n"/>
-      <c r="M13" s="66" t="n"/>
-      <c r="N13" s="66" t="n"/>
-      <c r="O13" s="66" t="n"/>
-      <c r="P13" s="66" t="n"/>
-      <c r="Q13" s="66" t="n"/>
-      <c r="R13" s="66" t="n"/>
-      <c r="S13" s="66" t="n"/>
-      <c r="T13" s="66" t="n"/>
-      <c r="U13" s="66" t="n"/>
-      <c r="V13" s="66" t="n"/>
+      <c r="K13" s="67" t="n"/>
+      <c r="L13" s="67" t="n"/>
+      <c r="M13" s="67" t="n"/>
+      <c r="N13" s="67" t="n"/>
+      <c r="O13" s="67" t="n"/>
+      <c r="P13" s="67" t="n"/>
+      <c r="Q13" s="67" t="n"/>
+      <c r="R13" s="67" t="n"/>
+      <c r="S13" s="67" t="n"/>
+      <c r="T13" s="67" t="n"/>
+      <c r="U13" s="67" t="n"/>
+      <c r="V13" s="67" t="n"/>
     </row>
     <row r="14" ht="12" customHeight="1"/>
     <row r="15" ht="24" customHeight="1">
@@ -2609,113 +2621,113 @@
       <c r="U15" s="58" t="n"/>
       <c r="V15" s="58" t="n"/>
     </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="25" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="59" t="inlineStr">
         <is>
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="59" t="inlineStr">
         <is>
           <t>Сделка / Клиент</t>
         </is>
       </c>
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="59" t="inlineStr">
         <is>
           <t>Менеджер</t>
         </is>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="59" t="inlineStr">
         <is>
           <t>Сумма (₽)</t>
         </is>
       </c>
-      <c r="E16" s="25" t="inlineStr">
+      <c r="E16" s="59" t="inlineStr">
         <is>
           <t>Длит.</t>
         </is>
       </c>
-      <c r="F16" s="25" t="inlineStr">
+      <c r="F16" s="59" t="inlineStr">
         <is>
           <t>Этап CRM</t>
         </is>
       </c>
-      <c r="G16" s="25" t="inlineStr">
+      <c r="G16" s="59" t="inlineStr">
         <is>
           <t>К1 NextStep</t>
         </is>
       </c>
-      <c r="H16" s="25" t="inlineStr">
+      <c r="H16" s="59" t="inlineStr">
         <is>
           <t>К2 Иниц.</t>
         </is>
       </c>
-      <c r="I16" s="25" t="inlineStr">
+      <c r="I16" s="59" t="inlineStr">
         <is>
           <t>К3 ЛПР</t>
         </is>
       </c>
-      <c r="J16" s="25" t="inlineStr">
+      <c r="J16" s="59" t="inlineStr">
         <is>
           <t>К4 Боли</t>
         </is>
       </c>
-      <c r="K16" s="25" t="inlineStr">
+      <c r="K16" s="59" t="inlineStr">
         <is>
           <t>К5 Дорого</t>
         </is>
       </c>
-      <c r="L16" s="25" t="inlineStr">
+      <c r="L16" s="59" t="inlineStr">
         <is>
           <t>К6 Подумаю</t>
         </is>
       </c>
-      <c r="M16" s="25" t="inlineStr">
+      <c r="M16" s="59" t="inlineStr">
         <is>
           <t>К7 Кейсы</t>
         </is>
       </c>
-      <c r="N16" s="25" t="inlineStr">
+      <c r="N16" s="59" t="inlineStr">
         <is>
           <t>К8 Закрытие</t>
         </is>
       </c>
-      <c r="O16" s="25" t="inlineStr">
+      <c r="O16" s="59" t="inlineStr">
         <is>
           <t>К9 Привет.</t>
         </is>
       </c>
-      <c r="P16" s="25" t="inlineStr">
+      <c r="P16" s="59" t="inlineStr">
         <is>
           <t>К10 Речь</t>
         </is>
       </c>
-      <c r="Q16" s="25" t="inlineStr">
+      <c r="Q16" s="59" t="inlineStr">
         <is>
           <t>К11 Слушан.</t>
         </is>
       </c>
-      <c r="R16" s="25" t="inlineStr">
+      <c r="R16" s="59" t="inlineStr">
         <is>
           <t>К12 Итог</t>
         </is>
       </c>
-      <c r="S16" s="25" t="inlineStr">
+      <c r="S16" s="59" t="inlineStr">
         <is>
           <t>К13 Маржа</t>
         </is>
       </c>
-      <c r="T16" s="25" t="inlineStr">
+      <c r="T16" s="59" t="inlineStr">
         <is>
           <t>Балл /13</t>
         </is>
       </c>
-      <c r="U16" s="25" t="inlineStr">
+      <c r="U16" s="59" t="inlineStr">
         <is>
           <t>Статус ИИ</t>
         </is>
       </c>
-      <c r="V16" s="25" t="inlineStr">
+      <c r="V16" s="59" t="inlineStr">
         <is>
           <t>Сумма в риске, ₽</t>
         </is>
@@ -2727,7 +2739,7 @@
           <t>C-501</t>
         </is>
       </c>
-      <c r="B17" s="60" t="inlineStr">
+      <c r="B17" s="61" t="inlineStr">
         <is>
           <t>D-101 (ООО Вектор Плюс)</t>
         </is>
@@ -2737,7 +2749,7 @@
           <t>Мельников</t>
         </is>
       </c>
-      <c r="D17" s="67" t="n">
+      <c r="D17" s="68" t="n">
         <v>850000</v>
       </c>
       <c r="E17" s="26" t="inlineStr">
@@ -2750,46 +2762,46 @@
           <t>КП отправлено</t>
         </is>
       </c>
-      <c r="G17" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="R17" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="T17" s="59">
+      <c r="G17" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T17" s="60">
         <f>SUM(G17:S17)</f>
         <v/>
       </c>
@@ -2808,7 +2820,7 @@
           <t>C-502</t>
         </is>
       </c>
-      <c r="B18" s="60" t="inlineStr">
+      <c r="B18" s="61" t="inlineStr">
         <is>
           <t>D-104 (ООО Вектор Плюс)</t>
         </is>
@@ -2818,7 +2830,7 @@
           <t>Васильева</t>
         </is>
       </c>
-      <c r="D18" s="67" t="n">
+      <c r="D18" s="68" t="n">
         <v>850000</v>
       </c>
       <c r="E18" s="26" t="inlineStr">
@@ -2831,46 +2843,46 @@
           <t>Переговоры</t>
         </is>
       </c>
-      <c r="G18" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" s="69" t="n">
+      <c r="G18" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="O18" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="P18" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="R18" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="S18" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="T18" s="59">
+      <c r="M18" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" s="60">
         <f>SUM(G18:S18)</f>
         <v/>
       </c>
@@ -2889,7 +2901,7 @@
           <t>C-503</t>
         </is>
       </c>
-      <c r="B19" s="60" t="inlineStr">
+      <c r="B19" s="61" t="inlineStr">
         <is>
           <t>D-106 (ООО СнабСервис)</t>
         </is>
@@ -2899,7 +2911,7 @@
           <t>Соколова</t>
         </is>
       </c>
-      <c r="D19" s="67" t="n">
+      <c r="D19" s="68" t="n">
         <v>280000</v>
       </c>
       <c r="E19" s="26" t="inlineStr">
@@ -2912,46 +2924,46 @@
           <t>Встреча/Демо</t>
         </is>
       </c>
-      <c r="G19" s="69" t="n">
+      <c r="G19" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="69" t="n">
+      <c r="H19" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" s="69" t="n">
+      <c r="K19" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" s="69" t="n">
+      <c r="M19" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="O19" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" s="69" t="n">
+      <c r="O19" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="R19" s="69" t="n">
+      <c r="Q19" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="S19" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="T19" s="63">
+      <c r="S19" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" s="64">
         <f>SUM(G19:S19)</f>
         <v/>
       </c>
@@ -2960,7 +2972,7 @@
           <t>⚠️ РИСК</t>
         </is>
       </c>
-      <c r="V19" s="61" t="n">
+      <c r="V19" s="62" t="n">
         <v>280000</v>
       </c>
     </row>
@@ -2970,7 +2982,7 @@
           <t>C-504</t>
         </is>
       </c>
-      <c r="B20" s="60" t="inlineStr">
+      <c r="B20" s="61" t="inlineStr">
         <is>
           <t>D-107 (ООО ТехноПром)</t>
         </is>
@@ -2980,7 +2992,7 @@
           <t>Соколова</t>
         </is>
       </c>
-      <c r="D20" s="67" t="n">
+      <c r="D20" s="68" t="n">
         <v>150000</v>
       </c>
       <c r="E20" s="26" t="inlineStr">
@@ -2993,46 +3005,46 @@
           <t>Квалификация</t>
         </is>
       </c>
-      <c r="G20" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="69" t="n">
+      <c r="G20" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" s="69" t="n">
+      <c r="K20" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="N20" s="69" t="n">
+      <c r="N20" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="O20" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="P20" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q20" s="69" t="n">
+      <c r="O20" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="R20" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="T20" s="62">
+      <c r="R20" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S20" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="63">
         <f>SUM(G20:S20)</f>
         <v/>
       </c>
@@ -3041,7 +3053,7 @@
           <t>⚠️ РИСК</t>
         </is>
       </c>
-      <c r="V20" s="61" t="n">
+      <c r="V20" s="62" t="n">
         <v>150000</v>
       </c>
     </row>
@@ -3051,7 +3063,7 @@
           <t>C-505</t>
         </is>
       </c>
-      <c r="B21" s="60" t="inlineStr">
+      <c r="B21" s="61" t="inlineStr">
         <is>
           <t>D-109 (ООО ПромКомплект)</t>
         </is>
@@ -3061,7 +3073,7 @@
           <t>Ковалев</t>
         </is>
       </c>
-      <c r="D21" s="67" t="n">
+      <c r="D21" s="68" t="n">
         <v>600000</v>
       </c>
       <c r="E21" s="26" t="inlineStr">
@@ -3074,46 +3086,46 @@
           <t>КП отправлено</t>
         </is>
       </c>
-      <c r="G21" s="69" t="n">
+      <c r="G21" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="69" t="n">
+      <c r="H21" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="69" t="n">
+      <c r="I21" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="69" t="n">
+      <c r="J21" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="69" t="n">
+      <c r="K21" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="69" t="n">
+      <c r="L21" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="M21" s="69" t="n">
+      <c r="M21" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="N21" s="69" t="n">
+      <c r="N21" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="P21" s="69" t="n">
+      <c r="O21" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" s="69" t="n">
+      <c r="Q21" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="R21" s="69" t="n">
+      <c r="R21" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="S21" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="T21" s="63">
+      <c r="S21" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" s="64">
         <f>SUM(G21:S21)</f>
         <v/>
       </c>
@@ -3122,7 +3134,7 @@
           <t>❌ СЛИВ</t>
         </is>
       </c>
-      <c r="V21" s="61" t="n">
+      <c r="V21" s="62" t="n">
         <v>600000</v>
       </c>
     </row>
@@ -3132,7 +3144,7 @@
           <t>C-506</t>
         </is>
       </c>
-      <c r="B22" s="60" t="inlineStr">
+      <c r="B22" s="61" t="inlineStr">
         <is>
           <t>D-111 (ООО Глобал Инвест)</t>
         </is>
@@ -3142,7 +3154,7 @@
           <t>Мельников</t>
         </is>
       </c>
-      <c r="D22" s="67" t="n">
+      <c r="D22" s="68" t="n">
         <v>3000000</v>
       </c>
       <c r="E22" s="26" t="inlineStr">
@@ -3155,46 +3167,46 @@
           <t>Финальные условия</t>
         </is>
       </c>
-      <c r="G22" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="P22" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q22" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="T22" s="59">
+      <c r="G22" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="60">
         <f>SUM(G22:S22)</f>
         <v/>
       </c>
@@ -3213,7 +3225,7 @@
           <t>C-507</t>
         </is>
       </c>
-      <c r="B23" s="60" t="inlineStr">
+      <c r="B23" s="61" t="inlineStr">
         <is>
           <t>D-114 (ООО АльфаТрейд)</t>
         </is>
@@ -3223,7 +3235,7 @@
           <t>Ковалев</t>
         </is>
       </c>
-      <c r="D23" s="67" t="n">
+      <c r="D23" s="68" t="n">
         <v>500000</v>
       </c>
       <c r="E23" s="26" t="inlineStr">
@@ -3236,46 +3248,46 @@
           <t>Дожим договора</t>
         </is>
       </c>
-      <c r="G23" s="69" t="n">
+      <c r="G23" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="69" t="n">
+      <c r="H23" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="K23" s="69" t="n">
+      <c r="K23" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="L23" s="69" t="n">
+      <c r="L23" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" s="69" t="n">
+      <c r="M23" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="O23" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="P23" s="69" t="n">
+      <c r="O23" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" s="69" t="n">
+      <c r="Q23" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="R23" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" s="69" t="n">
+      <c r="R23" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S23" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="T23" s="63">
+      <c r="T23" s="64">
         <f>SUM(G23:S23)</f>
         <v/>
       </c>
@@ -3284,7 +3296,7 @@
           <t>❌ СЛИВ</t>
         </is>
       </c>
-      <c r="V23" s="61" t="n">
+      <c r="V23" s="62" t="n">
         <v>500000</v>
       </c>
     </row>
@@ -3294,7 +3306,7 @@
           <t>C-508</t>
         </is>
       </c>
-      <c r="B24" s="60" t="inlineStr">
+      <c r="B24" s="61" t="inlineStr">
         <is>
           <t>D-118 (ООО СтройХолдинг)</t>
         </is>
@@ -3304,7 +3316,7 @@
           <t>Попов</t>
         </is>
       </c>
-      <c r="D24" s="67" t="n">
+      <c r="D24" s="68" t="n">
         <v>650000</v>
       </c>
       <c r="E24" s="26" t="inlineStr">
@@ -3317,46 +3329,46 @@
           <t>Входящий лид</t>
         </is>
       </c>
-      <c r="G24" s="69" t="n">
+      <c r="G24" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="H24" s="69" t="n">
+      <c r="H24" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="69" t="n">
+      <c r="I24" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="K24" s="69" t="n">
+      <c r="K24" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="L24" s="69" t="n">
+      <c r="L24" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="69" t="n">
+      <c r="M24" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="N24" s="69" t="n">
+      <c r="N24" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="O24" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="69" t="n">
+      <c r="O24" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="R24" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" s="69" t="n">
+      <c r="R24" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="T24" s="63">
+      <c r="T24" s="64">
         <f>SUM(G24:S24)</f>
         <v/>
       </c>
@@ -3365,7 +3377,7 @@
           <t>❌ СЛИВ</t>
         </is>
       </c>
-      <c r="V24" s="61" t="n">
+      <c r="V24" s="62" t="n">
         <v>650000</v>
       </c>
     </row>
@@ -3375,7 +3387,7 @@
           <t>C-509</t>
         </is>
       </c>
-      <c r="B25" s="60" t="inlineStr">
+      <c r="B25" s="61" t="inlineStr">
         <is>
           <t>D-121 (ООО СпецМаш)</t>
         </is>
@@ -3385,7 +3397,7 @@
           <t>Васильева</t>
         </is>
       </c>
-      <c r="D25" s="67" t="n">
+      <c r="D25" s="68" t="n">
         <v>420000</v>
       </c>
       <c r="E25" s="26" t="inlineStr">
@@ -3398,46 +3410,46 @@
           <t>Презентация КП</t>
         </is>
       </c>
-      <c r="G25" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" s="69" t="n">
+      <c r="G25" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="N25" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="O25" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q25" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="R25" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="T25" s="59">
+      <c r="O25" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S25" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" s="60">
         <f>SUM(G25:S25)</f>
         <v/>
       </c>
@@ -3456,7 +3468,7 @@
           <t>C-510</t>
         </is>
       </c>
-      <c r="B26" s="60" t="inlineStr">
+      <c r="B26" s="61" t="inlineStr">
         <is>
           <t>D-125 (ООО МегаТранс)</t>
         </is>
@@ -3466,7 +3478,7 @@
           <t>Попов</t>
         </is>
       </c>
-      <c r="D26" s="67" t="n">
+      <c r="D26" s="68" t="n">
         <v>450000</v>
       </c>
       <c r="E26" s="26" t="inlineStr">
@@ -3479,46 +3491,46 @@
           <t>Квалификация</t>
         </is>
       </c>
-      <c r="G26" s="69" t="n">
+      <c r="G26" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="69" t="n">
+      <c r="H26" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="69" t="n">
+      <c r="I26" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="L26" s="69" t="n">
+      <c r="J26" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" s="69" t="n">
+      <c r="M26" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="O26" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="P26" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" s="69" t="n">
+      <c r="O26" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="R26" s="68" t="n">
-        <v>1</v>
-      </c>
-      <c r="S26" s="69" t="n">
+      <c r="R26" s="69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S26" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="T26" s="63">
+      <c r="T26" s="64">
         <f>SUM(G26:S26)</f>
         <v/>
       </c>
@@ -3527,19 +3539,19 @@
           <t>⚠️ РИСК</t>
         </is>
       </c>
-      <c r="V26" s="61" t="n">
+      <c r="V26" s="62" t="n">
         <v>450000</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="29" t="inlineStr"/>
-      <c r="B27" s="30" t="inlineStr">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>ИТОГО ПОТЕРЬ И РИСКОВ ПО ЗВОНКАМ:</t>
         </is>
       </c>
-      <c r="C27" s="29" t="inlineStr"/>
-      <c r="D27" s="70">
+      <c r="B27" s="30" t="n"/>
+      <c r="C27" s="30" t="n"/>
+      <c r="D27" s="71">
         <f>SUM(D17:D26)</f>
         <v/>
       </c>
@@ -3558,11 +3570,11 @@
       <c r="Q27" s="29" t="inlineStr"/>
       <c r="R27" s="29" t="inlineStr"/>
       <c r="S27" s="29" t="inlineStr"/>
-      <c r="T27" s="71">
+      <c r="T27" s="72">
         <f>AVERAGE(T17:T26)</f>
         <v/>
       </c>
-      <c r="U27" s="72" t="inlineStr">
+      <c r="U27" s="73" t="inlineStr">
         <is>
           <t>6 сливов</t>
         </is>
@@ -3659,7 +3671,7 @@
           <t>C-505</t>
         </is>
       </c>
-      <c r="B31" s="73" t="inlineStr">
+      <c r="B31" s="74" t="inlineStr">
         <is>
           <t>D-109 (ООО «ПромКомплект»)</t>
         </is>
@@ -3669,39 +3681,39 @@
           <t>Дмитрий Ковалев</t>
         </is>
       </c>
-      <c r="D31" s="61" t="n">
+      <c r="D31" s="62" t="n">
         <v>600000</v>
       </c>
-      <c r="E31" s="74" t="inlineStr">
+      <c r="E31" s="75" t="inlineStr">
         <is>
           <t>Срыв контакта / грубость при цене</t>
         </is>
       </c>
-      <c r="F31" s="74" t="n"/>
-      <c r="G31" s="75" t="inlineStr">
+      <c r="F31" s="75" t="n"/>
+      <c r="G31" s="76" t="inlineStr">
         <is>
           <t>Клиент: «Почему у вас смета на 15% выше рынка?» → Менеджер: «Не знаю, везде всё дорожает. Не устраивает — берите у конкурентов без гарантии»</t>
         </is>
       </c>
-      <c r="H31" s="75" t="n"/>
-      <c r="I31" s="75" t="n"/>
-      <c r="J31" s="75" t="n"/>
-      <c r="K31" s="75" t="n"/>
-      <c r="L31" s="75" t="n"/>
-      <c r="M31" s="75" t="n"/>
-      <c r="N31" s="76" t="inlineStr">
+      <c r="H31" s="76" t="n"/>
+      <c r="I31" s="76" t="n"/>
+      <c r="J31" s="76" t="n"/>
+      <c r="K31" s="76" t="n"/>
+      <c r="L31" s="76" t="n"/>
+      <c r="M31" s="76" t="n"/>
+      <c r="N31" s="77" t="inlineStr">
         <is>
           <t>🚨 Экстренный звонок РОПа ЛПР до 12:00: принести извинения за консультацию, перехватить сделку, дать проект со спец-гарантией 24 мес.</t>
         </is>
       </c>
-      <c r="O31" s="76" t="n"/>
-      <c r="P31" s="76" t="n"/>
-      <c r="Q31" s="76" t="n"/>
-      <c r="R31" s="76" t="n"/>
-      <c r="S31" s="76" t="n"/>
-      <c r="T31" s="76" t="n"/>
-      <c r="U31" s="76" t="n"/>
-      <c r="V31" s="76" t="n"/>
+      <c r="O31" s="77" t="n"/>
+      <c r="P31" s="77" t="n"/>
+      <c r="Q31" s="77" t="n"/>
+      <c r="R31" s="77" t="n"/>
+      <c r="S31" s="77" t="n"/>
+      <c r="T31" s="77" t="n"/>
+      <c r="U31" s="77" t="n"/>
+      <c r="V31" s="77" t="n"/>
     </row>
     <row r="32" ht="54" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
@@ -3709,7 +3721,7 @@
           <t>C-503</t>
         </is>
       </c>
-      <c r="B32" s="73" t="inlineStr">
+      <c r="B32" s="74" t="inlineStr">
         <is>
           <t>D-106 (ООО «СнабСервис»)</t>
         </is>
@@ -3719,39 +3731,39 @@
           <t>Анна Соколова</t>
         </is>
       </c>
-      <c r="D32" s="61" t="n">
+      <c r="D32" s="62" t="n">
         <v>280000</v>
       </c>
-      <c r="E32" s="74" t="inlineStr">
+      <c r="E32" s="75" t="inlineStr">
         <is>
           <t>Слив жесткого Next Step (в никуда)</t>
         </is>
       </c>
-      <c r="F32" s="74" t="n"/>
-      <c r="G32" s="75" t="inlineStr">
+      <c r="F32" s="75" t="n"/>
+      <c r="G32" s="76" t="inlineStr">
         <is>
           <t>Менеджер: «Я вам КП на почту сбросила, посмотрите когда время будет». Клиент: «Хорошо, если что наберу»</t>
         </is>
       </c>
-      <c r="H32" s="75" t="n"/>
-      <c r="I32" s="75" t="n"/>
-      <c r="J32" s="75" t="n"/>
-      <c r="K32" s="75" t="n"/>
-      <c r="L32" s="75" t="n"/>
-      <c r="M32" s="75" t="n"/>
-      <c r="N32" s="76" t="inlineStr">
+      <c r="H32" s="76" t="n"/>
+      <c r="I32" s="76" t="n"/>
+      <c r="J32" s="76" t="n"/>
+      <c r="K32" s="76" t="n"/>
+      <c r="L32" s="76" t="n"/>
+      <c r="M32" s="76" t="n"/>
+      <c r="N32" s="77" t="inlineStr">
         <is>
           <t>Направить клиенту в WhatsApp 2 конкретных слота встречи (сегодня 16:00 / завтра 11:30) с демонстрацией интеграции с CRM.</t>
         </is>
       </c>
-      <c r="O32" s="76" t="n"/>
-      <c r="P32" s="76" t="n"/>
-      <c r="Q32" s="76" t="n"/>
-      <c r="R32" s="76" t="n"/>
-      <c r="S32" s="76" t="n"/>
-      <c r="T32" s="76" t="n"/>
-      <c r="U32" s="76" t="n"/>
-      <c r="V32" s="76" t="n"/>
+      <c r="O32" s="77" t="n"/>
+      <c r="P32" s="77" t="n"/>
+      <c r="Q32" s="77" t="n"/>
+      <c r="R32" s="77" t="n"/>
+      <c r="S32" s="77" t="n"/>
+      <c r="T32" s="77" t="n"/>
+      <c r="U32" s="77" t="n"/>
+      <c r="V32" s="77" t="n"/>
     </row>
     <row r="33" ht="54" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
@@ -3759,7 +3771,7 @@
           <t>C-507</t>
         </is>
       </c>
-      <c r="B33" s="73" t="inlineStr">
+      <c r="B33" s="74" t="inlineStr">
         <is>
           <t>D-114 (ООО «АльфаТрейд»)</t>
         </is>
@@ -3769,39 +3781,39 @@
           <t>Дмитрий Ковалев</t>
         </is>
       </c>
-      <c r="D33" s="61" t="n">
+      <c r="D33" s="62" t="n">
         <v>500000</v>
       </c>
-      <c r="E33" s="74" t="inlineStr">
+      <c r="E33" s="75" t="inlineStr">
         <is>
           <t>Необоснованная скидка вместо ценности</t>
         </is>
       </c>
-      <c r="F33" s="74" t="n"/>
-      <c r="G33" s="75" t="inlineStr">
+      <c r="F33" s="75" t="n"/>
+      <c r="G33" s="76" t="inlineStr">
         <is>
           <t>Клиент: «У нас бюджет строго ограничен». Менеджер: «Ну ладно, согласую вам скидку 10% прямо сейчас»</t>
         </is>
       </c>
-      <c r="H33" s="75" t="n"/>
-      <c r="I33" s="75" t="n"/>
-      <c r="J33" s="75" t="n"/>
-      <c r="K33" s="75" t="n"/>
-      <c r="L33" s="75" t="n"/>
-      <c r="M33" s="75" t="n"/>
-      <c r="N33" s="76" t="inlineStr">
+      <c r="H33" s="76" t="n"/>
+      <c r="I33" s="76" t="n"/>
+      <c r="J33" s="76" t="n"/>
+      <c r="K33" s="76" t="n"/>
+      <c r="L33" s="76" t="n"/>
+      <c r="M33" s="76" t="n"/>
+      <c r="N33" s="77" t="inlineStr">
         <is>
           <t>Заблокировать выставление счета со скидкой в CRM. РОПу пересогласовать условия: скидка 5% только в обмен на 100% предоплату за 24ч.</t>
         </is>
       </c>
-      <c r="O33" s="76" t="n"/>
-      <c r="P33" s="76" t="n"/>
-      <c r="Q33" s="76" t="n"/>
-      <c r="R33" s="76" t="n"/>
-      <c r="S33" s="76" t="n"/>
-      <c r="T33" s="76" t="n"/>
-      <c r="U33" s="76" t="n"/>
-      <c r="V33" s="76" t="n"/>
+      <c r="O33" s="77" t="n"/>
+      <c r="P33" s="77" t="n"/>
+      <c r="Q33" s="77" t="n"/>
+      <c r="R33" s="77" t="n"/>
+      <c r="S33" s="77" t="n"/>
+      <c r="T33" s="77" t="n"/>
+      <c r="U33" s="77" t="n"/>
+      <c r="V33" s="77" t="n"/>
     </row>
     <row r="34" ht="54" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
@@ -3809,7 +3821,7 @@
           <t>C-508</t>
         </is>
       </c>
-      <c r="B34" s="73" t="inlineStr">
+      <c r="B34" s="74" t="inlineStr">
         <is>
           <t>D-118 (ООО «СтройХолдинг»)</t>
         </is>
@@ -3819,39 +3831,39 @@
           <t>Иван Попов</t>
         </is>
       </c>
-      <c r="D34" s="61" t="n">
+      <c r="D34" s="62" t="n">
         <v>650000</v>
       </c>
-      <c r="E34" s="74" t="inlineStr">
+      <c r="E34" s="75" t="inlineStr">
         <is>
           <t>Слив возражения «Я подумаю»</t>
         </is>
       </c>
-      <c r="F34" s="74" t="n"/>
-      <c r="G34" s="75" t="inlineStr">
+      <c r="F34" s="75" t="n"/>
+      <c r="G34" s="76" t="inlineStr">
         <is>
           <t>Клиент: «Нам нужно всё обдумать и посоветоваться с руководством». Менеджер: «Да, конечно, думайте» (повесил трубку)</t>
         </is>
       </c>
-      <c r="H34" s="75" t="n"/>
-      <c r="I34" s="75" t="n"/>
-      <c r="J34" s="75" t="n"/>
-      <c r="K34" s="75" t="n"/>
-      <c r="L34" s="75" t="n"/>
-      <c r="M34" s="75" t="n"/>
-      <c r="N34" s="76" t="inlineStr">
+      <c r="H34" s="76" t="n"/>
+      <c r="I34" s="76" t="n"/>
+      <c r="J34" s="76" t="n"/>
+      <c r="K34" s="76" t="n"/>
+      <c r="L34" s="76" t="n"/>
+      <c r="M34" s="76" t="n"/>
+      <c r="N34" s="77" t="inlineStr">
         <is>
           <t>Передать лида старшему КАМу. Отправить в WhatsApp отраслевой кейс с аналогичным объектом и окупаемостью за 21 день.</t>
         </is>
       </c>
-      <c r="O34" s="76" t="n"/>
-      <c r="P34" s="76" t="n"/>
-      <c r="Q34" s="76" t="n"/>
-      <c r="R34" s="76" t="n"/>
-      <c r="S34" s="76" t="n"/>
-      <c r="T34" s="76" t="n"/>
-      <c r="U34" s="76" t="n"/>
-      <c r="V34" s="76" t="n"/>
+      <c r="O34" s="77" t="n"/>
+      <c r="P34" s="77" t="n"/>
+      <c r="Q34" s="77" t="n"/>
+      <c r="R34" s="77" t="n"/>
+      <c r="S34" s="77" t="n"/>
+      <c r="T34" s="77" t="n"/>
+      <c r="U34" s="77" t="n"/>
+      <c r="V34" s="77" t="n"/>
     </row>
     <row r="35" ht="54" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
@@ -3859,7 +3871,7 @@
           <t>C-510</t>
         </is>
       </c>
-      <c r="B35" s="73" t="inlineStr">
+      <c r="B35" s="74" t="inlineStr">
         <is>
           <t>D-125 (ООО «МегаТранс»)</t>
         </is>
@@ -3869,39 +3881,39 @@
           <t>Иван Попов</t>
         </is>
       </c>
-      <c r="D35" s="61" t="n">
+      <c r="D35" s="62" t="n">
         <v>450000</v>
       </c>
-      <c r="E35" s="74" t="inlineStr">
+      <c r="E35" s="75" t="inlineStr">
         <is>
           <t>Режим автоответчика, не выявлен ЛПР</t>
         </is>
       </c>
-      <c r="F35" s="74" t="n"/>
-      <c r="G35" s="75" t="inlineStr">
+      <c r="F35" s="75" t="n"/>
+      <c r="G35" s="76" t="inlineStr">
         <is>
           <t>Менеджер 5 минут зачитывал прайс-лист секретарю, не спросив, кто принимает решение по закупкам</t>
         </is>
       </c>
-      <c r="H35" s="75" t="n"/>
-      <c r="I35" s="75" t="n"/>
-      <c r="J35" s="75" t="n"/>
-      <c r="K35" s="75" t="n"/>
-      <c r="L35" s="75" t="n"/>
-      <c r="M35" s="75" t="n"/>
-      <c r="N35" s="76" t="inlineStr">
+      <c r="H35" s="76" t="n"/>
+      <c r="I35" s="76" t="n"/>
+      <c r="J35" s="76" t="n"/>
+      <c r="K35" s="76" t="n"/>
+      <c r="L35" s="76" t="n"/>
+      <c r="M35" s="76" t="n"/>
+      <c r="N35" s="77" t="inlineStr">
         <is>
           <t>Разбор на летучке: регламент квалификации BANT. Назначить повторный звонок с прямым выходом на генерального директора.</t>
         </is>
       </c>
-      <c r="O35" s="76" t="n"/>
-      <c r="P35" s="76" t="n"/>
-      <c r="Q35" s="76" t="n"/>
-      <c r="R35" s="76" t="n"/>
-      <c r="S35" s="76" t="n"/>
-      <c r="T35" s="76" t="n"/>
-      <c r="U35" s="76" t="n"/>
-      <c r="V35" s="76" t="n"/>
+      <c r="O35" s="77" t="n"/>
+      <c r="P35" s="77" t="n"/>
+      <c r="Q35" s="77" t="n"/>
+      <c r="R35" s="77" t="n"/>
+      <c r="S35" s="77" t="n"/>
+      <c r="T35" s="77" t="n"/>
+      <c r="U35" s="77" t="n"/>
+      <c r="V35" s="77" t="n"/>
     </row>
     <row r="36" ht="12" customHeight="1"/>
     <row r="37" ht="24" customHeight="1">
@@ -4010,29 +4022,29 @@
       </c>
       <c r="F39" s="27" t="n"/>
       <c r="G39" s="27" t="n"/>
-      <c r="H39" s="77" t="inlineStr">
+      <c r="H39" s="78" t="inlineStr">
         <is>
           <t>«Я вам перезвоню на днях», «Подумайте, наберите», отпускание без времени</t>
         </is>
       </c>
-      <c r="I39" s="77" t="n"/>
-      <c r="J39" s="77" t="n"/>
-      <c r="K39" s="77" t="n"/>
-      <c r="L39" s="77" t="n"/>
-      <c r="M39" s="73" t="inlineStr">
+      <c r="I39" s="78" t="n"/>
+      <c r="J39" s="78" t="n"/>
+      <c r="K39" s="78" t="n"/>
+      <c r="L39" s="78" t="n"/>
+      <c r="M39" s="74" t="inlineStr">
         <is>
           <t>Внедрить обязательный вопрос в конце диалога: «Во вторник в 14:30 или в среду в 11:00 удобно?»</t>
         </is>
       </c>
-      <c r="N39" s="73" t="n"/>
-      <c r="O39" s="73" t="n"/>
-      <c r="P39" s="73" t="n"/>
-      <c r="Q39" s="73" t="n"/>
-      <c r="R39" s="73" t="n"/>
-      <c r="S39" s="73" t="n"/>
-      <c r="T39" s="73" t="n"/>
-      <c r="U39" s="73" t="n"/>
-      <c r="V39" s="73" t="n"/>
+      <c r="N39" s="74" t="n"/>
+      <c r="O39" s="74" t="n"/>
+      <c r="P39" s="74" t="n"/>
+      <c r="Q39" s="74" t="n"/>
+      <c r="R39" s="74" t="n"/>
+      <c r="S39" s="74" t="n"/>
+      <c r="T39" s="74" t="n"/>
+      <c r="U39" s="74" t="n"/>
+      <c r="V39" s="74" t="n"/>
     </row>
     <row r="40" ht="34" customHeight="1">
       <c r="A40" s="26" t="n">
@@ -4060,29 +4072,29 @@
       </c>
       <c r="F40" s="27" t="n"/>
       <c r="G40" s="27" t="n"/>
-      <c r="H40" s="77" t="inlineStr">
+      <c r="H40" s="78" t="inlineStr">
         <is>
           <t>Клиент задает все вопросы сам, менеджер только отвечает короткими репликами</t>
         </is>
       </c>
-      <c r="I40" s="77" t="n"/>
-      <c r="J40" s="77" t="n"/>
-      <c r="K40" s="77" t="n"/>
-      <c r="L40" s="77" t="n"/>
-      <c r="M40" s="73" t="inlineStr">
+      <c r="I40" s="78" t="n"/>
+      <c r="J40" s="78" t="n"/>
+      <c r="K40" s="78" t="n"/>
+      <c r="L40" s="78" t="n"/>
+      <c r="M40" s="74" t="inlineStr">
         <is>
           <t>Правило «Ответ + Встречный вопрос». Завершать каждую реплику квалифицирующим вопросом.</t>
         </is>
       </c>
-      <c r="N40" s="73" t="n"/>
-      <c r="O40" s="73" t="n"/>
-      <c r="P40" s="73" t="n"/>
-      <c r="Q40" s="73" t="n"/>
-      <c r="R40" s="73" t="n"/>
-      <c r="S40" s="73" t="n"/>
-      <c r="T40" s="73" t="n"/>
-      <c r="U40" s="73" t="n"/>
-      <c r="V40" s="73" t="n"/>
+      <c r="N40" s="74" t="n"/>
+      <c r="O40" s="74" t="n"/>
+      <c r="P40" s="74" t="n"/>
+      <c r="Q40" s="74" t="n"/>
+      <c r="R40" s="74" t="n"/>
+      <c r="S40" s="74" t="n"/>
+      <c r="T40" s="74" t="n"/>
+      <c r="U40" s="74" t="n"/>
+      <c r="V40" s="74" t="n"/>
     </row>
     <row r="41" ht="34" customHeight="1">
       <c r="A41" s="26" t="n">
@@ -4110,29 +4122,29 @@
       </c>
       <c r="F41" s="27" t="n"/>
       <c r="G41" s="27" t="n"/>
-      <c r="H41" s="77" t="inlineStr">
+      <c r="H41" s="78" t="inlineStr">
         <is>
           <t>Трата 40 минут на презентацию инженеру или секретарю без полномочий подписания</t>
         </is>
       </c>
-      <c r="I41" s="77" t="n"/>
-      <c r="J41" s="77" t="n"/>
-      <c r="K41" s="77" t="n"/>
-      <c r="L41" s="77" t="n"/>
-      <c r="M41" s="73" t="inlineStr">
+      <c r="I41" s="78" t="n"/>
+      <c r="J41" s="78" t="n"/>
+      <c r="K41" s="78" t="n"/>
+      <c r="L41" s="78" t="n"/>
+      <c r="M41" s="74" t="inlineStr">
         <is>
           <t>«Кто кроме вас участвует в согласовании проекта и утверждении финансового бюджета?»</t>
         </is>
       </c>
-      <c r="N41" s="73" t="n"/>
-      <c r="O41" s="73" t="n"/>
-      <c r="P41" s="73" t="n"/>
-      <c r="Q41" s="73" t="n"/>
-      <c r="R41" s="73" t="n"/>
-      <c r="S41" s="73" t="n"/>
-      <c r="T41" s="73" t="n"/>
-      <c r="U41" s="73" t="n"/>
-      <c r="V41" s="73" t="n"/>
+      <c r="N41" s="74" t="n"/>
+      <c r="O41" s="74" t="n"/>
+      <c r="P41" s="74" t="n"/>
+      <c r="Q41" s="74" t="n"/>
+      <c r="R41" s="74" t="n"/>
+      <c r="S41" s="74" t="n"/>
+      <c r="T41" s="74" t="n"/>
+      <c r="U41" s="74" t="n"/>
+      <c r="V41" s="74" t="n"/>
     </row>
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="26" t="n">
@@ -4160,29 +4172,29 @@
       </c>
       <c r="F42" s="27" t="n"/>
       <c r="G42" s="27" t="n"/>
-      <c r="H42" s="77" t="inlineStr">
+      <c r="H42" s="78" t="inlineStr">
         <is>
           <t>Менеджер сразу начинает презентовать продукт, не узнав текущую ситуацию клиента</t>
         </is>
       </c>
-      <c r="I42" s="77" t="n"/>
-      <c r="J42" s="77" t="n"/>
-      <c r="K42" s="77" t="n"/>
-      <c r="L42" s="77" t="n"/>
-      <c r="M42" s="73" t="inlineStr">
+      <c r="I42" s="78" t="n"/>
+      <c r="J42" s="78" t="n"/>
+      <c r="K42" s="78" t="n"/>
+      <c r="L42" s="78" t="n"/>
+      <c r="M42" s="74" t="inlineStr">
         <is>
           <t>Сначала диагностика по методологии SPIN/BANT, затем презентация под конкретную боль.</t>
         </is>
       </c>
-      <c r="N42" s="73" t="n"/>
-      <c r="O42" s="73" t="n"/>
-      <c r="P42" s="73" t="n"/>
-      <c r="Q42" s="73" t="n"/>
-      <c r="R42" s="73" t="n"/>
-      <c r="S42" s="73" t="n"/>
-      <c r="T42" s="73" t="n"/>
-      <c r="U42" s="73" t="n"/>
-      <c r="V42" s="73" t="n"/>
+      <c r="N42" s="74" t="n"/>
+      <c r="O42" s="74" t="n"/>
+      <c r="P42" s="74" t="n"/>
+      <c r="Q42" s="74" t="n"/>
+      <c r="R42" s="74" t="n"/>
+      <c r="S42" s="74" t="n"/>
+      <c r="T42" s="74" t="n"/>
+      <c r="U42" s="74" t="n"/>
+      <c r="V42" s="74" t="n"/>
     </row>
     <row r="43" ht="34" customHeight="1">
       <c r="A43" s="26" t="n">
@@ -4210,29 +4222,29 @@
       </c>
       <c r="F43" s="27" t="n"/>
       <c r="G43" s="27" t="n"/>
-      <c r="H43" s="77" t="inlineStr">
+      <c r="H43" s="78" t="inlineStr">
         <is>
           <t>Моментальная скидка при первом сомнении клиента или согласие («Да, у нас недешево»)</t>
         </is>
       </c>
-      <c r="I43" s="77" t="n"/>
-      <c r="J43" s="77" t="n"/>
-      <c r="K43" s="77" t="n"/>
-      <c r="L43" s="77" t="n"/>
-      <c r="M43" s="73" t="inlineStr">
+      <c r="I43" s="78" t="n"/>
+      <c r="J43" s="78" t="n"/>
+      <c r="K43" s="78" t="n"/>
+      <c r="L43" s="78" t="n"/>
+      <c r="M43" s="74" t="inlineStr">
         <is>
           <t>Обосновать окупаемость: показать, сколько клиент теряет каждый день без внедрения решения.</t>
         </is>
       </c>
-      <c r="N43" s="73" t="n"/>
-      <c r="O43" s="73" t="n"/>
-      <c r="P43" s="73" t="n"/>
-      <c r="Q43" s="73" t="n"/>
-      <c r="R43" s="73" t="n"/>
-      <c r="S43" s="73" t="n"/>
-      <c r="T43" s="73" t="n"/>
-      <c r="U43" s="73" t="n"/>
-      <c r="V43" s="73" t="n"/>
+      <c r="N43" s="74" t="n"/>
+      <c r="O43" s="74" t="n"/>
+      <c r="P43" s="74" t="n"/>
+      <c r="Q43" s="74" t="n"/>
+      <c r="R43" s="74" t="n"/>
+      <c r="S43" s="74" t="n"/>
+      <c r="T43" s="74" t="n"/>
+      <c r="U43" s="74" t="n"/>
+      <c r="V43" s="74" t="n"/>
     </row>
     <row r="44" ht="34" customHeight="1">
       <c r="A44" s="26" t="n">
@@ -4260,29 +4272,29 @@
       </c>
       <c r="F44" s="27" t="n"/>
       <c r="G44" s="27" t="n"/>
-      <c r="H44" s="77" t="inlineStr">
+      <c r="H44" s="78" t="inlineStr">
         <is>
           <t>«Хорошо, думайте, ждем вашего звонка», завершение диалога на неопределенности</t>
         </is>
       </c>
-      <c r="I44" s="77" t="n"/>
-      <c r="J44" s="77" t="n"/>
-      <c r="K44" s="77" t="n"/>
-      <c r="L44" s="77" t="n"/>
-      <c r="M44" s="73" t="inlineStr">
+      <c r="I44" s="78" t="n"/>
+      <c r="J44" s="78" t="n"/>
+      <c r="K44" s="78" t="n"/>
+      <c r="L44" s="78" t="n"/>
+      <c r="M44" s="74" t="inlineStr">
         <is>
           <t>«Алексей, обычно говорят 'подумаю', когда смущает цена или функционал. Что именно из этого?»</t>
         </is>
       </c>
-      <c r="N44" s="73" t="n"/>
-      <c r="O44" s="73" t="n"/>
-      <c r="P44" s="73" t="n"/>
-      <c r="Q44" s="73" t="n"/>
-      <c r="R44" s="73" t="n"/>
-      <c r="S44" s="73" t="n"/>
-      <c r="T44" s="73" t="n"/>
-      <c r="U44" s="73" t="n"/>
-      <c r="V44" s="73" t="n"/>
+      <c r="N44" s="74" t="n"/>
+      <c r="O44" s="74" t="n"/>
+      <c r="P44" s="74" t="n"/>
+      <c r="Q44" s="74" t="n"/>
+      <c r="R44" s="74" t="n"/>
+      <c r="S44" s="74" t="n"/>
+      <c r="T44" s="74" t="n"/>
+      <c r="U44" s="74" t="n"/>
+      <c r="V44" s="74" t="n"/>
     </row>
     <row r="45" ht="34" customHeight="1">
       <c r="A45" s="26" t="n">
@@ -4310,29 +4322,29 @@
       </c>
       <c r="F45" s="27" t="n"/>
       <c r="G45" s="27" t="n"/>
-      <c r="H45" s="77" t="inlineStr">
+      <c r="H45" s="78" t="inlineStr">
         <is>
           <t>Абстрактные слова «мы надежные», «у нас высокое качество» без конкретных фактов</t>
         </is>
       </c>
-      <c r="I45" s="77" t="n"/>
-      <c r="J45" s="77" t="n"/>
-      <c r="K45" s="77" t="n"/>
-      <c r="L45" s="77" t="n"/>
-      <c r="M45" s="73" t="inlineStr">
+      <c r="I45" s="78" t="n"/>
+      <c r="J45" s="78" t="n"/>
+      <c r="K45" s="78" t="n"/>
+      <c r="L45" s="78" t="n"/>
+      <c r="M45" s="74" t="inlineStr">
         <is>
           <t>Показать схожий кейс из отрасли клиента: «Для завода X мы сократили потери на 1.4 млн ₽ за 21 день».</t>
         </is>
       </c>
-      <c r="N45" s="73" t="n"/>
-      <c r="O45" s="73" t="n"/>
-      <c r="P45" s="73" t="n"/>
-      <c r="Q45" s="73" t="n"/>
-      <c r="R45" s="73" t="n"/>
-      <c r="S45" s="73" t="n"/>
-      <c r="T45" s="73" t="n"/>
-      <c r="U45" s="73" t="n"/>
-      <c r="V45" s="73" t="n"/>
+      <c r="N45" s="74" t="n"/>
+      <c r="O45" s="74" t="n"/>
+      <c r="P45" s="74" t="n"/>
+      <c r="Q45" s="74" t="n"/>
+      <c r="R45" s="74" t="n"/>
+      <c r="S45" s="74" t="n"/>
+      <c r="T45" s="74" t="n"/>
+      <c r="U45" s="74" t="n"/>
+      <c r="V45" s="74" t="n"/>
     </row>
     <row r="46" ht="34" customHeight="1">
       <c r="A46" s="26" t="n">
@@ -4360,29 +4372,29 @@
       </c>
       <c r="F46" s="27" t="n"/>
       <c r="G46" s="27" t="n"/>
-      <c r="H46" s="77" t="inlineStr">
+      <c r="H46" s="78" t="inlineStr">
         <is>
           <t>Разговор закончился тепло, но менеджер не предложил сделать следующий шаг к оплате</t>
         </is>
       </c>
-      <c r="I46" s="77" t="n"/>
-      <c r="J46" s="77" t="n"/>
-      <c r="K46" s="77" t="n"/>
-      <c r="L46" s="77" t="n"/>
-      <c r="M46" s="73" t="inlineStr">
+      <c r="I46" s="78" t="n"/>
+      <c r="J46" s="78" t="n"/>
+      <c r="K46" s="78" t="n"/>
+      <c r="L46" s="78" t="n"/>
+      <c r="M46" s="74" t="inlineStr">
         <is>
           <t>«Если все параметры подходят, предлагаю сегодня запустить пилот. Куда отправить договор?»</t>
         </is>
       </c>
-      <c r="N46" s="73" t="n"/>
-      <c r="O46" s="73" t="n"/>
-      <c r="P46" s="73" t="n"/>
-      <c r="Q46" s="73" t="n"/>
-      <c r="R46" s="73" t="n"/>
-      <c r="S46" s="73" t="n"/>
-      <c r="T46" s="73" t="n"/>
-      <c r="U46" s="73" t="n"/>
-      <c r="V46" s="73" t="n"/>
+      <c r="N46" s="74" t="n"/>
+      <c r="O46" s="74" t="n"/>
+      <c r="P46" s="74" t="n"/>
+      <c r="Q46" s="74" t="n"/>
+      <c r="R46" s="74" t="n"/>
+      <c r="S46" s="74" t="n"/>
+      <c r="T46" s="74" t="n"/>
+      <c r="U46" s="74" t="n"/>
+      <c r="V46" s="74" t="n"/>
     </row>
     <row r="47" ht="34" customHeight="1">
       <c r="A47" s="26" t="n">
@@ -4398,7 +4410,7 @@
           <t>0.8x</t>
         </is>
       </c>
-      <c r="D47" s="78" t="inlineStr">
+      <c r="D47" s="79" t="inlineStr">
         <is>
           <t>🟢 P2 (Стандарт)</t>
         </is>
@@ -4410,29 +4422,29 @@
       </c>
       <c r="F47" s="27" t="n"/>
       <c r="G47" s="27" t="n"/>
-      <c r="H47" s="77" t="inlineStr">
+      <c r="H47" s="78" t="inlineStr">
         <is>
           <t>Невнятное приветствие, вопрос «Вам удобно говорить?» без обозначения повестки</t>
         </is>
       </c>
-      <c r="I47" s="77" t="n"/>
-      <c r="J47" s="77" t="n"/>
-      <c r="K47" s="77" t="n"/>
-      <c r="L47" s="77" t="n"/>
-      <c r="M47" s="73" t="inlineStr">
+      <c r="I47" s="78" t="n"/>
+      <c r="J47" s="78" t="n"/>
+      <c r="K47" s="78" t="n"/>
+      <c r="L47" s="78" t="n"/>
+      <c r="M47" s="74" t="inlineStr">
         <is>
           <t>«Добрый день! Дмитрий, компания RevOps. Звоню по вашей заявке на аудит воронки. Уделите 5 минут?»</t>
         </is>
       </c>
-      <c r="N47" s="73" t="n"/>
-      <c r="O47" s="73" t="n"/>
-      <c r="P47" s="73" t="n"/>
-      <c r="Q47" s="73" t="n"/>
-      <c r="R47" s="73" t="n"/>
-      <c r="S47" s="73" t="n"/>
-      <c r="T47" s="73" t="n"/>
-      <c r="U47" s="73" t="n"/>
-      <c r="V47" s="73" t="n"/>
+      <c r="N47" s="74" t="n"/>
+      <c r="O47" s="74" t="n"/>
+      <c r="P47" s="74" t="n"/>
+      <c r="Q47" s="74" t="n"/>
+      <c r="R47" s="74" t="n"/>
+      <c r="S47" s="74" t="n"/>
+      <c r="T47" s="74" t="n"/>
+      <c r="U47" s="74" t="n"/>
+      <c r="V47" s="74" t="n"/>
     </row>
     <row r="48" ht="34" customHeight="1">
       <c r="A48" s="26" t="n">
@@ -4448,7 +4460,7 @@
           <t>0.8x</t>
         </is>
       </c>
-      <c r="D48" s="78" t="inlineStr">
+      <c r="D48" s="79" t="inlineStr">
         <is>
           <t>🟢 P2 (Стандарт)</t>
         </is>
@@ -4460,29 +4472,29 @@
       </c>
       <c r="F48" s="27" t="n"/>
       <c r="G48" s="27" t="n"/>
-      <c r="H48" s="77" t="inlineStr">
+      <c r="H48" s="78" t="inlineStr">
         <is>
           <t>Дрожащий голос при озвучивании чека, слова сомнения («может быть», «наверное»)</t>
         </is>
       </c>
-      <c r="I48" s="77" t="n"/>
-      <c r="J48" s="77" t="n"/>
-      <c r="K48" s="77" t="n"/>
-      <c r="L48" s="77" t="n"/>
-      <c r="M48" s="73" t="inlineStr">
+      <c r="I48" s="78" t="n"/>
+      <c r="J48" s="78" t="n"/>
+      <c r="K48" s="78" t="n"/>
+      <c r="L48" s="78" t="n"/>
+      <c r="M48" s="74" t="inlineStr">
         <is>
           <t>Отработать блок цены на тренажере: уверенная пауза после озвучивания стоимости.</t>
         </is>
       </c>
-      <c r="N48" s="73" t="n"/>
-      <c r="O48" s="73" t="n"/>
-      <c r="P48" s="73" t="n"/>
-      <c r="Q48" s="73" t="n"/>
-      <c r="R48" s="73" t="n"/>
-      <c r="S48" s="73" t="n"/>
-      <c r="T48" s="73" t="n"/>
-      <c r="U48" s="73" t="n"/>
-      <c r="V48" s="73" t="n"/>
+      <c r="N48" s="74" t="n"/>
+      <c r="O48" s="74" t="n"/>
+      <c r="P48" s="74" t="n"/>
+      <c r="Q48" s="74" t="n"/>
+      <c r="R48" s="74" t="n"/>
+      <c r="S48" s="74" t="n"/>
+      <c r="T48" s="74" t="n"/>
+      <c r="U48" s="74" t="n"/>
+      <c r="V48" s="74" t="n"/>
     </row>
     <row r="49" ht="34" customHeight="1">
       <c r="A49" s="26" t="n">
@@ -4510,29 +4522,29 @@
       </c>
       <c r="F49" s="27" t="n"/>
       <c r="G49" s="27" t="n"/>
-      <c r="H49" s="77" t="inlineStr">
+      <c r="H49" s="78" t="inlineStr">
         <is>
           <t>Монолог менеджера &gt; 70% времени: клиент молчит и теряет фокус внимания</t>
         </is>
       </c>
-      <c r="I49" s="77" t="n"/>
-      <c r="J49" s="77" t="n"/>
-      <c r="K49" s="77" t="n"/>
-      <c r="L49" s="77" t="n"/>
-      <c r="M49" s="73" t="inlineStr">
+      <c r="I49" s="78" t="n"/>
+      <c r="J49" s="78" t="n"/>
+      <c r="K49" s="78" t="n"/>
+      <c r="L49" s="78" t="n"/>
+      <c r="M49" s="74" t="inlineStr">
         <is>
           <t>Держать баланс 50/50. Задавать открытые вопросы и давать клиенту выговориться о проблеме.</t>
         </is>
       </c>
-      <c r="N49" s="73" t="n"/>
-      <c r="O49" s="73" t="n"/>
-      <c r="P49" s="73" t="n"/>
-      <c r="Q49" s="73" t="n"/>
-      <c r="R49" s="73" t="n"/>
-      <c r="S49" s="73" t="n"/>
-      <c r="T49" s="73" t="n"/>
-      <c r="U49" s="73" t="n"/>
-      <c r="V49" s="73" t="n"/>
+      <c r="N49" s="74" t="n"/>
+      <c r="O49" s="74" t="n"/>
+      <c r="P49" s="74" t="n"/>
+      <c r="Q49" s="74" t="n"/>
+      <c r="R49" s="74" t="n"/>
+      <c r="S49" s="74" t="n"/>
+      <c r="T49" s="74" t="n"/>
+      <c r="U49" s="74" t="n"/>
+      <c r="V49" s="74" t="n"/>
     </row>
     <row r="50" ht="34" customHeight="1">
       <c r="A50" s="26" t="n">
@@ -4548,7 +4560,7 @@
           <t>1.0x</t>
         </is>
       </c>
-      <c r="D50" s="78" t="inlineStr">
+      <c r="D50" s="79" t="inlineStr">
         <is>
           <t>🟢 P2 (Стандарт)</t>
         </is>
@@ -4560,29 +4572,29 @@
       </c>
       <c r="F50" s="27" t="n"/>
       <c r="G50" s="27" t="n"/>
-      <c r="H50" s="77" t="inlineStr">
+      <c r="H50" s="78" t="inlineStr">
         <is>
           <t>Диалог оборвался, у клиента и менеджера разное понимание следующих действий</t>
         </is>
       </c>
-      <c r="I50" s="77" t="n"/>
-      <c r="J50" s="77" t="n"/>
-      <c r="K50" s="77" t="n"/>
-      <c r="L50" s="77" t="n"/>
-      <c r="M50" s="73" t="inlineStr">
+      <c r="I50" s="78" t="n"/>
+      <c r="J50" s="78" t="n"/>
+      <c r="K50" s="78" t="n"/>
+      <c r="L50" s="78" t="n"/>
+      <c r="M50" s="74" t="inlineStr">
         <is>
           <t>«Итак, резюмирую: я отправляю КП в WhatsApp до 15:00, а завтра в 11:00 мы созваниваемся по условиям».</t>
         </is>
       </c>
-      <c r="N50" s="73" t="n"/>
-      <c r="O50" s="73" t="n"/>
-      <c r="P50" s="73" t="n"/>
-      <c r="Q50" s="73" t="n"/>
-      <c r="R50" s="73" t="n"/>
-      <c r="S50" s="73" t="n"/>
-      <c r="T50" s="73" t="n"/>
-      <c r="U50" s="73" t="n"/>
-      <c r="V50" s="73" t="n"/>
+      <c r="N50" s="74" t="n"/>
+      <c r="O50" s="74" t="n"/>
+      <c r="P50" s="74" t="n"/>
+      <c r="Q50" s="74" t="n"/>
+      <c r="R50" s="74" t="n"/>
+      <c r="S50" s="74" t="n"/>
+      <c r="T50" s="74" t="n"/>
+      <c r="U50" s="74" t="n"/>
+      <c r="V50" s="74" t="n"/>
     </row>
     <row r="51" ht="34" customHeight="1">
       <c r="A51" s="26" t="n">
@@ -4610,29 +4622,29 @@
       </c>
       <c r="F51" s="27" t="n"/>
       <c r="G51" s="27" t="n"/>
-      <c r="H51" s="77" t="inlineStr">
+      <c r="H51" s="78" t="inlineStr">
         <is>
           <t>Раздача скидок из маржи компании без требования 100% предоплаты или большего объема</t>
         </is>
       </c>
-      <c r="I51" s="77" t="n"/>
-      <c r="J51" s="77" t="n"/>
-      <c r="K51" s="77" t="n"/>
-      <c r="L51" s="77" t="n"/>
-      <c r="M51" s="73" t="inlineStr">
+      <c r="I51" s="78" t="n"/>
+      <c r="J51" s="78" t="n"/>
+      <c r="K51" s="78" t="n"/>
+      <c r="L51" s="78" t="n"/>
+      <c r="M51" s="74" t="inlineStr">
         <is>
           <t>Скидка возможна только в обмен на ценность: «Готовы дать 5% при оплате счета в течение 24 часов».</t>
         </is>
       </c>
-      <c r="N51" s="73" t="n"/>
-      <c r="O51" s="73" t="n"/>
-      <c r="P51" s="73" t="n"/>
-      <c r="Q51" s="73" t="n"/>
-      <c r="R51" s="73" t="n"/>
-      <c r="S51" s="73" t="n"/>
-      <c r="T51" s="73" t="n"/>
-      <c r="U51" s="73" t="n"/>
-      <c r="V51" s="73" t="n"/>
+      <c r="N51" s="74" t="n"/>
+      <c r="O51" s="74" t="n"/>
+      <c r="P51" s="74" t="n"/>
+      <c r="Q51" s="74" t="n"/>
+      <c r="R51" s="74" t="n"/>
+      <c r="S51" s="74" t="n"/>
+      <c r="T51" s="74" t="n"/>
+      <c r="U51" s="74" t="n"/>
+      <c r="V51" s="74" t="n"/>
     </row>
     <row r="52" ht="12" customHeight="1"/>
     <row r="53" ht="24" customHeight="1">
@@ -4700,215 +4712,215 @@
       <c r="V54" s="25" t="n"/>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="79" t="inlineStr">
+      <c r="A55" s="80" t="inlineStr">
         <is>
           <t>Текущие потери от брака звонков в месяц (As-Is)</t>
         </is>
       </c>
-      <c r="B55" s="79" t="n"/>
-      <c r="C55" s="79" t="n"/>
-      <c r="D55" s="80" t="n">
+      <c r="B55" s="80" t="n"/>
+      <c r="C55" s="80" t="n"/>
+      <c r="D55" s="81" t="n">
         <v>1382500</v>
       </c>
-      <c r="E55" s="80" t="n"/>
-      <c r="F55" s="60" t="inlineStr">
+      <c r="E55" s="81" t="n"/>
+      <c r="F55" s="61" t="inlineStr">
         <is>
           <t>Сливы на этапе первичного звонка из-за отсутствия Next Step и слабой отработки возражений</t>
         </is>
       </c>
-      <c r="G55" s="60" t="n"/>
-      <c r="H55" s="60" t="n"/>
-      <c r="I55" s="60" t="n"/>
-      <c r="J55" s="60" t="n"/>
-      <c r="K55" s="60" t="n"/>
-      <c r="L55" s="60" t="n"/>
-      <c r="M55" s="60" t="n"/>
-      <c r="N55" s="60" t="n"/>
-      <c r="O55" s="60" t="n"/>
-      <c r="P55" s="60" t="n"/>
-      <c r="Q55" s="60" t="n"/>
-      <c r="R55" s="60" t="n"/>
-      <c r="S55" s="60" t="n"/>
-      <c r="T55" s="60" t="n"/>
-      <c r="U55" s="60" t="n"/>
-      <c r="V55" s="60" t="n"/>
+      <c r="G55" s="61" t="n"/>
+      <c r="H55" s="61" t="n"/>
+      <c r="I55" s="61" t="n"/>
+      <c r="J55" s="61" t="n"/>
+      <c r="K55" s="61" t="n"/>
+      <c r="L55" s="61" t="n"/>
+      <c r="M55" s="61" t="n"/>
+      <c r="N55" s="61" t="n"/>
+      <c r="O55" s="61" t="n"/>
+      <c r="P55" s="61" t="n"/>
+      <c r="Q55" s="61" t="n"/>
+      <c r="R55" s="61" t="n"/>
+      <c r="S55" s="61" t="n"/>
+      <c r="T55" s="61" t="n"/>
+      <c r="U55" s="61" t="n"/>
+      <c r="V55" s="61" t="n"/>
     </row>
     <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="79" t="inlineStr">
+      <c r="A56" s="80" t="inlineStr">
         <is>
           <t>Ожидаемый возврат выручки в кассу (M1 To-Be)</t>
         </is>
       </c>
-      <c r="B56" s="79" t="n"/>
-      <c r="C56" s="79" t="n"/>
-      <c r="D56" s="81" t="n">
+      <c r="B56" s="80" t="n"/>
+      <c r="C56" s="80" t="n"/>
+      <c r="D56" s="82" t="n">
         <v>414750</v>
       </c>
-      <c r="E56" s="81" t="n"/>
-      <c r="F56" s="60" t="inlineStr">
+      <c r="E56" s="82" t="n"/>
+      <c r="F56" s="61" t="inlineStr">
         <is>
           <t>Консервативный сценарий: устранение всего 30% выявленных дефектов речи</t>
         </is>
       </c>
-      <c r="G56" s="60" t="n"/>
-      <c r="H56" s="60" t="n"/>
-      <c r="I56" s="60" t="n"/>
-      <c r="J56" s="60" t="n"/>
-      <c r="K56" s="60" t="n"/>
-      <c r="L56" s="60" t="n"/>
-      <c r="M56" s="60" t="n"/>
-      <c r="N56" s="60" t="n"/>
-      <c r="O56" s="60" t="n"/>
-      <c r="P56" s="60" t="n"/>
-      <c r="Q56" s="60" t="n"/>
-      <c r="R56" s="60" t="n"/>
-      <c r="S56" s="60" t="n"/>
-      <c r="T56" s="60" t="n"/>
-      <c r="U56" s="60" t="n"/>
-      <c r="V56" s="60" t="n"/>
+      <c r="G56" s="61" t="n"/>
+      <c r="H56" s="61" t="n"/>
+      <c r="I56" s="61" t="n"/>
+      <c r="J56" s="61" t="n"/>
+      <c r="K56" s="61" t="n"/>
+      <c r="L56" s="61" t="n"/>
+      <c r="M56" s="61" t="n"/>
+      <c r="N56" s="61" t="n"/>
+      <c r="O56" s="61" t="n"/>
+      <c r="P56" s="61" t="n"/>
+      <c r="Q56" s="61" t="n"/>
+      <c r="R56" s="61" t="n"/>
+      <c r="S56" s="61" t="n"/>
+      <c r="T56" s="61" t="n"/>
+      <c r="U56" s="61" t="n"/>
+      <c r="V56" s="61" t="n"/>
     </row>
     <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="79" t="inlineStr">
+      <c r="A57" s="80" t="inlineStr">
         <is>
           <t>Стоимость модуля речевого ИИ-супервайзера</t>
         </is>
       </c>
-      <c r="B57" s="79" t="n"/>
-      <c r="C57" s="79" t="n"/>
-      <c r="D57" s="82" t="n">
+      <c r="B57" s="80" t="n"/>
+      <c r="C57" s="80" t="n"/>
+      <c r="D57" s="83" t="n">
         <v>150000</v>
       </c>
-      <c r="E57" s="82" t="n"/>
-      <c r="F57" s="60" t="inlineStr">
+      <c r="E57" s="83" t="n"/>
+      <c r="F57" s="61" t="inlineStr">
         <is>
           <t>В составе комплексного 4-недельного спринта оптимизации отдела продаж</t>
         </is>
       </c>
-      <c r="G57" s="60" t="n"/>
-      <c r="H57" s="60" t="n"/>
-      <c r="I57" s="60" t="n"/>
-      <c r="J57" s="60" t="n"/>
-      <c r="K57" s="60" t="n"/>
-      <c r="L57" s="60" t="n"/>
-      <c r="M57" s="60" t="n"/>
-      <c r="N57" s="60" t="n"/>
-      <c r="O57" s="60" t="n"/>
-      <c r="P57" s="60" t="n"/>
-      <c r="Q57" s="60" t="n"/>
-      <c r="R57" s="60" t="n"/>
-      <c r="S57" s="60" t="n"/>
-      <c r="T57" s="60" t="n"/>
-      <c r="U57" s="60" t="n"/>
-      <c r="V57" s="60" t="n"/>
+      <c r="G57" s="61" t="n"/>
+      <c r="H57" s="61" t="n"/>
+      <c r="I57" s="61" t="n"/>
+      <c r="J57" s="61" t="n"/>
+      <c r="K57" s="61" t="n"/>
+      <c r="L57" s="61" t="n"/>
+      <c r="M57" s="61" t="n"/>
+      <c r="N57" s="61" t="n"/>
+      <c r="O57" s="61" t="n"/>
+      <c r="P57" s="61" t="n"/>
+      <c r="Q57" s="61" t="n"/>
+      <c r="R57" s="61" t="n"/>
+      <c r="S57" s="61" t="n"/>
+      <c r="T57" s="61" t="n"/>
+      <c r="U57" s="61" t="n"/>
+      <c r="V57" s="61" t="n"/>
     </row>
     <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="79" t="inlineStr">
+      <c r="A58" s="80" t="inlineStr">
         <is>
           <t>Чистая прибыль компании от внедрения в первый месяц</t>
         </is>
       </c>
-      <c r="B58" s="79" t="n"/>
-      <c r="C58" s="79" t="n"/>
-      <c r="D58" s="81" t="n">
+      <c r="B58" s="80" t="n"/>
+      <c r="C58" s="80" t="n"/>
+      <c r="D58" s="82" t="n">
         <v>264750</v>
       </c>
-      <c r="E58" s="81" t="n"/>
-      <c r="F58" s="60" t="inlineStr">
+      <c r="E58" s="82" t="n"/>
+      <c r="F58" s="61" t="inlineStr">
         <is>
           <t>Чистый денежный плюс в кассе компании уже в первый месяц работы</t>
         </is>
       </c>
-      <c r="G58" s="60" t="n"/>
-      <c r="H58" s="60" t="n"/>
-      <c r="I58" s="60" t="n"/>
-      <c r="J58" s="60" t="n"/>
-      <c r="K58" s="60" t="n"/>
-      <c r="L58" s="60" t="n"/>
-      <c r="M58" s="60" t="n"/>
-      <c r="N58" s="60" t="n"/>
-      <c r="O58" s="60" t="n"/>
-      <c r="P58" s="60" t="n"/>
-      <c r="Q58" s="60" t="n"/>
-      <c r="R58" s="60" t="n"/>
-      <c r="S58" s="60" t="n"/>
-      <c r="T58" s="60" t="n"/>
-      <c r="U58" s="60" t="n"/>
-      <c r="V58" s="60" t="n"/>
+      <c r="G58" s="61" t="n"/>
+      <c r="H58" s="61" t="n"/>
+      <c r="I58" s="61" t="n"/>
+      <c r="J58" s="61" t="n"/>
+      <c r="K58" s="61" t="n"/>
+      <c r="L58" s="61" t="n"/>
+      <c r="M58" s="61" t="n"/>
+      <c r="N58" s="61" t="n"/>
+      <c r="O58" s="61" t="n"/>
+      <c r="P58" s="61" t="n"/>
+      <c r="Q58" s="61" t="n"/>
+      <c r="R58" s="61" t="n"/>
+      <c r="S58" s="61" t="n"/>
+      <c r="T58" s="61" t="n"/>
+      <c r="U58" s="61" t="n"/>
+      <c r="V58" s="61" t="n"/>
     </row>
     <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="79" t="inlineStr">
+      <c r="A59" s="80" t="inlineStr">
         <is>
           <t>Чистый ROI речевой аналитики</t>
         </is>
       </c>
-      <c r="B59" s="79" t="n"/>
-      <c r="C59" s="79" t="n"/>
-      <c r="D59" s="59" t="inlineStr">
+      <c r="B59" s="80" t="n"/>
+      <c r="C59" s="80" t="n"/>
+      <c r="D59" s="60" t="inlineStr">
         <is>
           <t>276%</t>
         </is>
       </c>
-      <c r="E59" s="59" t="n"/>
-      <c r="F59" s="60" t="inlineStr">
+      <c r="E59" s="60" t="n"/>
+      <c r="F59" s="61" t="inlineStr">
         <is>
           <t>Отдача на каждый вложенный рубль в первый месяц</t>
         </is>
       </c>
-      <c r="G59" s="60" t="n"/>
-      <c r="H59" s="60" t="n"/>
-      <c r="I59" s="60" t="n"/>
-      <c r="J59" s="60" t="n"/>
-      <c r="K59" s="60" t="n"/>
-      <c r="L59" s="60" t="n"/>
-      <c r="M59" s="60" t="n"/>
-      <c r="N59" s="60" t="n"/>
-      <c r="O59" s="60" t="n"/>
-      <c r="P59" s="60" t="n"/>
-      <c r="Q59" s="60" t="n"/>
-      <c r="R59" s="60" t="n"/>
-      <c r="S59" s="60" t="n"/>
-      <c r="T59" s="60" t="n"/>
-      <c r="U59" s="60" t="n"/>
-      <c r="V59" s="60" t="n"/>
+      <c r="G59" s="61" t="n"/>
+      <c r="H59" s="61" t="n"/>
+      <c r="I59" s="61" t="n"/>
+      <c r="J59" s="61" t="n"/>
+      <c r="K59" s="61" t="n"/>
+      <c r="L59" s="61" t="n"/>
+      <c r="M59" s="61" t="n"/>
+      <c r="N59" s="61" t="n"/>
+      <c r="O59" s="61" t="n"/>
+      <c r="P59" s="61" t="n"/>
+      <c r="Q59" s="61" t="n"/>
+      <c r="R59" s="61" t="n"/>
+      <c r="S59" s="61" t="n"/>
+      <c r="T59" s="61" t="n"/>
+      <c r="U59" s="61" t="n"/>
+      <c r="V59" s="61" t="n"/>
     </row>
     <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="79" t="inlineStr">
+      <c r="A60" s="80" t="inlineStr">
         <is>
           <t>Срок полной окупаемости модуля</t>
         </is>
       </c>
-      <c r="B60" s="79" t="n"/>
-      <c r="C60" s="79" t="n"/>
-      <c r="D60" s="59" t="inlineStr">
+      <c r="B60" s="80" t="n"/>
+      <c r="C60" s="80" t="n"/>
+      <c r="D60" s="60" t="inlineStr">
         <is>
           <t>11 дней</t>
         </is>
       </c>
-      <c r="E60" s="59" t="n"/>
-      <c r="F60" s="60" t="inlineStr">
+      <c r="E60" s="60" t="n"/>
+      <c r="F60" s="61" t="inlineStr">
         <is>
           <t>Количество рабочих дней до полной окупаемости внедрения речевого ИИ</t>
         </is>
       </c>
-      <c r="G60" s="60" t="n"/>
-      <c r="H60" s="60" t="n"/>
-      <c r="I60" s="60" t="n"/>
-      <c r="J60" s="60" t="n"/>
-      <c r="K60" s="60" t="n"/>
-      <c r="L60" s="60" t="n"/>
-      <c r="M60" s="60" t="n"/>
-      <c r="N60" s="60" t="n"/>
-      <c r="O60" s="60" t="n"/>
-      <c r="P60" s="60" t="n"/>
-      <c r="Q60" s="60" t="n"/>
-      <c r="R60" s="60" t="n"/>
-      <c r="S60" s="60" t="n"/>
-      <c r="T60" s="60" t="n"/>
-      <c r="U60" s="60" t="n"/>
-      <c r="V60" s="60" t="n"/>
+      <c r="G60" s="61" t="n"/>
+      <c r="H60" s="61" t="n"/>
+      <c r="I60" s="61" t="n"/>
+      <c r="J60" s="61" t="n"/>
+      <c r="K60" s="61" t="n"/>
+      <c r="L60" s="61" t="n"/>
+      <c r="M60" s="61" t="n"/>
+      <c r="N60" s="61" t="n"/>
+      <c r="O60" s="61" t="n"/>
+      <c r="P60" s="61" t="n"/>
+      <c r="Q60" s="61" t="n"/>
+      <c r="R60" s="61" t="n"/>
+      <c r="S60" s="61" t="n"/>
+      <c r="T60" s="61" t="n"/>
+      <c r="U60" s="61" t="n"/>
+      <c r="V60" s="61" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="112">
+  <mergeCells count="113">
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="D60:E60"/>
     <mergeCell ref="N2:P2"/>
@@ -4997,6 +5009,7 @@
     <mergeCell ref="M45:V45"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A27:C27"/>
     <mergeCell ref="H50:L50"/>
     <mergeCell ref="F54:V54"/>
     <mergeCell ref="M47:V47"/>
@@ -5046,7 +5059,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
     <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
@@ -5113,33 +5126,33 @@
           <t>Взвешенный пайплайн в работе</t>
         </is>
       </c>
-      <c r="D4" s="40" t="inlineStr">
+      <c r="D4" s="84" t="inlineStr">
         <is>
           <t>Выявленная упущенная прибыль</t>
         </is>
       </c>
-      <c r="E4" s="83" t="inlineStr">
+      <c r="E4" s="85" t="inlineStr">
         <is>
           <t>Потенциал выручки (To-Be)</t>
         </is>
       </c>
-      <c r="F4" s="83" t="inlineStr">
+      <c r="F4" s="85" t="inlineStr">
         <is>
           <t>Ожидаемый чистый ROI</t>
         </is>
       </c>
-      <c r="G4" s="83" t="inlineStr">
+      <c r="G4" s="85" t="inlineStr">
         <is>
           <t>Срок окупаемости проекта</t>
         </is>
       </c>
-      <c r="H4" s="83" t="n"/>
+      <c r="H4" s="85" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="84" t="n">
+      <c r="A5" s="86" t="n">
         <v>1650000</v>
       </c>
-      <c r="B5" s="84" t="n"/>
+      <c r="B5" s="86" t="n"/>
       <c r="C5" s="23" t="n">
         <v>2754000</v>
       </c>
@@ -5149,17 +5162,17 @@
       <c r="E5" s="22" t="n">
         <v>8651000</v>
       </c>
-      <c r="F5" s="85" t="inlineStr">
+      <c r="F5" s="87" t="inlineStr">
         <is>
           <t>367%</t>
         </is>
       </c>
-      <c r="G5" s="85" t="inlineStr">
+      <c r="G5" s="87" t="inlineStr">
         <is>
           <t>6 дн.</t>
         </is>
       </c>
-      <c r="H5" s="85" t="n"/>
+      <c r="H5" s="87" t="n"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
@@ -5216,7 +5229,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="B9" s="73" t="inlineStr">
+      <c r="B9" s="74" t="inlineStr">
         <is>
           <t>«Черный ящик» CRM: иллюзорный пайплайн</t>
         </is>
@@ -5226,13 +5239,13 @@
           <t>В CRM висит 5.3 млн ₽, но реальный взвешенный объем всего 2.6 млн ₽. Фаундер живет в иллюзии плана</t>
         </is>
       </c>
-      <c r="D9" s="67" t="n">
+      <c r="D9" s="68" t="n">
         <v>5530000</v>
       </c>
       <c r="E9" s="28" t="n">
         <v>2776000</v>
       </c>
-      <c r="F9" s="86" t="inlineStr">
+      <c r="F9" s="88" t="inlineStr">
         <is>
           <t>🔴 P0 (Критический)</t>
         </is>
@@ -5254,7 +5267,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B10" s="73" t="inlineStr">
+      <c r="B10" s="74" t="inlineStr">
         <is>
           <t>«Кладбище сделок»: срыв регламентов SLA</t>
         </is>
@@ -5264,13 +5277,13 @@
           <t>Сделки маринуются на этапе КП по 12–14 дней (норма 48ч). Вероятность закрытия падает на 45%</t>
         </is>
       </c>
-      <c r="D10" s="67" t="n">
+      <c r="D10" s="68" t="n">
         <v>3850000</v>
       </c>
       <c r="E10" s="28" t="n">
         <v>1732500</v>
       </c>
-      <c r="F10" s="86" t="inlineStr">
+      <c r="F10" s="88" t="inlineStr">
         <is>
           <t>🔴 P0 (Критический)</t>
         </is>
@@ -5292,7 +5305,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B11" s="73" t="inlineStr">
+      <c r="B11" s="74" t="inlineStr">
         <is>
           <t>РОП — «играющий тренер» и узкое горлышко</t>
         </is>
@@ -5302,13 +5315,13 @@
           <t>РОП ведет 80% сделок и перегружен (нагрузка 80%), а КАМы простаивают с 4% загрузки. Сделки тухнут без внимания</t>
         </is>
       </c>
-      <c r="D11" s="67" t="n">
+      <c r="D11" s="68" t="n">
         <v>850000</v>
       </c>
       <c r="E11" s="28" t="n">
         <v>255000</v>
       </c>
-      <c r="F11" s="86" t="inlineStr">
+      <c r="F11" s="88" t="inlineStr">
         <is>
           <t>🔴 P0 (Критический)</t>
         </is>
@@ -5330,7 +5343,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="B12" s="73" t="inlineStr">
+      <c r="B12" s="74" t="inlineStr">
         <is>
           <t>Менеджеры-автоответчики и слив звонков</t>
         </is>
@@ -5340,13 +5353,13 @@
           <t>В 33% звонков не зафиксирован Next Step. Средний балл речи &lt; 9/13. Лиды уходят в «подумаю»</t>
         </is>
       </c>
-      <c r="D12" s="67" t="n">
+      <c r="D12" s="68" t="n">
         <v>5530000</v>
       </c>
       <c r="E12" s="28" t="n">
         <v>1382500</v>
       </c>
-      <c r="F12" s="86" t="inlineStr">
+      <c r="F12" s="88" t="inlineStr">
         <is>
           <t>🔴 P0 (Критический)</t>
         </is>
@@ -5368,7 +5381,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B13" s="73" t="inlineStr">
+      <c r="B13" s="74" t="inlineStr">
         <is>
           <t>«Кладбище отказников» без реактивации</t>
         </is>
@@ -5378,13 +5391,13 @@
           <t>1 млн ₽ списан в отказ (L1 «дорого», L2 «подумаю»). База брошена в архиве без повторного прогрева</t>
         </is>
       </c>
-      <c r="D13" s="67" t="n">
+      <c r="D13" s="68" t="n">
         <v>1000000</v>
       </c>
       <c r="E13" s="28" t="n">
         <v>440000</v>
       </c>
-      <c r="F13" s="87" t="inlineStr">
+      <c r="F13" s="89" t="inlineStr">
         <is>
           <t>🟡 P1 (Высокий)</t>
         </is>
@@ -5406,7 +5419,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B14" s="73" t="inlineStr">
+      <c r="B14" s="74" t="inlineStr">
         <is>
           <t>Зависшая дебиторка и кассовые разрывы</t>
         </is>
@@ -5416,13 +5429,13 @@
           <t>Счета выставлены, но не оплачены (DSO &gt; 25 дней). 330к просрочки грозит кассовым разрывом</t>
         </is>
       </c>
-      <c r="D14" s="67" t="n">
+      <c r="D14" s="68" t="n">
         <v>330000</v>
       </c>
       <c r="E14" s="28" t="n">
         <v>330000</v>
       </c>
-      <c r="F14" s="87" t="inlineStr">
+      <c r="F14" s="89" t="inlineStr">
         <is>
           <t>🟡 P1 (Высокий)</t>
         </is>
@@ -5444,7 +5457,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B15" s="73" t="inlineStr">
+      <c r="B15" s="74" t="inlineStr">
         <is>
           <t>Слив маркетинга и война с отделом продаж</t>
         </is>
@@ -5454,13 +5467,13 @@
           <t>Google Ads слил 85 000 ₽ с ROMI -100% (0 оплат). Деньги сожжены без сквозного контроля окупаемости</t>
         </is>
       </c>
-      <c r="D15" s="67" t="n">
+      <c r="D15" s="68" t="n">
         <v>850000</v>
       </c>
       <c r="E15" s="28" t="n">
         <v>85000</v>
       </c>
-      <c r="F15" s="87" t="inlineStr">
+      <c r="F15" s="89" t="inlineStr">
         <is>
           <t>🟡 P1 (Высокий)</t>
         </is>
@@ -5484,7 +5497,7 @@
         </is>
       </c>
       <c r="C16" s="29" t="n"/>
-      <c r="D16" s="88">
+      <c r="D16" s="90">
         <f>SUM(D9:D15)</f>
         <v/>
       </c>
@@ -5492,7 +5505,7 @@
         <f>SUM(E9:E15)</f>
         <v/>
       </c>
-      <c r="F16" s="89" t="inlineStr">
+      <c r="F16" s="91" t="inlineStr">
         <is>
           <t>ИТОГО ПОТЕРЬ</t>
         </is>
@@ -5540,7 +5553,7 @@
       </c>
       <c r="B20" s="51" t="n"/>
       <c r="C20" s="51" t="n"/>
-      <c r="D20" s="82" t="n">
+      <c r="D20" s="83" t="n">
         <v>450000</v>
       </c>
       <c r="E20" s="10" t="inlineStr">
@@ -5560,7 +5573,7 @@
       </c>
       <c r="B21" s="51" t="n"/>
       <c r="C21" s="51" t="n"/>
-      <c r="D21" s="81" t="n">
+      <c r="D21" s="82" t="n">
         <v>2100300</v>
       </c>
       <c r="E21" s="10" t="inlineStr">
@@ -5580,7 +5593,7 @@
       </c>
       <c r="B22" s="51" t="n"/>
       <c r="C22" s="51" t="n"/>
-      <c r="D22" s="81">
+      <c r="D22" s="82">
         <f>D21-D20</f>
         <v/>
       </c>
@@ -5601,7 +5614,7 @@
       </c>
       <c r="B23" s="51" t="n"/>
       <c r="C23" s="51" t="n"/>
-      <c r="D23" s="59">
+      <c r="D23" s="60">
         <f>(D22/D20)*100 &amp; "%"</f>
         <v/>
       </c>
@@ -5622,7 +5635,7 @@
       </c>
       <c r="B24" s="51" t="n"/>
       <c r="C24" s="51" t="n"/>
-      <c r="D24" s="59">
+      <c r="D24" s="60">
         <f>ROUND(D20/(D21/30), 0) &amp; " дн."</f>
         <v/>
       </c>
@@ -5636,21 +5649,21 @@
       <c r="H24" s="51" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="90" t="inlineStr">
+      <c r="A26" s="92" t="inlineStr">
         <is>
           <t>👉 УТВЕРДИТЬ ПРОЕКТ ОПТИМИЗАЦИИ И СФОРМИРОВАТЬ ИНВОЙС (450 000 ₽)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="91" t="inlineStr">
+      <c r="A27" s="93" t="inlineStr">
         <is>
           <t>Не готовы к спринту? 👉 Бесплатный тест-драйв на 3 звонках на вкладке «⚡ Экспресс_Калькулятор_3_Цифры»</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="92" t="inlineStr">
+      <c r="A28" s="94" t="inlineStr">
         <is>
           <t>🔒 Безопасный B2B-расчет: безналичный платеж по счету (УПД / Диадок) • 152-ФЗ РФ • Старт спринта за 24 часа</t>
         </is>
@@ -5708,7 +5721,7 @@
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
@@ -5767,24 +5780,24 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="39" t="inlineStr">
+      <c r="A4" s="95" t="inlineStr">
         <is>
           <t>Выручка (Closed-Won)</t>
         </is>
       </c>
-      <c r="B4" s="39" t="inlineStr">
+      <c r="B4" s="95" t="inlineStr">
         <is>
           <t>% Выполнения плана</t>
         </is>
       </c>
-      <c r="C4" s="53" t="inlineStr">
+      <c r="C4" s="96" t="inlineStr">
         <is>
           <t>Взвешенный прогноз</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr">
-        <is>
-          <t>Run-Rate касса (Прогноз)</t>
+      <c r="D4" s="95" t="inlineStr">
+        <is>
+          <t>Run-Rate касса (мес)</t>
         </is>
       </c>
       <c r="F4" s="39" t="inlineStr">
@@ -5802,14 +5815,14 @@
           <t>Качество речи ОП (ИИ)</t>
         </is>
       </c>
-      <c r="I4" s="83" t="inlineStr">
+      <c r="I4" s="85" t="inlineStr">
         <is>
           <t>Data Quality Index</t>
         </is>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="84" t="n">
+      <c r="A5" s="86" t="n">
         <v>1650000</v>
       </c>
       <c r="B5" s="41" t="inlineStr">
@@ -5820,10 +5833,10 @@
       <c r="C5" s="23" t="n">
         <v>2754000</v>
       </c>
-      <c r="D5" s="84" t="n">
+      <c r="D5" s="86" t="n">
         <v>1706897</v>
       </c>
-      <c r="F5" s="84" t="n">
+      <c r="F5" s="86" t="n">
         <v>5530000</v>
       </c>
       <c r="G5" s="42" t="inlineStr">
@@ -5836,7 +5849,7 @@
           <t>73.1%</t>
         </is>
       </c>
-      <c r="I5" s="85" t="inlineStr">
+      <c r="I5" s="87" t="inlineStr">
         <is>
           <t>100.0% (Эталон)</t>
         </is>
@@ -5911,7 +5924,7 @@
       <c r="D9" s="26" t="n">
         <v>24</v>
       </c>
-      <c r="F9" s="79" t="inlineStr">
+      <c r="F9" s="80" t="inlineStr">
         <is>
           <t>D-104 (ООО Вектор)</t>
         </is>
@@ -5921,7 +5934,7 @@
           <t>КП без ответа &gt; 48ч</t>
         </is>
       </c>
-      <c r="H9" s="61" t="n">
+      <c r="H9" s="62" t="n">
         <v>850000</v>
       </c>
       <c r="I9" s="27" t="inlineStr">
@@ -5945,7 +5958,7 @@
       <c r="D10" s="26" t="n">
         <v>48</v>
       </c>
-      <c r="F10" s="79" t="inlineStr">
+      <c r="F10" s="80" t="inlineStr">
         <is>
           <t>D-103 (ИнвестХолдинг)</t>
         </is>
@@ -5955,7 +5968,7 @@
           <t>Просрочен счёт на оплату</t>
         </is>
       </c>
-      <c r="H10" s="61" t="n">
+      <c r="H10" s="62" t="n">
         <v>150000</v>
       </c>
       <c r="I10" s="27" t="inlineStr">
@@ -5979,7 +5992,7 @@
       <c r="D11" s="26" t="n">
         <v>120</v>
       </c>
-      <c r="F11" s="79" t="inlineStr">
+      <c r="F11" s="80" t="inlineStr">
         <is>
           <t>D-109 (ПромКомплект)</t>
         </is>
@@ -5989,7 +6002,7 @@
           <t>Критический брак речи (&lt;9)</t>
         </is>
       </c>
-      <c r="H11" s="61" t="n">
+      <c r="H11" s="62" t="n">
         <v>600000</v>
       </c>
       <c r="I11" s="27" t="inlineStr">
@@ -6013,7 +6026,7 @@
       <c r="D12" s="26" t="n">
         <v>48</v>
       </c>
-      <c r="F12" s="79" t="inlineStr">
+      <c r="F12" s="80" t="inlineStr">
         <is>
           <t>D-106 (СнабСервис)</t>
         </is>
@@ -6023,7 +6036,7 @@
           <t>Зависание на этапе КП</t>
         </is>
       </c>
-      <c r="H12" s="61" t="n">
+      <c r="H12" s="62" t="n">
         <v>280000</v>
       </c>
       <c r="I12" s="27" t="inlineStr">
@@ -6047,7 +6060,7 @@
       <c r="D13" s="26" t="n">
         <v>72</v>
       </c>
-      <c r="F13" s="79" t="inlineStr">
+      <c r="F13" s="80" t="inlineStr">
         <is>
           <t>D-107 (ТехноПром)</t>
         </is>
@@ -6057,7 +6070,7 @@
           <t>Крупная сделка без движения</t>
         </is>
       </c>
-      <c r="H13" s="61" t="n">
+      <c r="H13" s="62" t="n">
         <v>3000000</v>
       </c>
       <c r="I13" s="27" t="inlineStr">
@@ -6083,19 +6096,19 @@
       </c>
     </row>
     <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="93" t="inlineStr">
+      <c r="A16" s="97" t="inlineStr">
         <is>
           <t>🎯 ГЛАВНЫЙ ФОКУС РУКОВОДСТВА ДО КОНЦА МЕСЯЦА: Перехват сделки D-104 (850 000 ₽) и перераспределение 3 лидов с перегруженного РОПа на КАМов.</t>
         </is>
       </c>
-      <c r="B16" s="93" t="n"/>
-      <c r="C16" s="93" t="n"/>
-      <c r="D16" s="93" t="n"/>
-      <c r="E16" s="93" t="n"/>
-      <c r="F16" s="93" t="n"/>
-      <c r="G16" s="93" t="n"/>
-      <c r="H16" s="93" t="n"/>
-      <c r="I16" s="93" t="n"/>
+      <c r="B16" s="97" t="n"/>
+      <c r="C16" s="97" t="n"/>
+      <c r="D16" s="97" t="n"/>
+      <c r="E16" s="97" t="n"/>
+      <c r="F16" s="97" t="n"/>
+      <c r="G16" s="97" t="n"/>
+      <c r="H16" s="97" t="n"/>
+      <c r="I16" s="97" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -6151,32 +6164,32 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>⚡ Экспресс-Калькулятор</t>
+          <t>⚡ Калькулятор</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>📋 Пульт РОПа (15 мин)</t>
+          <t>📋 Пульт РОПа</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>🎙️ ИИ-Аудит звонков</t>
+          <t>🎙️ ИИ-Аудит</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>💸 7 Грехов (Диагностика)</t>
+          <t>💸 7 Грехов ОП</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>📄 Executive One-Pager</t>
+          <t>📄 One-Pager</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>🔐 152-ФЗ Безопасность</t>
+          <t>🔐 152-ФЗ</t>
         </is>
       </c>
     </row>
@@ -6223,7 +6236,7 @@
       <c r="A6" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="73" t="inlineStr">
+      <c r="B6" s="74" t="inlineStr">
         <is>
           <t>Локализация баз данных</t>
         </is>
@@ -6238,7 +6251,7 @@
           <t>Дата-центры в Москве (Yandex Cloud / Selectel), аттестация ФСТЭК УЗ 1-2</t>
         </is>
       </c>
-      <c r="E6" s="85" t="inlineStr">
+      <c r="E6" s="87" t="inlineStr">
         <is>
           <t>✅ 100% Соответствие</t>
         </is>
@@ -6253,7 +6266,7 @@
       <c r="A7" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="73" t="inlineStr">
+      <c r="B7" s="74" t="inlineStr">
         <is>
           <t>Криптографическая токенизация</t>
         </is>
@@ -6268,7 +6281,7 @@
           <t>Модуль PIISanitizer: замена телефонов, ФИО и карт на токены [PHONE_TOKEN_X]</t>
         </is>
       </c>
-      <c r="E7" s="85" t="inlineStr">
+      <c r="E7" s="87" t="inlineStr">
         <is>
           <t>✅ Автоматически</t>
         </is>
@@ -6283,7 +6296,7 @@
       <c r="A8" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="73" t="inlineStr">
+      <c r="B8" s="74" t="inlineStr">
         <is>
           <t>Срок хранения аудиозаписей</t>
         </is>
@@ -6298,7 +6311,7 @@
           <t>Автоматическое безвозвратное удаление исходных аудио через 30 дней</t>
         </is>
       </c>
-      <c r="E8" s="85" t="inlineStr">
+      <c r="E8" s="87" t="inlineStr">
         <is>
           <t>✅ Настроено в cron</t>
         </is>
@@ -6313,7 +6326,7 @@
       <c r="A9" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="73" t="inlineStr">
+      <c r="B9" s="74" t="inlineStr">
         <is>
           <t>Согласие сотрудников ОП</t>
         </is>
@@ -6328,7 +6341,7 @@
           <t>Готовый пакет документов: Приказ, Положение о контроле, Согласие</t>
         </is>
       </c>
-      <c r="E9" s="85" t="inlineStr">
+      <c r="E9" s="87" t="inlineStr">
         <is>
           <t>✅ Комплект включен</t>
         </is>
@@ -6343,7 +6356,7 @@
       <c r="A10" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="73" t="inlineStr">
+      <c r="B10" s="74" t="inlineStr">
         <is>
           <t>Юридический статус исполнителя</t>
         </is>
@@ -6358,7 +6371,7 @@
           <t>Плательщик НПД (Самозанятый), чек приложения «Мой Налог», договор, акт</t>
         </is>
       </c>
-      <c r="E10" s="85" t="inlineStr">
+      <c r="E10" s="87" t="inlineStr">
         <is>
           <t>✅ Безопасно для бухгалтерии</t>
         </is>
@@ -6373,7 +6386,7 @@
       <c r="A11" s="26" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="73" t="inlineStr">
+      <c r="B11" s="74" t="inlineStr">
         <is>
           <t>Гарантия конфиденциальности NDA</t>
         </is>
@@ -6388,7 +6401,7 @@
           <t>Подписание двустороннего соглашения о неразглашении конфиденциальных данных</t>
         </is>
       </c>
-      <c r="E11" s="85" t="inlineStr">
+      <c r="E11" s="87" t="inlineStr">
         <is>
           <t>✅ Подписание в ЭДО</t>
         </is>

--- a/web/RevOps_Platform_Demo_Sample.xlsx
+++ b/web/RevOps_Platform_Demo_Sample.xlsx
@@ -1207,8 +1207,9 @@
           <t>30% выручки теряется из-за ошибок менеджеров</t>
         </is>
       </c>
-      <c r="D15" s="28" t="n">
-        <v>412500</v>
+      <c r="D15" s="28">
+        <f>ROUND(H6*0.3968, -2)</f>
+        <v/>
       </c>
       <c r="E15" s="27" t="inlineStr">
         <is>
@@ -1237,8 +1238,9 @@
           <t>18% выручки теряется из-за просрочки follow-up</t>
         </is>
       </c>
-      <c r="D16" s="28" t="n">
-        <v>297000</v>
+      <c r="D16" s="28">
+        <f>ROUND(H6*0.2857, -2)</f>
+        <v/>
       </c>
       <c r="E16" s="27" t="inlineStr">
         <is>
@@ -1267,8 +1269,9 @@
           <t>8% — потенциал реактивации списанных сделок</t>
         </is>
       </c>
-      <c r="D17" s="28" t="n">
-        <v>132000</v>
+      <c r="D17" s="28">
+        <f>ROUND(H6*0.1270, -2)</f>
+        <v/>
       </c>
       <c r="E17" s="27" t="inlineStr">
         <is>
@@ -1297,8 +1300,9 @@
           <t>12% выставленных счетов с просрочкой 20+ дней</t>
         </is>
       </c>
-      <c r="D18" s="28" t="n">
-        <v>198000</v>
+      <c r="D18" s="28">
+        <f>H6-D15-D16-D17</f>
+        <v/>
       </c>
       <c r="E18" s="27" t="inlineStr">
         <is>
@@ -3665,7 +3669,7 @@
       <c r="U30" s="25" t="n"/>
       <c r="V30" s="25" t="n"/>
     </row>
-    <row r="31" ht="54" customHeight="1">
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" s="44" t="inlineStr">
         <is>
           <t>C-505</t>
@@ -3715,7 +3719,7 @@
       <c r="U31" s="77" t="n"/>
       <c r="V31" s="77" t="n"/>
     </row>
-    <row r="32" ht="54" customHeight="1">
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="44" t="inlineStr">
         <is>
           <t>C-503</t>
@@ -3765,7 +3769,7 @@
       <c r="U32" s="77" t="n"/>
       <c r="V32" s="77" t="n"/>
     </row>
-    <row r="33" ht="54" customHeight="1">
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="44" t="inlineStr">
         <is>
           <t>C-507</t>
@@ -3815,7 +3819,7 @@
       <c r="U33" s="77" t="n"/>
       <c r="V33" s="77" t="n"/>
     </row>
-    <row r="34" ht="54" customHeight="1">
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="44" t="inlineStr">
         <is>
           <t>C-508</t>
@@ -3865,7 +3869,7 @@
       <c r="U34" s="77" t="n"/>
       <c r="V34" s="77" t="n"/>
     </row>
-    <row r="35" ht="54" customHeight="1">
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="44" t="inlineStr">
         <is>
           <t>C-510</t>
@@ -3996,7 +4000,7 @@
       <c r="U38" s="25" t="n"/>
       <c r="V38" s="25" t="n"/>
     </row>
-    <row r="39" ht="34" customHeight="1">
+    <row r="39" ht="46" customHeight="1">
       <c r="A39" s="26" t="n">
         <v>1</v>
       </c>
@@ -4046,7 +4050,7 @@
       <c r="U39" s="74" t="n"/>
       <c r="V39" s="74" t="n"/>
     </row>
-    <row r="40" ht="34" customHeight="1">
+    <row r="40" ht="46" customHeight="1">
       <c r="A40" s="26" t="n">
         <v>2</v>
       </c>
@@ -4096,7 +4100,7 @@
       <c r="U40" s="74" t="n"/>
       <c r="V40" s="74" t="n"/>
     </row>
-    <row r="41" ht="34" customHeight="1">
+    <row r="41" ht="46" customHeight="1">
       <c r="A41" s="26" t="n">
         <v>3</v>
       </c>
@@ -4146,7 +4150,7 @@
       <c r="U41" s="74" t="n"/>
       <c r="V41" s="74" t="n"/>
     </row>
-    <row r="42" ht="34" customHeight="1">
+    <row r="42" ht="46" customHeight="1">
       <c r="A42" s="26" t="n">
         <v>4</v>
       </c>
@@ -4196,7 +4200,7 @@
       <c r="U42" s="74" t="n"/>
       <c r="V42" s="74" t="n"/>
     </row>
-    <row r="43" ht="34" customHeight="1">
+    <row r="43" ht="46" customHeight="1">
       <c r="A43" s="26" t="n">
         <v>5</v>
       </c>
@@ -4246,7 +4250,7 @@
       <c r="U43" s="74" t="n"/>
       <c r="V43" s="74" t="n"/>
     </row>
-    <row r="44" ht="34" customHeight="1">
+    <row r="44" ht="46" customHeight="1">
       <c r="A44" s="26" t="n">
         <v>6</v>
       </c>
@@ -4296,7 +4300,7 @@
       <c r="U44" s="74" t="n"/>
       <c r="V44" s="74" t="n"/>
     </row>
-    <row r="45" ht="34" customHeight="1">
+    <row r="45" ht="46" customHeight="1">
       <c r="A45" s="26" t="n">
         <v>7</v>
       </c>
@@ -4346,7 +4350,7 @@
       <c r="U45" s="74" t="n"/>
       <c r="V45" s="74" t="n"/>
     </row>
-    <row r="46" ht="34" customHeight="1">
+    <row r="46" ht="46" customHeight="1">
       <c r="A46" s="26" t="n">
         <v>8</v>
       </c>
@@ -4396,7 +4400,7 @@
       <c r="U46" s="74" t="n"/>
       <c r="V46" s="74" t="n"/>
     </row>
-    <row r="47" ht="34" customHeight="1">
+    <row r="47" ht="46" customHeight="1">
       <c r="A47" s="26" t="n">
         <v>9</v>
       </c>
@@ -4446,7 +4450,7 @@
       <c r="U47" s="74" t="n"/>
       <c r="V47" s="74" t="n"/>
     </row>
-    <row r="48" ht="34" customHeight="1">
+    <row r="48" ht="46" customHeight="1">
       <c r="A48" s="26" t="n">
         <v>10</v>
       </c>
@@ -4496,7 +4500,7 @@
       <c r="U48" s="74" t="n"/>
       <c r="V48" s="74" t="n"/>
     </row>
-    <row r="49" ht="34" customHeight="1">
+    <row r="49" ht="46" customHeight="1">
       <c r="A49" s="26" t="n">
         <v>11</v>
       </c>
@@ -4546,7 +4550,7 @@
       <c r="U49" s="74" t="n"/>
       <c r="V49" s="74" t="n"/>
     </row>
-    <row r="50" ht="34" customHeight="1">
+    <row r="50" ht="46" customHeight="1">
       <c r="A50" s="26" t="n">
         <v>12</v>
       </c>
@@ -4596,7 +4600,7 @@
       <c r="U50" s="74" t="n"/>
       <c r="V50" s="74" t="n"/>
     </row>
-    <row r="51" ht="34" customHeight="1">
+    <row r="51" ht="46" customHeight="1">
       <c r="A51" s="26" t="n">
         <v>13</v>
       </c>

--- a/web/RevOps_Platform_Demo_Sample.xlsx
+++ b/web/RevOps_Platform_Demo_Sample.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0 &quot;ср.&quot;"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -189,6 +189,12 @@
       <color rgb="001E293B"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0038BDF8"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -264,7 +270,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -300,11 +306,93 @@
         <color rgb="000F172A"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="double">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="double">
+        <color rgb="000F172A"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="001E293B"/>
+      </left>
+      <right style="thin">
+        <color rgb="001E293B"/>
+      </right>
+      <top style="thin">
+        <color rgb="00334155"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00334155"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -562,6 +650,110 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -948,50 +1140,46 @@
           <t>⚡ ЭКСПРЕСС-КАЛЬКУЛЯТОР УПУЩЕННОЙ ПРИБЫЛИ ОП (ДИАГНОСТИКА ЗА 30 СЕКУНД)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>⚡ Экспресс-Калькулятор</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>📋 Пульт РОПа (15 мин)</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>🎙️ ИИ-Аудит звонков</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>💸 7 Грехов (Диагностика)</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>📄 Executive One-Pager</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>🔐 152-ФЗ Безопасность</t>
-        </is>
-      </c>
-    </row>
+      <c r="A2" s="133">
+        <f>HYPERLINK("#'📄 Executive_OnePager'!A1", "📄 1. One-Pager")</f>
+        <v/>
+      </c>
+      <c r="B2" s="133">
+        <f>HYPERLINK("#'⚡ Пульс_Компании'!A1", "⚡ 2. Пульс компании")</f>
+        <v/>
+      </c>
+      <c r="C2" s="133">
+        <f>HYPERLINK("#'📋 Пульт_РОПа_15_Минут'!A1", "📋 3. Пульт РОПа")</f>
+        <v/>
+      </c>
+      <c r="D2" s="133">
+        <f>HYPERLINK("#'💸 Диагностика_Утечек_ОП'!A1", "💸 4. 7 Грехов ОП")</f>
+        <v/>
+      </c>
+      <c r="E2" s="133">
+        <f>HYPERLINK("#'🎯 Action_Center'!A1", "🎯 5. Action Center")</f>
+        <v/>
+      </c>
+      <c r="F2" s="133">
+        <f>HYPERLINK("#'🎙️ ИИ_Аудит'!A1", "🎙️ 6. ИИ-Аудит")</f>
+        <v/>
+      </c>
+      <c r="G2" s="133">
+        <f>HYPERLINK("#'⚡ Экспресс_Калькулятор_3_Цифры'!A1", "⚡ 7. Экспресс 3 цифры")</f>
+        <v/>
+      </c>
+      <c r="H2" s="133">
+        <f>HYPERLINK("#'🧪 QA_Suite'!A1", "🧪 8. QA Suite")</f>
+        <v/>
+      </c>
+      <c r="I2" s="133">
+        <f>HYPERLINK("#'⚙️ Настройки'!A1", "⚙️ 9. Настройки")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -1008,7 +1196,6 @@
           <t>Категория капитала</t>
         </is>
       </c>
-      <c r="H4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -1112,46 +1299,56 @@
         <v/>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="17" t="inlineStr">
         <is>
           <t>🔴 ВЫЯВЛЕННЫЙ РИСК ПОТЕРЬ</t>
         </is>
       </c>
+      <c r="B10" s="98" t="n"/>
       <c r="C10" s="18" t="inlineStr">
         <is>
           <t>🟢 КОНСЕРВАТИВНЫЙ (+15%)</t>
         </is>
       </c>
+      <c r="D10" s="98" t="n"/>
       <c r="E10" s="19" t="inlineStr">
         <is>
           <t>🚀 БАЗОВЫЙ ПЛАН (+30%)</t>
         </is>
       </c>
+      <c r="F10" s="98" t="n"/>
       <c r="G10" s="20" t="inlineStr">
         <is>
           <t>⭐ ОПТИМИСТИЧНЫЙ (+50%)</t>
         </is>
       </c>
+      <c r="H10" s="98" t="n"/>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="21">
         <f>H6</f>
         <v/>
       </c>
+      <c r="B11" s="98" t="n"/>
       <c r="C11" s="22">
         <f>H5*1.0945</f>
         <v/>
       </c>
+      <c r="D11" s="98" t="n"/>
       <c r="E11" s="23">
         <f>H5*1.189</f>
         <v/>
       </c>
+      <c r="F11" s="98" t="n"/>
       <c r="G11" s="24">
         <f>H5*1.315</f>
         <v/>
       </c>
-    </row>
+      <c r="H11" s="98" t="n"/>
+    </row>
+    <row r="12"/>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
@@ -1337,20 +1534,13 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="33" t="inlineStr">
         <is>
           <t>🎁 СЛЕДУЮЩИЙ ШАГ: БЕСПЛАТНЫЙ ТЕСТ-ДРАЙВ НА 3 ВАШИХ ЗВОНКАХ</t>
         </is>
       </c>
-      <c r="B21" s="33" t="n"/>
-      <c r="C21" s="33" t="n"/>
-      <c r="D21" s="33" t="n"/>
-      <c r="E21" s="33" t="n"/>
-      <c r="F21" s="33" t="n"/>
-      <c r="G21" s="33" t="n"/>
-      <c r="H21" s="33" t="n"/>
-      <c r="I21" s="33" t="n"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="34" t="inlineStr">
@@ -1358,14 +1548,6 @@
           <t>Хотите проверить эту математику на реальных данных вашей компании за 15 минут?</t>
         </is>
       </c>
-      <c r="B22" s="34" t="n"/>
-      <c r="C22" s="34" t="n"/>
-      <c r="D22" s="34" t="n"/>
-      <c r="E22" s="34" t="n"/>
-      <c r="F22" s="34" t="n"/>
-      <c r="G22" s="34" t="n"/>
-      <c r="H22" s="34" t="n"/>
-      <c r="I22" s="34" t="n"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="35" t="inlineStr">
@@ -1373,14 +1555,6 @@
           <t>👉 Отправьте 3 аудиозаписи любых вчерашних звонков ваших менеджеров в Telegram бот.</t>
         </is>
       </c>
-      <c r="B23" s="35" t="n"/>
-      <c r="C23" s="35" t="n"/>
-      <c r="D23" s="35" t="n"/>
-      <c r="E23" s="35" t="n"/>
-      <c r="F23" s="35" t="n"/>
-      <c r="G23" s="35" t="n"/>
-      <c r="H23" s="35" t="n"/>
-      <c r="I23" s="35" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="35" t="inlineStr">
@@ -1388,14 +1562,6 @@
           <t>ИИ бесплатно разберет их по 13 критериям, покажет ошибки речи и рассчитает точную сумму под угрозой слива.</t>
         </is>
       </c>
-      <c r="B24" s="35" t="n"/>
-      <c r="C24" s="35" t="n"/>
-      <c r="D24" s="35" t="n"/>
-      <c r="E24" s="35" t="n"/>
-      <c r="F24" s="35" t="n"/>
-      <c r="G24" s="35" t="n"/>
-      <c r="H24" s="35" t="n"/>
-      <c r="I24" s="35" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="36" t="inlineStr">
@@ -1403,14 +1569,6 @@
           <t>🚀 ЗАПУСТИТЬ БЕСПЛАТНЫЙ ТЕСТ-ДРАЙВ: @RevOps_Super_Audit_Bot (https://t.me/RevOps_Super_Audit_Bot)</t>
         </is>
       </c>
-      <c r="B25" s="36" t="n"/>
-      <c r="C25" s="36" t="n"/>
-      <c r="D25" s="36" t="n"/>
-      <c r="E25" s="36" t="n"/>
-      <c r="F25" s="36" t="n"/>
-      <c r="G25" s="36" t="n"/>
-      <c r="H25" s="36" t="n"/>
-      <c r="I25" s="36" t="n"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="37" t="inlineStr">
@@ -1418,14 +1576,6 @@
           <t>Нужен комплексный аудит отдела продаж? 👉 Экономика спринта оптимизации (450 000 ₽) на вкладке «4. 7 Грехов ОП»</t>
         </is>
       </c>
-      <c r="B26" s="37" t="n"/>
-      <c r="C26" s="37" t="n"/>
-      <c r="D26" s="37" t="n"/>
-      <c r="E26" s="37" t="n"/>
-      <c r="F26" s="37" t="n"/>
-      <c r="G26" s="37" t="n"/>
-      <c r="H26" s="37" t="n"/>
-      <c r="I26" s="37" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="38" t="inlineStr">
@@ -1433,28 +1583,17 @@
           <t>🔒 Конфиденциально • Без передачи персональных данных • Экспресс-разбор за 15 минут (152-ФЗ РФ)</t>
         </is>
       </c>
-      <c r="B27" s="38" t="n"/>
-      <c r="C27" s="38" t="n"/>
-      <c r="D27" s="38" t="n"/>
-      <c r="E27" s="38" t="n"/>
-      <c r="F27" s="38" t="n"/>
-      <c r="G27" s="38" t="n"/>
-      <c r="H27" s="38" t="n"/>
-      <c r="I27" s="38" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="20">
     <mergeCell ref="A25:I25"/>
-    <mergeCell ref="G2:H2"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="G11:H11"/>
     <mergeCell ref="A27:I27"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="A21:I21"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B2:C2"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="G10:H10"/>
     <mergeCell ref="A23:I23"/>
@@ -1486,7 +1625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1505,55 +1644,53 @@
           <t>📋 СТРАТЕГИЧЕСКИЙ ПУЛЬТ СОБСТВЕННИКА: «5 РЕШЕНИЙ МЕСЯЦА»</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>⚡ Экспресс-Калькулятор</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>📋 Пульт РОПа</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>🎙️ ИИ-Аудит</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>💸 7 Грехов ОП</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>📄 One-Pager</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>🔐 152-ФЗ Безопасность</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="n"/>
-    </row>
+      <c r="A2" s="133">
+        <f>HYPERLINK("#'📄 Executive_OnePager'!A1", "📄 1. One-Pager")</f>
+        <v/>
+      </c>
+      <c r="B2" s="133">
+        <f>HYPERLINK("#'⚡ Пульс_Компании'!A1", "⚡ 2. Пульс компании")</f>
+        <v/>
+      </c>
+      <c r="C2" s="133">
+        <f>HYPERLINK("#'📋 Пульт_РОПа_15_Минут'!A1", "📋 3. Пульт РОПа")</f>
+        <v/>
+      </c>
+      <c r="D2" s="133">
+        <f>HYPERLINK("#'💸 Диагностика_Утечек_ОП'!A1", "💸 4. 7 Грехов ОП")</f>
+        <v/>
+      </c>
+      <c r="E2" s="133">
+        <f>HYPERLINK("#'🎯 Action_Center'!A1", "🎯 5. Action Center")</f>
+        <v/>
+      </c>
+      <c r="F2" s="133">
+        <f>HYPERLINK("#'🎙️ ИИ_Аудит'!A1", "🎙️ 6. ИИ-Аудит")</f>
+        <v/>
+      </c>
+      <c r="G2" s="133">
+        <f>HYPERLINK("#'⚡ Экспресс_Калькулятор_3_Цифры'!A1", "⚡ 7. Экспресс 3 цифры")</f>
+        <v/>
+      </c>
+      <c r="H2" s="133">
+        <f>HYPERLINK("#'🧪 QA_Suite'!A1", "🧪 8. QA Suite")</f>
+        <v/>
+      </c>
+      <c r="I2" s="133">
+        <f>HYPERLINK("#'⚙️ Настройки'!A1", "⚙️ 9. Настройки")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Звонков за вчера</t>
         </is>
       </c>
-      <c r="B4" s="39" t="n"/>
+      <c r="B4" s="98" t="n"/>
       <c r="C4" s="40" t="inlineStr">
         <is>
           <t>Диалогов с браком (&lt;9)</t>
@@ -1574,14 +1711,14 @@
           <t>Статус дня для РОПа</t>
         </is>
       </c>
-      <c r="G4" s="40" t="n"/>
-      <c r="H4" s="40" t="n"/>
+      <c r="G4" s="99" t="n"/>
+      <c r="H4" s="98" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="B5" s="41" t="n"/>
+      <c r="B5" s="98" t="n"/>
       <c r="C5" s="42" t="n">
         <v>2</v>
       </c>
@@ -1596,9 +1733,10 @@
           <t>🚨 ТРЕБУЕТСЯ 15 МИНУТ КОНТРОЛЯ РОПа</t>
         </is>
       </c>
-      <c r="G5" s="43" t="n"/>
-      <c r="H5" s="43" t="n"/>
-    </row>
+      <c r="G5" s="99" t="n"/>
+      <c r="H5" s="98" t="n"/>
+    </row>
+    <row r="6"/>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -1867,6 +2005,8 @@
       </c>
       <c r="H14" s="29" t="n"/>
     </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17" ht="24" customHeight="1">
       <c r="E17" s="50" t="inlineStr">
         <is>
@@ -1885,8 +2025,8 @@
           <t>Проверка ночного ИИ-аудита: 2 звонка с браком (&lt;9 баллов)</t>
         </is>
       </c>
-      <c r="G18" s="51" t="n"/>
-      <c r="H18" s="51" t="n"/>
+      <c r="G18" s="99" t="n"/>
+      <c r="H18" s="98" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="E19" s="44" t="inlineStr">
@@ -1899,8 +2039,8 @@
           <t>Перехват сделки D-109 (600 т.р.) и звонок ЛПР до 12:00</t>
         </is>
       </c>
-      <c r="G19" s="51" t="n"/>
-      <c r="H19" s="51" t="n"/>
+      <c r="G19" s="99" t="n"/>
+      <c r="H19" s="98" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="E20" s="44" t="inlineStr">
@@ -1913,8 +2053,8 @@
           <t>Согласование спецусловий по D-104 (850 т.р.)</t>
         </is>
       </c>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="51" t="n"/>
+      <c r="G20" s="99" t="n"/>
+      <c r="H20" s="98" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="E21" s="44" t="inlineStr">
@@ -1927,8 +2067,8 @@
           <t>Делегирование 2 сделок с РОПа на свободного КАМа</t>
         </is>
       </c>
-      <c r="G21" s="51" t="n"/>
-      <c r="H21" s="51" t="n"/>
+      <c r="G21" s="99" t="n"/>
+      <c r="H21" s="98" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="E22" s="18" t="inlineStr">
@@ -1941,19 +2081,17 @@
           <t>2 730 000 ₽ защищено от слива за 15 минут</t>
         </is>
       </c>
-      <c r="G22" s="51" t="n"/>
-      <c r="H22" s="51" t="n"/>
+      <c r="G22" s="99" t="n"/>
+      <c r="H22" s="98" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="12">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="F20:H20"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="E17:H17"/>
     <mergeCell ref="F5:H5"/>
     <mergeCell ref="F19:H19"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="G2:H2"/>
     <mergeCell ref="F18:H18"/>
     <mergeCell ref="F22:H22"/>
     <mergeCell ref="A5:B5"/>
@@ -1982,18 +2120,18 @@
   <dimension ref="A1:V60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
@@ -2007,203 +2145,134 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="100" t="inlineStr">
         <is>
           <t>🎙️ ИИ-СУПЕРВАЙЗЕР ЗВОНКОВ: РЕЧЕВАЯ АНАЛИТИКА 100% ДИАЛОГОВ (WHISPER LARGE V3 + LLM)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
-      <c r="M1" s="2" t="n"/>
-      <c r="N1" s="2" t="n"/>
-      <c r="O1" s="2" t="n"/>
-      <c r="P1" s="2" t="n"/>
-      <c r="Q1" s="2" t="n"/>
-      <c r="R1" s="2" t="n"/>
-      <c r="S1" s="2" t="n"/>
-      <c r="T1" s="2" t="n"/>
-      <c r="U1" s="2" t="n"/>
-      <c r="V1" s="2" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>⚡ Экспресс-Калькулятор</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>📋 Пульт РОПа (15 мин)</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>🎙️ ИИ-Аудит звонков</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="A2" s="133">
+        <f>HYPERLINK("#'📄 Executive_OnePager'!A1", "📄 1. One-Pager")</f>
+        <v/>
+      </c>
+      <c r="B2" s="133">
+        <f>HYPERLINK("#'⚡ Пульс_Компании'!A1", "⚡ 2. Пульс компании")</f>
+        <v/>
+      </c>
+      <c r="C2" s="133">
+        <f>HYPERLINK("#'📋 Пульт_РОПа_15_Минут'!A1", "📋 3. Пульт РОПа")</f>
+        <v/>
+      </c>
+      <c r="D2" s="133">
+        <f>HYPERLINK("#'💸 Диагностика_Утечек_ОП'!A1", "💸 4. 7 Грехов ОП")</f>
+        <v/>
+      </c>
+      <c r="E2" s="133">
+        <f>HYPERLINK("#'🎯 Action_Center'!A1", "🎯 5. Action Center")</f>
+        <v/>
+      </c>
+      <c r="F2" s="133">
+        <f>HYPERLINK("#'🎙️ ИИ_Аудит'!A1", "🎙️ 6. ИИ-Аудит")</f>
+        <v/>
+      </c>
+      <c r="G2" s="133">
+        <f>HYPERLINK("#'⚡ Экспресс_Калькулятор_3_Цифры'!A1", "⚡ 7. Экспресс 3 цифры")</f>
+        <v/>
+      </c>
+      <c r="H2" s="133">
+        <f>HYPERLINK("#'🧪 QA_Suite'!A1", "🧪 8. QA Suite")</f>
+        <v/>
+      </c>
+      <c r="I2" s="133">
+        <f>HYPERLINK("#'⚙️ Настройки'!A1", "⚙️ 9. Настройки")</f>
+        <v/>
+      </c>
+      <c r="K2" s="102" t="inlineStr">
         <is>
           <t>💸 7 Грехов (Диагностика)</t>
         </is>
       </c>
-      <c r="L2" s="4" t="n"/>
-      <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="inlineStr">
+      <c r="N2" s="102" t="inlineStr">
         <is>
           <t>📄 Executive One-Pager</t>
         </is>
       </c>
-      <c r="O2" s="4" t="n"/>
-      <c r="P2" s="4" t="n"/>
       <c r="Q2" s="4" t="inlineStr">
         <is>
           <t>🔐 152-ФЗ Безопасность</t>
         </is>
       </c>
-      <c r="R2" s="4" t="n"/>
-      <c r="S2" s="4" t="n"/>
-      <c r="T2" s="4" t="n"/>
-      <c r="U2" s="4" t="n"/>
-      <c r="V2" s="4" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="95" t="inlineStr">
         <is>
           <t>Проанализировано звонков</t>
         </is>
       </c>
-      <c r="B3" s="39" t="n"/>
-      <c r="C3" s="53" t="inlineStr">
+      <c r="C3" s="96" t="inlineStr">
         <is>
           <t>Средний балл качества</t>
         </is>
       </c>
-      <c r="D3" s="53" t="n"/>
-      <c r="E3" s="54" t="inlineStr">
+      <c r="E3" s="103" t="inlineStr">
         <is>
           <t>Фиксация жесткого Next Step</t>
         </is>
       </c>
-      <c r="F3" s="54" t="n"/>
-      <c r="G3" s="40" t="inlineStr">
+      <c r="G3" s="84" t="inlineStr">
         <is>
           <t>Критический брак речи (&lt;9)</t>
         </is>
       </c>
-      <c r="H3" s="40" t="n"/>
-      <c r="I3" s="40" t="n"/>
-      <c r="J3" s="40" t="inlineStr">
+      <c r="J3" s="84" t="inlineStr">
         <is>
           <t>Выручка под угрозой слива</t>
         </is>
       </c>
-      <c r="K3" s="40" t="n"/>
-      <c r="L3" s="40" t="n"/>
-      <c r="M3" s="40" t="inlineStr">
+      <c r="M3" s="84" t="inlineStr">
         <is>
           <t>Вердикт ИИ-супервайзера</t>
         </is>
       </c>
-      <c r="N3" s="40" t="n"/>
-      <c r="O3" s="40" t="n"/>
-      <c r="P3" s="40" t="n"/>
-      <c r="Q3" s="40" t="n"/>
-      <c r="R3" s="40" t="n"/>
-      <c r="S3" s="40" t="n"/>
-      <c r="T3" s="40" t="n"/>
-      <c r="U3" s="40" t="n"/>
-      <c r="V3" s="40" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="41" t="inlineStr">
+      <c r="A4" s="104" t="inlineStr">
         <is>
           <t>25 звонков / сут</t>
         </is>
       </c>
-      <c r="B4" s="41" t="n"/>
-      <c r="C4" s="55" t="inlineStr">
+      <c r="C4" s="105" t="inlineStr">
         <is>
           <t>8.9 из 13</t>
         </is>
       </c>
-      <c r="D4" s="55" t="n"/>
-      <c r="E4" s="56" t="inlineStr">
+      <c r="E4" s="106" t="inlineStr">
         <is>
           <t>60.0% (норма ≥85%)</t>
         </is>
       </c>
-      <c r="F4" s="56" t="n"/>
-      <c r="G4" s="42" t="inlineStr">
+      <c r="G4" s="107" t="inlineStr">
         <is>
           <t>6 диалогов</t>
         </is>
       </c>
-      <c r="H4" s="42" t="n"/>
-      <c r="I4" s="42" t="n"/>
-      <c r="J4" s="21" t="n">
+      <c r="J4" s="108" t="n">
         <v>2840000</v>
       </c>
-      <c r="K4" s="21" t="n"/>
-      <c r="L4" s="21" t="n"/>
-      <c r="M4" s="57" t="inlineStr">
+      <c r="M4" s="109" t="inlineStr">
         <is>
           <t>🚨 ВЫСОКИЙ РИСК СЛИВА VIP-КЛИЕНТОВ (ТРЕБУЕТСЯ ВМЕШАТЕЛЬСТВО РОПа)</t>
         </is>
       </c>
-      <c r="N4" s="57" t="n"/>
-      <c r="O4" s="57" t="n"/>
-      <c r="P4" s="57" t="n"/>
-      <c r="Q4" s="57" t="n"/>
-      <c r="R4" s="57" t="n"/>
-      <c r="S4" s="57" t="n"/>
-      <c r="T4" s="57" t="n"/>
-      <c r="U4" s="57" t="n"/>
-      <c r="V4" s="57" t="n"/>
     </row>
     <row r="5" ht="12" customHeight="1"/>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="58" t="inlineStr">
+      <c r="A6" s="110" t="inlineStr">
         <is>
           <t>👥 РЕЙТИНГ МЕНЕДЖЕРОВ ОП ПО КАЧЕСТВУ РЕЧИ (ЛИДЕРБОРД РОПа)</t>
         </is>
       </c>
-      <c r="B6" s="58" t="n"/>
-      <c r="C6" s="58" t="n"/>
-      <c r="D6" s="58" t="n"/>
-      <c r="E6" s="58" t="n"/>
-      <c r="F6" s="58" t="n"/>
-      <c r="G6" s="58" t="n"/>
-      <c r="H6" s="58" t="n"/>
-      <c r="I6" s="58" t="n"/>
-      <c r="J6" s="58" t="n"/>
-      <c r="K6" s="58" t="n"/>
-      <c r="L6" s="58" t="n"/>
-      <c r="M6" s="58" t="n"/>
-      <c r="N6" s="58" t="n"/>
-      <c r="O6" s="58" t="n"/>
-      <c r="P6" s="58" t="n"/>
-      <c r="Q6" s="58" t="n"/>
-      <c r="R6" s="58" t="n"/>
-      <c r="S6" s="58" t="n"/>
-      <c r="T6" s="58" t="n"/>
-      <c r="U6" s="58" t="n"/>
-      <c r="V6" s="58" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="59" t="inlineStr">
@@ -2251,45 +2320,33 @@
           <t>Грейд ИИ</t>
         </is>
       </c>
-      <c r="J7" s="25" t="inlineStr">
+      <c r="J7" s="59" t="inlineStr">
         <is>
           <t>Статус и рекомендация РОПу</t>
         </is>
       </c>
-      <c r="K7" s="25" t="n"/>
-      <c r="L7" s="25" t="n"/>
-      <c r="M7" s="25" t="n"/>
-      <c r="N7" s="25" t="n"/>
-      <c r="O7" s="25" t="n"/>
-      <c r="P7" s="25" t="n"/>
-      <c r="Q7" s="25" t="n"/>
-      <c r="R7" s="25" t="n"/>
-      <c r="S7" s="25" t="n"/>
-      <c r="T7" s="25" t="n"/>
-      <c r="U7" s="25" t="n"/>
-      <c r="V7" s="25" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="A8" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="74" t="inlineStr">
         <is>
           <t>Алексей Мельников</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="111" t="n">
         <v>6</v>
       </c>
-      <c r="D8" s="60" t="n">
+      <c r="D8" s="112" t="n">
         <v>12.2</v>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="111" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="111" t="inlineStr">
         <is>
           <t>48% / 52%</t>
         </is>
@@ -2300,330 +2357,237 @@
       <c r="H8" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="18" t="inlineStr">
+      <c r="I8" s="113" t="inlineStr">
         <is>
           <t>⭐ А (Эталон)</t>
         </is>
       </c>
-      <c r="J8" s="61" t="inlineStr">
+      <c r="J8" s="27" t="inlineStr">
         <is>
           <t>Эталонный скрипт, рекомендован в базу знаний компании</t>
         </is>
       </c>
-      <c r="K8" s="61" t="n"/>
-      <c r="L8" s="61" t="n"/>
-      <c r="M8" s="61" t="n"/>
-      <c r="N8" s="61" t="n"/>
-      <c r="O8" s="61" t="n"/>
-      <c r="P8" s="61" t="n"/>
-      <c r="Q8" s="61" t="n"/>
-      <c r="R8" s="61" t="n"/>
-      <c r="S8" s="61" t="n"/>
-      <c r="T8" s="61" t="n"/>
-      <c r="U8" s="61" t="n"/>
-      <c r="V8" s="61" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="26" t="n">
+      <c r="A9" s="111" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="74" t="inlineStr">
         <is>
           <t>Елена Васильева</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C9" s="111" t="n">
         <v>5</v>
       </c>
-      <c r="D9" s="60" t="n">
+      <c r="D9" s="112" t="n">
         <v>10.8</v>
       </c>
-      <c r="E9" s="26" t="inlineStr">
+      <c r="E9" s="111" t="inlineStr">
         <is>
           <t>80.0%</t>
         </is>
       </c>
-      <c r="F9" s="26" t="inlineStr">
+      <c r="F9" s="111" t="inlineStr">
         <is>
           <t>51% / 49%</t>
         </is>
       </c>
-      <c r="G9" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="62" t="n">
+      <c r="G9" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="114" t="n">
         <v>160000</v>
       </c>
-      <c r="I9" s="18" t="inlineStr">
+      <c r="I9" s="113" t="inlineStr">
         <is>
           <t>🟢 B (Норма)</t>
         </is>
       </c>
-      <c r="J9" s="61" t="inlineStr">
+      <c r="J9" s="27" t="inlineStr">
         <is>
           <t>Высокая конверсия, мелкие замечания по регламенту встречи</t>
         </is>
       </c>
-      <c r="K9" s="61" t="n"/>
-      <c r="L9" s="61" t="n"/>
-      <c r="M9" s="61" t="n"/>
-      <c r="N9" s="61" t="n"/>
-      <c r="O9" s="61" t="n"/>
-      <c r="P9" s="61" t="n"/>
-      <c r="Q9" s="61" t="n"/>
-      <c r="R9" s="61" t="n"/>
-      <c r="S9" s="61" t="n"/>
-      <c r="T9" s="61" t="n"/>
-      <c r="U9" s="61" t="n"/>
-      <c r="V9" s="61" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="26" t="n">
+      <c r="A10" s="111" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="74" t="inlineStr">
         <is>
           <t>Анна Соколова</t>
         </is>
       </c>
-      <c r="C10" s="26" t="n">
+      <c r="C10" s="111" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="63" t="n">
+      <c r="D10" s="115" t="n">
         <v>8.4</v>
       </c>
-      <c r="E10" s="26" t="inlineStr">
+      <c r="E10" s="111" t="inlineStr">
         <is>
           <t>60.0%</t>
         </is>
       </c>
-      <c r="F10" s="26" t="inlineStr">
+      <c r="F10" s="111" t="inlineStr">
         <is>
           <t>58% / 42%</t>
         </is>
       </c>
-      <c r="G10" s="26" t="n">
+      <c r="G10" s="111" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="62" t="n">
+      <c r="H10" s="114" t="n">
         <v>480000</v>
       </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="I10" s="116" t="inlineStr">
         <is>
           <t>🟡 C (Зона риска)</t>
         </is>
       </c>
-      <c r="J10" s="61" t="inlineStr">
+      <c r="J10" s="27" t="inlineStr">
         <is>
           <t>Забывает фиксировать дату звонка, требуется тренинг</t>
         </is>
       </c>
-      <c r="K10" s="61" t="n"/>
-      <c r="L10" s="61" t="n"/>
-      <c r="M10" s="61" t="n"/>
-      <c r="N10" s="61" t="n"/>
-      <c r="O10" s="61" t="n"/>
-      <c r="P10" s="61" t="n"/>
-      <c r="Q10" s="61" t="n"/>
-      <c r="R10" s="61" t="n"/>
-      <c r="S10" s="61" t="n"/>
-      <c r="T10" s="61" t="n"/>
-      <c r="U10" s="61" t="n"/>
-      <c r="V10" s="61" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="26" t="n">
+      <c r="A11" s="111" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="74" t="inlineStr">
         <is>
           <t>Дмитрий Ковалев</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n">
+      <c r="C11" s="111" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="64" t="n">
+      <c r="D11" s="117" t="n">
         <v>6.2</v>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="111" t="inlineStr">
         <is>
           <t>40.0%</t>
         </is>
       </c>
-      <c r="F11" s="26" t="inlineStr">
+      <c r="F11" s="111" t="inlineStr">
         <is>
           <t>72% / 28%</t>
         </is>
       </c>
-      <c r="G11" s="26" t="n">
+      <c r="G11" s="111" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="62" t="n">
+      <c r="H11" s="114" t="n">
         <v>1100000</v>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I11" s="118" t="inlineStr">
         <is>
           <t>🔴 D (Брак речи)</t>
         </is>
       </c>
-      <c r="J11" s="61" t="inlineStr">
+      <c r="J11" s="27" t="inlineStr">
         <is>
           <t>Срыв контакта, перебивание клиента, демпинг скидок</t>
         </is>
       </c>
-      <c r="K11" s="61" t="n"/>
-      <c r="L11" s="61" t="n"/>
-      <c r="M11" s="61" t="n"/>
-      <c r="N11" s="61" t="n"/>
-      <c r="O11" s="61" t="n"/>
-      <c r="P11" s="61" t="n"/>
-      <c r="Q11" s="61" t="n"/>
-      <c r="R11" s="61" t="n"/>
-      <c r="S11" s="61" t="n"/>
-      <c r="T11" s="61" t="n"/>
-      <c r="U11" s="61" t="n"/>
-      <c r="V11" s="61" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="26" t="n">
+      <c r="A12" s="111" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="74" t="inlineStr">
         <is>
           <t>Иван Попов</t>
         </is>
       </c>
-      <c r="C12" s="26" t="n">
+      <c r="C12" s="111" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="64" t="n">
+      <c r="D12" s="117" t="n">
         <v>5.5</v>
       </c>
-      <c r="E12" s="26" t="inlineStr">
+      <c r="E12" s="111" t="inlineStr">
         <is>
           <t>25.0%</t>
         </is>
       </c>
-      <c r="F12" s="26" t="inlineStr">
+      <c r="F12" s="111" t="inlineStr">
         <is>
           <t>79% / 21%</t>
         </is>
       </c>
-      <c r="G12" s="26" t="n">
+      <c r="G12" s="111" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="62" t="n">
+      <c r="H12" s="114" t="n">
         <v>1100000</v>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I12" s="118" t="inlineStr">
         <is>
           <t>🔴 D (Брак речи)</t>
         </is>
       </c>
-      <c r="J12" s="61" t="inlineStr">
+      <c r="J12" s="27" t="inlineStr">
         <is>
           <t>Режим 'автоответчика', нет попыток закрытия на встречу</t>
         </is>
       </c>
-      <c r="K12" s="61" t="n"/>
-      <c r="L12" s="61" t="n"/>
-      <c r="M12" s="61" t="n"/>
-      <c r="N12" s="61" t="n"/>
-      <c r="O12" s="61" t="n"/>
-      <c r="P12" s="61" t="n"/>
-      <c r="Q12" s="61" t="n"/>
-      <c r="R12" s="61" t="n"/>
-      <c r="S12" s="61" t="n"/>
-      <c r="T12" s="61" t="n"/>
-      <c r="U12" s="61" t="n"/>
-      <c r="V12" s="61" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="29" t="inlineStr"/>
-      <c r="B13" s="30" t="inlineStr">
+      <c r="B13" s="119" t="inlineStr">
         <is>
           <t>ИТОГО ПО ОТДЕЛУ ПРОДАЖ:</t>
         </is>
       </c>
-      <c r="C13" s="65">
+      <c r="C13" s="120">
         <f>SUM(C8:C12)</f>
         <v/>
       </c>
-      <c r="D13" s="65" t="inlineStr">
+      <c r="D13" s="120" t="inlineStr">
         <is>
           <t>8.9 / 13</t>
         </is>
       </c>
-      <c r="E13" s="65" t="inlineStr">
+      <c r="E13" s="120" t="inlineStr">
         <is>
           <t>60.0%</t>
         </is>
       </c>
-      <c r="F13" s="65" t="inlineStr">
+      <c r="F13" s="120" t="inlineStr">
         <is>
           <t>61% / 39%</t>
         </is>
       </c>
-      <c r="G13" s="65">
+      <c r="G13" s="120">
         <f>SUM(G8:G12)</f>
         <v/>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="121">
         <f>SUM(H8:H12)</f>
         <v/>
       </c>
-      <c r="I13" s="66" t="inlineStr">
+      <c r="I13" s="122" t="inlineStr">
         <is>
           <t>⚠️ РИСК</t>
         </is>
       </c>
-      <c r="J13" s="67" t="inlineStr">
+      <c r="J13" s="123" t="inlineStr">
         <is>
           <t>Требуется экспресс-коучинг по отработке возражений</t>
         </is>
       </c>
-      <c r="K13" s="67" t="n"/>
-      <c r="L13" s="67" t="n"/>
-      <c r="M13" s="67" t="n"/>
-      <c r="N13" s="67" t="n"/>
-      <c r="O13" s="67" t="n"/>
-      <c r="P13" s="67" t="n"/>
-      <c r="Q13" s="67" t="n"/>
-      <c r="R13" s="67" t="n"/>
-      <c r="S13" s="67" t="n"/>
-      <c r="T13" s="67" t="n"/>
-      <c r="U13" s="67" t="n"/>
-      <c r="V13" s="67" t="n"/>
     </row>
     <row r="14" ht="12" customHeight="1"/>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="58" t="inlineStr">
+      <c r="A15" s="110" t="inlineStr">
         <is>
           <t>🔍 ДЕТАЛИЗИРОВАННАЯ МАТРИЦА ОЦЕНКИ ЗВОНКОВ ПО ВСЕМ 13 КРИТЕРИЯМ (0 / 1)</t>
         </is>
       </c>
-      <c r="B15" s="58" t="n"/>
-      <c r="C15" s="58" t="n"/>
-      <c r="D15" s="58" t="n"/>
-      <c r="E15" s="58" t="n"/>
-      <c r="F15" s="58" t="n"/>
-      <c r="G15" s="58" t="n"/>
-      <c r="H15" s="58" t="n"/>
-      <c r="I15" s="58" t="n"/>
-      <c r="J15" s="58" t="n"/>
-      <c r="K15" s="58" t="n"/>
-      <c r="L15" s="58" t="n"/>
-      <c r="M15" s="58" t="n"/>
-      <c r="N15" s="58" t="n"/>
-      <c r="O15" s="58" t="n"/>
-      <c r="P15" s="58" t="n"/>
-      <c r="Q15" s="58" t="n"/>
-      <c r="R15" s="58" t="n"/>
-      <c r="S15" s="58" t="n"/>
-      <c r="T15" s="58" t="n"/>
-      <c r="U15" s="58" t="n"/>
-      <c r="V15" s="58" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="59" t="inlineStr">
@@ -2738,56 +2702,56 @@
       </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="44" t="inlineStr">
+      <c r="A17" s="124" t="inlineStr">
         <is>
           <t>C-501</t>
         </is>
       </c>
-      <c r="B17" s="61" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>D-101 (ООО Вектор Плюс)</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C17" s="111" t="inlineStr">
         <is>
           <t>Мельников</t>
         </is>
       </c>
-      <c r="D17" s="68" t="n">
+      <c r="D17" s="125" t="n">
         <v>850000</v>
       </c>
-      <c r="E17" s="26" t="inlineStr">
+      <c r="E17" s="111" t="inlineStr">
         <is>
           <t>05:40</t>
         </is>
       </c>
-      <c r="F17" s="26" t="inlineStr">
+      <c r="F17" s="111" t="inlineStr">
         <is>
           <t>КП отправлено</t>
         </is>
       </c>
-      <c r="G17" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="K17" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="L17" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" s="69" t="n">
+      <c r="G17" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" s="126" t="n">
         <v>1</v>
       </c>
       <c r="O17" s="69" t="n">
@@ -2819,56 +2783,56 @@
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="44" t="inlineStr">
+      <c r="A18" s="124" t="inlineStr">
         <is>
           <t>C-502</t>
         </is>
       </c>
-      <c r="B18" s="61" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>D-104 (ООО Вектор Плюс)</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="111" t="inlineStr">
         <is>
           <t>Васильева</t>
         </is>
       </c>
-      <c r="D18" s="68" t="n">
+      <c r="D18" s="125" t="n">
         <v>850000</v>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="111" t="inlineStr">
         <is>
           <t>04:20</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="111" t="inlineStr">
         <is>
           <t>Переговоры</t>
         </is>
       </c>
-      <c r="G18" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" s="69" t="n">
+      <c r="G18" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="126" t="n">
         <v>1</v>
       </c>
       <c r="L18" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" s="69" t="n">
+      <c r="M18" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="126" t="n">
         <v>1</v>
       </c>
       <c r="O18" s="69" t="n">
@@ -2900,30 +2864,30 @@
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="44" t="inlineStr">
+      <c r="A19" s="124" t="inlineStr">
         <is>
           <t>C-503</t>
         </is>
       </c>
-      <c r="B19" s="61" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>D-106 (ООО СнабСервис)</t>
         </is>
       </c>
-      <c r="C19" s="26" t="inlineStr">
+      <c r="C19" s="111" t="inlineStr">
         <is>
           <t>Соколова</t>
         </is>
       </c>
-      <c r="D19" s="68" t="n">
+      <c r="D19" s="125" t="n">
         <v>280000</v>
       </c>
-      <c r="E19" s="26" t="inlineStr">
+      <c r="E19" s="111" t="inlineStr">
         <is>
           <t>03:10</t>
         </is>
       </c>
-      <c r="F19" s="26" t="inlineStr">
+      <c r="F19" s="111" t="inlineStr">
         <is>
           <t>Встреча/Демо</t>
         </is>
@@ -2931,22 +2895,22 @@
       <c r="G19" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="69" t="n">
+      <c r="H19" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="126" t="n">
         <v>1</v>
       </c>
       <c r="J19" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="69" t="n">
+      <c r="K19" s="126" t="n">
         <v>1</v>
       </c>
       <c r="L19" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="69" t="n">
+      <c r="M19" s="126" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="70" t="n">
@@ -2981,50 +2945,50 @@
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="44" t="inlineStr">
+      <c r="A20" s="124" t="inlineStr">
         <is>
           <t>C-504</t>
         </is>
       </c>
-      <c r="B20" s="61" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>D-107 (ООО ТехноПром)</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="C20" s="111" t="inlineStr">
         <is>
           <t>Соколова</t>
         </is>
       </c>
-      <c r="D20" s="68" t="n">
+      <c r="D20" s="125" t="n">
         <v>150000</v>
       </c>
-      <c r="E20" s="26" t="inlineStr">
+      <c r="E20" s="111" t="inlineStr">
         <is>
           <t>06:15</t>
         </is>
       </c>
-      <c r="F20" s="26" t="inlineStr">
+      <c r="F20" s="111" t="inlineStr">
         <is>
           <t>Квалификация</t>
         </is>
       </c>
-      <c r="G20" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="69" t="n">
+      <c r="G20" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="126" t="n">
         <v>1</v>
       </c>
       <c r="J20" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="L20" s="69" t="n">
+      <c r="K20" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="126" t="n">
         <v>1</v>
       </c>
       <c r="M20" s="70" t="n">
@@ -3062,30 +3026,30 @@
       </c>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="44" t="inlineStr">
+      <c r="A21" s="124" t="inlineStr">
         <is>
           <t>C-505</t>
         </is>
       </c>
-      <c r="B21" s="61" t="inlineStr">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>D-109 (ООО ПромКомплект)</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
+      <c r="C21" s="111" t="inlineStr">
         <is>
           <t>Ковалев</t>
         </is>
       </c>
-      <c r="D21" s="68" t="n">
+      <c r="D21" s="125" t="n">
         <v>600000</v>
       </c>
-      <c r="E21" s="26" t="inlineStr">
+      <c r="E21" s="111" t="inlineStr">
         <is>
           <t>03:30</t>
         </is>
       </c>
-      <c r="F21" s="26" t="inlineStr">
+      <c r="F21" s="111" t="inlineStr">
         <is>
           <t>КП отправлено</t>
         </is>
@@ -3143,56 +3107,56 @@
       </c>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="44" t="inlineStr">
+      <c r="A22" s="124" t="inlineStr">
         <is>
           <t>C-506</t>
         </is>
       </c>
-      <c r="B22" s="61" t="inlineStr">
+      <c r="B22" s="27" t="inlineStr">
         <is>
           <t>D-111 (ООО Глобал Инвест)</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C22" s="111" t="inlineStr">
         <is>
           <t>Мельников</t>
         </is>
       </c>
-      <c r="D22" s="68" t="n">
+      <c r="D22" s="125" t="n">
         <v>3000000</v>
       </c>
-      <c r="E22" s="26" t="inlineStr">
+      <c r="E22" s="111" t="inlineStr">
         <is>
           <t>07:15</t>
         </is>
       </c>
-      <c r="F22" s="26" t="inlineStr">
+      <c r="F22" s="111" t="inlineStr">
         <is>
           <t>Финальные условия</t>
         </is>
       </c>
-      <c r="G22" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="K22" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="M22" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" s="69" t="n">
+      <c r="G22" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="L22" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" s="126" t="n">
         <v>1</v>
       </c>
       <c r="O22" s="69" t="n">
@@ -3224,30 +3188,30 @@
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="44" t="inlineStr">
+      <c r="A23" s="124" t="inlineStr">
         <is>
           <t>C-507</t>
         </is>
       </c>
-      <c r="B23" s="61" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>D-114 (ООО АльфаТрейд)</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C23" s="111" t="inlineStr">
         <is>
           <t>Ковалев</t>
         </is>
       </c>
-      <c r="D23" s="68" t="n">
+      <c r="D23" s="125" t="n">
         <v>500000</v>
       </c>
-      <c r="E23" s="26" t="inlineStr">
+      <c r="E23" s="111" t="inlineStr">
         <is>
           <t>04:45</t>
         </is>
       </c>
-      <c r="F23" s="26" t="inlineStr">
+      <c r="F23" s="111" t="inlineStr">
         <is>
           <t>Дожим договора</t>
         </is>
@@ -3255,10 +3219,10 @@
       <c r="G23" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" s="69" t="n">
+      <c r="H23" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" s="126" t="n">
         <v>1</v>
       </c>
       <c r="J23" s="70" t="n">
@@ -3270,7 +3234,7 @@
       <c r="L23" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="M23" s="69" t="n">
+      <c r="M23" s="126" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="70" t="n">
@@ -3305,30 +3269,30 @@
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="44" t="inlineStr">
+      <c r="A24" s="124" t="inlineStr">
         <is>
           <t>C-508</t>
         </is>
       </c>
-      <c r="B24" s="61" t="inlineStr">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>D-118 (ООО СтройХолдинг)</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C24" s="111" t="inlineStr">
         <is>
           <t>Попов</t>
         </is>
       </c>
-      <c r="D24" s="68" t="n">
+      <c r="D24" s="125" t="n">
         <v>650000</v>
       </c>
-      <c r="E24" s="26" t="inlineStr">
+      <c r="E24" s="111" t="inlineStr">
         <is>
           <t>02:50</t>
         </is>
       </c>
-      <c r="F24" s="26" t="inlineStr">
+      <c r="F24" s="111" t="inlineStr">
         <is>
           <t>Входящий лид</t>
         </is>
@@ -3339,7 +3303,7 @@
       <c r="H24" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="I24" s="69" t="n">
+      <c r="I24" s="126" t="n">
         <v>1</v>
       </c>
       <c r="J24" s="70" t="n">
@@ -3386,53 +3350,53 @@
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="44" t="inlineStr">
+      <c r="A25" s="124" t="inlineStr">
         <is>
           <t>C-509</t>
         </is>
       </c>
-      <c r="B25" s="61" t="inlineStr">
+      <c r="B25" s="27" t="inlineStr">
         <is>
           <t>D-121 (ООО СпецМаш)</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
+      <c r="C25" s="111" t="inlineStr">
         <is>
           <t>Васильева</t>
         </is>
       </c>
-      <c r="D25" s="68" t="n">
+      <c r="D25" s="125" t="n">
         <v>420000</v>
       </c>
-      <c r="E25" s="26" t="inlineStr">
+      <c r="E25" s="111" t="inlineStr">
         <is>
           <t>05:10</t>
         </is>
       </c>
-      <c r="F25" s="26" t="inlineStr">
+      <c r="F25" s="111" t="inlineStr">
         <is>
           <t>Презентация КП</t>
         </is>
       </c>
-      <c r="G25" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="K25" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="M25" s="69" t="n">
+      <c r="G25" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" s="126" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="70" t="n">
@@ -3467,30 +3431,30 @@
       </c>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="44" t="inlineStr">
+      <c r="A26" s="124" t="inlineStr">
         <is>
           <t>C-510</t>
         </is>
       </c>
-      <c r="B26" s="61" t="inlineStr">
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>D-125 (ООО МегаТранс)</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="C26" s="111" t="inlineStr">
         <is>
           <t>Попов</t>
         </is>
       </c>
-      <c r="D26" s="68" t="n">
+      <c r="D26" s="125" t="n">
         <v>450000</v>
       </c>
-      <c r="E26" s="26" t="inlineStr">
+      <c r="E26" s="111" t="inlineStr">
         <is>
           <t>03:40</t>
         </is>
       </c>
-      <c r="F26" s="26" t="inlineStr">
+      <c r="F26" s="111" t="inlineStr">
         <is>
           <t>Квалификация</t>
         </is>
@@ -3504,16 +3468,16 @@
       <c r="I26" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="69" t="n">
-        <v>1</v>
-      </c>
-      <c r="K26" s="69" t="n">
+      <c r="J26" s="126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="126" t="n">
         <v>1</v>
       </c>
       <c r="L26" s="70" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="69" t="n">
+      <c r="M26" s="126" t="n">
         <v>1</v>
       </c>
       <c r="N26" s="70" t="n">
@@ -3548,14 +3512,12 @@
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="30" t="inlineStr">
+      <c r="A27" s="119" t="inlineStr">
         <is>
           <t>ИТОГО ПОТЕРЬ И РИСКОВ ПО ЗВОНКАМ:</t>
         </is>
       </c>
-      <c r="B27" s="30" t="n"/>
-      <c r="C27" s="30" t="n"/>
-      <c r="D27" s="71">
+      <c r="D27" s="127">
         <f>SUM(D17:D26)</f>
         <v/>
       </c>
@@ -3590,87 +3552,51 @@
     </row>
     <row r="28" ht="12" customHeight="1"/>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="58" t="inlineStr">
+      <c r="A29" s="110" t="inlineStr">
         <is>
           <t>🚨 РЕЕСТР ДЕФЕКТОВ РЕЧИ: РАСШИФРОВАННЫЕ ЦИТАТЫ ИЗ РАЗГОВОРОВ И РЕШЕНИЯ РОПа</t>
         </is>
       </c>
-      <c r="B29" s="58" t="n"/>
-      <c r="C29" s="58" t="n"/>
-      <c r="D29" s="58" t="n"/>
-      <c r="E29" s="58" t="n"/>
-      <c r="F29" s="58" t="n"/>
-      <c r="G29" s="58" t="n"/>
-      <c r="H29" s="58" t="n"/>
-      <c r="I29" s="58" t="n"/>
-      <c r="J29" s="58" t="n"/>
-      <c r="K29" s="58" t="n"/>
-      <c r="L29" s="58" t="n"/>
-      <c r="M29" s="58" t="n"/>
-      <c r="N29" s="58" t="n"/>
-      <c r="O29" s="58" t="n"/>
-      <c r="P29" s="58" t="n"/>
-      <c r="Q29" s="58" t="n"/>
-      <c r="R29" s="58" t="n"/>
-      <c r="S29" s="58" t="n"/>
-      <c r="T29" s="58" t="n"/>
-      <c r="U29" s="58" t="n"/>
-      <c r="V29" s="58" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="59" t="inlineStr">
         <is>
           <t>Call ID</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B30" s="59" t="inlineStr">
         <is>
           <t>Сделка / Контрагент</t>
         </is>
       </c>
-      <c r="C30" s="25" t="inlineStr">
+      <c r="C30" s="59" t="inlineStr">
         <is>
           <t>Менеджер</t>
         </is>
       </c>
-      <c r="D30" s="25" t="inlineStr">
+      <c r="D30" s="59" t="inlineStr">
         <is>
           <t>Сумма в риске</t>
         </is>
       </c>
-      <c r="E30" s="25" t="inlineStr">
+      <c r="E30" s="59" t="inlineStr">
         <is>
           <t>Критический дефект речи</t>
         </is>
       </c>
-      <c r="F30" s="25" t="n"/>
-      <c r="G30" s="25" t="inlineStr">
+      <c r="G30" s="59" t="inlineStr">
         <is>
           <t>💬 Цитата из диалога (Расшифровка Whisper Large V3)</t>
         </is>
       </c>
-      <c r="H30" s="25" t="n"/>
-      <c r="I30" s="25" t="n"/>
-      <c r="J30" s="25" t="n"/>
-      <c r="K30" s="25" t="n"/>
-      <c r="L30" s="25" t="n"/>
-      <c r="M30" s="25" t="n"/>
-      <c r="N30" s="25" t="inlineStr">
+      <c r="N30" s="59" t="inlineStr">
         <is>
           <t>🤖 Решение ИИ и Срочное действие РОПа</t>
         </is>
       </c>
-      <c r="O30" s="25" t="n"/>
-      <c r="P30" s="25" t="n"/>
-      <c r="Q30" s="25" t="n"/>
-      <c r="R30" s="25" t="n"/>
-      <c r="S30" s="25" t="n"/>
-      <c r="T30" s="25" t="n"/>
-      <c r="U30" s="25" t="n"/>
-      <c r="V30" s="25" t="n"/>
     </row>
     <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="44" t="inlineStr">
+      <c r="A31" s="124" t="inlineStr">
         <is>
           <t>C-505</t>
         </is>
@@ -3680,12 +3606,12 @@
           <t>D-109 (ООО «ПромКомплект»)</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="C31" s="111" t="inlineStr">
         <is>
           <t>Дмитрий Ковалев</t>
         </is>
       </c>
-      <c r="D31" s="62" t="n">
+      <c r="D31" s="114" t="n">
         <v>600000</v>
       </c>
       <c r="E31" s="75" t="inlineStr">
@@ -3693,34 +3619,19 @@
           <t>Срыв контакта / грубость при цене</t>
         </is>
       </c>
-      <c r="F31" s="75" t="n"/>
       <c r="G31" s="76" t="inlineStr">
         <is>
           <t>Клиент: «Почему у вас смета на 15% выше рынка?» → Менеджер: «Не знаю, везде всё дорожает. Не устраивает — берите у конкурентов без гарантии»</t>
         </is>
       </c>
-      <c r="H31" s="76" t="n"/>
-      <c r="I31" s="76" t="n"/>
-      <c r="J31" s="76" t="n"/>
-      <c r="K31" s="76" t="n"/>
-      <c r="L31" s="76" t="n"/>
-      <c r="M31" s="76" t="n"/>
       <c r="N31" s="77" t="inlineStr">
         <is>
           <t>🚨 Экстренный звонок РОПа ЛПР до 12:00: принести извинения за консультацию, перехватить сделку, дать проект со спец-гарантией 24 мес.</t>
         </is>
       </c>
-      <c r="O31" s="77" t="n"/>
-      <c r="P31" s="77" t="n"/>
-      <c r="Q31" s="77" t="n"/>
-      <c r="R31" s="77" t="n"/>
-      <c r="S31" s="77" t="n"/>
-      <c r="T31" s="77" t="n"/>
-      <c r="U31" s="77" t="n"/>
-      <c r="V31" s="77" t="n"/>
     </row>
     <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="44" t="inlineStr">
+      <c r="A32" s="124" t="inlineStr">
         <is>
           <t>C-503</t>
         </is>
@@ -3730,12 +3641,12 @@
           <t>D-106 (ООО «СнабСервис»)</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="C32" s="111" t="inlineStr">
         <is>
           <t>Анна Соколова</t>
         </is>
       </c>
-      <c r="D32" s="62" t="n">
+      <c r="D32" s="114" t="n">
         <v>280000</v>
       </c>
       <c r="E32" s="75" t="inlineStr">
@@ -3743,34 +3654,19 @@
           <t>Слив жесткого Next Step (в никуда)</t>
         </is>
       </c>
-      <c r="F32" s="75" t="n"/>
       <c r="G32" s="76" t="inlineStr">
         <is>
           <t>Менеджер: «Я вам КП на почту сбросила, посмотрите когда время будет». Клиент: «Хорошо, если что наберу»</t>
         </is>
       </c>
-      <c r="H32" s="76" t="n"/>
-      <c r="I32" s="76" t="n"/>
-      <c r="J32" s="76" t="n"/>
-      <c r="K32" s="76" t="n"/>
-      <c r="L32" s="76" t="n"/>
-      <c r="M32" s="76" t="n"/>
       <c r="N32" s="77" t="inlineStr">
         <is>
           <t>Направить клиенту в WhatsApp 2 конкретных слота встречи (сегодня 16:00 / завтра 11:30) с демонстрацией интеграции с CRM.</t>
         </is>
       </c>
-      <c r="O32" s="77" t="n"/>
-      <c r="P32" s="77" t="n"/>
-      <c r="Q32" s="77" t="n"/>
-      <c r="R32" s="77" t="n"/>
-      <c r="S32" s="77" t="n"/>
-      <c r="T32" s="77" t="n"/>
-      <c r="U32" s="77" t="n"/>
-      <c r="V32" s="77" t="n"/>
     </row>
     <row r="33" ht="60" customHeight="1">
-      <c r="A33" s="44" t="inlineStr">
+      <c r="A33" s="124" t="inlineStr">
         <is>
           <t>C-507</t>
         </is>
@@ -3780,12 +3676,12 @@
           <t>D-114 (ООО «АльфаТрейд»)</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
+      <c r="C33" s="111" t="inlineStr">
         <is>
           <t>Дмитрий Ковалев</t>
         </is>
       </c>
-      <c r="D33" s="62" t="n">
+      <c r="D33" s="114" t="n">
         <v>500000</v>
       </c>
       <c r="E33" s="75" t="inlineStr">
@@ -3793,34 +3689,19 @@
           <t>Необоснованная скидка вместо ценности</t>
         </is>
       </c>
-      <c r="F33" s="75" t="n"/>
       <c r="G33" s="76" t="inlineStr">
         <is>
           <t>Клиент: «У нас бюджет строго ограничен». Менеджер: «Ну ладно, согласую вам скидку 10% прямо сейчас»</t>
         </is>
       </c>
-      <c r="H33" s="76" t="n"/>
-      <c r="I33" s="76" t="n"/>
-      <c r="J33" s="76" t="n"/>
-      <c r="K33" s="76" t="n"/>
-      <c r="L33" s="76" t="n"/>
-      <c r="M33" s="76" t="n"/>
       <c r="N33" s="77" t="inlineStr">
         <is>
           <t>Заблокировать выставление счета со скидкой в CRM. РОПу пересогласовать условия: скидка 5% только в обмен на 100% предоплату за 24ч.</t>
         </is>
       </c>
-      <c r="O33" s="77" t="n"/>
-      <c r="P33" s="77" t="n"/>
-      <c r="Q33" s="77" t="n"/>
-      <c r="R33" s="77" t="n"/>
-      <c r="S33" s="77" t="n"/>
-      <c r="T33" s="77" t="n"/>
-      <c r="U33" s="77" t="n"/>
-      <c r="V33" s="77" t="n"/>
     </row>
     <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="44" t="inlineStr">
+      <c r="A34" s="124" t="inlineStr">
         <is>
           <t>C-508</t>
         </is>
@@ -3830,12 +3711,12 @@
           <t>D-118 (ООО «СтройХолдинг»)</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="C34" s="111" t="inlineStr">
         <is>
           <t>Иван Попов</t>
         </is>
       </c>
-      <c r="D34" s="62" t="n">
+      <c r="D34" s="114" t="n">
         <v>650000</v>
       </c>
       <c r="E34" s="75" t="inlineStr">
@@ -3843,34 +3724,19 @@
           <t>Слив возражения «Я подумаю»</t>
         </is>
       </c>
-      <c r="F34" s="75" t="n"/>
       <c r="G34" s="76" t="inlineStr">
         <is>
           <t>Клиент: «Нам нужно всё обдумать и посоветоваться с руководством». Менеджер: «Да, конечно, думайте» (повесил трубку)</t>
         </is>
       </c>
-      <c r="H34" s="76" t="n"/>
-      <c r="I34" s="76" t="n"/>
-      <c r="J34" s="76" t="n"/>
-      <c r="K34" s="76" t="n"/>
-      <c r="L34" s="76" t="n"/>
-      <c r="M34" s="76" t="n"/>
       <c r="N34" s="77" t="inlineStr">
         <is>
           <t>Передать лида старшему КАМу. Отправить в WhatsApp отраслевой кейс с аналогичным объектом и окупаемостью за 21 день.</t>
         </is>
       </c>
-      <c r="O34" s="77" t="n"/>
-      <c r="P34" s="77" t="n"/>
-      <c r="Q34" s="77" t="n"/>
-      <c r="R34" s="77" t="n"/>
-      <c r="S34" s="77" t="n"/>
-      <c r="T34" s="77" t="n"/>
-      <c r="U34" s="77" t="n"/>
-      <c r="V34" s="77" t="n"/>
     </row>
     <row r="35" ht="60" customHeight="1">
-      <c r="A35" s="44" t="inlineStr">
+      <c r="A35" s="124" t="inlineStr">
         <is>
           <t>C-510</t>
         </is>
@@ -3880,12 +3746,12 @@
           <t>D-125 (ООО «МегаТранс»)</t>
         </is>
       </c>
-      <c r="C35" s="26" t="inlineStr">
+      <c r="C35" s="111" t="inlineStr">
         <is>
           <t>Иван Попов</t>
         </is>
       </c>
-      <c r="D35" s="62" t="n">
+      <c r="D35" s="114" t="n">
         <v>450000</v>
       </c>
       <c r="E35" s="75" t="inlineStr">
@@ -3893,128 +3759,77 @@
           <t>Режим автоответчика, не выявлен ЛПР</t>
         </is>
       </c>
-      <c r="F35" s="75" t="n"/>
       <c r="G35" s="76" t="inlineStr">
         <is>
           <t>Менеджер 5 минут зачитывал прайс-лист секретарю, не спросив, кто принимает решение по закупкам</t>
         </is>
       </c>
-      <c r="H35" s="76" t="n"/>
-      <c r="I35" s="76" t="n"/>
-      <c r="J35" s="76" t="n"/>
-      <c r="K35" s="76" t="n"/>
-      <c r="L35" s="76" t="n"/>
-      <c r="M35" s="76" t="n"/>
       <c r="N35" s="77" t="inlineStr">
         <is>
           <t>Разбор на летучке: регламент квалификации BANT. Назначить повторный звонок с прямым выходом на генерального директора.</t>
         </is>
       </c>
-      <c r="O35" s="77" t="n"/>
-      <c r="P35" s="77" t="n"/>
-      <c r="Q35" s="77" t="n"/>
-      <c r="R35" s="77" t="n"/>
-      <c r="S35" s="77" t="n"/>
-      <c r="T35" s="77" t="n"/>
-      <c r="U35" s="77" t="n"/>
-      <c r="V35" s="77" t="n"/>
     </row>
     <row r="36" ht="12" customHeight="1"/>
     <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="58" t="inlineStr">
+      <c r="A37" s="110" t="inlineStr">
         <is>
           <t>📋 ЭТАЛОННЫЙ СТАНДАРТ 13 КРИТЕРИЕВ ОЦЕНКИ B2B-ДИАЛОГОВ (WHISPER LARGE V3 + LLM SUPERVISOR)</t>
         </is>
       </c>
-      <c r="B37" s="58" t="n"/>
-      <c r="C37" s="58" t="n"/>
-      <c r="D37" s="58" t="n"/>
-      <c r="E37" s="58" t="n"/>
-      <c r="F37" s="58" t="n"/>
-      <c r="G37" s="58" t="n"/>
-      <c r="H37" s="58" t="n"/>
-      <c r="I37" s="58" t="n"/>
-      <c r="J37" s="58" t="n"/>
-      <c r="K37" s="58" t="n"/>
-      <c r="L37" s="58" t="n"/>
-      <c r="M37" s="58" t="n"/>
-      <c r="N37" s="58" t="n"/>
-      <c r="O37" s="58" t="n"/>
-      <c r="P37" s="58" t="n"/>
-      <c r="Q37" s="58" t="n"/>
-      <c r="R37" s="58" t="n"/>
-      <c r="S37" s="58" t="n"/>
-      <c r="T37" s="58" t="n"/>
-      <c r="U37" s="58" t="n"/>
-      <c r="V37" s="58" t="n"/>
     </row>
     <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="25" t="inlineStr">
+      <c r="A38" s="59" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B38" s="25" t="inlineStr">
+      <c r="B38" s="59" t="inlineStr">
         <is>
           <t>Параметр оценки диалога</t>
         </is>
       </c>
-      <c r="C38" s="25" t="inlineStr">
+      <c r="C38" s="59" t="inlineStr">
         <is>
           <t>Вес</t>
         </is>
       </c>
-      <c r="D38" s="25" t="inlineStr">
+      <c r="D38" s="59" t="inlineStr">
         <is>
           <t>Приоритет</t>
         </is>
       </c>
-      <c r="E38" s="25" t="inlineStr">
+      <c r="E38" s="59" t="inlineStr">
         <is>
           <t>Что проверяет алгоритм ИИ (Суть критерия)</t>
         </is>
       </c>
-      <c r="F38" s="25" t="n"/>
-      <c r="G38" s="25" t="n"/>
-      <c r="H38" s="25" t="inlineStr">
+      <c r="H38" s="59" t="inlineStr">
         <is>
           <t>Маркеры дефекта в речи (Почему сделка срывается)</t>
         </is>
       </c>
-      <c r="I38" s="25" t="n"/>
-      <c r="J38" s="25" t="n"/>
-      <c r="K38" s="25" t="n"/>
-      <c r="L38" s="25" t="n"/>
-      <c r="M38" s="25" t="inlineStr">
+      <c r="M38" s="59" t="inlineStr">
         <is>
           <t>Coaching Tip: как обучить менеджера и защитить выручку</t>
         </is>
       </c>
-      <c r="N38" s="25" t="n"/>
-      <c r="O38" s="25" t="n"/>
-      <c r="P38" s="25" t="n"/>
-      <c r="Q38" s="25" t="n"/>
-      <c r="R38" s="25" t="n"/>
-      <c r="S38" s="25" t="n"/>
-      <c r="T38" s="25" t="n"/>
-      <c r="U38" s="25" t="n"/>
-      <c r="V38" s="25" t="n"/>
     </row>
     <row r="39" ht="46" customHeight="1">
-      <c r="A39" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
+      <c r="A39" s="111" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" s="74" t="inlineStr">
         <is>
           <t>Жёсткий Next Step</t>
         </is>
       </c>
-      <c r="C39" s="26" t="inlineStr">
+      <c r="C39" s="111" t="inlineStr">
         <is>
           <t>2.0x</t>
         </is>
       </c>
-      <c r="D39" s="17" t="inlineStr">
+      <c r="D39" s="118" t="inlineStr">
         <is>
           <t>🔴 P0 (Критический)</t>
         </is>
@@ -4024,47 +3839,32 @@
           <t>Зафиксирована точная дата и время следующего контакта (календарный слот)</t>
         </is>
       </c>
-      <c r="F39" s="27" t="n"/>
-      <c r="G39" s="27" t="n"/>
       <c r="H39" s="78" t="inlineStr">
         <is>
           <t>«Я вам перезвоню на днях», «Подумайте, наберите», отпускание без времени</t>
         </is>
       </c>
-      <c r="I39" s="78" t="n"/>
-      <c r="J39" s="78" t="n"/>
-      <c r="K39" s="78" t="n"/>
-      <c r="L39" s="78" t="n"/>
       <c r="M39" s="74" t="inlineStr">
         <is>
           <t>Внедрить обязательный вопрос в конце диалога: «Во вторник в 14:30 или в среду в 11:00 удобно?»</t>
         </is>
       </c>
-      <c r="N39" s="74" t="n"/>
-      <c r="O39" s="74" t="n"/>
-      <c r="P39" s="74" t="n"/>
-      <c r="Q39" s="74" t="n"/>
-      <c r="R39" s="74" t="n"/>
-      <c r="S39" s="74" t="n"/>
-      <c r="T39" s="74" t="n"/>
-      <c r="U39" s="74" t="n"/>
-      <c r="V39" s="74" t="n"/>
     </row>
     <row r="40" ht="46" customHeight="1">
-      <c r="A40" s="26" t="n">
+      <c r="A40" s="111" t="n">
         <v>2</v>
       </c>
-      <c r="B40" s="8" t="inlineStr">
+      <c r="B40" s="74" t="inlineStr">
         <is>
           <t>Инициатива диалога</t>
         </is>
       </c>
-      <c r="C40" s="26" t="inlineStr">
+      <c r="C40" s="111" t="inlineStr">
         <is>
           <t>1.0x</t>
         </is>
       </c>
-      <c r="D40" s="20" t="inlineStr">
+      <c r="D40" s="116" t="inlineStr">
         <is>
           <t>🟡 P1 (Высокий)</t>
         </is>
@@ -4074,47 +3874,32 @@
           <t>Менеджер ведёт диалог вопросами, держит сценарий, а не работает автоответчиком</t>
         </is>
       </c>
-      <c r="F40" s="27" t="n"/>
-      <c r="G40" s="27" t="n"/>
       <c r="H40" s="78" t="inlineStr">
         <is>
           <t>Клиент задает все вопросы сам, менеджер только отвечает короткими репликами</t>
         </is>
       </c>
-      <c r="I40" s="78" t="n"/>
-      <c r="J40" s="78" t="n"/>
-      <c r="K40" s="78" t="n"/>
-      <c r="L40" s="78" t="n"/>
       <c r="M40" s="74" t="inlineStr">
         <is>
           <t>Правило «Ответ + Встречный вопрос». Завершать каждую реплику квалифицирующим вопросом.</t>
         </is>
       </c>
-      <c r="N40" s="74" t="n"/>
-      <c r="O40" s="74" t="n"/>
-      <c r="P40" s="74" t="n"/>
-      <c r="Q40" s="74" t="n"/>
-      <c r="R40" s="74" t="n"/>
-      <c r="S40" s="74" t="n"/>
-      <c r="T40" s="74" t="n"/>
-      <c r="U40" s="74" t="n"/>
-      <c r="V40" s="74" t="n"/>
     </row>
     <row r="41" ht="46" customHeight="1">
-      <c r="A41" s="26" t="n">
+      <c r="A41" s="111" t="n">
         <v>3</v>
       </c>
-      <c r="B41" s="8" t="inlineStr">
+      <c r="B41" s="74" t="inlineStr">
         <is>
           <t>Квалификация ЛПР / ЛВПР</t>
         </is>
       </c>
-      <c r="C41" s="26" t="inlineStr">
+      <c r="C41" s="111" t="inlineStr">
         <is>
           <t>1.5x</t>
         </is>
       </c>
-      <c r="D41" s="17" t="inlineStr">
+      <c r="D41" s="118" t="inlineStr">
         <is>
           <t>🔴 P0 (Критический)</t>
         </is>
@@ -4124,47 +3909,32 @@
           <t>Установлен статус собеседника: принимает ли решения по бюджету и согласованию</t>
         </is>
       </c>
-      <c r="F41" s="27" t="n"/>
-      <c r="G41" s="27" t="n"/>
       <c r="H41" s="78" t="inlineStr">
         <is>
           <t>Трата 40 минут на презентацию инженеру или секретарю без полномочий подписания</t>
         </is>
       </c>
-      <c r="I41" s="78" t="n"/>
-      <c r="J41" s="78" t="n"/>
-      <c r="K41" s="78" t="n"/>
-      <c r="L41" s="78" t="n"/>
       <c r="M41" s="74" t="inlineStr">
         <is>
           <t>«Кто кроме вас участвует в согласовании проекта и утверждении финансового бюджета?»</t>
         </is>
       </c>
-      <c r="N41" s="74" t="n"/>
-      <c r="O41" s="74" t="n"/>
-      <c r="P41" s="74" t="n"/>
-      <c r="Q41" s="74" t="n"/>
-      <c r="R41" s="74" t="n"/>
-      <c r="S41" s="74" t="n"/>
-      <c r="T41" s="74" t="n"/>
-      <c r="U41" s="74" t="n"/>
-      <c r="V41" s="74" t="n"/>
     </row>
     <row r="42" ht="46" customHeight="1">
-      <c r="A42" s="26" t="n">
+      <c r="A42" s="111" t="n">
         <v>4</v>
       </c>
-      <c r="B42" s="8" t="inlineStr">
+      <c r="B42" s="74" t="inlineStr">
         <is>
           <t>Выявление болей и срочности</t>
         </is>
       </c>
-      <c r="C42" s="26" t="inlineStr">
+      <c r="C42" s="111" t="inlineStr">
         <is>
           <t>1.2x</t>
         </is>
       </c>
-      <c r="D42" s="20" t="inlineStr">
+      <c r="D42" s="116" t="inlineStr">
         <is>
           <t>🟡 P1 (Высокий)</t>
         </is>
@@ -4174,47 +3944,32 @@
           <t>Понятна ли бизнес-задача клиента, текущие потери и дедлайн решения проблемы</t>
         </is>
       </c>
-      <c r="F42" s="27" t="n"/>
-      <c r="G42" s="27" t="n"/>
       <c r="H42" s="78" t="inlineStr">
         <is>
           <t>Менеджер сразу начинает презентовать продукт, не узнав текущую ситуацию клиента</t>
         </is>
       </c>
-      <c r="I42" s="78" t="n"/>
-      <c r="J42" s="78" t="n"/>
-      <c r="K42" s="78" t="n"/>
-      <c r="L42" s="78" t="n"/>
       <c r="M42" s="74" t="inlineStr">
         <is>
           <t>Сначала диагностика по методологии SPIN/BANT, затем презентация под конкретную боль.</t>
         </is>
       </c>
-      <c r="N42" s="74" t="n"/>
-      <c r="O42" s="74" t="n"/>
-      <c r="P42" s="74" t="n"/>
-      <c r="Q42" s="74" t="n"/>
-      <c r="R42" s="74" t="n"/>
-      <c r="S42" s="74" t="n"/>
-      <c r="T42" s="74" t="n"/>
-      <c r="U42" s="74" t="n"/>
-      <c r="V42" s="74" t="n"/>
     </row>
     <row r="43" ht="46" customHeight="1">
-      <c r="A43" s="26" t="n">
+      <c r="A43" s="111" t="n">
         <v>5</v>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B43" s="74" t="inlineStr">
         <is>
           <t>Отработка возражения «Дорого»</t>
         </is>
       </c>
-      <c r="C43" s="26" t="inlineStr">
+      <c r="C43" s="111" t="inlineStr">
         <is>
           <t>1.5x</t>
         </is>
       </c>
-      <c r="D43" s="17" t="inlineStr">
+      <c r="D43" s="118" t="inlineStr">
         <is>
           <t>🔴 P0 (Критический)</t>
         </is>
@@ -4224,47 +3979,32 @@
           <t>Обоснование ценности, расчет ROI/окупаемости, рассрочка (без моментальной скидки)</t>
         </is>
       </c>
-      <c r="F43" s="27" t="n"/>
-      <c r="G43" s="27" t="n"/>
       <c r="H43" s="78" t="inlineStr">
         <is>
           <t>Моментальная скидка при первом сомнении клиента или согласие («Да, у нас недешево»)</t>
         </is>
       </c>
-      <c r="I43" s="78" t="n"/>
-      <c r="J43" s="78" t="n"/>
-      <c r="K43" s="78" t="n"/>
-      <c r="L43" s="78" t="n"/>
       <c r="M43" s="74" t="inlineStr">
         <is>
           <t>Обосновать окупаемость: показать, сколько клиент теряет каждый день без внедрения решения.</t>
         </is>
       </c>
-      <c r="N43" s="74" t="n"/>
-      <c r="O43" s="74" t="n"/>
-      <c r="P43" s="74" t="n"/>
-      <c r="Q43" s="74" t="n"/>
-      <c r="R43" s="74" t="n"/>
-      <c r="S43" s="74" t="n"/>
-      <c r="T43" s="74" t="n"/>
-      <c r="U43" s="74" t="n"/>
-      <c r="V43" s="74" t="n"/>
     </row>
     <row r="44" ht="46" customHeight="1">
-      <c r="A44" s="26" t="n">
+      <c r="A44" s="111" t="n">
         <v>6</v>
       </c>
-      <c r="B44" s="8" t="inlineStr">
+      <c r="B44" s="74" t="inlineStr">
         <is>
           <t>Отработка «Я подумаю»</t>
         </is>
       </c>
-      <c r="C44" s="26" t="inlineStr">
+      <c r="C44" s="111" t="inlineStr">
         <is>
           <t>1.0x</t>
         </is>
       </c>
-      <c r="D44" s="20" t="inlineStr">
+      <c r="D44" s="116" t="inlineStr">
         <is>
           <t>🟡 P1 (Высокий)</t>
         </is>
@@ -4274,47 +4014,32 @@
           <t>Вскрытие истинного сомнения клиента, а не молчаливое отпускание в архив</t>
         </is>
       </c>
-      <c r="F44" s="27" t="n"/>
-      <c r="G44" s="27" t="n"/>
       <c r="H44" s="78" t="inlineStr">
         <is>
           <t>«Хорошо, думайте, ждем вашего звонка», завершение диалога на неопределенности</t>
         </is>
       </c>
-      <c r="I44" s="78" t="n"/>
-      <c r="J44" s="78" t="n"/>
-      <c r="K44" s="78" t="n"/>
-      <c r="L44" s="78" t="n"/>
       <c r="M44" s="74" t="inlineStr">
         <is>
           <t>«Алексей, обычно говорят 'подумаю', когда смущает цена или функционал. Что именно из этого?»</t>
         </is>
       </c>
-      <c r="N44" s="74" t="n"/>
-      <c r="O44" s="74" t="n"/>
-      <c r="P44" s="74" t="n"/>
-      <c r="Q44" s="74" t="n"/>
-      <c r="R44" s="74" t="n"/>
-      <c r="S44" s="74" t="n"/>
-      <c r="T44" s="74" t="n"/>
-      <c r="U44" s="74" t="n"/>
-      <c r="V44" s="74" t="n"/>
     </row>
     <row r="45" ht="46" customHeight="1">
-      <c r="A45" s="26" t="n">
+      <c r="A45" s="111" t="n">
         <v>7</v>
       </c>
-      <c r="B45" s="8" t="inlineStr">
+      <c r="B45" s="74" t="inlineStr">
         <is>
           <t>Презентация через кейсы и цифры</t>
         </is>
       </c>
-      <c r="C45" s="26" t="inlineStr">
+      <c r="C45" s="111" t="inlineStr">
         <is>
           <t>1.0x</t>
         </is>
       </c>
-      <c r="D45" s="20" t="inlineStr">
+      <c r="D45" s="116" t="inlineStr">
         <is>
           <t>🟡 P1 (Высокий)</t>
         </is>
@@ -4324,47 +4049,32 @@
           <t>Приведение аналогичных проектов, оцифрованных результатов и сроков возврата</t>
         </is>
       </c>
-      <c r="F45" s="27" t="n"/>
-      <c r="G45" s="27" t="n"/>
       <c r="H45" s="78" t="inlineStr">
         <is>
           <t>Абстрактные слова «мы надежные», «у нас высокое качество» без конкретных фактов</t>
         </is>
       </c>
-      <c r="I45" s="78" t="n"/>
-      <c r="J45" s="78" t="n"/>
-      <c r="K45" s="78" t="n"/>
-      <c r="L45" s="78" t="n"/>
       <c r="M45" s="74" t="inlineStr">
         <is>
           <t>Показать схожий кейс из отрасли клиента: «Для завода X мы сократили потери на 1.4 млн ₽ за 21 день».</t>
         </is>
       </c>
-      <c r="N45" s="74" t="n"/>
-      <c r="O45" s="74" t="n"/>
-      <c r="P45" s="74" t="n"/>
-      <c r="Q45" s="74" t="n"/>
-      <c r="R45" s="74" t="n"/>
-      <c r="S45" s="74" t="n"/>
-      <c r="T45" s="74" t="n"/>
-      <c r="U45" s="74" t="n"/>
-      <c r="V45" s="74" t="n"/>
     </row>
     <row r="46" ht="46" customHeight="1">
-      <c r="A46" s="26" t="n">
+      <c r="A46" s="111" t="n">
         <v>8</v>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B46" s="74" t="inlineStr">
         <is>
           <t>Попытка закрытия сделки</t>
         </is>
       </c>
-      <c r="C46" s="26" t="inlineStr">
+      <c r="C46" s="111" t="inlineStr">
         <is>
           <t>1.5x</t>
         </is>
       </c>
-      <c r="D46" s="17" t="inlineStr">
+      <c r="D46" s="118" t="inlineStr">
         <is>
           <t>🔴 P0 (Критический)</t>
         </is>
@@ -4374,47 +4084,32 @@
           <t>Прямое предложение заключить договор, забронировать слот аудита или выставить счет</t>
         </is>
       </c>
-      <c r="F46" s="27" t="n"/>
-      <c r="G46" s="27" t="n"/>
       <c r="H46" s="78" t="inlineStr">
         <is>
           <t>Разговор закончился тепло, но менеджер не предложил сделать следующий шаг к оплате</t>
         </is>
       </c>
-      <c r="I46" s="78" t="n"/>
-      <c r="J46" s="78" t="n"/>
-      <c r="K46" s="78" t="n"/>
-      <c r="L46" s="78" t="n"/>
       <c r="M46" s="74" t="inlineStr">
         <is>
           <t>«Если все параметры подходят, предлагаю сегодня запустить пилот. Куда отправить договор?»</t>
         </is>
       </c>
-      <c r="N46" s="74" t="n"/>
-      <c r="O46" s="74" t="n"/>
-      <c r="P46" s="74" t="n"/>
-      <c r="Q46" s="74" t="n"/>
-      <c r="R46" s="74" t="n"/>
-      <c r="S46" s="74" t="n"/>
-      <c r="T46" s="74" t="n"/>
-      <c r="U46" s="74" t="n"/>
-      <c r="V46" s="74" t="n"/>
     </row>
     <row r="47" ht="46" customHeight="1">
-      <c r="A47" s="26" t="n">
+      <c r="A47" s="111" t="n">
         <v>9</v>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="74" t="inlineStr">
         <is>
           <t>Регламент приветствия и повестка</t>
         </is>
       </c>
-      <c r="C47" s="26" t="inlineStr">
+      <c r="C47" s="111" t="inlineStr">
         <is>
           <t>0.8x</t>
         </is>
       </c>
-      <c r="D47" s="79" t="inlineStr">
+      <c r="D47" s="128" t="inlineStr">
         <is>
           <t>🟢 P2 (Стандарт)</t>
         </is>
@@ -4424,47 +4119,32 @@
           <t>Представление имени, компании, уточнение времени и согласование цели разговора</t>
         </is>
       </c>
-      <c r="F47" s="27" t="n"/>
-      <c r="G47" s="27" t="n"/>
       <c r="H47" s="78" t="inlineStr">
         <is>
           <t>Невнятное приветствие, вопрос «Вам удобно говорить?» без обозначения повестки</t>
         </is>
       </c>
-      <c r="I47" s="78" t="n"/>
-      <c r="J47" s="78" t="n"/>
-      <c r="K47" s="78" t="n"/>
-      <c r="L47" s="78" t="n"/>
       <c r="M47" s="74" t="inlineStr">
         <is>
           <t>«Добрый день! Дмитрий, компания RevOps. Звоню по вашей заявке на аудит воронки. Уделите 5 минут?»</t>
         </is>
       </c>
-      <c r="N47" s="74" t="n"/>
-      <c r="O47" s="74" t="n"/>
-      <c r="P47" s="74" t="n"/>
-      <c r="Q47" s="74" t="n"/>
-      <c r="R47" s="74" t="n"/>
-      <c r="S47" s="74" t="n"/>
-      <c r="T47" s="74" t="n"/>
-      <c r="U47" s="74" t="n"/>
-      <c r="V47" s="74" t="n"/>
     </row>
     <row r="48" ht="46" customHeight="1">
-      <c r="A48" s="26" t="n">
+      <c r="A48" s="111" t="n">
         <v>10</v>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B48" s="74" t="inlineStr">
         <is>
           <t>Чистота речи и уверенность</t>
         </is>
       </c>
-      <c r="C48" s="26" t="inlineStr">
+      <c r="C48" s="111" t="inlineStr">
         <is>
           <t>0.8x</t>
         </is>
       </c>
-      <c r="D48" s="79" t="inlineStr">
+      <c r="D48" s="128" t="inlineStr">
         <is>
           <t>🟢 P2 (Стандарт)</t>
         </is>
@@ -4474,47 +4154,32 @@
           <t>Отсутствие слов-паразитов («как бы», «э-э-э»), пауз и извиняющихся интонаций при цене</t>
         </is>
       </c>
-      <c r="F48" s="27" t="n"/>
-      <c r="G48" s="27" t="n"/>
       <c r="H48" s="78" t="inlineStr">
         <is>
           <t>Дрожащий голос при озвучивании чека, слова сомнения («может быть», «наверное»)</t>
         </is>
       </c>
-      <c r="I48" s="78" t="n"/>
-      <c r="J48" s="78" t="n"/>
-      <c r="K48" s="78" t="n"/>
-      <c r="L48" s="78" t="n"/>
       <c r="M48" s="74" t="inlineStr">
         <is>
           <t>Отработать блок цены на тренажере: уверенная пауза после озвучивания стоимости.</t>
         </is>
       </c>
-      <c r="N48" s="74" t="n"/>
-      <c r="O48" s="74" t="n"/>
-      <c r="P48" s="74" t="n"/>
-      <c r="Q48" s="74" t="n"/>
-      <c r="R48" s="74" t="n"/>
-      <c r="S48" s="74" t="n"/>
-      <c r="T48" s="74" t="n"/>
-      <c r="U48" s="74" t="n"/>
-      <c r="V48" s="74" t="n"/>
     </row>
     <row r="49" ht="46" customHeight="1">
-      <c r="A49" s="26" t="n">
+      <c r="A49" s="111" t="n">
         <v>11</v>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B49" s="74" t="inlineStr">
         <is>
           <t>Слушание клиента (Talk/Listen)</t>
         </is>
       </c>
-      <c r="C49" s="26" t="inlineStr">
+      <c r="C49" s="111" t="inlineStr">
         <is>
           <t>1.2x</t>
         </is>
       </c>
-      <c r="D49" s="20" t="inlineStr">
+      <c r="D49" s="116" t="inlineStr">
         <is>
           <t>🟡 P1 (Высокий)</t>
         </is>
@@ -4524,47 +4189,32 @@
           <t>Менеджер слушает клиента не менее 45–50% общего времени разговора</t>
         </is>
       </c>
-      <c r="F49" s="27" t="n"/>
-      <c r="G49" s="27" t="n"/>
       <c r="H49" s="78" t="inlineStr">
         <is>
           <t>Монолог менеджера &gt; 70% времени: клиент молчит и теряет фокус внимания</t>
         </is>
       </c>
-      <c r="I49" s="78" t="n"/>
-      <c r="J49" s="78" t="n"/>
-      <c r="K49" s="78" t="n"/>
-      <c r="L49" s="78" t="n"/>
       <c r="M49" s="74" t="inlineStr">
         <is>
           <t>Держать баланс 50/50. Задавать открытые вопросы и давать клиенту выговориться о проблеме.</t>
         </is>
       </c>
-      <c r="N49" s="74" t="n"/>
-      <c r="O49" s="74" t="n"/>
-      <c r="P49" s="74" t="n"/>
-      <c r="Q49" s="74" t="n"/>
-      <c r="R49" s="74" t="n"/>
-      <c r="S49" s="74" t="n"/>
-      <c r="T49" s="74" t="n"/>
-      <c r="U49" s="74" t="n"/>
-      <c r="V49" s="74" t="n"/>
     </row>
     <row r="50" ht="46" customHeight="1">
-      <c r="A50" s="26" t="n">
+      <c r="A50" s="111" t="n">
         <v>12</v>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B50" s="74" t="inlineStr">
         <is>
           <t>Фиксация договорённостей</t>
         </is>
       </c>
-      <c r="C50" s="26" t="inlineStr">
+      <c r="C50" s="111" t="inlineStr">
         <is>
           <t>1.0x</t>
         </is>
       </c>
-      <c r="D50" s="79" t="inlineStr">
+      <c r="D50" s="128" t="inlineStr">
         <is>
           <t>🟢 P2 (Стандарт)</t>
         </is>
@@ -4574,47 +4224,32 @@
           <t>Резюмирование договоренностей перед окончанием звонка: кто, что и когда делает</t>
         </is>
       </c>
-      <c r="F50" s="27" t="n"/>
-      <c r="G50" s="27" t="n"/>
       <c r="H50" s="78" t="inlineStr">
         <is>
           <t>Диалог оборвался, у клиента и менеджера разное понимание следующих действий</t>
         </is>
       </c>
-      <c r="I50" s="78" t="n"/>
-      <c r="J50" s="78" t="n"/>
-      <c r="K50" s="78" t="n"/>
-      <c r="L50" s="78" t="n"/>
       <c r="M50" s="74" t="inlineStr">
         <is>
           <t>«Итак, резюмирую: я отправляю КП в WhatsApp до 15:00, а завтра в 11:00 мы созваниваемся по условиям».</t>
         </is>
       </c>
-      <c r="N50" s="74" t="n"/>
-      <c r="O50" s="74" t="n"/>
-      <c r="P50" s="74" t="n"/>
-      <c r="Q50" s="74" t="n"/>
-      <c r="R50" s="74" t="n"/>
-      <c r="S50" s="74" t="n"/>
-      <c r="T50" s="74" t="n"/>
-      <c r="U50" s="74" t="n"/>
-      <c r="V50" s="74" t="n"/>
     </row>
     <row r="51" ht="46" customHeight="1">
-      <c r="A51" s="26" t="n">
+      <c r="A51" s="111" t="n">
         <v>13</v>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B51" s="74" t="inlineStr">
         <is>
           <t>Защита маржинальности</t>
         </is>
       </c>
-      <c r="C51" s="26" t="inlineStr">
+      <c r="C51" s="111" t="inlineStr">
         <is>
           <t>1.5x</t>
         </is>
       </c>
-      <c r="D51" s="17" t="inlineStr">
+      <c r="D51" s="118" t="inlineStr">
         <is>
           <t>🔴 P0 (Критический)</t>
         </is>
@@ -4624,421 +4259,137 @@
           <t>Отсутствие необоснованных скидок без встречных уступок по объему или предоплате</t>
         </is>
       </c>
-      <c r="F51" s="27" t="n"/>
-      <c r="G51" s="27" t="n"/>
       <c r="H51" s="78" t="inlineStr">
         <is>
           <t>Раздача скидок из маржи компании без требования 100% предоплаты или большего объема</t>
         </is>
       </c>
-      <c r="I51" s="78" t="n"/>
-      <c r="J51" s="78" t="n"/>
-      <c r="K51" s="78" t="n"/>
-      <c r="L51" s="78" t="n"/>
       <c r="M51" s="74" t="inlineStr">
         <is>
           <t>Скидка возможна только в обмен на ценность: «Готовы дать 5% при оплате счета в течение 24 часов».</t>
         </is>
       </c>
-      <c r="N51" s="74" t="n"/>
-      <c r="O51" s="74" t="n"/>
-      <c r="P51" s="74" t="n"/>
-      <c r="Q51" s="74" t="n"/>
-      <c r="R51" s="74" t="n"/>
-      <c r="S51" s="74" t="n"/>
-      <c r="T51" s="74" t="n"/>
-      <c r="U51" s="74" t="n"/>
-      <c r="V51" s="74" t="n"/>
     </row>
     <row r="52" ht="12" customHeight="1"/>
     <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="58" t="inlineStr">
+      <c r="A53" s="110" t="inlineStr">
         <is>
           <t>💰 ЭКОНОМИЧЕСКИЙ ЭФФЕКТ РЕЧЕВОЙ АНАЛИТИКИ (ROI ВНЕДРЕНИЯ И ОКУПАЕМОСТЬ)</t>
         </is>
       </c>
-      <c r="B53" s="58" t="n"/>
-      <c r="C53" s="58" t="n"/>
-      <c r="D53" s="58" t="n"/>
-      <c r="E53" s="58" t="n"/>
-      <c r="F53" s="58" t="n"/>
-      <c r="G53" s="58" t="n"/>
-      <c r="H53" s="58" t="n"/>
-      <c r="I53" s="58" t="n"/>
-      <c r="J53" s="58" t="n"/>
-      <c r="K53" s="58" t="n"/>
-      <c r="L53" s="58" t="n"/>
-      <c r="M53" s="58" t="n"/>
-      <c r="N53" s="58" t="n"/>
-      <c r="O53" s="58" t="n"/>
-      <c r="P53" s="58" t="n"/>
-      <c r="Q53" s="58" t="n"/>
-      <c r="R53" s="58" t="n"/>
-      <c r="S53" s="58" t="n"/>
-      <c r="T53" s="58" t="n"/>
-      <c r="U53" s="58" t="n"/>
-      <c r="V53" s="58" t="n"/>
     </row>
     <row r="54" ht="26" customHeight="1">
-      <c r="A54" s="25" t="inlineStr">
+      <c r="A54" s="59" t="inlineStr">
         <is>
           <t>Параметр эффекта речевой аналитики</t>
         </is>
       </c>
-      <c r="B54" s="25" t="n"/>
-      <c r="C54" s="25" t="n"/>
-      <c r="D54" s="25" t="inlineStr">
+      <c r="D54" s="59" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
-      <c r="E54" s="25" t="n"/>
-      <c r="F54" s="25" t="inlineStr">
+      <c r="F54" s="59" t="inlineStr">
         <is>
           <t>Комментарий и логика окупаемости</t>
         </is>
       </c>
-      <c r="G54" s="25" t="n"/>
-      <c r="H54" s="25" t="n"/>
-      <c r="I54" s="25" t="n"/>
-      <c r="J54" s="25" t="n"/>
-      <c r="K54" s="25" t="n"/>
-      <c r="L54" s="25" t="n"/>
-      <c r="M54" s="25" t="n"/>
-      <c r="N54" s="25" t="n"/>
-      <c r="O54" s="25" t="n"/>
-      <c r="P54" s="25" t="n"/>
-      <c r="Q54" s="25" t="n"/>
-      <c r="R54" s="25" t="n"/>
-      <c r="S54" s="25" t="n"/>
-      <c r="T54" s="25" t="n"/>
-      <c r="U54" s="25" t="n"/>
-      <c r="V54" s="25" t="n"/>
     </row>
     <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="80" t="inlineStr">
+      <c r="A55" s="74" t="inlineStr">
         <is>
           <t>Текущие потери от брака звонков в месяц (As-Is)</t>
         </is>
       </c>
-      <c r="B55" s="80" t="n"/>
-      <c r="C55" s="80" t="n"/>
-      <c r="D55" s="81" t="n">
+      <c r="D55" s="129" t="n">
         <v>1382500</v>
       </c>
-      <c r="E55" s="81" t="n"/>
-      <c r="F55" s="61" t="inlineStr">
+      <c r="F55" s="27" t="inlineStr">
         <is>
           <t>Сливы на этапе первичного звонка из-за отсутствия Next Step и слабой отработки возражений</t>
         </is>
       </c>
-      <c r="G55" s="61" t="n"/>
-      <c r="H55" s="61" t="n"/>
-      <c r="I55" s="61" t="n"/>
-      <c r="J55" s="61" t="n"/>
-      <c r="K55" s="61" t="n"/>
-      <c r="L55" s="61" t="n"/>
-      <c r="M55" s="61" t="n"/>
-      <c r="N55" s="61" t="n"/>
-      <c r="O55" s="61" t="n"/>
-      <c r="P55" s="61" t="n"/>
-      <c r="Q55" s="61" t="n"/>
-      <c r="R55" s="61" t="n"/>
-      <c r="S55" s="61" t="n"/>
-      <c r="T55" s="61" t="n"/>
-      <c r="U55" s="61" t="n"/>
-      <c r="V55" s="61" t="n"/>
     </row>
     <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="80" t="inlineStr">
+      <c r="A56" s="74" t="inlineStr">
         <is>
           <t>Ожидаемый возврат выручки в кассу (M1 To-Be)</t>
         </is>
       </c>
-      <c r="B56" s="80" t="n"/>
-      <c r="C56" s="80" t="n"/>
-      <c r="D56" s="82" t="n">
+      <c r="D56" s="130" t="n">
         <v>414750</v>
       </c>
-      <c r="E56" s="82" t="n"/>
-      <c r="F56" s="61" t="inlineStr">
+      <c r="F56" s="27" t="inlineStr">
         <is>
           <t>Консервативный сценарий: устранение всего 30% выявленных дефектов речи</t>
         </is>
       </c>
-      <c r="G56" s="61" t="n"/>
-      <c r="H56" s="61" t="n"/>
-      <c r="I56" s="61" t="n"/>
-      <c r="J56" s="61" t="n"/>
-      <c r="K56" s="61" t="n"/>
-      <c r="L56" s="61" t="n"/>
-      <c r="M56" s="61" t="n"/>
-      <c r="N56" s="61" t="n"/>
-      <c r="O56" s="61" t="n"/>
-      <c r="P56" s="61" t="n"/>
-      <c r="Q56" s="61" t="n"/>
-      <c r="R56" s="61" t="n"/>
-      <c r="S56" s="61" t="n"/>
-      <c r="T56" s="61" t="n"/>
-      <c r="U56" s="61" t="n"/>
-      <c r="V56" s="61" t="n"/>
     </row>
     <row r="57" ht="24" customHeight="1">
-      <c r="A57" s="80" t="inlineStr">
+      <c r="A57" s="74" t="inlineStr">
         <is>
           <t>Стоимость модуля речевого ИИ-супервайзера</t>
         </is>
       </c>
-      <c r="B57" s="80" t="n"/>
-      <c r="C57" s="80" t="n"/>
-      <c r="D57" s="83" t="n">
+      <c r="D57" s="131" t="n">
         <v>150000</v>
       </c>
-      <c r="E57" s="83" t="n"/>
-      <c r="F57" s="61" t="inlineStr">
+      <c r="F57" s="27" t="inlineStr">
         <is>
           <t>В составе комплексного 4-недельного спринта оптимизации отдела продаж</t>
         </is>
       </c>
-      <c r="G57" s="61" t="n"/>
-      <c r="H57" s="61" t="n"/>
-      <c r="I57" s="61" t="n"/>
-      <c r="J57" s="61" t="n"/>
-      <c r="K57" s="61" t="n"/>
-      <c r="L57" s="61" t="n"/>
-      <c r="M57" s="61" t="n"/>
-      <c r="N57" s="61" t="n"/>
-      <c r="O57" s="61" t="n"/>
-      <c r="P57" s="61" t="n"/>
-      <c r="Q57" s="61" t="n"/>
-      <c r="R57" s="61" t="n"/>
-      <c r="S57" s="61" t="n"/>
-      <c r="T57" s="61" t="n"/>
-      <c r="U57" s="61" t="n"/>
-      <c r="V57" s="61" t="n"/>
     </row>
     <row r="58" ht="24" customHeight="1">
-      <c r="A58" s="80" t="inlineStr">
+      <c r="A58" s="74" t="inlineStr">
         <is>
           <t>Чистая прибыль компании от внедрения в первый месяц</t>
         </is>
       </c>
-      <c r="B58" s="80" t="n"/>
-      <c r="C58" s="80" t="n"/>
-      <c r="D58" s="82" t="n">
+      <c r="D58" s="130" t="n">
         <v>264750</v>
       </c>
-      <c r="E58" s="82" t="n"/>
-      <c r="F58" s="61" t="inlineStr">
+      <c r="F58" s="27" t="inlineStr">
         <is>
           <t>Чистый денежный плюс в кассе компании уже в первый месяц работы</t>
         </is>
       </c>
-      <c r="G58" s="61" t="n"/>
-      <c r="H58" s="61" t="n"/>
-      <c r="I58" s="61" t="n"/>
-      <c r="J58" s="61" t="n"/>
-      <c r="K58" s="61" t="n"/>
-      <c r="L58" s="61" t="n"/>
-      <c r="M58" s="61" t="n"/>
-      <c r="N58" s="61" t="n"/>
-      <c r="O58" s="61" t="n"/>
-      <c r="P58" s="61" t="n"/>
-      <c r="Q58" s="61" t="n"/>
-      <c r="R58" s="61" t="n"/>
-      <c r="S58" s="61" t="n"/>
-      <c r="T58" s="61" t="n"/>
-      <c r="U58" s="61" t="n"/>
-      <c r="V58" s="61" t="n"/>
     </row>
     <row r="59" ht="24" customHeight="1">
-      <c r="A59" s="80" t="inlineStr">
+      <c r="A59" s="74" t="inlineStr">
         <is>
           <t>Чистый ROI речевой аналитики</t>
         </is>
       </c>
-      <c r="B59" s="80" t="n"/>
-      <c r="C59" s="80" t="n"/>
-      <c r="D59" s="60" t="inlineStr">
+      <c r="D59" s="112" t="inlineStr">
         <is>
           <t>276%</t>
         </is>
       </c>
-      <c r="E59" s="60" t="n"/>
-      <c r="F59" s="61" t="inlineStr">
+      <c r="F59" s="27" t="inlineStr">
         <is>
           <t>Отдача на каждый вложенный рубль в первый месяц</t>
         </is>
       </c>
-      <c r="G59" s="61" t="n"/>
-      <c r="H59" s="61" t="n"/>
-      <c r="I59" s="61" t="n"/>
-      <c r="J59" s="61" t="n"/>
-      <c r="K59" s="61" t="n"/>
-      <c r="L59" s="61" t="n"/>
-      <c r="M59" s="61" t="n"/>
-      <c r="N59" s="61" t="n"/>
-      <c r="O59" s="61" t="n"/>
-      <c r="P59" s="61" t="n"/>
-      <c r="Q59" s="61" t="n"/>
-      <c r="R59" s="61" t="n"/>
-      <c r="S59" s="61" t="n"/>
-      <c r="T59" s="61" t="n"/>
-      <c r="U59" s="61" t="n"/>
-      <c r="V59" s="61" t="n"/>
     </row>
     <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="80" t="inlineStr">
+      <c r="A60" s="74" t="inlineStr">
         <is>
           <t>Срок полной окупаемости модуля</t>
         </is>
       </c>
-      <c r="B60" s="80" t="n"/>
-      <c r="C60" s="80" t="n"/>
-      <c r="D60" s="60" t="inlineStr">
+      <c r="D60" s="112" t="inlineStr">
         <is>
           <t>11 дней</t>
         </is>
       </c>
-      <c r="E60" s="60" t="n"/>
-      <c r="F60" s="61" t="inlineStr">
+      <c r="F60" s="27" t="inlineStr">
         <is>
           <t>Количество рабочих дней до полной окупаемости внедрения речевого ИИ</t>
         </is>
       </c>
-      <c r="G60" s="61" t="n"/>
-      <c r="H60" s="61" t="n"/>
-      <c r="I60" s="61" t="n"/>
-      <c r="J60" s="61" t="n"/>
-      <c r="K60" s="61" t="n"/>
-      <c r="L60" s="61" t="n"/>
-      <c r="M60" s="61" t="n"/>
-      <c r="N60" s="61" t="n"/>
-      <c r="O60" s="61" t="n"/>
-      <c r="P60" s="61" t="n"/>
-      <c r="Q60" s="61" t="n"/>
-      <c r="R60" s="61" t="n"/>
-      <c r="S60" s="61" t="n"/>
-      <c r="T60" s="61" t="n"/>
-      <c r="U60" s="61" t="n"/>
-      <c r="V60" s="61" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="113">
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="D60:E60"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="M41:V41"/>
-    <mergeCell ref="H43:L43"/>
-    <mergeCell ref="E40:G40"/>
-    <mergeCell ref="H41:L41"/>
-    <mergeCell ref="A29:V29"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="H49:L49"/>
-    <mergeCell ref="N31:V31"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="A15:V15"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="M39:V39"/>
-    <mergeCell ref="J9:V9"/>
-    <mergeCell ref="M48:V48"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="N35:V35"/>
-    <mergeCell ref="E42:G42"/>
-    <mergeCell ref="H48:L48"/>
-    <mergeCell ref="E44:G44"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="G33:M33"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="H38:L38"/>
-    <mergeCell ref="G35:M35"/>
-    <mergeCell ref="H44:L44"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="M38:V38"/>
-    <mergeCell ref="H40:L40"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E46:G46"/>
-    <mergeCell ref="H51:L51"/>
-    <mergeCell ref="F59:V59"/>
-    <mergeCell ref="M43:V43"/>
-    <mergeCell ref="J8:V8"/>
-    <mergeCell ref="F55:V55"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="N30:V30"/>
-    <mergeCell ref="J10:V10"/>
-    <mergeCell ref="E41:G41"/>
-    <mergeCell ref="A58:C58"/>
-    <mergeCell ref="E47:G47"/>
-    <mergeCell ref="E43:G43"/>
-    <mergeCell ref="A60:C60"/>
-    <mergeCell ref="F58:V58"/>
-    <mergeCell ref="N32:V32"/>
-    <mergeCell ref="G30:M30"/>
-    <mergeCell ref="H42:L42"/>
-    <mergeCell ref="F60:V60"/>
-    <mergeCell ref="M46:V46"/>
-    <mergeCell ref="F57:V57"/>
-    <mergeCell ref="M42:V42"/>
-    <mergeCell ref="M3:V3"/>
-    <mergeCell ref="N33:V33"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="J12:V12"/>
-    <mergeCell ref="A53:V53"/>
-    <mergeCell ref="G32:M32"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="M4:V4"/>
-    <mergeCell ref="H46:L46"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="M44:V44"/>
-    <mergeCell ref="Q2:V2"/>
-    <mergeCell ref="H45:L45"/>
-    <mergeCell ref="A1:V1"/>
-    <mergeCell ref="M51:V51"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="H47:L47"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="F56:V56"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="A37:V37"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="J11:V11"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="A54:C54"/>
-    <mergeCell ref="M45:V45"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="H50:L50"/>
-    <mergeCell ref="F54:V54"/>
-    <mergeCell ref="M47:V47"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="G31:M31"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="H39:L39"/>
-    <mergeCell ref="E49:G49"/>
-    <mergeCell ref="M50:V50"/>
-    <mergeCell ref="D57:E57"/>
-    <mergeCell ref="J7:V7"/>
-    <mergeCell ref="N34:V34"/>
-    <mergeCell ref="M49:V49"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="J13:V13"/>
-    <mergeCell ref="A6:V6"/>
-    <mergeCell ref="E50:G50"/>
-    <mergeCell ref="D58:E58"/>
-    <mergeCell ref="M40:V40"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="G34:M34"/>
-    <mergeCell ref="D59:E59"/>
-    <mergeCell ref="E38:G38"/>
-  </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId2"/>
@@ -5057,7 +4408,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5076,55 +4427,53 @@
           <t>💸 ДИАГНОСТИЧЕСКИЙ АУДИТ УПУЩЕННОЙ ПРИБЫЛИ И УЗКИХ МЕСТ ОТДЕЛА ПРОДАЖ</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>⚡ Экспресс-Калькулятор</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>📋 Пульт РОПа</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>🎙️ ИИ-Аудит</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>💸 7 Грехов ОП</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>📄 One-Pager</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>🔐 152-ФЗ Безопасность</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="n"/>
-    </row>
+      <c r="A2" s="133">
+        <f>HYPERLINK("#'📄 Executive_OnePager'!A1", "📄 1. One-Pager")</f>
+        <v/>
+      </c>
+      <c r="B2" s="133">
+        <f>HYPERLINK("#'⚡ Пульс_Компании'!A1", "⚡ 2. Пульс компании")</f>
+        <v/>
+      </c>
+      <c r="C2" s="133">
+        <f>HYPERLINK("#'📋 Пульт_РОПа_15_Минут'!A1", "📋 3. Пульт РОПа")</f>
+        <v/>
+      </c>
+      <c r="D2" s="133">
+        <f>HYPERLINK("#'💸 Диагностика_Утечек_ОП'!A1", "💸 4. 7 Грехов ОП")</f>
+        <v/>
+      </c>
+      <c r="E2" s="133">
+        <f>HYPERLINK("#'🎯 Action_Center'!A1", "🎯 5. Action Center")</f>
+        <v/>
+      </c>
+      <c r="F2" s="133">
+        <f>HYPERLINK("#'🎙️ ИИ_Аудит'!A1", "🎙️ 6. ИИ-Аудит")</f>
+        <v/>
+      </c>
+      <c r="G2" s="133">
+        <f>HYPERLINK("#'⚡ Экспресс_Калькулятор_3_Цифры'!A1", "⚡ 7. Экспресс 3 цифры")</f>
+        <v/>
+      </c>
+      <c r="H2" s="133">
+        <f>HYPERLINK("#'🧪 QA_Suite'!A1", "🧪 8. QA Suite")</f>
+        <v/>
+      </c>
+      <c r="I2" s="133">
+        <f>HYPERLINK("#'⚙️ Настройки'!A1", "⚙️ 9. Настройки")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="39" t="inlineStr">
         <is>
           <t>Фактическая выручка месяца</t>
         </is>
       </c>
-      <c r="B4" s="39" t="n"/>
+      <c r="B4" s="98" t="n"/>
       <c r="C4" s="53" t="inlineStr">
         <is>
           <t>Взвешенный пайплайн в работе</t>
@@ -5150,13 +4499,13 @@
           <t>Срок окупаемости проекта</t>
         </is>
       </c>
-      <c r="H4" s="85" t="n"/>
+      <c r="H4" s="98" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="86" t="n">
         <v>1650000</v>
       </c>
-      <c r="B5" s="86" t="n"/>
+      <c r="B5" s="98" t="n"/>
       <c r="C5" s="23" t="n">
         <v>2754000</v>
       </c>
@@ -5176,8 +4525,9 @@
           <t>6 дн.</t>
         </is>
       </c>
-      <c r="H5" s="87" t="n"/>
-    </row>
+      <c r="H5" s="98" t="n"/>
+    </row>
+    <row r="6"/>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -5525,6 +4875,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="50" t="inlineStr">
         <is>
@@ -5555,8 +4906,8 @@
           <t>Стоимость проекта оптимизации ОП</t>
         </is>
       </c>
-      <c r="B20" s="51" t="n"/>
-      <c r="C20" s="51" t="n"/>
+      <c r="B20" s="99" t="n"/>
+      <c r="C20" s="98" t="n"/>
       <c r="D20" s="83" t="n">
         <v>450000</v>
       </c>
@@ -5565,9 +4916,9 @@
           <t>Фиксированная стоимость внедрения (4 недели спринтов)</t>
         </is>
       </c>
-      <c r="F20" s="51" t="n"/>
-      <c r="G20" s="51" t="n"/>
-      <c r="H20" s="51" t="n"/>
+      <c r="F20" s="99" t="n"/>
+      <c r="G20" s="99" t="n"/>
+      <c r="H20" s="98" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
@@ -5575,8 +4926,8 @@
           <t>Ожидаемый возврат выручки (M1 факт)</t>
         </is>
       </c>
-      <c r="B21" s="51" t="n"/>
-      <c r="C21" s="51" t="n"/>
+      <c r="B21" s="99" t="n"/>
+      <c r="C21" s="98" t="n"/>
       <c r="D21" s="82" t="n">
         <v>2100300</v>
       </c>
@@ -5585,9 +4936,9 @@
           <t>Консервативный ориентир: устранение всего 30% найденных узких мест</t>
         </is>
       </c>
-      <c r="F21" s="51" t="n"/>
-      <c r="G21" s="51" t="n"/>
-      <c r="H21" s="51" t="n"/>
+      <c r="F21" s="99" t="n"/>
+      <c r="G21" s="99" t="n"/>
+      <c r="H21" s="98" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -5595,8 +4946,8 @@
           <t>Чистая прибыль собственника за вычетом услуг</t>
         </is>
       </c>
-      <c r="B22" s="51" t="n"/>
-      <c r="C22" s="51" t="n"/>
+      <c r="B22" s="99" t="n"/>
+      <c r="C22" s="98" t="n"/>
       <c r="D22" s="82">
         <f>D21-D20</f>
         <v/>
@@ -5606,9 +4957,9 @@
           <t>Чистый денежный плюс в кассе компании в первый же месяц</t>
         </is>
       </c>
-      <c r="F22" s="51" t="n"/>
-      <c r="G22" s="51" t="n"/>
-      <c r="H22" s="51" t="n"/>
+      <c r="F22" s="99" t="n"/>
+      <c r="G22" s="99" t="n"/>
+      <c r="H22" s="98" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
@@ -5616,8 +4967,8 @@
           <t>Чистый ROI инвестиций в проект</t>
         </is>
       </c>
-      <c r="B23" s="51" t="n"/>
-      <c r="C23" s="51" t="n"/>
+      <c r="B23" s="99" t="n"/>
+      <c r="C23" s="98" t="n"/>
       <c r="D23" s="60">
         <f>(D22/D20)*100 &amp; "%"</f>
         <v/>
@@ -5627,9 +4978,9 @@
           <t>Процент отдачи на каждый вложенный рубль</t>
         </is>
       </c>
-      <c r="F23" s="51" t="n"/>
-      <c r="G23" s="51" t="n"/>
-      <c r="H23" s="51" t="n"/>
+      <c r="F23" s="99" t="n"/>
+      <c r="G23" s="99" t="n"/>
+      <c r="H23" s="98" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
@@ -5637,8 +4988,8 @@
           <t>Срок полной окупаемости проекта</t>
         </is>
       </c>
-      <c r="B24" s="51" t="n"/>
-      <c r="C24" s="51" t="n"/>
+      <c r="B24" s="99" t="n"/>
+      <c r="C24" s="98" t="n"/>
       <c r="D24" s="60">
         <f>ROUND(D20/(D21/30), 0) &amp; " дн."</f>
         <v/>
@@ -5648,10 +4999,11 @@
           <t>Количество дней работы ОП до полной окупаемости чека внедрения</t>
         </is>
       </c>
-      <c r="F24" s="51" t="n"/>
-      <c r="G24" s="51" t="n"/>
-      <c r="H24" s="51" t="n"/>
-    </row>
+      <c r="F24" s="99" t="n"/>
+      <c r="G24" s="99" t="n"/>
+      <c r="H24" s="98" t="n"/>
+    </row>
+    <row r="25"/>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="92" t="inlineStr">
         <is>
@@ -5674,8 +5026,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="G2:H2"/>
+  <mergeCells count="23">
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="E22:H22"/>
@@ -5689,7 +5040,6 @@
     <mergeCell ref="E24:H24"/>
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A2:B2"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="E23:H23"/>
     <mergeCell ref="A5:B5"/>
@@ -5739,50 +5089,46 @@
           <t>📄 REVOPS ENTERPRISE EXECUTIVE ONE-PAGER (УПРАВЛЕНЧЕСКИЙ ДАЙДЖЕСТ)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>⚡ Экспресс-Калькулятор</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>📋 Пульт РОПа (15 мин)</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>🎙️ ИИ-Аудит звонков</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>💸 7 Грехов (Диагностика)</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>📄 Executive One-Pager</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="n"/>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>🔐 152-ФЗ Безопасность</t>
-        </is>
-      </c>
-    </row>
+      <c r="A2" s="133">
+        <f>HYPERLINK("#'📄 Executive_OnePager'!A1", "📄 1. One-Pager")</f>
+        <v/>
+      </c>
+      <c r="B2" s="133">
+        <f>HYPERLINK("#'⚡ Пульс_Компании'!A1", "⚡ 2. Пульс компании")</f>
+        <v/>
+      </c>
+      <c r="C2" s="133">
+        <f>HYPERLINK("#'📋 Пульт_РОПа_15_Минут'!A1", "📋 3. Пульт РОПа")</f>
+        <v/>
+      </c>
+      <c r="D2" s="133">
+        <f>HYPERLINK("#'💸 Диагностика_Утечек_ОП'!A1", "💸 4. 7 Грехов ОП")</f>
+        <v/>
+      </c>
+      <c r="E2" s="133">
+        <f>HYPERLINK("#'🎯 Action_Center'!A1", "🎯 5. Action Center")</f>
+        <v/>
+      </c>
+      <c r="F2" s="133">
+        <f>HYPERLINK("#'🎙️ ИИ_Аудит'!A1", "🎙️ 6. ИИ-Аудит")</f>
+        <v/>
+      </c>
+      <c r="G2" s="133">
+        <f>HYPERLINK("#'⚡ Экспресс_Калькулятор_3_Цифры'!A1", "⚡ 7. Экспресс 3 цифры")</f>
+        <v/>
+      </c>
+      <c r="H2" s="133">
+        <f>HYPERLINK("#'🧪 QA_Suite'!A1", "🧪 8. QA Suite")</f>
+        <v/>
+      </c>
+      <c r="I2" s="133">
+        <f>HYPERLINK("#'⚙️ Настройки'!A1", "⚙️ 9. Настройки")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="95" t="inlineStr">
         <is>
@@ -5859,6 +5205,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
@@ -6099,26 +5446,24 @@
         <v>0</v>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="32" customHeight="1">
       <c r="A16" s="97" t="inlineStr">
         <is>
           <t>🎯 ГЛАВНЫЙ ФОКУС РУКОВОДСТВА ДО КОНЦА МЕСЯЦА: Перехват сделки D-104 (850 000 ₽) и перераспределение 3 лидов с перегруженного РОПа на КАМов.</t>
         </is>
       </c>
-      <c r="B16" s="97" t="n"/>
-      <c r="C16" s="97" t="n"/>
-      <c r="D16" s="97" t="n"/>
-      <c r="E16" s="97" t="n"/>
-      <c r="F16" s="97" t="n"/>
-      <c r="G16" s="97" t="n"/>
-      <c r="H16" s="97" t="n"/>
-      <c r="I16" s="97" t="n"/>
+      <c r="B16" s="99" t="n"/>
+      <c r="C16" s="99" t="n"/>
+      <c r="D16" s="99" t="n"/>
+      <c r="E16" s="99" t="n"/>
+      <c r="F16" s="99" t="n"/>
+      <c r="G16" s="99" t="n"/>
+      <c r="H16" s="99" t="n"/>
+      <c r="I16" s="98" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="G2:H2"/>
+  <mergeCells count="4">
     <mergeCell ref="F7:I7"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A7:D7"/>
@@ -6159,11 +5504,6 @@
           <t>🔐 ЮРИДИЧЕСКИЙ КОНТУР БЕЗОПАСНОСТИ И ОБЕЗЛИЧИВАНИЯ ПДН (152-ФЗ РФ)</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -6197,6 +5537,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
